--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sshfs\torisuten@192.168.12.9\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8242209-1EDC-4138-96AF-EAA2E98D8286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C097F1-00FC-4FCE-AF4F-5387B83E0989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28785" yWindow="-21435" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -2641,48 +2641,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
     <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Avertissement" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Calcul" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Cellule liée" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Entrée" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Insatisfaisant" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Neutre" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Satisfaisant" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Sortie" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Texte explicatif" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Titre" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Titre 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Titre 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Titre 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Titre 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Vérification" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2961,17 +2961,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M234"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="37" customWidth="1"/>
-    <col min="8" max="13" width="39.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="37" customWidth="1"/>
+    <col min="8" max="13" width="39.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>532</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>537</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>4.1666666999999998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>4.1666666999999998E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>5.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>1.22E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>1453890.8941884842</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>1.3888888888888888E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>6.5011574074074071E-4</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>4.7400000000000003E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>282528</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>745476480000</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>60479.999999999993</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>518400</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>5184000</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>3.6636136999999999E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>6.0000000000000002E-6</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -6581,7 +6581,7 @@
         <v>374999999.99999994</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -6619,7 +6619,7 @@
         <v>3.7037037037037038E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>165600</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>501</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>502</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
         <v>503</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>504</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
         <v>505</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -7205,7 +7205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>1589759.9999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -7281,7 +7281,7 @@
         <v>6171428.5714285718</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>6171428.5714285718</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>28080</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>0.11100000000000002</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
         <v>498</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>499</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>459648</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
         <v>500</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>0.13875000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>2.0833333333333335E-4</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>5.7899999999999998E-7</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>2.0833333333333335E-4</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -7909,7 +7909,7 @@
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -8064,7 +8064,7 @@
         <v>4.9999999999999999E-13</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -8102,7 +8102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="21" t="s">
         <v>68</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>1.9999999999999999E-7</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -8368,7 +8368,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>5.0000000000000004E-6</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>3.9999999999999998E-6</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>3.7699999999999999E-10</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -8672,7 +8672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>0.89100000000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>5.8333333333333335E-9</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>0.89100000000000001</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>4.0000000000000001E-8</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -9128,7 +9128,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>-4.4200000000000003E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>2.7799999999999998E-4</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>2.4999999999999998E-12</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -9394,7 +9394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -9508,7 +9508,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>2.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -9660,7 +9660,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -9736,7 +9736,7 @@
         <v>1.6666666666666666E-4</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>1E-8</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -9926,7 +9926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -9964,7 +9964,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>2.3533050791148899E-8</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>-0.187</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>6.1060227588121015E-4</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -10268,7 +10268,7 @@
         <v>3.9999999999999998E-7</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -10458,7 +10458,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -10496,7 +10496,7 @@
         <v>3.9999999999999998E-7</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -10724,7 +10724,7 @@
         <v>1.9999999999999999E-7</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -10762,7 +10762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -10800,7 +10800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -10876,7 +10876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="210" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>569</v>
       </c>
@@ -10994,7 +10994,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="211" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>572</v>
       </c>
@@ -11033,7 +11033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>516</v>
       </c>
@@ -11060,11 +11060,10 @@
         <v>0.3</v>
       </c>
       <c r="I212" s="83">
-        <f t="shared" ref="I212:J212" si="4">I211</f>
-        <v>0.3</v>
+        <v>-10000</v>
       </c>
       <c r="J212" s="83">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I212:J212" si="4">J211</f>
         <v>0.3</v>
       </c>
       <c r="K212" s="1"/>
@@ -11075,7 +11074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>575</v>
       </c>
@@ -11116,7 +11115,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="214" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -11155,7 +11154,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="215" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -11194,7 +11193,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="216" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>510</v>
       </c>
@@ -11233,7 +11232,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -11271,7 +11270,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>520</v>
       </c>
@@ -11313,7 +11312,7 @@
         <v>2.5000000000000001E-4</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>523</v>
       </c>
@@ -11351,7 +11350,7 @@
         <v>9.9999999999999994E-12</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>526</v>
       </c>
@@ -11389,7 +11388,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>542</v>
       </c>
@@ -11421,7 +11420,7 @@
         <v>2.4999999999999999E-13</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>543</v>
       </c>
@@ -11456,7 +11455,7 @@
         <v>1.1999999999999999E-5</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>544</v>
       </c>
@@ -11488,7 +11487,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>545</v>
       </c>
@@ -11521,7 +11520,7 @@
         <v>5.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>523</v>
       </c>
@@ -11557,7 +11556,7 @@
         <v>8.0000000000000003E-10</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>546</v>
       </c>
@@ -11593,7 +11592,7 @@
         <v>8.0000000000000005E-9</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>547</v>
       </c>
@@ -11629,7 +11628,7 @@
         <v>0.10886399999999999</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>548</v>
       </c>
@@ -11661,7 +11660,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>549</v>
       </c>
@@ -11693,7 +11692,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>550</v>
       </c>
@@ -11729,7 +11728,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>551</v>
       </c>
@@ -11761,7 +11760,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>552</v>
       </c>
@@ -11793,7 +11792,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>578</v>
       </c>
@@ -11813,7 +11812,7 @@
         <v>571</v>
       </c>
       <c r="G233" s="83">
-        <f t="shared" ref="G233:J234" si="12">0.00002 / 14 / 5</f>
+        <f t="shared" ref="G233:J233" si="12">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="H233" s="83">
@@ -11821,15 +11820,14 @@
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="I233" s="83">
-        <f t="shared" si="12"/>
-        <v>2.8571428571428575E-7</v>
+        <v>0</v>
       </c>
       <c r="J233" s="83">
         <f t="shared" si="12"/>
         <v>2.8571428571428575E-7</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>579</v>
       </c>
@@ -11857,8 +11855,7 @@
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="I234" s="83">
-        <f>0.00002 / 14 / 5 /10</f>
-        <v>2.8571428571428575E-8</v>
+        <v>0</v>
       </c>
       <c r="J234" s="83">
         <f>0.00002 / 14 / 5 /10</f>
@@ -11866,8 +11863,216 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L127:M128">
-    <cfRule type="colorScale" priority="45">
+  <conditionalFormatting sqref="G233:I234">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G234:J234">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H127:J128">
+    <cfRule type="colorScale" priority="287">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H129:J129 L129:M129">
+    <cfRule type="colorScale" priority="289">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="290">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H130:J130 L130:M130">
+    <cfRule type="colorScale" priority="293">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="294">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H132:J132 L132:M132">
+    <cfRule type="colorScale" priority="297">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="298">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H133:J133 L133:M133">
+    <cfRule type="colorScale" priority="302">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="301">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H138:J138 L138:M138">
+    <cfRule type="colorScale" priority="305">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H144:J144 L144:M144">
+    <cfRule type="colorScale" priority="309">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="308">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="307">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H160:J160 L160:M160">
+    <cfRule type="colorScale" priority="315">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="314">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11967,7 +12172,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H214:J214">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11977,7 +12182,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11989,7 +12194,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H215:J215">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11999,7 +12204,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12011,16 +12216,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H216:J216">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -12031,205 +12226,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H127:J128">
-    <cfRule type="colorScale" priority="287">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H129:J129 L129:M129">
-    <cfRule type="colorScale" priority="289">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="290">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H130:J130 L130:M130">
-    <cfRule type="colorScale" priority="293">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="294">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H132:J132 L132:M132">
-    <cfRule type="colorScale" priority="297">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="298">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H133:J133 L133:M133">
-    <cfRule type="colorScale" priority="301">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="302">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H138:J138 L138:M138">
-    <cfRule type="colorScale" priority="305">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H144:J144 L144:M144">
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="309">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H160:J160 L160:M160">
-    <cfRule type="colorScale" priority="313">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="314">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="315">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L166:M166 H166:J166">
-    <cfRule type="colorScale" priority="319">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="320">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="321">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12395,16 +12392,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H228:J232">
-    <cfRule type="colorScale" priority="353">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="354">
       <colorScale>
         <cfvo type="min"/>
@@ -12415,19 +12402,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G233:I234">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="353">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12439,6 +12414,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J233">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -12449,7 +12434,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="8">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L127:M128">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12460,8 +12447,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G234:J234">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="L166:M166 H166:J166">
+    <cfRule type="colorScale" priority="320">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12471,7 +12458,17 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="319">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="321">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12490,13 +12487,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C169"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="3" width="49.5703125" customWidth="1"/>
+    <col min="1" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="3" width="49.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>286</v>
       </c>
@@ -12507,7 +12504,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>206</v>
       </c>
@@ -12519,7 +12516,7 @@
         <v>pi</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -12531,7 +12528,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -12543,7 +12540,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>207</v>
       </c>
@@ -12555,7 +12552,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -12567,7 +12564,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -12579,7 +12576,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -12591,7 +12588,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -12603,7 +12600,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -12615,7 +12612,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -12627,7 +12624,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -12639,7 +12636,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -12651,7 +12648,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -12663,7 +12660,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -12675,7 +12672,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>208</v>
       </c>
@@ -12687,7 +12684,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -12699,7 +12696,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -12711,7 +12708,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>205</v>
       </c>
@@ -12723,7 +12720,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -12735,7 +12732,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -12747,7 +12744,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -12759,7 +12756,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -12771,7 +12768,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -12783,7 +12780,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -12795,7 +12792,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>209</v>
       </c>
@@ -12807,7 +12804,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>210</v>
       </c>
@@ -12819,7 +12816,7 @@
         <v>root_growth_T_ref</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>211</v>
       </c>
@@ -12831,7 +12828,7 @@
         <v>root_growth_A</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>212</v>
       </c>
@@ -12843,7 +12840,7 @@
         <v>root_growth_B</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>213</v>
       </c>
@@ -12855,7 +12852,7 @@
         <v>root_growth_C</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>214</v>
       </c>
@@ -12867,7 +12864,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>215</v>
       </c>
@@ -12879,7 +12876,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>216</v>
       </c>
@@ -12891,7 +12888,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>217</v>
       </c>
@@ -12903,7 +12900,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>218</v>
       </c>
@@ -12915,7 +12912,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -12927,7 +12924,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -12939,7 +12936,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>219</v>
       </c>
@@ -12951,7 +12948,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>220</v>
       </c>
@@ -12963,7 +12960,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>221</v>
       </c>
@@ -12975,7 +12972,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>222</v>
       </c>
@@ -12987,7 +12984,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -12999,7 +12996,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>223</v>
       </c>
@@ -13011,7 +13008,7 @@
         <v>expected_C_sucrose_root</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>224</v>
       </c>
@@ -13023,7 +13020,7 @@
         <v>expected_C_hexose_root</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>225</v>
       </c>
@@ -13035,7 +13032,7 @@
         <v>expected_C_hexose_soil</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>226</v>
       </c>
@@ -13047,7 +13044,7 @@
         <v>expected_C_hexose_reserve</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>65</v>
       </c>
@@ -13059,7 +13056,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>77</v>
       </c>
@@ -13071,7 +13068,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>227</v>
       </c>
@@ -13083,7 +13080,7 @@
         <v>surfacic_unloading_rate_reference</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>228</v>
       </c>
@@ -13095,7 +13092,7 @@
         <v>surfacic_unloading_rate_primordium</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -13107,7 +13104,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>229</v>
       </c>
@@ -13119,7 +13116,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>230</v>
       </c>
@@ -13131,7 +13128,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>231</v>
       </c>
@@ -13143,7 +13140,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>232</v>
       </c>
@@ -13155,7 +13152,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -13167,7 +13164,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>233</v>
       </c>
@@ -13179,7 +13176,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>234</v>
       </c>
@@ -13191,7 +13188,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>235</v>
       </c>
@@ -13203,7 +13200,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>236</v>
       </c>
@@ -13215,7 +13212,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -13227,7 +13224,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -13239,7 +13236,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -13251,7 +13248,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -13263,7 +13260,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>56</v>
       </c>
@@ -13275,7 +13272,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>58</v>
       </c>
@@ -13287,7 +13284,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -13299,7 +13296,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>237</v>
       </c>
@@ -13311,7 +13308,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>238</v>
       </c>
@@ -13323,7 +13320,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>239</v>
       </c>
@@ -13335,7 +13332,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>240</v>
       </c>
@@ -13347,7 +13344,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -13359,7 +13356,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -13371,7 +13368,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>241</v>
       </c>
@@ -13383,7 +13380,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>242</v>
       </c>
@@ -13395,7 +13392,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>243</v>
       </c>
@@ -13407,7 +13404,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>244</v>
       </c>
@@ -13419,7 +13416,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>74</v>
       </c>
@@ -13431,7 +13428,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>245</v>
       </c>
@@ -13443,7 +13440,7 @@
         <v>expected_exudation_efflux</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -13455,7 +13452,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>246</v>
       </c>
@@ -13467,7 +13464,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>247</v>
       </c>
@@ -13479,7 +13476,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>248</v>
       </c>
@@ -13491,7 +13488,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>249</v>
       </c>
@@ -13503,7 +13500,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>79</v>
       </c>
@@ -13515,7 +13512,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>80</v>
       </c>
@@ -13527,7 +13524,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>250</v>
       </c>
@@ -13539,7 +13536,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>251</v>
       </c>
@@ -13551,7 +13548,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -13563,7 +13560,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>253</v>
       </c>
@@ -13575,7 +13572,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>81</v>
       </c>
@@ -13587,7 +13584,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>254</v>
       </c>
@@ -13599,7 +13596,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -13611,7 +13608,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>256</v>
       </c>
@@ -13623,7 +13620,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>257</v>
       </c>
@@ -13635,7 +13632,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>258</v>
       </c>
@@ -13647,7 +13644,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>259</v>
       </c>
@@ -13659,7 +13656,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>260</v>
       </c>
@@ -13671,7 +13668,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>261</v>
       </c>
@@ -13683,7 +13680,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>262</v>
       </c>
@@ -13695,7 +13692,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>263</v>
       </c>
@@ -13707,7 +13704,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>264</v>
       </c>
@@ -13719,7 +13716,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>265</v>
       </c>
@@ -13731,7 +13728,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>266</v>
       </c>
@@ -13743,7 +13740,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>267</v>
       </c>
@@ -13755,7 +13752,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>268</v>
       </c>
@@ -13767,7 +13764,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>269</v>
       </c>
@@ -13779,7 +13776,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>270</v>
       </c>
@@ -13791,7 +13788,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>271</v>
       </c>
@@ -13803,7 +13800,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>272</v>
       </c>
@@ -13815,7 +13812,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>273</v>
       </c>
@@ -13827,7 +13824,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>274</v>
       </c>
@@ -13839,7 +13836,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>275</v>
       </c>
@@ -13851,7 +13848,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>276</v>
       </c>
@@ -13863,7 +13860,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>277</v>
       </c>
@@ -13875,7 +13872,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>278</v>
       </c>
@@ -13887,7 +13884,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>279</v>
       </c>
@@ -13899,7 +13896,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>280</v>
       </c>
@@ -13911,7 +13908,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>281</v>
       </c>
@@ -13923,7 +13920,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>282</v>
       </c>
@@ -13935,7 +13932,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>283</v>
       </c>
@@ -13947,7 +13944,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>284</v>
       </c>
@@ -13959,7 +13956,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>59</v>
       </c>
@@ -13971,7 +13968,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>62</v>
       </c>
@@ -13983,7 +13980,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>64</v>
       </c>
@@ -13995,7 +13992,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>63</v>
       </c>
@@ -14007,7 +14004,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>82</v>
       </c>
@@ -14019,7 +14016,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>83</v>
       </c>
@@ -14031,7 +14028,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>85</v>
       </c>
@@ -14043,7 +14040,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>84</v>
       </c>
@@ -14055,7 +14052,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>2</v>
       </c>
@@ -14067,7 +14064,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -14079,7 +14076,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -14091,7 +14088,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>20</v>
       </c>
@@ -14103,7 +14100,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>0</v>
       </c>
@@ -14115,7 +14112,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>1</v>
       </c>
@@ -14127,7 +14124,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>6</v>
       </c>
@@ -14139,7 +14136,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -14151,7 +14148,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -14163,7 +14160,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -14175,7 +14172,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -14187,7 +14184,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -14199,7 +14196,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>12</v>
       </c>
@@ -14211,7 +14208,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -14223,7 +14220,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>14</v>
       </c>
@@ -14235,7 +14232,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -14247,7 +14244,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -14259,7 +14256,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -14271,7 +14268,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14283,7 +14280,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -14295,7 +14292,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>21</v>
       </c>
@@ -14307,7 +14304,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>22</v>
       </c>
@@ -14319,7 +14316,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>23</v>
       </c>
@@ -14331,7 +14328,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -14343,7 +14340,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>25</v>
       </c>
@@ -14355,7 +14352,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>26</v>
       </c>
@@ -14367,7 +14364,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>27</v>
       </c>
@@ -14379,7 +14376,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>28</v>
       </c>
@@ -14388,7 +14385,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>29</v>
       </c>
@@ -14397,7 +14394,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>30</v>
       </c>
@@ -14406,7 +14403,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>31</v>
       </c>
@@ -14415,7 +14412,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>32</v>
       </c>
@@ -14424,7 +14421,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>33</v>
       </c>
@@ -14433,7 +14430,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>34</v>
       </c>
@@ -14442,7 +14439,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>35</v>
       </c>
@@ -14451,7 +14448,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>36</v>
       </c>
@@ -14460,7 +14457,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>37</v>
       </c>
@@ -14469,7 +14466,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>38</v>
       </c>
@@ -14478,7 +14475,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>362</v>
       </c>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sshfs\torisuten@192.168.12.9\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C097F1-00FC-4FCE-AF4F-5387B83E0989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831C3B7B-8260-4227-8FA1-E55A1B3F506F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28785" yWindow="-21435" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -1722,9 +1722,6 @@
     <t>Apoplasmic water conductivity</t>
   </si>
   <si>
-    <t>m.s-1.Pa-2</t>
-  </si>
-  <si>
     <t>ratio of water volume relative to segment volume. In principle &lt;1, but can be increased to prevent too harsh pressure and water content drop</t>
   </si>
   <si>
@@ -1774,6 +1771,9 @@
   </si>
   <si>
     <t>DON</t>
+  </si>
+  <si>
+    <t>mol.s-1.Pa-1.m-2</t>
   </si>
 </sst>
 </file>
@@ -2961,17 +2961,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M234"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="37" customWidth="1"/>
-    <col min="8" max="13" width="39.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="37" customWidth="1"/>
+    <col min="8" max="13" width="39.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -2997,10 +2997,10 @@
         <v>496</v>
       </c>
       <c r="I1" s="97" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1" s="97" t="s">
         <v>576</v>
-      </c>
-      <c r="J1" s="97" t="s">
-        <v>577</v>
       </c>
       <c r="L1" s="97" t="s">
         <v>530</v>
@@ -3009,7 +3009,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>532</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>537</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>4.1666666999999998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>4.1666666999999998E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>5.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>1.22E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>1453890.8941884842</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>1.3888888888888888E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>6.5011574074074071E-4</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>4.7400000000000003E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>282528</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>745476480000</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>60479.999999999993</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>518400</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>5184000</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>3.6636136999999999E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>6.0000000000000002E-6</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -6581,7 +6581,7 @@
         <v>374999999.99999994</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -6619,7 +6619,7 @@
         <v>3.7037037037037038E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>165600</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="23" t="s">
         <v>501</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="23" t="s">
         <v>502</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="23" t="s">
         <v>503</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="23" t="s">
         <v>504</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="23" t="s">
         <v>505</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -7205,7 +7205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>1589759.9999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -7281,7 +7281,7 @@
         <v>6171428.5714285718</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>6171428.5714285718</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>28080</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>0.11100000000000002</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="23" t="s">
         <v>498</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="23" t="s">
         <v>499</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>459648</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="23" t="s">
         <v>500</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>0.13875000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>2.0833333333333335E-4</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>5.7899999999999998E-7</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>2.0833333333333335E-4</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -7909,7 +7909,7 @@
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -8064,7 +8064,7 @@
         <v>4.9999999999999999E-13</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -8102,7 +8102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
         <v>68</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>1.9999999999999999E-7</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -8368,7 +8368,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>5.0000000000000004E-6</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>3.9999999999999998E-6</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>3.7699999999999999E-10</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -8672,7 +8672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>0.89100000000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>5.8333333333333335E-9</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>0.89100000000000001</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>4.0000000000000001E-8</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -9128,7 +9128,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>-4.4200000000000003E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>2.7799999999999998E-4</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>2.4999999999999998E-12</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -9394,7 +9394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -9508,7 +9508,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>2.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -9660,7 +9660,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -9736,7 +9736,7 @@
         <v>1.6666666666666666E-4</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>1E-8</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -9926,7 +9926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -9964,7 +9964,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>2.3533050791148899E-8</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>-0.187</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>6.1060227588121015E-4</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -10268,7 +10268,7 @@
         <v>3.9999999999999998E-7</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -10458,7 +10458,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -10496,7 +10496,7 @@
         <v>3.9999999999999998E-7</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -10724,7 +10724,7 @@
         <v>1.9999999999999999E-7</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -10762,7 +10762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -10800,7 +10800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -10876,7 +10876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -10952,24 +10952,24 @@
         <v>90</v>
       </c>
     </row>
-    <row r="210" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="E210" s="30" t="s">
         <v>569</v>
       </c>
-      <c r="B210" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="E210" s="30" t="s">
+      <c r="F210" s="30" t="s">
         <v>570</v>
-      </c>
-      <c r="F210" s="30" t="s">
-        <v>571</v>
       </c>
       <c r="G210" s="2">
         <v>0.5</v>
@@ -10994,24 +10994,24 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="211" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="E211" s="30" t="s">
         <v>572</v>
       </c>
-      <c r="B211" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C211" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="E211" s="30" t="s">
+      <c r="F211" s="30" t="s">
         <v>573</v>
-      </c>
-      <c r="F211" s="30" t="s">
-        <v>574</v>
       </c>
       <c r="G211" s="98">
         <v>-100000</v>
@@ -11033,7 +11033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>516</v>
       </c>
@@ -11063,7 +11063,7 @@
         <v>-10000</v>
       </c>
       <c r="J212" s="83">
-        <f t="shared" ref="I212:J212" si="4">J211</f>
+        <f t="shared" ref="J212" si="4">J211</f>
         <v>0.3</v>
       </c>
       <c r="K212" s="1"/>
@@ -11074,9 +11074,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>471</v>
@@ -11115,7 +11115,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="214" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="215" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -11193,7 +11193,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="216" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>510</v>
       </c>
@@ -11232,7 +11232,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>520</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>2.5000000000000001E-4</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>523</v>
       </c>
@@ -11350,7 +11350,7 @@
         <v>9.9999999999999994E-12</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>526</v>
       </c>
@@ -11388,7 +11388,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>542</v>
       </c>
@@ -11420,7 +11420,7 @@
         <v>2.4999999999999999E-13</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>543</v>
       </c>
@@ -11455,7 +11455,7 @@
         <v>1.1999999999999999E-5</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>544</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>545</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>5.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>523</v>
       </c>
@@ -11537,26 +11537,26 @@
         <v>560</v>
       </c>
       <c r="F225" s="96" t="s">
-        <v>525</v>
+        <v>579</v>
       </c>
       <c r="G225" s="99">
         <f>0.00000000000001 * 1000</f>
         <v>9.9999999999999994E-12</v>
       </c>
       <c r="H225" s="83">
-        <f t="shared" ref="H225:J225" si="7">0.00000000000001*10000*8</f>
-        <v>8.0000000000000003E-10</v>
+        <f>104 * 0.000000001 / 18</f>
+        <v>5.777777777777778E-9</v>
       </c>
       <c r="I225" s="83">
-        <f t="shared" si="7"/>
-        <v>8.0000000000000003E-10</v>
+        <f>104 * 0.000000001 / 18</f>
+        <v>5.777777777777778E-9</v>
       </c>
       <c r="J225" s="83">
-        <f t="shared" si="7"/>
-        <v>8.0000000000000003E-10</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+        <f>104 * 0.000000001 / 18</f>
+        <v>5.777777777777778E-9</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>546</v>
       </c>
@@ -11573,26 +11573,26 @@
         <v>561</v>
       </c>
       <c r="F226" s="96" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="G226" s="99">
         <f>0.00000000000001 * 10000</f>
         <v>1E-10</v>
       </c>
       <c r="H226" s="83">
-        <f t="shared" ref="H226" si="8">H225*10</f>
-        <v>8.0000000000000005E-9</v>
+        <f t="shared" ref="H226" si="7">H225*10</f>
+        <v>5.7777777777777781E-8</v>
       </c>
       <c r="I226" s="83">
-        <f t="shared" ref="I226:J226" si="9">I225*10</f>
-        <v>8.0000000000000005E-9</v>
+        <f t="shared" ref="I226:J226" si="8">I225*10</f>
+        <v>5.7777777777777781E-8</v>
       </c>
       <c r="J226" s="83">
-        <f t="shared" si="9"/>
-        <v>8.0000000000000005E-9</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>5.7777777777777781E-8</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>547</v>
       </c>
@@ -11606,7 +11606,7 @@
         <v>540</v>
       </c>
       <c r="E227" s="96" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F227" s="96" t="s">
         <v>507</v>
@@ -11616,19 +11616,19 @@
         <v>0.10886399999999999</v>
       </c>
       <c r="H227" s="83">
-        <f t="shared" ref="H227:J227" si="10">0.84*(0.36^2)</f>
+        <f t="shared" ref="H227:J227" si="9">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
       <c r="I227" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="J227" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.10886399999999999</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>548</v>
       </c>
@@ -11642,7 +11642,7 @@
         <v>540</v>
       </c>
       <c r="E228" s="96" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F228" s="96" t="s">
         <v>495</v>
@@ -11660,7 +11660,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>549</v>
       </c>
@@ -11674,7 +11674,7 @@
         <v>540</v>
       </c>
       <c r="E229" s="96" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F229" s="96" t="s">
         <v>511</v>
@@ -11692,7 +11692,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>550</v>
       </c>
@@ -11706,7 +11706,7 @@
         <v>540</v>
       </c>
       <c r="E230" s="96" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F230" s="96" t="s">
         <v>511</v>
@@ -11716,19 +11716,19 @@
         <v>0.2</v>
       </c>
       <c r="H230" s="83">
-        <f t="shared" ref="H230:J230" si="11">2*0.1</f>
+        <f t="shared" ref="H230:J230" si="10">2*0.1</f>
         <v>0.2</v>
       </c>
       <c r="I230" s="83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J230" s="83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>551</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>540</v>
       </c>
       <c r="E231" s="96" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F231" s="96" t="s">
         <v>511</v>
@@ -11760,7 +11760,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>552</v>
       </c>
@@ -11774,7 +11774,7 @@
         <v>540</v>
       </c>
       <c r="E232" s="96" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F232" s="96" t="s">
         <v>511</v>
@@ -11792,9 +11792,9 @@
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>471</v>
@@ -11806,30 +11806,30 @@
         <v>540</v>
       </c>
       <c r="E233" s="30" t="s">
+        <v>569</v>
+      </c>
+      <c r="F233" s="30" t="s">
         <v>570</v>
       </c>
-      <c r="F233" s="30" t="s">
-        <v>571</v>
-      </c>
       <c r="G233" s="83">
-        <f t="shared" ref="G233:J233" si="12">0.00002 / 14 / 5</f>
+        <f t="shared" ref="G233:J233" si="11">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="H233" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="I233" s="83">
         <v>0</v>
       </c>
       <c r="J233" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428575E-7</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>471</v>
@@ -11841,10 +11841,10 @@
         <v>540</v>
       </c>
       <c r="E234" s="30" t="s">
+        <v>569</v>
+      </c>
+      <c r="F234" s="30" t="s">
         <v>570</v>
-      </c>
-      <c r="F234" s="30" t="s">
-        <v>571</v>
       </c>
       <c r="G234" s="83">
         <f>0.00002 / 14 / 5 /10</f>
@@ -12487,13 +12487,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C169"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="35.6640625" customWidth="1"/>
-    <col min="3" max="3" width="49.5546875" customWidth="1"/>
+    <col min="1" max="2" width="35.7109375" customWidth="1"/>
+    <col min="3" max="3" width="49.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>286</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>206</v>
       </c>
@@ -12516,7 +12516,7 @@
         <v>pi</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -12540,7 +12540,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>207</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -12588,7 +12588,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -12612,7 +12612,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -12648,7 +12648,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -12660,7 +12660,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>208</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -12696,7 +12696,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>205</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -12732,7 +12732,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -12756,7 +12756,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -12768,7 +12768,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -12780,7 +12780,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -12792,7 +12792,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>209</v>
       </c>
@@ -12804,7 +12804,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>210</v>
       </c>
@@ -12816,7 +12816,7 @@
         <v>root_growth_T_ref</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>211</v>
       </c>
@@ -12828,7 +12828,7 @@
         <v>root_growth_A</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>212</v>
       </c>
@@ -12840,7 +12840,7 @@
         <v>root_growth_B</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>213</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>root_growth_C</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>214</v>
       </c>
@@ -12864,7 +12864,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>215</v>
       </c>
@@ -12876,7 +12876,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>216</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>217</v>
       </c>
@@ -12900,7 +12900,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>218</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -12936,7 +12936,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>219</v>
       </c>
@@ -12948,7 +12948,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>220</v>
       </c>
@@ -12960,7 +12960,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>221</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>222</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>223</v>
       </c>
@@ -13008,7 +13008,7 @@
         <v>expected_C_sucrose_root</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>224</v>
       </c>
@@ -13020,7 +13020,7 @@
         <v>expected_C_hexose_root</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>225</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>expected_C_hexose_soil</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>226</v>
       </c>
@@ -13044,7 +13044,7 @@
         <v>expected_C_hexose_reserve</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>65</v>
       </c>
@@ -13056,7 +13056,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>77</v>
       </c>
@@ -13068,7 +13068,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>227</v>
       </c>
@@ -13080,7 +13080,7 @@
         <v>surfacic_unloading_rate_reference</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>228</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>surfacic_unloading_rate_primordium</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -13104,7 +13104,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>229</v>
       </c>
@@ -13116,7 +13116,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>230</v>
       </c>
@@ -13128,7 +13128,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>231</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>232</v>
       </c>
@@ -13152,7 +13152,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -13164,7 +13164,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>233</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>234</v>
       </c>
@@ -13188,7 +13188,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>235</v>
       </c>
@@ -13200,7 +13200,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>236</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -13224,7 +13224,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -13236,7 +13236,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>56</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>58</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -13296,7 +13296,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>237</v>
       </c>
@@ -13308,7 +13308,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>238</v>
       </c>
@@ -13320,7 +13320,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>239</v>
       </c>
@@ -13332,7 +13332,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>240</v>
       </c>
@@ -13344,7 +13344,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -13368,7 +13368,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>241</v>
       </c>
@@ -13380,7 +13380,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>242</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>243</v>
       </c>
@@ -13404,7 +13404,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>244</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>74</v>
       </c>
@@ -13428,7 +13428,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>245</v>
       </c>
@@ -13440,7 +13440,7 @@
         <v>expected_exudation_efflux</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -13452,7 +13452,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>246</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>247</v>
       </c>
@@ -13476,7 +13476,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>248</v>
       </c>
@@ -13488,7 +13488,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>249</v>
       </c>
@@ -13500,7 +13500,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>79</v>
       </c>
@@ -13512,7 +13512,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>80</v>
       </c>
@@ -13524,7 +13524,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>250</v>
       </c>
@@ -13536,7 +13536,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>251</v>
       </c>
@@ -13548,7 +13548,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -13560,7 +13560,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>253</v>
       </c>
@@ -13572,7 +13572,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>81</v>
       </c>
@@ -13584,7 +13584,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>254</v>
       </c>
@@ -13596,7 +13596,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -13608,7 +13608,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>256</v>
       </c>
@@ -13620,7 +13620,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>257</v>
       </c>
@@ -13632,7 +13632,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>258</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>259</v>
       </c>
@@ -13656,7 +13656,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>260</v>
       </c>
@@ -13668,7 +13668,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>261</v>
       </c>
@@ -13680,7 +13680,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>262</v>
       </c>
@@ -13692,7 +13692,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>263</v>
       </c>
@@ -13704,7 +13704,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>264</v>
       </c>
@@ -13716,7 +13716,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>265</v>
       </c>
@@ -13728,7 +13728,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>266</v>
       </c>
@@ -13740,7 +13740,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>267</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>268</v>
       </c>
@@ -13764,7 +13764,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>269</v>
       </c>
@@ -13776,7 +13776,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>270</v>
       </c>
@@ -13788,7 +13788,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>271</v>
       </c>
@@ -13800,7 +13800,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>272</v>
       </c>
@@ -13812,7 +13812,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>273</v>
       </c>
@@ -13824,7 +13824,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>274</v>
       </c>
@@ -13836,7 +13836,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>275</v>
       </c>
@@ -13848,7 +13848,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>276</v>
       </c>
@@ -13860,7 +13860,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>277</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>278</v>
       </c>
@@ -13884,7 +13884,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>279</v>
       </c>
@@ -13896,7 +13896,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>280</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>281</v>
       </c>
@@ -13920,7 +13920,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>282</v>
       </c>
@@ -13932,7 +13932,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>283</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>284</v>
       </c>
@@ -13956,7 +13956,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>59</v>
       </c>
@@ -13968,7 +13968,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>62</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>64</v>
       </c>
@@ -13992,7 +13992,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>63</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>82</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>83</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>85</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>84</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>2</v>
       </c>
@@ -14064,7 +14064,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -14076,7 +14076,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>20</v>
       </c>
@@ -14100,7 +14100,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>0</v>
       </c>
@@ -14112,7 +14112,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>6</v>
       </c>
@@ -14136,7 +14136,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -14148,7 +14148,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -14184,7 +14184,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>12</v>
       </c>
@@ -14208,7 +14208,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>14</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -14268,7 +14268,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14280,7 +14280,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>21</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>22</v>
       </c>
@@ -14316,7 +14316,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>23</v>
       </c>
@@ -14328,7 +14328,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>25</v>
       </c>
@@ -14352,7 +14352,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>26</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>27</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>28</v>
       </c>
@@ -14385,7 +14385,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>29</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>30</v>
       </c>
@@ -14403,7 +14403,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>31</v>
       </c>
@@ -14412,7 +14412,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>32</v>
       </c>
@@ -14421,7 +14421,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>33</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>34</v>
       </c>
@@ -14439,7 +14439,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>35</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>36</v>
       </c>
@@ -14457,7 +14457,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>37</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>38</v>
       </c>
@@ -14475,7 +14475,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>362</v>
       </c>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sshfs\torisuten@192.168.12.9\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831C3B7B-8260-4227-8FA1-E55A1B3F506F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD01C8A-0E31-4F57-92F6-C5E8F5E3F57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11443,16 +11443,16 @@
         <v>1.2E-8</v>
       </c>
       <c r="H222" s="83">
-        <f>0.00000012*100</f>
-        <v>1.1999999999999999E-5</v>
+        <f>0.000000012 / 100</f>
+        <v>1.2E-10</v>
       </c>
       <c r="I222" s="83">
-        <f t="shared" ref="I222:J222" si="6">0.00000012*100</f>
-        <v>1.1999999999999999E-5</v>
+        <f>0.000000012 / 100</f>
+        <v>1.2E-10</v>
       </c>
       <c r="J222" s="83">
-        <f t="shared" si="6"/>
-        <v>1.1999999999999999E-5</v>
+        <f>0.000000012 / 100</f>
+        <v>1.2E-10</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.25">
@@ -11478,13 +11478,16 @@
         <v>9.9999999999999995E-8</v>
       </c>
       <c r="H223" s="83">
-        <v>9.9999999999999995E-7</v>
+        <f>0.000001 / 10000</f>
+        <v>9.9999999999999991E-11</v>
       </c>
       <c r="I223" s="83">
-        <v>9.9999999999999995E-7</v>
+        <f>0.000001 / 10000</f>
+        <v>9.9999999999999991E-11</v>
       </c>
       <c r="J223" s="83">
-        <v>9.9999999999999995E-7</v>
+        <f>0.000001 / 10000</f>
+        <v>9.9999999999999991E-11</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.25">
@@ -11580,15 +11583,15 @@
         <v>1E-10</v>
       </c>
       <c r="H226" s="83">
-        <f t="shared" ref="H226" si="7">H225*10</f>
+        <f t="shared" ref="H226" si="6">H225*10</f>
         <v>5.7777777777777781E-8</v>
       </c>
       <c r="I226" s="83">
-        <f t="shared" ref="I226:J226" si="8">I225*10</f>
+        <f t="shared" ref="I226:J226" si="7">I225*10</f>
         <v>5.7777777777777781E-8</v>
       </c>
       <c r="J226" s="83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5.7777777777777781E-8</v>
       </c>
     </row>
@@ -11616,15 +11619,15 @@
         <v>0.10886399999999999</v>
       </c>
       <c r="H227" s="83">
-        <f t="shared" ref="H227:J227" si="9">0.84*(0.36^2)</f>
+        <f t="shared" ref="H227:J227" si="8">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
       <c r="I227" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="J227" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.10886399999999999</v>
       </c>
     </row>
@@ -11716,15 +11719,15 @@
         <v>0.2</v>
       </c>
       <c r="H230" s="83">
-        <f t="shared" ref="H230:J230" si="10">2*0.1</f>
+        <f t="shared" ref="H230:J230" si="9">2*0.1</f>
         <v>0.2</v>
       </c>
       <c r="I230" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="J230" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
     </row>
@@ -11812,18 +11815,18 @@
         <v>570</v>
       </c>
       <c r="G233" s="83">
-        <f t="shared" ref="G233:J233" si="11">0.00002 / 14 / 5</f>
+        <f t="shared" ref="G233:J233" si="10">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="H233" s="83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="I233" s="83">
         <v>0</v>
       </c>
       <c r="J233" s="83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>2.8571428571428575E-7</v>
       </c>
     </row>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sshfs\torisuten@192.168.12.9\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD01C8A-0E31-4F57-92F6-C5E8F5E3F57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FB7C66-4E82-4D37-A0FA-15B43491F40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="568">
   <si>
     <t>input_file</t>
   </si>
@@ -1527,9 +1527,6 @@
     <t>Reference_Fischer</t>
   </si>
   <si>
-    <t>Pa</t>
-  </si>
-  <si>
     <t>epidermis_a</t>
   </si>
   <si>
@@ -1584,18 +1581,6 @@
     <t>Variance of the normal law smooting the boundary transition of a nitrate patch with the background concentration</t>
   </si>
   <si>
-    <t>xylem_total_pressure</t>
-  </si>
-  <si>
-    <t>xylem uniform pressure</t>
-  </si>
-  <si>
-    <t>cortical_surfacic_fraction</t>
-  </si>
-  <si>
-    <t>Cortex (+epidermis) parenchyma surface ratio over root segment's cylinder surface</t>
-  </si>
-  <si>
     <t>Km_elongation_amino_acids</t>
   </si>
   <si>
@@ -1605,15 +1590,6 @@
     <t>mol.g-1 DW</t>
   </si>
   <si>
-    <t>cortex_water_conductivity</t>
-  </si>
-  <si>
-    <t>Symplasmic absorption water conductivity</t>
-  </si>
-  <si>
-    <t>m.s-1.Pa-1</t>
-  </si>
-  <si>
     <t>span_N_regulation</t>
   </si>
   <si>
@@ -1674,9 +1650,6 @@
     <t>vmax_Nm_xylem</t>
   </si>
   <si>
-    <t>apoplasmic_water_conductivity</t>
-  </si>
-  <si>
     <t>xylem_cross_area_ratio</t>
   </si>
   <si>
@@ -1716,12 +1689,6 @@
     <t>mol.s-1.m-2</t>
   </si>
   <si>
-    <t>Transmembrane water conductivity</t>
-  </si>
-  <si>
-    <t>Apoplasmic water conductivity</t>
-  </si>
-  <si>
     <t>ratio of water volume relative to segment volume. In principle &lt;1, but can be increased to prevent too harsh pressure and water content drop</t>
   </si>
   <si>
@@ -1771,9 +1738,6 @@
   </si>
   <si>
     <t>DON</t>
-  </si>
-  <si>
-    <t>mol.s-1.Pa-1.m-2</t>
   </si>
 </sst>
 </file>
@@ -2960,18 +2924,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M234"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M229"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="37" customWidth="1"/>
-    <col min="8" max="13" width="39.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="37" customWidth="1"/>
+    <col min="8" max="13" width="39.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -2997,39 +2961,39 @@
         <v>496</v>
       </c>
       <c r="I1" s="97" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="J1" s="97" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="L1" s="97" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="M1" s="97" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>487</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E2" s="96" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="F2" s="96" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="H2" s="36" t="s">
         <v>476</v>
@@ -3041,13 +3005,13 @@
         <v>476</v>
       </c>
       <c r="L2" s="36" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="M2" s="36" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3058,7 +3022,7 @@
         <v>487</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>477</v>
@@ -3085,7 +3049,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3096,7 +3060,7 @@
         <v>487</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>474</v>
@@ -3123,7 +3087,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3134,7 +3098,7 @@
         <v>487</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>479</v>
@@ -3161,7 +3125,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3172,7 +3136,7 @@
         <v>487</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>491</v>
@@ -3187,19 +3151,19 @@
         <v>494</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="J6" s="36" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="L6" s="36" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="M6" s="36" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3210,7 +3174,7 @@
         <v>487</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>480</v>
@@ -3237,9 +3201,9 @@
         <v>494</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>471</v>
@@ -3248,13 +3212,13 @@
         <v>487</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="G8" s="51">
         <v>0</v>
@@ -3275,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3286,7 +3250,7 @@
         <v>487</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>130</v>
@@ -3313,7 +3277,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,7 +3288,7 @@
         <v>487</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>131</v>
@@ -3351,7 +3315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3362,7 +3326,7 @@
         <v>487</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E11" s="75" t="s">
         <v>445</v>
@@ -3389,7 +3353,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3400,7 +3364,7 @@
         <v>487</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>115</v>
@@ -3427,7 +3391,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3438,7 +3402,7 @@
         <v>487</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>116</v>
@@ -3465,7 +3429,7 @@
         <v>4.1666666999999998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3476,7 +3440,7 @@
         <v>487</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>124</v>
@@ -3503,7 +3467,7 @@
         <v>4.1666666999999998E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3514,7 +3478,7 @@
         <v>487</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>114</v>
@@ -3541,7 +3505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3552,7 +3516,7 @@
         <v>487</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>449</v>
@@ -3579,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3590,7 +3554,7 @@
         <v>487</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>132</v>
@@ -3617,7 +3581,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3628,7 +3592,7 @@
         <v>487</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>117</v>
@@ -3655,7 +3619,7 @@
         <v>5.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -3666,7 +3630,7 @@
         <v>487</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>118</v>
@@ -3693,7 +3657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -3704,7 +3668,7 @@
         <v>487</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>456</v>
@@ -3731,7 +3695,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -3742,7 +3706,7 @@
         <v>487</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>463</v>
@@ -3769,7 +3733,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -3780,7 +3744,7 @@
         <v>487</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>466</v>
@@ -3807,7 +3771,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -3818,7 +3782,7 @@
         <v>487</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>468</v>
@@ -3845,7 +3809,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -3856,7 +3820,7 @@
         <v>487</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>134</v>
@@ -3883,7 +3847,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -3894,7 +3858,7 @@
         <v>487</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>119</v>
@@ -3921,7 +3885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -3932,7 +3896,7 @@
         <v>487</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>364</v>
@@ -3959,7 +3923,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -3970,7 +3934,7 @@
         <v>487</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>366</v>
@@ -3997,7 +3961,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -4008,7 +3972,7 @@
         <v>487</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>378</v>
@@ -4035,7 +3999,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4046,7 +4010,7 @@
         <v>487</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>374</v>
@@ -4073,7 +4037,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4084,7 +4048,7 @@
         <v>487</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>373</v>
@@ -4111,7 +4075,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4122,7 +4086,7 @@
         <v>487</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>140</v>
@@ -4149,7 +4113,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4160,7 +4124,7 @@
         <v>487</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>120</v>
@@ -4187,7 +4151,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4198,7 +4162,7 @@
         <v>487</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>135</v>
@@ -4225,7 +4189,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4236,7 +4200,7 @@
         <v>487</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>133</v>
@@ -4263,7 +4227,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4274,7 +4238,7 @@
         <v>487</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>455</v>
@@ -4301,7 +4265,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4312,7 +4276,7 @@
         <v>487</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>138</v>
@@ -4339,7 +4303,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4350,7 +4314,7 @@
         <v>487</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>125</v>
@@ -4377,7 +4341,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -4388,7 +4352,7 @@
         <v>487</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>126</v>
@@ -4415,7 +4379,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -4426,7 +4390,7 @@
         <v>487</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>127</v>
@@ -4453,7 +4417,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -4464,7 +4428,7 @@
         <v>487</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E40" s="14" t="s">
         <v>139</v>
@@ -4491,7 +4455,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -4502,7 +4466,7 @@
         <v>487</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>128</v>
@@ -4529,7 +4493,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -4540,7 +4504,7 @@
         <v>487</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>129</v>
@@ -4567,7 +4531,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -4578,7 +4542,7 @@
         <v>487</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>141</v>
@@ -4605,7 +4569,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -4616,7 +4580,7 @@
         <v>487</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>142</v>
@@ -4643,7 +4607,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -4654,7 +4618,7 @@
         <v>487</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>143</v>
@@ -4681,7 +4645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -4692,7 +4656,7 @@
         <v>487</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E46" s="14" t="s">
         <v>144</v>
@@ -4719,7 +4683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -4730,7 +4694,7 @@
         <v>487</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>145</v>
@@ -4757,7 +4721,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -4768,7 +4732,7 @@
         <v>487</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>146</v>
@@ -4795,7 +4759,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -4806,7 +4770,7 @@
         <v>487</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>147</v>
@@ -4833,7 +4797,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -4844,7 +4808,7 @@
         <v>487</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>148</v>
@@ -4871,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -4882,7 +4846,7 @@
         <v>487</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>436</v>
@@ -4909,7 +4873,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -4920,7 +4884,7 @@
         <v>487</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>437</v>
@@ -4947,7 +4911,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -4958,7 +4922,7 @@
         <v>487</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>458</v>
@@ -4985,7 +4949,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -4996,7 +4960,7 @@
         <v>487</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>136</v>
@@ -5023,7 +4987,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5034,7 +4998,7 @@
         <v>487</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>137</v>
@@ -5061,7 +5025,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -5072,7 +5036,7 @@
         <v>487</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>121</v>
@@ -5099,7 +5063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -5110,7 +5074,7 @@
         <v>487</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>122</v>
@@ -5137,7 +5101,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -5148,7 +5112,7 @@
         <v>487</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>123</v>
@@ -5175,7 +5139,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -5186,7 +5150,7 @@
         <v>487</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E59" s="16" t="s">
         <v>149</v>
@@ -5213,7 +5177,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -5224,7 +5188,7 @@
         <v>487</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E60" s="16" t="s">
         <v>381</v>
@@ -5251,7 +5215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -5262,7 +5226,7 @@
         <v>487</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E61" s="16" t="s">
         <v>150</v>
@@ -5289,7 +5253,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -5300,7 +5264,7 @@
         <v>487</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E62" s="16" t="s">
         <v>151</v>
@@ -5327,7 +5291,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -5338,7 +5302,7 @@
         <v>487</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E63" s="18" t="s">
         <v>152</v>
@@ -5365,7 +5329,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -5376,7 +5340,7 @@
         <v>487</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E64" s="18" t="s">
         <v>153</v>
@@ -5403,7 +5367,7 @@
         <v>1.22E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -5414,7 +5378,7 @@
         <v>487</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E65" s="18" t="s">
         <v>285</v>
@@ -5441,7 +5405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -5452,7 +5416,7 @@
         <v>487</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E66" s="18" t="s">
         <v>156</v>
@@ -5479,7 +5443,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -5490,7 +5454,7 @@
         <v>487</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E67" s="18" t="s">
         <v>407</v>
@@ -5517,7 +5481,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -5528,7 +5492,7 @@
         <v>487</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E68" s="18" t="s">
         <v>154</v>
@@ -5555,7 +5519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -5566,7 +5530,7 @@
         <v>487</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E69" s="18" t="s">
         <v>409</v>
@@ -5593,7 +5557,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -5604,7 +5568,7 @@
         <v>487</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E70" s="18" t="s">
         <v>155</v>
@@ -5631,7 +5595,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -5642,7 +5606,7 @@
         <v>487</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E71" s="18" t="s">
         <v>289</v>
@@ -5669,7 +5633,7 @@
         <v>1453890.8941884842</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -5680,7 +5644,7 @@
         <v>487</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E72" s="18" t="s">
         <v>382</v>
@@ -5707,7 +5671,7 @@
         <v>1.3888888888888888E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -5718,7 +5682,7 @@
         <v>487</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E73" s="18" t="s">
         <v>157</v>
@@ -5745,7 +5709,7 @@
         <v>6.5011574074074071E-4</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -5756,7 +5720,7 @@
         <v>487</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E74" s="18" t="s">
         <v>158</v>
@@ -5783,7 +5747,7 @@
         <v>4.7400000000000003E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -5794,7 +5758,7 @@
         <v>487</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E75" s="18" t="s">
         <v>159</v>
@@ -5821,7 +5785,7 @@
         <v>282528</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -5832,7 +5796,7 @@
         <v>487</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E76" s="18" t="s">
         <v>160</v>
@@ -5859,7 +5823,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -5870,7 +5834,7 @@
         <v>487</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E77" s="18" t="s">
         <v>161</v>
@@ -5897,7 +5861,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -5908,7 +5872,7 @@
         <v>487</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E78" s="18" t="s">
         <v>162</v>
@@ -5935,7 +5899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -5946,7 +5910,7 @@
         <v>487</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E79" s="34" t="s">
         <v>419</v>
@@ -5973,7 +5937,7 @@
         <v>745476480000</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -5984,7 +5948,7 @@
         <v>487</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E80" s="34" t="s">
         <v>413</v>
@@ -6011,7 +5975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -6022,7 +5986,7 @@
         <v>487</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E81" s="34" t="s">
         <v>420</v>
@@ -6049,7 +6013,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -6060,7 +6024,7 @@
         <v>487</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E82" s="34" t="s">
         <v>403</v>
@@ -6087,7 +6051,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -6098,7 +6062,7 @@
         <v>487</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E83" s="34" t="s">
         <v>416</v>
@@ -6125,7 +6089,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -6136,7 +6100,7 @@
         <v>487</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E84" s="34" t="s">
         <v>415</v>
@@ -6163,7 +6127,7 @@
         <v>60479.999999999993</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -6174,7 +6138,7 @@
         <v>487</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E85" s="34" t="s">
         <v>417</v>
@@ -6201,7 +6165,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -6212,7 +6176,7 @@
         <v>487</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E86" s="34" t="s">
         <v>404</v>
@@ -6239,7 +6203,7 @@
         <v>518400</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -6250,7 +6214,7 @@
         <v>487</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E87" s="34" t="s">
         <v>405</v>
@@ -6277,7 +6241,7 @@
         <v>5184000</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -6288,7 +6252,7 @@
         <v>487</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E88" s="18" t="s">
         <v>163</v>
@@ -6315,7 +6279,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -6326,7 +6290,7 @@
         <v>487</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E89" s="18" t="s">
         <v>164</v>
@@ -6353,7 +6317,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -6364,7 +6328,7 @@
         <v>487</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E90" s="18" t="s">
         <v>165</v>
@@ -6391,7 +6355,7 @@
         <v>3.6636136999999999E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -6402,7 +6366,7 @@
         <v>487</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E91" s="18" t="s">
         <v>166</v>
@@ -6429,7 +6393,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -6440,7 +6404,7 @@
         <v>487</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E92" s="18" t="s">
         <v>167</v>
@@ -6467,7 +6431,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -6478,7 +6442,7 @@
         <v>487</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E93" s="20" t="s">
         <v>291</v>
@@ -6505,7 +6469,7 @@
         <v>6.0000000000000002E-6</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -6516,7 +6480,7 @@
         <v>487</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E94" s="20" t="s">
         <v>292</v>
@@ -6543,7 +6507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -6554,7 +6518,7 @@
         <v>487</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E95" s="20" t="s">
         <v>296</v>
@@ -6581,7 +6545,7 @@
         <v>374999999.99999994</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -6592,7 +6556,7 @@
         <v>487</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E96" s="20" t="s">
         <v>293</v>
@@ -6619,7 +6583,7 @@
         <v>3.7037037037037038E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -6630,7 +6594,7 @@
         <v>487</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E97" s="20" t="s">
         <v>294</v>
@@ -6657,7 +6621,7 @@
         <v>165600</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -6668,7 +6632,7 @@
         <v>487</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E98" s="14" t="s">
         <v>172</v>
@@ -6695,7 +6659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -6706,7 +6670,7 @@
         <v>487</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>290</v>
@@ -6733,7 +6697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -6744,7 +6708,7 @@
         <v>487</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>171</v>
@@ -6771,7 +6735,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -6782,7 +6746,7 @@
         <v>487</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E101" s="24" t="s">
         <v>177</v>
@@ -6809,7 +6773,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -6820,7 +6784,7 @@
         <v>487</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E102" s="24" t="s">
         <v>370</v>
@@ -6847,7 +6811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -6858,7 +6822,7 @@
         <v>487</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E103" s="24" t="s">
         <v>371</v>
@@ -6885,7 +6849,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -6896,7 +6860,7 @@
         <v>487</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E104" s="24" t="s">
         <v>372</v>
@@ -6923,9 +6887,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>471</v>
@@ -6934,7 +6898,7 @@
         <v>487</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E105" s="24" t="s">
         <v>384</v>
@@ -6961,7 +6925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -6972,7 +6936,7 @@
         <v>487</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E106" s="24" t="s">
         <v>386</v>
@@ -6999,9 +6963,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>471</v>
@@ -7010,13 +6974,13 @@
         <v>487</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E107" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="F107" s="24" t="s">
         <v>506</v>
-      </c>
-      <c r="F107" s="24" t="s">
-        <v>507</v>
       </c>
       <c r="G107" s="58">
         <f>G105</f>
@@ -7041,9 +7005,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>471</v>
@@ -7052,13 +7016,13 @@
         <v>487</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E108" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="F108" s="24" t="s">
         <v>506</v>
-      </c>
-      <c r="F108" s="24" t="s">
-        <v>507</v>
       </c>
       <c r="G108" s="58">
         <f>3*G105</f>
@@ -7083,9 +7047,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>471</v>
@@ -7094,13 +7058,13 @@
         <v>487</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E109" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="F109" s="24" t="s">
         <v>506</v>
-      </c>
-      <c r="F109" s="24" t="s">
-        <v>507</v>
       </c>
       <c r="G109" s="58">
         <f>G100</f>
@@ -7125,24 +7089,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E110" s="24" t="s">
         <v>505</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E110" s="24" t="s">
+      <c r="F110" s="24" t="s">
         <v>506</v>
-      </c>
-      <c r="F110" s="24" t="s">
-        <v>507</v>
       </c>
       <c r="G110" s="58">
         <f>10*G100</f>
@@ -7167,7 +7131,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -7178,7 +7142,7 @@
         <v>487</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E111" s="24" t="s">
         <v>388</v>
@@ -7205,7 +7169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -7216,7 +7180,7 @@
         <v>487</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E112" s="24" t="s">
         <v>390</v>
@@ -7243,7 +7207,7 @@
         <v>1589759.9999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -7254,7 +7218,7 @@
         <v>487</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E113" s="24" t="s">
         <v>392</v>
@@ -7281,7 +7245,7 @@
         <v>6171428.5714285718</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -7292,7 +7256,7 @@
         <v>487</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E114" s="24" t="s">
         <v>394</v>
@@ -7319,7 +7283,7 @@
         <v>6171428.5714285718</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -7330,7 +7294,7 @@
         <v>487</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E115" s="24" t="s">
         <v>422</v>
@@ -7357,7 +7321,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -7368,7 +7332,7 @@
         <v>487</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E116" s="24" t="s">
         <v>424</v>
@@ -7399,7 +7363,7 @@
         <v>28080</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -7410,7 +7374,7 @@
         <v>487</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E117" s="24" t="s">
         <v>426</v>
@@ -7441,9 +7405,9 @@
         <v>0.11100000000000002</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>471</v>
@@ -7452,7 +7416,7 @@
         <v>487</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E118" s="24" t="s">
         <v>427</v>
@@ -7479,9 +7443,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>471</v>
@@ -7490,7 +7454,7 @@
         <v>487</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E119" s="24" t="s">
         <v>428</v>
@@ -7521,9 +7485,9 @@
         <v>459648</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>471</v>
@@ -7532,7 +7496,7 @@
         <v>487</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E120" s="24" t="s">
         <v>429</v>
@@ -7563,7 +7527,7 @@
         <v>0.13875000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -7574,7 +7538,7 @@
         <v>487</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E121" s="24" t="s">
         <v>396</v>
@@ -7601,7 +7565,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -7612,7 +7576,7 @@
         <v>487</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E122" s="24" t="s">
         <v>398</v>
@@ -7639,7 +7603,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -7650,7 +7614,7 @@
         <v>487</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E123" s="14" t="s">
         <v>173</v>
@@ -7677,7 +7641,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -7688,7 +7652,7 @@
         <v>487</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E124" s="14" t="s">
         <v>174</v>
@@ -7716,7 +7680,7 @@
         <v>2.0833333333333335E-4</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -7727,7 +7691,7 @@
         <v>487</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E125" s="14" t="s">
         <v>175</v>
@@ -7754,7 +7718,7 @@
         <v>5.7899999999999998E-7</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -7765,7 +7729,7 @@
         <v>487</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E126" s="14" t="s">
         <v>176</v>
@@ -7792,7 +7756,7 @@
         <v>2.0833333333333335E-4</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -7803,7 +7767,7 @@
         <v>487</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E127" s="14" t="s">
         <v>451</v>
@@ -7830,7 +7794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -7841,7 +7805,7 @@
         <v>487</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E128" s="14" t="s">
         <v>453</v>
@@ -7868,7 +7832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -7879,7 +7843,7 @@
         <v>487</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E129" s="69" t="s">
         <v>179</v>
@@ -7909,7 +7873,7 @@
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -7920,7 +7884,7 @@
         <v>487</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E130" s="69" t="s">
         <v>442</v>
@@ -7950,7 +7914,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -7961,7 +7925,7 @@
         <v>487</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E131" s="69" t="s">
         <v>447</v>
@@ -7973,22 +7937,22 @@
         <v>88</v>
       </c>
       <c r="H131" s="89" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="I131" s="89" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="J131" s="89" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="L131" s="89" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="M131" s="89" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -7999,7 +7963,7 @@
         <v>487</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E132" s="22" t="s">
         <v>178</v>
@@ -8026,7 +7990,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -8037,7 +8001,7 @@
         <v>487</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E133" s="22" t="s">
         <v>439</v>
@@ -8064,7 +8028,7 @@
         <v>4.9999999999999999E-13</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -8075,7 +8039,7 @@
         <v>487</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E134" s="22" t="s">
         <v>312</v>
@@ -8102,7 +8066,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -8113,7 +8077,7 @@
         <v>487</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E135" s="22" t="s">
         <v>313</v>
@@ -8140,7 +8104,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -8151,7 +8115,7 @@
         <v>487</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E136" s="22" t="s">
         <v>314</v>
@@ -8178,7 +8142,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -8189,7 +8153,7 @@
         <v>487</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E137" s="22" t="s">
         <v>315</v>
@@ -8216,7 +8180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="21" t="s">
         <v>68</v>
       </c>
@@ -8227,7 +8191,7 @@
         <v>487</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E138" s="22" t="s">
         <v>179</v>
@@ -8254,7 +8218,7 @@
         <v>1.9999999999999999E-7</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -8265,7 +8229,7 @@
         <v>487</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E139" s="22" t="s">
         <v>316</v>
@@ -8292,7 +8256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -8303,7 +8267,7 @@
         <v>487</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E140" s="22" t="s">
         <v>317</v>
@@ -8330,7 +8294,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -8341,7 +8305,7 @@
         <v>487</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E141" s="22" t="s">
         <v>318</v>
@@ -8368,7 +8332,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -8379,7 +8343,7 @@
         <v>487</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E142" s="22" t="s">
         <v>319</v>
@@ -8406,7 +8370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -8417,7 +8381,7 @@
         <v>487</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E143" s="22" t="s">
         <v>181</v>
@@ -8444,7 +8408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -8455,7 +8419,7 @@
         <v>487</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E144" s="73" t="s">
         <v>182</v>
@@ -8482,7 +8446,7 @@
         <v>5.0000000000000004E-6</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -8493,7 +8457,7 @@
         <v>487</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E145" s="24" t="s">
         <v>168</v>
@@ -8520,7 +8484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -8531,7 +8495,7 @@
         <v>487</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E146" s="24" t="s">
         <v>169</v>
@@ -8558,7 +8522,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -8569,7 +8533,7 @@
         <v>487</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E147" s="24" t="s">
         <v>170</v>
@@ -8596,7 +8560,7 @@
         <v>3.9999999999999998E-6</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -8607,7 +8571,7 @@
         <v>487</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E148" s="24" t="s">
         <v>184</v>
@@ -8634,7 +8598,7 @@
         <v>3.7699999999999999E-10</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -8645,7 +8609,7 @@
         <v>487</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E149" s="24" t="s">
         <v>304</v>
@@ -8672,7 +8636,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -8683,7 +8647,7 @@
         <v>487</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E150" s="24" t="s">
         <v>305</v>
@@ -8710,7 +8674,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -8721,7 +8685,7 @@
         <v>487</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E151" s="24" t="s">
         <v>306</v>
@@ -8748,7 +8712,7 @@
         <v>0.89100000000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -8759,7 +8723,7 @@
         <v>487</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E152" s="24" t="s">
         <v>307</v>
@@ -8786,7 +8750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -8797,7 +8761,7 @@
         <v>487</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E153" s="24" t="s">
         <v>185</v>
@@ -8824,7 +8788,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -8835,7 +8799,7 @@
         <v>487</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E154" s="14" t="s">
         <v>187</v>
@@ -8862,7 +8826,7 @@
         <v>5.8333333333333335E-9</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -8873,7 +8837,7 @@
         <v>487</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E155" s="14" t="s">
         <v>308</v>
@@ -8900,7 +8864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -8911,7 +8875,7 @@
         <v>487</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E156" s="14" t="s">
         <v>309</v>
@@ -8938,7 +8902,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -8949,7 +8913,7 @@
         <v>487</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E157" s="14" t="s">
         <v>310</v>
@@ -8976,7 +8940,7 @@
         <v>0.89100000000000001</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -8987,7 +8951,7 @@
         <v>487</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E158" s="14" t="s">
         <v>311</v>
@@ -9014,7 +8978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -9025,7 +8989,7 @@
         <v>487</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E159" s="14" t="s">
         <v>186</v>
@@ -9052,7 +9016,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -9063,7 +9027,7 @@
         <v>487</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E160" s="10" t="s">
         <v>188</v>
@@ -9090,7 +9054,7 @@
         <v>4.0000000000000001E-8</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -9101,7 +9065,7 @@
         <v>487</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>299</v>
@@ -9128,7 +9092,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -9139,7 +9103,7 @@
         <v>487</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E162" s="10" t="s">
         <v>300</v>
@@ -9166,7 +9130,7 @@
         <v>-4.4200000000000003E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -9177,7 +9141,7 @@
         <v>487</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>301</v>
@@ -9204,7 +9168,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -9215,7 +9179,7 @@
         <v>487</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E164" s="10" t="s">
         <v>303</v>
@@ -9242,7 +9206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -9253,7 +9217,7 @@
         <v>487</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>189</v>
@@ -9280,7 +9244,7 @@
         <v>2.7799999999999998E-4</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -9291,7 +9255,7 @@
         <v>487</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E166" s="26" t="s">
         <v>190</v>
@@ -9318,7 +9282,7 @@
         <v>2.4999999999999998E-12</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -9329,7 +9293,7 @@
         <v>487</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E167" s="26" t="s">
         <v>320</v>
@@ -9356,7 +9320,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -9367,7 +9331,7 @@
         <v>487</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E168" s="26" t="s">
         <v>321</v>
@@ -9394,7 +9358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -9405,7 +9369,7 @@
         <v>487</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E169" s="26" t="s">
         <v>322</v>
@@ -9432,7 +9396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -9443,7 +9407,7 @@
         <v>487</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E170" s="26" t="s">
         <v>323</v>
@@ -9470,7 +9434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -9481,7 +9445,7 @@
         <v>487</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E171" s="26" t="s">
         <v>191</v>
@@ -9508,7 +9472,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -9519,7 +9483,7 @@
         <v>487</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E172" s="32" t="s">
         <v>192</v>
@@ -9546,7 +9510,7 @@
         <v>2.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -9557,7 +9521,7 @@
         <v>487</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E173" s="32" t="s">
         <v>324</v>
@@ -9584,7 +9548,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -9595,7 +9559,7 @@
         <v>487</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E174" s="32" t="s">
         <v>325</v>
@@ -9622,7 +9586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -9633,7 +9597,7 @@
         <v>487</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E175" s="32" t="s">
         <v>326</v>
@@ -9660,7 +9624,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -9671,7 +9635,7 @@
         <v>487</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E176" s="32" t="s">
         <v>327</v>
@@ -9698,7 +9662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -9709,7 +9673,7 @@
         <v>487</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E177" s="32" t="s">
         <v>193</v>
@@ -9736,7 +9700,7 @@
         <v>1.6666666666666666E-4</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -9747,7 +9711,7 @@
         <v>487</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E178" s="12" t="s">
         <v>328</v>
@@ -9774,7 +9738,7 @@
         <v>1E-8</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -9785,7 +9749,7 @@
         <v>487</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E179" s="12" t="s">
         <v>330</v>
@@ -9812,7 +9776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -9823,7 +9787,7 @@
         <v>487</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E180" s="12" t="s">
         <v>331</v>
@@ -9850,7 +9814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -9861,7 +9825,7 @@
         <v>487</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E181" s="12" t="s">
         <v>332</v>
@@ -9888,7 +9852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -9899,7 +9863,7 @@
         <v>487</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E182" s="12" t="s">
         <v>333</v>
@@ -9926,7 +9890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -9937,7 +9901,7 @@
         <v>487</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E183" s="12" t="s">
         <v>350</v>
@@ -9964,7 +9928,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -9975,7 +9939,7 @@
         <v>487</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E184" s="12" t="s">
         <v>351</v>
@@ -10002,7 +9966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -10013,7 +9977,7 @@
         <v>487</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E185" s="28" t="s">
         <v>352</v>
@@ -10040,7 +10004,7 @@
         <v>2.3533050791148899E-8</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -10051,7 +10015,7 @@
         <v>487</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E186" s="28" t="s">
         <v>334</v>
@@ -10078,7 +10042,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -10089,7 +10053,7 @@
         <v>487</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E187" s="28" t="s">
         <v>335</v>
@@ -10116,7 +10080,7 @@
         <v>-0.187</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -10127,7 +10091,7 @@
         <v>487</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E188" s="28" t="s">
         <v>336</v>
@@ -10154,7 +10118,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -10165,7 +10129,7 @@
         <v>487</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E189" s="28" t="s">
         <v>337</v>
@@ -10192,7 +10156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -10203,7 +10167,7 @@
         <v>487</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E190" s="28" t="s">
         <v>354</v>
@@ -10230,7 +10194,7 @@
         <v>6.1060227588121015E-4</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -10241,7 +10205,7 @@
         <v>487</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E191" s="24" t="s">
         <v>194</v>
@@ -10268,7 +10232,7 @@
         <v>3.9999999999999998E-7</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -10279,7 +10243,7 @@
         <v>487</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E192" s="24" t="s">
         <v>338</v>
@@ -10306,7 +10270,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -10317,7 +10281,7 @@
         <v>487</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E193" s="24" t="s">
         <v>339</v>
@@ -10344,7 +10308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -10355,7 +10319,7 @@
         <v>487</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E194" s="24" t="s">
         <v>340</v>
@@ -10382,7 +10346,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -10393,7 +10357,7 @@
         <v>487</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E195" s="24" t="s">
         <v>341</v>
@@ -10420,7 +10384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -10431,7 +10395,7 @@
         <v>487</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E196" s="24" t="s">
         <v>195</v>
@@ -10458,7 +10422,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -10469,7 +10433,7 @@
         <v>487</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E197" s="8" t="s">
         <v>356</v>
@@ -10496,7 +10460,7 @@
         <v>3.9999999999999998E-7</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -10507,7 +10471,7 @@
         <v>487</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E198" s="8" t="s">
         <v>342</v>
@@ -10534,7 +10498,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -10545,7 +10509,7 @@
         <v>487</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E199" s="8" t="s">
         <v>343</v>
@@ -10572,7 +10536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -10583,7 +10547,7 @@
         <v>487</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E200" s="8" t="s">
         <v>344</v>
@@ -10610,7 +10574,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -10621,7 +10585,7 @@
         <v>487</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E201" s="8" t="s">
         <v>345</v>
@@ -10648,7 +10612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -10659,7 +10623,7 @@
         <v>487</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E202" s="8" t="s">
         <v>359</v>
@@ -10686,7 +10650,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -10697,7 +10661,7 @@
         <v>487</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E203" s="30" t="s">
         <v>357</v>
@@ -10724,7 +10688,7 @@
         <v>1.9999999999999999E-7</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -10735,7 +10699,7 @@
         <v>487</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E204" s="30" t="s">
         <v>346</v>
@@ -10762,7 +10726,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -10773,7 +10737,7 @@
         <v>487</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E205" s="30" t="s">
         <v>347</v>
@@ -10800,7 +10764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -10811,7 +10775,7 @@
         <v>487</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E206" s="30" t="s">
         <v>348</v>
@@ -10838,7 +10802,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -10849,7 +10813,7 @@
         <v>487</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E207" s="30" t="s">
         <v>349</v>
@@ -10876,7 +10840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -10887,7 +10851,7 @@
         <v>487</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E208" s="30" t="s">
         <v>361</v>
@@ -10914,7 +10878,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -10925,7 +10889,7 @@
         <v>487</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E209" s="93" t="s">
         <v>204</v>
@@ -10952,9 +10916,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="210" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>471</v>
@@ -10963,13 +10927,13 @@
         <v>487</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="F210" s="30" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="G210" s="2">
         <v>0.5</v>
@@ -10994,9 +10958,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="211" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>471</v>
@@ -11005,13 +10969,13 @@
         <v>487</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="F211" s="30" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="G211" s="98">
         <v>-100000</v>
@@ -11020,10 +10984,10 @@
         <v>0.3</v>
       </c>
       <c r="I211" s="83">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J211" s="83">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K211" s="1"/>
       <c r="L211" s="99">
@@ -11033,9 +10997,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>516</v>
+        <v>563</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>471</v>
@@ -11044,39 +11008,39 @@
         <v>487</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="E212" s="30" t="s">
-        <v>517</v>
-      </c>
-      <c r="F212" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="G212" s="98">
-        <v>-100000</v>
+        <v>532</v>
+      </c>
+      <c r="E212" s="96" t="s">
+        <v>511</v>
+      </c>
+      <c r="F212" s="96" t="s">
+        <v>495</v>
+      </c>
+      <c r="G212" s="100">
+        <v>0.5</v>
       </c>
       <c r="H212" s="83">
-        <f t="shared" ref="H212" si="3">H211</f>
-        <v>0.3</v>
+        <f t="shared" ref="H212:I212" si="3">0.00002 / 14</f>
+        <v>1.4285714285714286E-6</v>
       </c>
       <c r="I212" s="83">
-        <v>-10000</v>
+        <f t="shared" si="3"/>
+        <v>1.4285714285714286E-6</v>
       </c>
       <c r="J212" s="83">
-        <f t="shared" ref="J212" si="4">J211</f>
-        <v>0.3</v>
+        <v>2E-3</v>
       </c>
       <c r="K212" s="1"/>
-      <c r="L212" s="99">
-        <v>0</v>
-      </c>
-      <c r="M212" s="99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L212" s="100">
+        <v>1</v>
+      </c>
+      <c r="M212" s="100">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>574</v>
+        <v>507</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>471</v>
@@ -11085,37 +11049,35 @@
         <v>487</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E213" s="96" t="s">
         <v>512</v>
       </c>
       <c r="F213" s="96" t="s">
-        <v>495</v>
-      </c>
-      <c r="G213" s="100">
-        <v>0.5</v>
-      </c>
-      <c r="H213" s="83">
-        <f t="shared" ref="H213:I213" si="5">0.00002 / 14</f>
-        <v>1.4285714285714286E-6</v>
-      </c>
-      <c r="I213" s="83">
-        <f t="shared" si="5"/>
-        <v>1.4285714285714286E-6</v>
+        <v>510</v>
+      </c>
+      <c r="G213" s="100" t="s">
+        <v>476</v>
+      </c>
+      <c r="H213" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="I213" s="83" t="s">
+        <v>476</v>
       </c>
       <c r="J213" s="83">
-        <v>2E-3</v>
+        <v>0.1</v>
       </c>
       <c r="K213" s="1"/>
-      <c r="L213" s="100">
-        <v>1</v>
-      </c>
-      <c r="M213" s="100">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="214" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L213" s="98">
+        <v>0.1</v>
+      </c>
+      <c r="M213" s="98" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -11126,35 +11088,35 @@
         <v>487</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E214" s="96" t="s">
         <v>513</v>
       </c>
       <c r="F214" s="96" t="s">
-        <v>511</v>
-      </c>
-      <c r="G214" s="100" t="s">
-        <v>476</v>
-      </c>
-      <c r="H214" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="I214" s="83" t="s">
-        <v>476</v>
+        <v>510</v>
+      </c>
+      <c r="G214" s="100">
+        <v>0</v>
+      </c>
+      <c r="H214" s="83">
+        <v>0</v>
+      </c>
+      <c r="I214" s="83">
+        <v>0</v>
       </c>
       <c r="J214" s="83">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="K214" s="1"/>
       <c r="L214" s="98">
-        <v>0.1</v>
-      </c>
-      <c r="M214" s="98" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="215" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.04</v>
+      </c>
+      <c r="M214" s="98">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -11165,74 +11127,77 @@
         <v>487</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E215" s="96" t="s">
         <v>514</v>
       </c>
       <c r="F215" s="96" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G215" s="100">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="H215" s="83">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="I215" s="83">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="J215" s="83">
-        <v>0.04</v>
+        <v>1E-3</v>
       </c>
       <c r="K215" s="1"/>
       <c r="L215" s="98">
-        <v>0.04</v>
+        <v>1E-3</v>
       </c>
       <c r="M215" s="98">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="216" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.25">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C216" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>540</v>
+      <c r="C216" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>532</v>
       </c>
       <c r="E216" s="96" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F216" s="96" t="s">
-        <v>511</v>
-      </c>
-      <c r="G216" s="100">
-        <v>1E-3</v>
-      </c>
-      <c r="H216" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="I216" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="J216" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="K216" s="1"/>
-      <c r="L216" s="98">
-        <v>1E-3</v>
-      </c>
-      <c r="M216" s="98">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="G216" s="99">
+        <f>1.25*0.000001</f>
+        <v>1.2499999999999999E-6</v>
+      </c>
+      <c r="H216" s="99">
+        <f>1250*0.000001/5</f>
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="I216" s="99">
+        <f>1250*0.000001/5</f>
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="J216" s="99">
+        <f>1250*0.000001/5</f>
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="L216" s="99">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="M216" s="99">
+        <v>2.5000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -11243,36 +11208,36 @@
         <v>487</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E217" s="96" t="s">
         <v>519</v>
       </c>
       <c r="F217" s="96" t="s">
-        <v>507</v>
-      </c>
-      <c r="G217" s="100">
-        <v>29</v>
-      </c>
-      <c r="H217" s="2">
-        <v>29</v>
-      </c>
-      <c r="I217" s="2">
-        <v>29</v>
-      </c>
-      <c r="J217" s="2">
-        <v>29</v>
-      </c>
-      <c r="L217" s="2">
-        <v>29</v>
-      </c>
-      <c r="M217" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="G217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="H217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="I217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="J217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="L217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="M217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>471</v>
@@ -11281,40 +11246,30 @@
         <v>487</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E218" s="96" t="s">
-        <v>521</v>
+        <v>544</v>
       </c>
       <c r="F218" s="96" t="s">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="G218" s="99">
-        <f>1.25*0.000001</f>
-        <v>1.2499999999999999E-6</v>
-      </c>
-      <c r="H218" s="99">
-        <f>1250*0.000001/5</f>
-        <v>2.5000000000000001E-4</v>
-      </c>
-      <c r="I218" s="99">
-        <f>1250*0.000001/5</f>
-        <v>2.5000000000000001E-4</v>
-      </c>
-      <c r="J218" s="99">
-        <f>1250*0.000001/5</f>
-        <v>2.5000000000000001E-4</v>
-      </c>
-      <c r="L218" s="99">
-        <v>2.5000000000000001E-4</v>
-      </c>
-      <c r="M218" s="99">
-        <v>2.5000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="H218" s="83">
+        <v>2.4999999999999999E-13</v>
+      </c>
+      <c r="I218" s="83">
+        <v>2.4999999999999999E-13</v>
+      </c>
+      <c r="J218" s="83">
+        <v>2.4999999999999999E-13</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>471</v>
@@ -11323,550 +11278,370 @@
         <v>487</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E219" s="96" t="s">
-        <v>524</v>
+        <v>546</v>
       </c>
       <c r="F219" s="96" t="s">
-        <v>525</v>
-      </c>
-      <c r="G219" s="100">
-        <v>9.9999999999999994E-12</v>
-      </c>
-      <c r="H219" s="100">
-        <v>9.9999999999999994E-12</v>
-      </c>
-      <c r="I219" s="100">
-        <v>9.9999999999999994E-12</v>
-      </c>
-      <c r="J219" s="100">
-        <v>9.9999999999999994E-12</v>
-      </c>
-      <c r="L219" s="100">
-        <v>9.9999999999999994E-12</v>
-      </c>
-      <c r="M219" s="100">
-        <v>9.9999999999999994E-12</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="B220" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E220" s="96" t="s">
-        <v>527</v>
-      </c>
-      <c r="F220" s="96" t="s">
-        <v>528</v>
-      </c>
-      <c r="G220" s="99">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="H220" s="99">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="I220" s="99">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="J220" s="99">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="L220" s="99">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="M220" s="99">
-        <v>2.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A221" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E221" s="96" t="s">
-        <v>553</v>
-      </c>
-      <c r="F221" s="96" t="s">
-        <v>554</v>
-      </c>
-      <c r="G221" s="99">
-        <v>2.4999999999999998E-12</v>
-      </c>
-      <c r="H221" s="83">
-        <v>2.4999999999999999E-13</v>
-      </c>
-      <c r="I221" s="83">
-        <v>2.4999999999999999E-13</v>
-      </c>
-      <c r="J221" s="83">
-        <v>2.4999999999999999E-13</v>
-      </c>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A222" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E222" s="96" t="s">
-        <v>555</v>
-      </c>
-      <c r="F222" s="96" t="s">
-        <v>554</v>
-      </c>
-      <c r="G222" s="99">
+        <v>545</v>
+      </c>
+      <c r="G219" s="99">
         <v>1.2E-8</v>
       </c>
-      <c r="H222" s="83">
+      <c r="H219" s="83">
         <f>0.000000012 / 100</f>
         <v>1.2E-10</v>
       </c>
-      <c r="I222" s="83">
+      <c r="I219" s="83">
         <f>0.000000012 / 100</f>
         <v>1.2E-10</v>
       </c>
-      <c r="J222" s="83">
+      <c r="J219" s="83">
         <f>0.000000012 / 100</f>
         <v>1.2E-10</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A223" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E223" s="96" t="s">
-        <v>556</v>
-      </c>
-      <c r="F223" s="96" t="s">
-        <v>557</v>
-      </c>
-      <c r="G223" s="99">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A220" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E220" s="96" t="s">
+        <v>547</v>
+      </c>
+      <c r="F220" s="96" t="s">
+        <v>548</v>
+      </c>
+      <c r="G220" s="99">
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="H223" s="83">
+      <c r="H220" s="83">
         <f>0.000001 / 10000</f>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="I223" s="83">
+      <c r="I220" s="83">
         <f>0.000001 / 10000</f>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="J223" s="83">
+      <c r="J220" s="83">
         <f>0.000001 / 10000</f>
         <v>9.9999999999999991E-11</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A224" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E224" s="96" t="s">
-        <v>558</v>
-      </c>
-      <c r="F224" s="96" t="s">
-        <v>559</v>
-      </c>
-      <c r="G224" s="99">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A221" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E221" s="96" t="s">
+        <v>549</v>
+      </c>
+      <c r="F221" s="96" t="s">
+        <v>550</v>
+      </c>
+      <c r="G221" s="99">
         <f>2*0.00001</f>
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="H224" s="83">
+      <c r="H221" s="83">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="I224" s="83">
+      <c r="I221" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J221" s="83">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="J224" s="83">
-        <v>5.0000000000000002E-5</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E225" s="96" t="s">
-        <v>560</v>
-      </c>
-      <c r="F225" s="96" t="s">
-        <v>579</v>
-      </c>
-      <c r="G225" s="99">
-        <f>0.00000000000001 * 1000</f>
-        <v>9.9999999999999994E-12</v>
-      </c>
-      <c r="H225" s="83">
-        <f>104 * 0.000000001 / 18</f>
-        <v>5.777777777777778E-9</v>
-      </c>
-      <c r="I225" s="83">
-        <f>104 * 0.000000001 / 18</f>
-        <v>5.777777777777778E-9</v>
-      </c>
-      <c r="J225" s="83">
-        <f>104 * 0.000000001 / 18</f>
-        <v>5.777777777777778E-9</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A226" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E226" s="96" t="s">
-        <v>561</v>
-      </c>
-      <c r="F226" s="96" t="s">
-        <v>579</v>
-      </c>
-      <c r="G226" s="99">
-        <f>0.00000000000001 * 10000</f>
-        <v>1E-10</v>
-      </c>
-      <c r="H226" s="83">
-        <f t="shared" ref="H226" si="6">H225*10</f>
-        <v>5.7777777777777781E-8</v>
-      </c>
-      <c r="I226" s="83">
-        <f t="shared" ref="I226:J226" si="7">I225*10</f>
-        <v>5.7777777777777781E-8</v>
-      </c>
-      <c r="J226" s="83">
-        <f t="shared" si="7"/>
-        <v>5.7777777777777781E-8</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A227" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E227" s="96" t="s">
-        <v>562</v>
-      </c>
-      <c r="F227" s="96" t="s">
-        <v>507</v>
-      </c>
-      <c r="G227" s="99">
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E222" s="96" t="s">
+        <v>551</v>
+      </c>
+      <c r="F222" s="96" t="s">
+        <v>506</v>
+      </c>
+      <c r="G222" s="99">
         <f>0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
-      <c r="H227" s="83">
-        <f t="shared" ref="H227:J227" si="8">0.84*(0.36^2)</f>
+      <c r="H222" s="83">
+        <f t="shared" ref="H222:J222" si="4">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
-      <c r="I227" s="83">
-        <f t="shared" si="8"/>
+      <c r="I222" s="83">
+        <f t="shared" si="4"/>
         <v>0.10886399999999999</v>
       </c>
-      <c r="J227" s="83">
-        <f t="shared" si="8"/>
+      <c r="J222" s="83">
+        <f t="shared" si="4"/>
         <v>0.10886399999999999</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A228" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D228" s="2" t="s">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E223" s="96" t="s">
+        <v>552</v>
+      </c>
+      <c r="F223" s="96" t="s">
+        <v>495</v>
+      </c>
+      <c r="G223" s="100">
+        <v>0.2</v>
+      </c>
+      <c r="H223" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="I223" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="J223" s="83">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="E228" s="96" t="s">
-        <v>563</v>
-      </c>
-      <c r="F228" s="96" t="s">
-        <v>495</v>
-      </c>
-      <c r="G228" s="100">
-        <v>0.2</v>
-      </c>
-      <c r="H228" s="83">
-        <v>0.2</v>
-      </c>
-      <c r="I228" s="83">
-        <v>0.2</v>
-      </c>
-      <c r="J228" s="83">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A229" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E229" s="96" t="s">
-        <v>564</v>
-      </c>
-      <c r="F229" s="96" t="s">
-        <v>511</v>
-      </c>
-      <c r="G229" s="100" t="s">
+      <c r="B224" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E224" s="96" t="s">
+        <v>553</v>
+      </c>
+      <c r="F224" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G224" s="100" t="s">
         <v>476</v>
       </c>
-      <c r="H229" s="83" t="s">
+      <c r="H224" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="I229" s="83" t="s">
+      <c r="I224" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="J229" s="83" t="s">
+      <c r="J224" s="83" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A230" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E230" s="96" t="s">
-        <v>565</v>
-      </c>
-      <c r="F230" s="96" t="s">
-        <v>511</v>
-      </c>
-      <c r="G230" s="100">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E225" s="96" t="s">
+        <v>554</v>
+      </c>
+      <c r="F225" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G225" s="100">
         <f>2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="H230" s="83">
-        <f t="shared" ref="H230:J230" si="9">2*0.1</f>
+      <c r="H225" s="83">
+        <f t="shared" ref="H225:J225" si="5">2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="I230" s="83">
-        <f t="shared" si="9"/>
+      <c r="I225" s="83">
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
-      <c r="J230" s="83">
-        <f t="shared" si="9"/>
+      <c r="J225" s="83">
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A231" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E231" s="96" t="s">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E226" s="96" t="s">
+        <v>555</v>
+      </c>
+      <c r="F226" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G226" s="100">
+        <v>1E-3</v>
+      </c>
+      <c r="H226" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="I226" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="J226" s="83">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E227" s="96" t="s">
+        <v>556</v>
+      </c>
+      <c r="F227" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G227" s="98">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H227" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I227" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J227" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="F231" s="96" t="s">
-        <v>511</v>
-      </c>
-      <c r="G231" s="100">
-        <v>1E-3</v>
-      </c>
-      <c r="H231" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="I231" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="J231" s="83">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A232" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E232" s="96" t="s">
+      <c r="B228" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E228" s="30" t="s">
+        <v>558</v>
+      </c>
+      <c r="F228" s="30" t="s">
+        <v>559</v>
+      </c>
+      <c r="G228" s="83">
+        <f t="shared" ref="G228:J228" si="6">0.00002 / 14 / 5</f>
+        <v>2.8571428571428575E-7</v>
+      </c>
+      <c r="H228" s="83">
+        <f t="shared" si="6"/>
+        <v>2.8571428571428575E-7</v>
+      </c>
+      <c r="I228" s="83">
+        <v>0</v>
+      </c>
+      <c r="J228" s="83">
+        <f t="shared" si="6"/>
+        <v>2.8571428571428575E-7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="F232" s="96" t="s">
-        <v>511</v>
-      </c>
-      <c r="G232" s="98">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="H232" s="83">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="I232" s="83">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J232" s="83">
-        <v>1.0000000000000001E-5</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A233" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C233" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="E233" s="30" t="s">
-        <v>569</v>
-      </c>
-      <c r="F233" s="30" t="s">
-        <v>570</v>
-      </c>
-      <c r="G233" s="83">
-        <f t="shared" ref="G233:J233" si="10">0.00002 / 14 / 5</f>
-        <v>2.8571428571428575E-7</v>
-      </c>
-      <c r="H233" s="83">
-        <f t="shared" si="10"/>
-        <v>2.8571428571428575E-7</v>
-      </c>
-      <c r="I233" s="83">
-        <v>0</v>
-      </c>
-      <c r="J233" s="83">
-        <f t="shared" si="10"/>
-        <v>2.8571428571428575E-7</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A234" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="E234" s="30" t="s">
-        <v>569</v>
-      </c>
-      <c r="F234" s="30" t="s">
-        <v>570</v>
-      </c>
-      <c r="G234" s="83">
+      <c r="B229" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E229" s="30" t="s">
+        <v>558</v>
+      </c>
+      <c r="F229" s="30" t="s">
+        <v>559</v>
+      </c>
+      <c r="G229" s="83">
         <f>0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="H234" s="83">
+      <c r="H229" s="83">
         <f>0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="I234" s="83">
+      <c r="I229" s="83">
         <v>0</v>
       </c>
-      <c r="J234" s="83">
+      <c r="J229" s="83">
         <f>0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G233:I234">
+  <conditionalFormatting sqref="G228:I229">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -11888,7 +11663,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G234:J234">
+  <conditionalFormatting sqref="G229:J229">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11989,7 +11764,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H133:J133 L133:M133">
-    <cfRule type="colorScale" priority="302">
+    <cfRule type="colorScale" priority="301">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11999,7 +11774,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="301">
+    <cfRule type="colorScale" priority="302">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12023,7 +11798,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H144:J144 L144:M144">
-    <cfRule type="colorScale" priority="309">
+    <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12043,7 +11818,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="307">
+    <cfRule type="colorScale" priority="309">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12055,7 +11830,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H160:J160 L160:M160">
-    <cfRule type="colorScale" priority="315">
+    <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12075,7 +11850,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="313">
+    <cfRule type="colorScale" priority="315">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12131,28 +11906,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H212:J212">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H213:J213">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -12174,7 +11927,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H214:J214">
+  <conditionalFormatting sqref="H213:J213">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -12185,7 +11948,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="19">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H214:J214">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12197,7 +11972,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H215:J215">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12207,7 +11982,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12218,29 +11993,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H216:J216">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H221:J221">
+  <conditionalFormatting sqref="H218:J218">
     <cfRule type="colorScale" priority="325">
       <colorScale>
         <cfvo type="min"/>
@@ -12262,7 +12015,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H222:J222">
+  <conditionalFormatting sqref="H219:J219">
     <cfRule type="colorScale" priority="329">
       <colorScale>
         <cfvo type="min"/>
@@ -12284,7 +12037,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H223:J223">
+  <conditionalFormatting sqref="H220:J220">
     <cfRule type="colorScale" priority="333">
       <colorScale>
         <cfvo type="min"/>
@@ -12306,7 +12059,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H224:J224">
+  <conditionalFormatting sqref="H221:J221">
     <cfRule type="colorScale" priority="337">
       <colorScale>
         <cfvo type="min"/>
@@ -12328,51 +12081,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H225:J225">
-    <cfRule type="colorScale" priority="341">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="342">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H226:J226">
-    <cfRule type="colorScale" priority="345">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="346">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H227:J227">
+  <conditionalFormatting sqref="H222:J222">
     <cfRule type="colorScale" priority="349">
       <colorScale>
         <cfvo type="min"/>
@@ -12394,7 +12103,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H228:J232">
+  <conditionalFormatting sqref="H223:J227">
+    <cfRule type="colorScale" priority="353">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="354">
       <colorScale>
         <cfvo type="min"/>
@@ -12405,7 +12124,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="353">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J228">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12415,19 +12136,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J233">
     <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12451,7 +12160,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L166:M166 H166:J166">
-    <cfRule type="colorScale" priority="320">
+    <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12461,7 +12170,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="319">
+    <cfRule type="colorScale" priority="320">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12490,13 +12199,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C169"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="3" width="49.5703125" customWidth="1"/>
+    <col min="1" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="3" width="49.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>286</v>
       </c>
@@ -12507,7 +12216,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>206</v>
       </c>
@@ -12519,7 +12228,7 @@
         <v>pi</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -12531,7 +12240,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -12543,7 +12252,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>207</v>
       </c>
@@ -12555,7 +12264,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -12567,7 +12276,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -12579,7 +12288,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -12591,7 +12300,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -12603,7 +12312,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -12615,7 +12324,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -12627,7 +12336,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -12639,7 +12348,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -12651,7 +12360,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -12663,7 +12372,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -12675,7 +12384,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>208</v>
       </c>
@@ -12687,7 +12396,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -12699,7 +12408,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -12711,7 +12420,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>205</v>
       </c>
@@ -12723,7 +12432,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -12735,7 +12444,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -12747,7 +12456,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -12759,7 +12468,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -12771,7 +12480,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -12783,7 +12492,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -12795,7 +12504,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>209</v>
       </c>
@@ -12807,7 +12516,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>210</v>
       </c>
@@ -12819,7 +12528,7 @@
         <v>root_growth_T_ref</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>211</v>
       </c>
@@ -12831,7 +12540,7 @@
         <v>root_growth_A</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>212</v>
       </c>
@@ -12843,7 +12552,7 @@
         <v>root_growth_B</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>213</v>
       </c>
@@ -12855,7 +12564,7 @@
         <v>root_growth_C</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>214</v>
       </c>
@@ -12867,7 +12576,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>215</v>
       </c>
@@ -12879,7 +12588,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>216</v>
       </c>
@@ -12891,7 +12600,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>217</v>
       </c>
@@ -12903,7 +12612,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>218</v>
       </c>
@@ -12915,7 +12624,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -12927,7 +12636,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -12939,7 +12648,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>219</v>
       </c>
@@ -12951,7 +12660,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>220</v>
       </c>
@@ -12963,7 +12672,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>221</v>
       </c>
@@ -12975,7 +12684,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>222</v>
       </c>
@@ -12987,7 +12696,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -12999,7 +12708,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>223</v>
       </c>
@@ -13011,7 +12720,7 @@
         <v>expected_C_sucrose_root</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>224</v>
       </c>
@@ -13023,7 +12732,7 @@
         <v>expected_C_hexose_root</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>225</v>
       </c>
@@ -13035,7 +12744,7 @@
         <v>expected_C_hexose_soil</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>226</v>
       </c>
@@ -13047,7 +12756,7 @@
         <v>expected_C_hexose_reserve</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>65</v>
       </c>
@@ -13059,7 +12768,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>77</v>
       </c>
@@ -13071,7 +12780,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>227</v>
       </c>
@@ -13083,7 +12792,7 @@
         <v>surfacic_unloading_rate_reference</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>228</v>
       </c>
@@ -13095,7 +12804,7 @@
         <v>surfacic_unloading_rate_primordium</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -13107,7 +12816,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>229</v>
       </c>
@@ -13119,7 +12828,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>230</v>
       </c>
@@ -13131,7 +12840,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>231</v>
       </c>
@@ -13143,7 +12852,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>232</v>
       </c>
@@ -13155,7 +12864,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -13167,7 +12876,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>233</v>
       </c>
@@ -13179,7 +12888,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>234</v>
       </c>
@@ -13191,7 +12900,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>235</v>
       </c>
@@ -13203,7 +12912,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>236</v>
       </c>
@@ -13215,7 +12924,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -13227,7 +12936,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -13239,7 +12948,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -13251,7 +12960,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -13263,7 +12972,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>56</v>
       </c>
@@ -13275,7 +12984,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>58</v>
       </c>
@@ -13287,7 +12996,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -13299,7 +13008,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>237</v>
       </c>
@@ -13311,7 +13020,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>238</v>
       </c>
@@ -13323,7 +13032,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>239</v>
       </c>
@@ -13335,7 +13044,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>240</v>
       </c>
@@ -13347,7 +13056,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -13359,7 +13068,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -13371,7 +13080,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>241</v>
       </c>
@@ -13383,7 +13092,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>242</v>
       </c>
@@ -13395,7 +13104,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>243</v>
       </c>
@@ -13407,7 +13116,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>244</v>
       </c>
@@ -13419,7 +13128,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>74</v>
       </c>
@@ -13431,7 +13140,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>245</v>
       </c>
@@ -13443,7 +13152,7 @@
         <v>expected_exudation_efflux</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -13455,7 +13164,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>246</v>
       </c>
@@ -13467,7 +13176,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>247</v>
       </c>
@@ -13479,7 +13188,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>248</v>
       </c>
@@ -13491,7 +13200,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>249</v>
       </c>
@@ -13503,7 +13212,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>79</v>
       </c>
@@ -13515,7 +13224,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>80</v>
       </c>
@@ -13527,7 +13236,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>250</v>
       </c>
@@ -13539,7 +13248,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>251</v>
       </c>
@@ -13551,7 +13260,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -13563,7 +13272,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>253</v>
       </c>
@@ -13575,7 +13284,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>81</v>
       </c>
@@ -13587,7 +13296,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>254</v>
       </c>
@@ -13599,7 +13308,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -13611,7 +13320,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>256</v>
       </c>
@@ -13623,7 +13332,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>257</v>
       </c>
@@ -13635,7 +13344,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>258</v>
       </c>
@@ -13647,7 +13356,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>259</v>
       </c>
@@ -13659,7 +13368,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>260</v>
       </c>
@@ -13671,7 +13380,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>261</v>
       </c>
@@ -13683,7 +13392,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>262</v>
       </c>
@@ -13695,7 +13404,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>263</v>
       </c>
@@ -13707,7 +13416,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>264</v>
       </c>
@@ -13719,7 +13428,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>265</v>
       </c>
@@ -13731,7 +13440,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>266</v>
       </c>
@@ -13743,7 +13452,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>267</v>
       </c>
@@ -13755,7 +13464,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>268</v>
       </c>
@@ -13767,7 +13476,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>269</v>
       </c>
@@ -13779,7 +13488,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>270</v>
       </c>
@@ -13791,7 +13500,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>271</v>
       </c>
@@ -13803,7 +13512,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>272</v>
       </c>
@@ -13815,7 +13524,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>273</v>
       </c>
@@ -13827,7 +13536,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>274</v>
       </c>
@@ -13839,7 +13548,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>275</v>
       </c>
@@ -13851,7 +13560,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>276</v>
       </c>
@@ -13863,7 +13572,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>277</v>
       </c>
@@ -13875,7 +13584,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>278</v>
       </c>
@@ -13887,7 +13596,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>279</v>
       </c>
@@ -13899,7 +13608,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>280</v>
       </c>
@@ -13911,7 +13620,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>281</v>
       </c>
@@ -13923,7 +13632,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>282</v>
       </c>
@@ -13935,7 +13644,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>283</v>
       </c>
@@ -13947,7 +13656,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>284</v>
       </c>
@@ -13959,7 +13668,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>59</v>
       </c>
@@ -13971,7 +13680,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>62</v>
       </c>
@@ -13983,7 +13692,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>64</v>
       </c>
@@ -13995,7 +13704,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>63</v>
       </c>
@@ -14007,7 +13716,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>82</v>
       </c>
@@ -14019,7 +13728,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>83</v>
       </c>
@@ -14031,7 +13740,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>85</v>
       </c>
@@ -14043,7 +13752,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>84</v>
       </c>
@@ -14055,7 +13764,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>2</v>
       </c>
@@ -14067,7 +13776,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -14079,7 +13788,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -14091,7 +13800,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>20</v>
       </c>
@@ -14103,7 +13812,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>0</v>
       </c>
@@ -14115,7 +13824,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>1</v>
       </c>
@@ -14127,7 +13836,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>6</v>
       </c>
@@ -14139,7 +13848,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -14151,7 +13860,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -14163,7 +13872,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -14175,7 +13884,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -14187,7 +13896,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -14199,7 +13908,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>12</v>
       </c>
@@ -14211,7 +13920,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -14223,7 +13932,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>14</v>
       </c>
@@ -14235,7 +13944,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -14247,7 +13956,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -14259,7 +13968,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -14271,7 +13980,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14283,7 +13992,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -14295,7 +14004,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>21</v>
       </c>
@@ -14307,7 +14016,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>22</v>
       </c>
@@ -14319,7 +14028,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>23</v>
       </c>
@@ -14331,7 +14040,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -14343,7 +14052,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>25</v>
       </c>
@@ -14355,7 +14064,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>26</v>
       </c>
@@ -14367,7 +14076,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>27</v>
       </c>
@@ -14379,7 +14088,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>28</v>
       </c>
@@ -14388,7 +14097,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>29</v>
       </c>
@@ -14397,7 +14106,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>30</v>
       </c>
@@ -14406,7 +14115,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>31</v>
       </c>
@@ -14415,7 +14124,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>32</v>
       </c>
@@ -14424,7 +14133,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>33</v>
       </c>
@@ -14433,7 +14142,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>34</v>
       </c>
@@ -14442,7 +14151,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>35</v>
       </c>
@@ -14451,7 +14160,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>36</v>
       </c>
@@ -14460,7 +14169,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>37</v>
       </c>
@@ -14469,7 +14178,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>38</v>
       </c>
@@ -14478,7 +14187,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>362</v>
       </c>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sshfs\torisuten@192.168.12.9\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FB7C66-4E82-4D37-A0FA-15B43491F40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3BDE18-D6B2-4B1C-9266-6B7933559CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="571">
   <si>
     <t>input_file</t>
   </si>
@@ -1738,6 +1738,15 @@
   </si>
   <si>
     <t>DON</t>
+  </si>
+  <si>
+    <t>RC_ref</t>
+  </si>
+  <si>
+    <t>vmax_unloading_AA_phloem</t>
+  </si>
+  <si>
+    <t>RC_debug</t>
   </si>
 </sst>
 </file>
@@ -2924,7 +2933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M229"/>
+  <dimension ref="A1:O230"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" style="1" customWidth="1"/>
@@ -2932,10 +2941,10 @@
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="22.6640625" customWidth="1"/>
     <col min="7" max="7" width="19.5546875" style="37" customWidth="1"/>
-    <col min="8" max="13" width="39.88671875" style="1" customWidth="1"/>
+    <col min="8" max="15" width="39.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -2966,14 +2975,20 @@
       <c r="J1" s="97" t="s">
         <v>565</v>
       </c>
+      <c r="K1" s="97" t="s">
+        <v>568</v>
+      </c>
       <c r="L1" s="97" t="s">
+        <v>570</v>
+      </c>
+      <c r="N1" s="97" t="s">
         <v>522</v>
       </c>
-      <c r="M1" s="97" t="s">
+      <c r="O1" s="97" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>524</v>
       </c>
@@ -3004,14 +3019,20 @@
       <c r="J2" s="36" t="s">
         <v>476</v>
       </c>
+      <c r="K2" s="36" t="s">
+        <v>476</v>
+      </c>
       <c r="L2" s="36" t="s">
+        <v>476</v>
+      </c>
+      <c r="N2" s="36" t="s">
         <v>528</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="O2" s="36" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3042,14 +3063,20 @@
       <c r="J3" s="36" t="s">
         <v>489</v>
       </c>
+      <c r="K3" s="36" t="s">
+        <v>489</v>
+      </c>
       <c r="L3" s="36" t="s">
         <v>489</v>
       </c>
-      <c r="M3" s="36" t="s">
+      <c r="N3" s="36" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="36" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3080,14 +3107,20 @@
       <c r="J4" s="36" t="s">
         <v>482</v>
       </c>
+      <c r="K4" s="36" t="s">
+        <v>482</v>
+      </c>
       <c r="L4" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="N4" s="36" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O4" s="36" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3118,14 +3151,20 @@
       <c r="J5" s="36" t="s">
         <v>494</v>
       </c>
+      <c r="K5" s="36" t="s">
+        <v>482</v>
+      </c>
       <c r="L5" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="N5" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="M5" s="36" t="s">
+      <c r="O5" s="36" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3156,14 +3195,20 @@
       <c r="J6" s="36" t="s">
         <v>521</v>
       </c>
+      <c r="K6" s="36" t="s">
+        <v>521</v>
+      </c>
       <c r="L6" s="36" t="s">
         <v>521</v>
       </c>
-      <c r="M6" s="36" t="s">
+      <c r="N6" s="36" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O6" s="36" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3194,14 +3239,20 @@
       <c r="J7" s="36" t="s">
         <v>494</v>
       </c>
+      <c r="K7" s="36" t="s">
+        <v>494</v>
+      </c>
       <c r="L7" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="M7" s="36" t="s">
+      <c r="N7" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O7" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>529</v>
       </c>
@@ -3232,14 +3283,20 @@
       <c r="J8" s="36">
         <v>0</v>
       </c>
+      <c r="K8" s="36">
+        <v>0</v>
+      </c>
       <c r="L8" s="36">
         <v>0</v>
       </c>
-      <c r="M8" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N8" s="36">
+        <v>0</v>
+      </c>
+      <c r="O8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3270,14 +3327,20 @@
       <c r="J9" s="77" t="s">
         <v>87</v>
       </c>
+      <c r="K9" s="77" t="s">
+        <v>87</v>
+      </c>
       <c r="L9" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="77" t="s">
+      <c r="N9" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O9" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3308,14 +3371,20 @@
       <c r="J10" s="77">
         <v>1</v>
       </c>
+      <c r="K10" s="77">
+        <v>1</v>
+      </c>
       <c r="L10" s="77">
         <v>1</v>
       </c>
-      <c r="M10" s="77">
+      <c r="N10" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O10" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3346,14 +3415,20 @@
       <c r="J11" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K11" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="77" t="s">
+      <c r="N11" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O11" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3384,14 +3459,20 @@
       <c r="J12" s="85">
         <v>180</v>
       </c>
+      <c r="K12" s="85">
+        <v>180</v>
+      </c>
       <c r="L12" s="85">
         <v>180</v>
       </c>
-      <c r="M12" s="85">
+      <c r="N12" s="85">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O12" s="85">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3422,14 +3503,20 @@
       <c r="J13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
+      <c r="K13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
       <c r="L13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="M13" s="78">
+      <c r="N13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3460,14 +3547,20 @@
       <c r="J14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
+      <c r="K14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
       <c r="L14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="M14" s="79">
+      <c r="N14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3498,14 +3591,20 @@
       <c r="J15" s="77">
         <v>1</v>
       </c>
+      <c r="K15" s="77">
+        <v>1</v>
+      </c>
       <c r="L15" s="77">
         <v>1</v>
       </c>
-      <c r="M15" s="77">
+      <c r="N15" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O15" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3536,14 +3635,20 @@
       <c r="J16" s="77">
         <v>0</v>
       </c>
+      <c r="K16" s="77">
+        <v>0</v>
+      </c>
       <c r="L16" s="77">
         <v>0</v>
       </c>
-      <c r="M16" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N16" s="77">
+        <v>0</v>
+      </c>
+      <c r="O16" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3574,14 +3679,20 @@
       <c r="J17" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K17" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L17" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M17" s="77" t="s">
+      <c r="N17" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O17" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3612,14 +3723,20 @@
       <c r="J18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
+      <c r="K18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
       <c r="L18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="M18" s="80">
+      <c r="N18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -3650,14 +3767,20 @@
       <c r="J19" s="77">
         <v>10</v>
       </c>
+      <c r="K19" s="77">
+        <v>10</v>
+      </c>
       <c r="L19" s="77">
         <v>10</v>
       </c>
-      <c r="M19" s="77">
+      <c r="N19" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O19" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -3688,14 +3811,20 @@
       <c r="J20" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K20" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L20" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M20" s="77" t="s">
+      <c r="N20" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O20" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -3726,14 +3855,20 @@
       <c r="J21" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K21" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L21" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M21" s="77" t="s">
+      <c r="N21" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O21" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -3764,14 +3899,20 @@
       <c r="J22" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K22" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L22" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M22" s="77" t="s">
+      <c r="N22" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O22" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -3802,14 +3943,20 @@
       <c r="J23" s="77">
         <v>86400</v>
       </c>
+      <c r="K23" s="77">
+        <v>86400</v>
+      </c>
       <c r="L23" s="77">
         <v>86400</v>
       </c>
-      <c r="M23" s="77">
+      <c r="N23" s="77">
         <v>86400</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O23" s="77">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -3840,14 +3987,20 @@
       <c r="J24" s="77" t="s">
         <v>87</v>
       </c>
+      <c r="K24" s="77" t="s">
+        <v>87</v>
+      </c>
       <c r="L24" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M24" s="77" t="s">
+      <c r="N24" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O24" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -3878,14 +4031,20 @@
       <c r="J25" s="77">
         <v>3</v>
       </c>
+      <c r="K25" s="77">
+        <v>3</v>
+      </c>
       <c r="L25" s="77">
         <v>3</v>
       </c>
-      <c r="M25" s="77">
+      <c r="N25" s="77">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O25" s="77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -3916,14 +4075,20 @@
       <c r="J26" s="81" t="s">
         <v>88</v>
       </c>
+      <c r="K26" s="81" t="s">
+        <v>88</v>
+      </c>
       <c r="L26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="M26" s="81" t="s">
+      <c r="N26" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O26" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -3954,14 +4119,20 @@
       <c r="J27" s="81" t="s">
         <v>88</v>
       </c>
+      <c r="K27" s="81" t="s">
+        <v>88</v>
+      </c>
       <c r="L27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="M27" s="81" t="s">
+      <c r="N27" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O27" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -3992,14 +4163,20 @@
       <c r="J28" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K28" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L28" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M28" s="77" t="s">
+      <c r="N28" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O28" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4030,14 +4207,20 @@
       <c r="J29" s="81" t="s">
         <v>88</v>
       </c>
+      <c r="K29" s="81" t="s">
+        <v>88</v>
+      </c>
       <c r="L29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="M29" s="81" t="s">
+      <c r="N29" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O29" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4068,14 +4251,20 @@
       <c r="J30" s="81" t="s">
         <v>88</v>
       </c>
+      <c r="K30" s="81" t="s">
+        <v>88</v>
+      </c>
       <c r="L30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="M30" s="81" t="s">
+      <c r="N30" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O30" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4106,14 +4295,20 @@
       <c r="J31" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K31" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L31" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M31" s="77" t="s">
+      <c r="N31" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O31" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4144,14 +4339,20 @@
       <c r="J32" s="77">
         <v>0.33</v>
       </c>
+      <c r="K32" s="77">
+        <v>0.33</v>
+      </c>
       <c r="L32" s="77">
         <v>0.33</v>
       </c>
-      <c r="M32" s="77">
+      <c r="N32" s="77">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O32" s="77">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4182,14 +4383,20 @@
       <c r="J33" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K33" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M33" s="77" t="s">
+      <c r="N33" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O33" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4220,14 +4427,20 @@
       <c r="J34" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K34" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L34" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M34" s="77" t="s">
+      <c r="N34" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O34" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4258,14 +4471,20 @@
       <c r="J35" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K35" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L35" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M35" s="77" t="s">
+      <c r="N35" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O35" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4296,14 +4515,20 @@
       <c r="J36" s="77" t="s">
         <v>87</v>
       </c>
+      <c r="K36" s="77" t="s">
+        <v>87</v>
+      </c>
       <c r="L36" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M36" s="77" t="s">
+      <c r="N36" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O36" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4334,14 +4559,20 @@
       <c r="J37" s="85" t="s">
         <v>433</v>
       </c>
+      <c r="K37" s="85" t="s">
+        <v>433</v>
+      </c>
       <c r="L37" s="85" t="s">
         <v>433</v>
       </c>
-      <c r="M37" s="85" t="s">
+      <c r="N37" s="85" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O37" s="85" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -4372,14 +4603,20 @@
       <c r="J38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
+      <c r="K38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
       <c r="L38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="M38" s="80">
+      <c r="N38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -4410,14 +4647,20 @@
       <c r="J39" s="86">
         <v>1E-3</v>
       </c>
+      <c r="K39" s="86">
+        <v>1E-3</v>
+      </c>
       <c r="L39" s="86">
         <v>1E-3</v>
       </c>
-      <c r="M39" s="86">
+      <c r="N39" s="86">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O39" s="86">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -4448,14 +4691,20 @@
       <c r="J40" s="77" t="s">
         <v>87</v>
       </c>
+      <c r="K40" s="77" t="s">
+        <v>87</v>
+      </c>
       <c r="L40" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M40" s="77" t="s">
+      <c r="N40" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O40" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -4486,14 +4735,20 @@
       <c r="J41" s="77" t="s">
         <v>89</v>
       </c>
+      <c r="K41" s="77" t="s">
+        <v>89</v>
+      </c>
       <c r="L41" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="M41" s="77" t="s">
+      <c r="N41" s="77" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O41" s="77" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -4524,14 +4779,20 @@
       <c r="J42" s="77" t="s">
         <v>87</v>
       </c>
+      <c r="K42" s="77" t="s">
+        <v>87</v>
+      </c>
       <c r="L42" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M42" s="77" t="s">
+      <c r="N42" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O42" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -4562,14 +4823,20 @@
       <c r="J43" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K43" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L43" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M43" s="77" t="s">
+      <c r="N43" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O43" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -4600,14 +4867,20 @@
       <c r="J44" s="77">
         <v>120</v>
       </c>
+      <c r="K44" s="77">
+        <v>120</v>
+      </c>
       <c r="L44" s="77">
         <v>120</v>
       </c>
-      <c r="M44" s="77">
+      <c r="N44" s="77">
         <v>120</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O44" s="77">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -4638,14 +4911,20 @@
       <c r="J45" s="77">
         <v>0</v>
       </c>
+      <c r="K45" s="77">
+        <v>0</v>
+      </c>
       <c r="L45" s="77">
         <v>0</v>
       </c>
-      <c r="M45" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N45" s="77">
+        <v>0</v>
+      </c>
+      <c r="O45" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -4676,14 +4955,20 @@
       <c r="J46" s="77">
         <v>0</v>
       </c>
+      <c r="K46" s="77">
+        <v>0</v>
+      </c>
       <c r="L46" s="77">
         <v>0</v>
       </c>
-      <c r="M46" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N46" s="77">
+        <v>0</v>
+      </c>
+      <c r="O46" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -4714,14 +4999,20 @@
       <c r="J47" s="77">
         <v>-0.1</v>
       </c>
+      <c r="K47" s="77">
+        <v>-0.1</v>
+      </c>
       <c r="L47" s="77">
         <v>-0.1</v>
       </c>
-      <c r="M47" s="77">
+      <c r="N47" s="77">
         <v>-0.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O47" s="77">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -4752,14 +5043,20 @@
       <c r="J48" s="77">
         <v>-0.2</v>
       </c>
+      <c r="K48" s="77">
+        <v>-0.2</v>
+      </c>
       <c r="L48" s="77">
         <v>-0.2</v>
       </c>
-      <c r="M48" s="77">
+      <c r="N48" s="77">
         <v>-0.2</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O48" s="77">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -4790,14 +5087,20 @@
       <c r="J49" s="77">
         <v>0.4</v>
       </c>
+      <c r="K49" s="77">
+        <v>0.4</v>
+      </c>
       <c r="L49" s="77">
         <v>0.4</v>
       </c>
-      <c r="M49" s="77">
+      <c r="N49" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O49" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -4828,14 +5131,20 @@
       <c r="J50" s="77">
         <v>0</v>
       </c>
+      <c r="K50" s="77">
+        <v>0</v>
+      </c>
       <c r="L50" s="77">
         <v>0</v>
       </c>
-      <c r="M50" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N50" s="77">
+        <v>0</v>
+      </c>
+      <c r="O50" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -4866,14 +5175,20 @@
       <c r="J51" s="77">
         <v>1200</v>
       </c>
+      <c r="K51" s="77">
+        <v>1200</v>
+      </c>
       <c r="L51" s="77">
         <v>1200</v>
       </c>
-      <c r="M51" s="77">
+      <c r="N51" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O51" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -4904,14 +5219,20 @@
       <c r="J52" s="77">
         <v>1200</v>
       </c>
+      <c r="K52" s="77">
+        <v>1200</v>
+      </c>
       <c r="L52" s="77">
         <v>1200</v>
       </c>
-      <c r="M52" s="77">
+      <c r="N52" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O52" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -4942,14 +5263,20 @@
       <c r="J53" s="35" t="s">
         <v>460</v>
       </c>
+      <c r="K53" s="35" t="s">
+        <v>460</v>
+      </c>
       <c r="L53" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="M53" s="35" t="s">
+      <c r="N53" s="35" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O53" s="35" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -4980,14 +5307,20 @@
       <c r="J54" s="77" t="s">
         <v>87</v>
       </c>
+      <c r="K54" s="77" t="s">
+        <v>87</v>
+      </c>
       <c r="L54" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M54" s="77" t="s">
+      <c r="N54" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O54" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5018,14 +5351,20 @@
       <c r="J55" s="77" t="s">
         <v>87</v>
       </c>
+      <c r="K55" s="77" t="s">
+        <v>87</v>
+      </c>
       <c r="L55" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M55" s="77" t="s">
+      <c r="N55" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O55" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -5056,14 +5395,20 @@
       <c r="J56" s="77">
         <v>0</v>
       </c>
+      <c r="K56" s="77">
+        <v>0</v>
+      </c>
       <c r="L56" s="77">
         <v>0</v>
       </c>
-      <c r="M56" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N56" s="77">
+        <v>0</v>
+      </c>
+      <c r="O56" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -5094,14 +5439,20 @@
       <c r="J57" s="77">
         <v>0.5</v>
       </c>
+      <c r="K57" s="77">
+        <v>0.5</v>
+      </c>
       <c r="L57" s="77">
         <v>0.5</v>
       </c>
-      <c r="M57" s="77">
+      <c r="N57" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O57" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -5132,14 +5483,20 @@
       <c r="J58" s="77">
         <v>0.05</v>
       </c>
+      <c r="K58" s="77">
+        <v>0.05</v>
+      </c>
       <c r="L58" s="77">
         <v>0.05</v>
       </c>
-      <c r="M58" s="77">
+      <c r="N58" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O58" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -5170,14 +5527,20 @@
       <c r="J59" s="80">
         <v>1E-3</v>
       </c>
+      <c r="K59" s="80">
+        <v>1E-3</v>
+      </c>
       <c r="L59" s="80">
         <v>1E-3</v>
       </c>
-      <c r="M59" s="80">
+      <c r="N59" s="80">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O59" s="80">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -5208,14 +5571,20 @@
       <c r="J60" s="77">
         <v>0</v>
       </c>
+      <c r="K60" s="77">
+        <v>0</v>
+      </c>
       <c r="L60" s="77">
         <v>0</v>
       </c>
-      <c r="M60" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N60" s="77">
+        <v>0</v>
+      </c>
+      <c r="O60" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -5246,14 +5615,20 @@
       <c r="J61" s="77">
         <v>1E-4</v>
       </c>
+      <c r="K61" s="77">
+        <v>1E-4</v>
+      </c>
       <c r="L61" s="77">
         <v>1E-4</v>
       </c>
-      <c r="M61" s="77">
+      <c r="N61" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O61" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -5284,14 +5659,20 @@
       <c r="J62" s="77">
         <v>1E-4</v>
       </c>
+      <c r="K62" s="77">
+        <v>1E-4</v>
+      </c>
       <c r="L62" s="77">
         <v>1E-4</v>
       </c>
-      <c r="M62" s="77">
+      <c r="N62" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O62" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -5322,14 +5703,20 @@
       <c r="J63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
+      <c r="K63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
       <c r="L63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="M63" s="77">
+      <c r="N63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -5360,14 +5747,20 @@
       <c r="J64" s="77">
         <v>1.22E-4</v>
       </c>
+      <c r="K64" s="77">
+        <v>1.22E-4</v>
+      </c>
       <c r="L64" s="77">
         <v>1.22E-4</v>
       </c>
-      <c r="M64" s="77">
+      <c r="N64" s="77">
         <v>1.22E-4</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O64" s="77">
+        <v>1.22E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -5398,14 +5791,20 @@
       <c r="J65" s="77">
         <v>1</v>
       </c>
+      <c r="K65" s="77">
+        <v>1</v>
+      </c>
       <c r="L65" s="77">
         <v>1</v>
       </c>
-      <c r="M65" s="77">
+      <c r="N65" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O65" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -5436,14 +5835,20 @@
       <c r="J66" s="77">
         <v>0.95</v>
       </c>
+      <c r="K66" s="77">
+        <v>0.95</v>
+      </c>
       <c r="L66" s="77">
         <v>0.95</v>
       </c>
-      <c r="M66" s="77">
+      <c r="N66" s="77">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O66" s="77">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -5474,14 +5879,20 @@
       <c r="J67" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K67" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L67" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M67" s="77" t="s">
+      <c r="N67" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O67" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -5512,14 +5923,20 @@
       <c r="J68" s="77">
         <v>5</v>
       </c>
+      <c r="K68" s="77">
+        <v>5</v>
+      </c>
       <c r="L68" s="77">
         <v>5</v>
       </c>
-      <c r="M68" s="77">
+      <c r="N68" s="77">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O68" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -5550,14 +5967,20 @@
       <c r="J69" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K69" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L69" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M69" s="77" t="s">
+      <c r="N69" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O69" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -5588,14 +6011,20 @@
       <c r="J70" s="77">
         <v>50</v>
       </c>
+      <c r="K70" s="77">
+        <v>50</v>
+      </c>
       <c r="L70" s="77">
         <v>50</v>
       </c>
-      <c r="M70" s="77">
+      <c r="N70" s="77">
         <v>50</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O70" s="77">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -5626,14 +6055,20 @@
       <c r="J71" s="78">
         <v>1453890.8941884842</v>
       </c>
+      <c r="K71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
       <c r="L71" s="78">
         <v>1453890.8941884842</v>
       </c>
-      <c r="M71" s="78">
+      <c r="N71" s="78">
         <v>1453890.8941884842</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -5664,14 +6099,20 @@
       <c r="J72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
+      <c r="K72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
       <c r="L72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-      <c r="M72" s="78">
+      <c r="N72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -5702,14 +6143,20 @@
       <c r="J73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
+      <c r="K73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
       <c r="L73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-      <c r="M73" s="79">
+      <c r="N73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -5740,14 +6187,20 @@
       <c r="J74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
+      <c r="K74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
       <c r="L74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-      <c r="M74" s="85">
+      <c r="N74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -5778,14 +6231,20 @@
       <c r="J75" s="79">
         <v>282528</v>
       </c>
+      <c r="K75" s="79">
+        <v>282528</v>
+      </c>
       <c r="L75" s="79">
         <v>282528</v>
       </c>
-      <c r="M75" s="79">
+      <c r="N75" s="79">
         <v>282528</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O75" s="79">
+        <v>282528</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -5816,14 +6275,20 @@
       <c r="J76" s="85">
         <v>0.56999999999999995</v>
       </c>
+      <c r="K76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L76" s="85">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M76" s="85">
+      <c r="N76" s="85">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -5854,14 +6319,20 @@
       <c r="J77" s="87">
         <v>0.16</v>
       </c>
+      <c r="K77" s="87">
+        <v>0.16</v>
+      </c>
       <c r="L77" s="87">
         <v>0.16</v>
       </c>
-      <c r="M77" s="87">
+      <c r="N77" s="87">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O77" s="87">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -5892,14 +6363,20 @@
       <c r="J78" s="77">
         <v>0</v>
       </c>
+      <c r="K78" s="77">
+        <v>0</v>
+      </c>
       <c r="L78" s="77">
         <v>0</v>
       </c>
-      <c r="M78" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N78" s="77">
+        <v>0</v>
+      </c>
+      <c r="O78" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -5930,14 +6407,20 @@
       <c r="J79" s="78">
         <v>745476480000</v>
       </c>
+      <c r="K79" s="78">
+        <v>745476480000</v>
+      </c>
       <c r="L79" s="78">
         <v>745476480000</v>
       </c>
-      <c r="M79" s="78">
+      <c r="N79" s="78">
         <v>745476480000</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O79" s="78">
+        <v>745476480000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -5968,14 +6451,20 @@
       <c r="J80" s="77">
         <v>100</v>
       </c>
+      <c r="K80" s="77">
+        <v>100</v>
+      </c>
       <c r="L80" s="77">
         <v>100</v>
       </c>
-      <c r="M80" s="77">
+      <c r="N80" s="77">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O80" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -6006,14 +6495,20 @@
       <c r="J81" s="77" t="s">
         <v>88</v>
       </c>
+      <c r="K81" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="L81" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M81" s="77" t="s">
+      <c r="N81" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O81" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -6044,14 +6539,20 @@
       <c r="J82" s="85">
         <v>21600</v>
       </c>
+      <c r="K82" s="85">
+        <v>21600</v>
+      </c>
       <c r="L82" s="85">
         <v>21600</v>
       </c>
-      <c r="M82" s="85">
+      <c r="N82" s="85">
         <v>21600</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O82" s="85">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -6082,14 +6583,20 @@
       <c r="J83" s="77">
         <v>0.5</v>
       </c>
+      <c r="K83" s="77">
+        <v>0.5</v>
+      </c>
       <c r="L83" s="77">
         <v>0.5</v>
       </c>
-      <c r="M83" s="77">
+      <c r="N83" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O83" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -6120,14 +6627,20 @@
       <c r="J84" s="85">
         <v>60479.999999999993</v>
       </c>
+      <c r="K84" s="85">
+        <v>60479.999999999993</v>
+      </c>
       <c r="L84" s="85">
         <v>60479.999999999993</v>
       </c>
-      <c r="M84" s="85">
+      <c r="N84" s="85">
         <v>60479.999999999993</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -6158,14 +6671,20 @@
       <c r="J85" s="77">
         <v>0.85</v>
       </c>
+      <c r="K85" s="77">
+        <v>0.85</v>
+      </c>
       <c r="L85" s="77">
         <v>0.85</v>
       </c>
-      <c r="M85" s="77">
+      <c r="N85" s="77">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O85" s="77">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -6196,14 +6715,20 @@
       <c r="J86" s="77">
         <v>518400</v>
       </c>
+      <c r="K86" s="77">
+        <v>518400</v>
+      </c>
       <c r="L86" s="77">
         <v>518400</v>
       </c>
-      <c r="M86" s="77">
+      <c r="N86" s="77">
         <v>518400</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O86" s="77">
+        <v>518400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -6234,14 +6759,20 @@
       <c r="J87" s="77">
         <v>5184000</v>
       </c>
+      <c r="K87" s="77">
+        <v>5184000</v>
+      </c>
       <c r="L87" s="77">
         <v>5184000</v>
       </c>
-      <c r="M87" s="77">
+      <c r="N87" s="77">
         <v>5184000</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O87" s="77">
+        <v>5184000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -6272,14 +6803,20 @@
       <c r="J88" s="86">
         <v>50000</v>
       </c>
+      <c r="K88" s="86">
+        <v>50000</v>
+      </c>
       <c r="L88" s="86">
         <v>50000</v>
       </c>
-      <c r="M88" s="86">
+      <c r="N88" s="86">
         <v>50000</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O88" s="86">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -6310,14 +6847,20 @@
       <c r="J89" s="77">
         <v>140000</v>
       </c>
+      <c r="K89" s="77">
+        <v>140000</v>
+      </c>
       <c r="L89" s="77">
         <v>140000</v>
       </c>
-      <c r="M89" s="77">
+      <c r="N89" s="77">
         <v>140000</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O89" s="77">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -6348,14 +6891,20 @@
       <c r="J90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
+      <c r="K90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
       <c r="L90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-      <c r="M90" s="78">
+      <c r="N90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -6386,14 +6935,20 @@
       <c r="J91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
+      <c r="K91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
       <c r="L91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="M91" s="77">
+      <c r="N91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -6424,14 +6979,20 @@
       <c r="J92" s="77">
         <v>0.05</v>
       </c>
+      <c r="K92" s="77">
+        <v>0.05</v>
+      </c>
       <c r="L92" s="77">
         <v>0.05</v>
       </c>
-      <c r="M92" s="77">
+      <c r="N92" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O92" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -6462,14 +7023,20 @@
       <c r="J93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
+      <c r="K93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
       <c r="L93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="M93" s="77">
+      <c r="N93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -6500,14 +7067,20 @@
       <c r="J94" s="77">
         <v>1E-3</v>
       </c>
+      <c r="K94" s="77">
+        <v>1E-3</v>
+      </c>
       <c r="L94" s="77">
-        <v>0</v>
-      </c>
-      <c r="M94" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1E-3</v>
+      </c>
+      <c r="N94" s="77">
+        <v>0</v>
+      </c>
+      <c r="O94" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -6538,14 +7111,20 @@
       <c r="J95" s="77">
         <v>374999999.99999994</v>
       </c>
+      <c r="K95" s="77">
+        <v>374999999.99999994</v>
+      </c>
       <c r="L95" s="77">
         <v>374999999.99999994</v>
       </c>
-      <c r="M95" s="77">
+      <c r="N95" s="77">
         <v>374999999.99999994</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -6576,14 +7155,20 @@
       <c r="J96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
+      <c r="K96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
       <c r="L96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="M96" s="78">
+      <c r="N96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -6614,14 +7199,20 @@
       <c r="J97" s="77">
         <v>165600</v>
       </c>
+      <c r="K97" s="77">
+        <v>165600</v>
+      </c>
       <c r="L97" s="77">
         <v>165600</v>
       </c>
-      <c r="M97" s="77">
+      <c r="N97" s="77">
         <v>165600</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O97" s="77">
+        <v>165600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -6652,14 +7243,20 @@
       <c r="J98" s="77">
         <v>20</v>
       </c>
+      <c r="K98" s="77">
+        <v>20</v>
+      </c>
       <c r="L98" s="77">
         <v>20</v>
       </c>
-      <c r="M98" s="77">
+      <c r="N98" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O98" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -6690,14 +7287,20 @@
       <c r="J99" s="77">
         <v>1</v>
       </c>
+      <c r="K99" s="77">
+        <v>1</v>
+      </c>
       <c r="L99" s="77">
         <v>1</v>
       </c>
-      <c r="M99" s="77">
+      <c r="N99" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O99" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -6728,14 +7331,20 @@
       <c r="J100" s="77">
         <v>21</v>
       </c>
+      <c r="K100" s="77">
+        <v>21</v>
+      </c>
       <c r="L100" s="77">
         <v>21</v>
       </c>
-      <c r="M100" s="77">
+      <c r="N100" s="77">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O100" s="77">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -6766,14 +7375,20 @@
       <c r="J101" s="77">
         <v>0.64</v>
       </c>
+      <c r="K101" s="77">
+        <v>0.64</v>
+      </c>
       <c r="L101" s="77">
         <v>0.64</v>
       </c>
-      <c r="M101" s="77">
+      <c r="N101" s="77">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O101" s="77">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -6804,14 +7419,20 @@
       <c r="J102" s="77">
         <v>8</v>
       </c>
+      <c r="K102" s="77">
+        <v>8</v>
+      </c>
       <c r="L102" s="77">
         <v>8</v>
       </c>
-      <c r="M102" s="77">
+      <c r="N102" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O102" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -6842,14 +7463,20 @@
       <c r="J103" s="77">
         <v>10</v>
       </c>
+      <c r="K103" s="77">
+        <v>10</v>
+      </c>
       <c r="L103" s="77">
         <v>10</v>
       </c>
-      <c r="M103" s="77">
+      <c r="N103" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O103" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -6880,14 +7507,20 @@
       <c r="J104" s="77">
         <v>8</v>
       </c>
+      <c r="K104" s="77">
+        <v>8</v>
+      </c>
       <c r="L104" s="77">
         <v>8</v>
       </c>
-      <c r="M104" s="77">
+      <c r="N104" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O104" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>500</v>
       </c>
@@ -6918,14 +7551,20 @@
       <c r="J105" s="77">
         <v>1</v>
       </c>
+      <c r="K105" s="77">
+        <v>1</v>
+      </c>
       <c r="L105" s="77">
         <v>1</v>
       </c>
-      <c r="M105" s="77">
+      <c r="N105" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O105" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -6956,14 +7595,20 @@
       <c r="J106" s="77">
         <v>0.5</v>
       </c>
+      <c r="K106" s="77">
+        <v>0.5</v>
+      </c>
       <c r="L106" s="77">
         <v>0.5</v>
       </c>
-      <c r="M106" s="77">
+      <c r="N106" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O106" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>501</v>
       </c>
@@ -6998,14 +7643,22 @@
         <f>J105</f>
         <v>1</v>
       </c>
+      <c r="K107" s="58">
+        <f>K105</f>
+        <v>1</v>
+      </c>
       <c r="L107" s="58">
+        <f>L105</f>
         <v>1</v>
       </c>
-      <c r="M107" s="58">
+      <c r="N107" s="58">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O107" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
         <v>502</v>
       </c>
@@ -7040,14 +7693,22 @@
         <f>150*J105</f>
         <v>150</v>
       </c>
+      <c r="K108" s="58">
+        <f>150*K105</f>
+        <v>150</v>
+      </c>
       <c r="L108" s="58">
+        <f>150*L105</f>
         <v>150</v>
       </c>
-      <c r="M108" s="58">
+      <c r="N108" s="58">
         <v>150</v>
       </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O108" s="58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>503</v>
       </c>
@@ -7082,14 +7743,22 @@
         <f>J100</f>
         <v>21</v>
       </c>
+      <c r="K109" s="58">
+        <f>K100</f>
+        <v>21</v>
+      </c>
       <c r="L109" s="58">
+        <f>L100</f>
         <v>21</v>
       </c>
-      <c r="M109" s="58">
+      <c r="N109" s="58">
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O109" s="58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
         <v>504</v>
       </c>
@@ -7124,14 +7793,22 @@
         <f>70*J100</f>
         <v>1470</v>
       </c>
+      <c r="K110" s="58">
+        <f>70*K100</f>
+        <v>1470</v>
+      </c>
       <c r="L110" s="58">
+        <f>70*L100</f>
         <v>1470</v>
       </c>
-      <c r="M110" s="58">
+      <c r="N110" s="58">
         <v>1470</v>
       </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O110" s="58">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -7162,14 +7839,20 @@
       <c r="J111" s="77">
         <v>0</v>
       </c>
+      <c r="K111" s="77">
+        <v>0</v>
+      </c>
       <c r="L111" s="77">
         <v>0</v>
       </c>
-      <c r="M111" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N111" s="77">
+        <v>0</v>
+      </c>
+      <c r="O111" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -7200,14 +7883,20 @@
       <c r="J112" s="82">
         <v>1589759.9999999998</v>
       </c>
+      <c r="K112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
       <c r="L112" s="82">
         <v>1589759.9999999998</v>
       </c>
-      <c r="M112" s="82">
+      <c r="N112" s="82">
         <v>1589759.9999999998</v>
       </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -7238,14 +7927,20 @@
       <c r="J113" s="82">
         <v>6171428.5714285718</v>
       </c>
+      <c r="K113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
       <c r="L113" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="M113" s="82">
+      <c r="N113" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -7276,14 +7971,20 @@
       <c r="J114" s="82">
         <v>6171428.5714285718</v>
       </c>
+      <c r="K114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
       <c r="L114" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="M114" s="82">
+      <c r="N114" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -7314,14 +8015,20 @@
       <c r="J115" s="82">
         <v>100</v>
       </c>
+      <c r="K115" s="82">
+        <v>100</v>
+      </c>
       <c r="L115" s="82">
         <v>100</v>
       </c>
-      <c r="M115" s="82">
+      <c r="N115" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="116" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O115" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -7356,14 +8063,22 @@
         <f>0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
+      <c r="K116" s="67">
+        <f>0.1 * 3.25 * (60*60*24)</f>
+        <v>28080</v>
+      </c>
       <c r="L116" s="67">
+        <f>0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
-      <c r="M116" s="67">
+      <c r="N116" s="67">
         <v>28080</v>
       </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O116" s="67">
+        <v>28080</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -7398,14 +8113,22 @@
         <f>1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
+      <c r="K117" s="67">
+        <f>1.11 / 10</f>
+        <v>0.11100000000000002</v>
+      </c>
       <c r="L117" s="67">
+        <f>1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
-      <c r="M117" s="67">
+      <c r="N117" s="67">
         <v>0.11100000000000002</v>
       </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O117" s="67">
+        <v>0.11100000000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
         <v>497</v>
       </c>
@@ -7436,14 +8159,20 @@
       <c r="J118" s="82">
         <v>100</v>
       </c>
+      <c r="K118" s="82">
+        <v>100</v>
+      </c>
       <c r="L118" s="82">
         <v>100</v>
       </c>
-      <c r="M118" s="82">
+      <c r="N118" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="119" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O118" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>498</v>
       </c>
@@ -7478,14 +8207,22 @@
         <f>5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
+      <c r="K119" s="67">
+        <f>5.32 * (60*60*24)</f>
+        <v>459648</v>
+      </c>
       <c r="L119" s="67">
+        <f>5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
-      <c r="M119" s="67">
+      <c r="N119" s="67">
         <v>459648</v>
       </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O119" s="67">
+        <v>459648</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
         <v>499</v>
       </c>
@@ -7520,14 +8257,22 @@
         <f>1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
+      <c r="K120" s="67">
+        <f>1.11/8</f>
+        <v>0.13875000000000001</v>
+      </c>
       <c r="L120" s="67">
+        <f>1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
-      <c r="M120" s="67">
+      <c r="N120" s="67">
         <v>0.13875000000000001</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O120" s="67">
+        <v>0.13875000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -7558,14 +8303,20 @@
       <c r="J121" s="82">
         <v>21600</v>
       </c>
+      <c r="K121" s="82">
+        <v>21600</v>
+      </c>
       <c r="L121" s="82">
         <v>21600</v>
       </c>
-      <c r="M121" s="82">
+      <c r="N121" s="82">
         <v>21600</v>
       </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O121" s="82">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -7596,14 +8347,20 @@
       <c r="J122" s="88">
         <v>43200</v>
       </c>
+      <c r="K122" s="88">
+        <v>43200</v>
+      </c>
       <c r="L122" s="88">
         <v>43200</v>
       </c>
-      <c r="M122" s="88">
+      <c r="N122" s="88">
         <v>43200</v>
       </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O122" s="88">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -7634,14 +8391,20 @@
       <c r="J123" s="77">
         <v>0.8</v>
       </c>
+      <c r="K123" s="77">
+        <v>0.8</v>
+      </c>
       <c r="L123" s="77">
         <v>0.8</v>
       </c>
-      <c r="M123" s="77">
+      <c r="N123" s="77">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O123" s="77">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -7673,14 +8436,20 @@
       <c r="J124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
+      <c r="K124" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
       <c r="L124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="M124" s="78">
+      <c r="N124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O124" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -7711,14 +8480,20 @@
       <c r="J125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
+      <c r="K125" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
       <c r="L125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-      <c r="M125" s="77">
+      <c r="N125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O125" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -7749,14 +8524,20 @@
       <c r="J126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
+      <c r="K126" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
       <c r="L126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="M126" s="78">
+      <c r="N126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O126" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -7787,14 +8568,20 @@
       <c r="J127" s="78">
         <v>0</v>
       </c>
+      <c r="K127" s="78">
+        <v>0</v>
+      </c>
       <c r="L127" s="78">
         <v>0</v>
       </c>
-      <c r="M127" s="78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N127" s="78">
+        <v>0</v>
+      </c>
+      <c r="O127" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -7825,14 +8612,20 @@
       <c r="J128" s="78">
         <v>0</v>
       </c>
+      <c r="K128" s="78">
+        <v>0</v>
+      </c>
       <c r="L128" s="78">
         <v>0</v>
       </c>
-      <c r="M128" s="78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N128" s="78">
+        <v>0</v>
+      </c>
+      <c r="O128" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -7857,23 +8650,31 @@
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="I129" s="83">
-        <f t="shared" ref="I129:M129" si="0">0.0000002*3</f>
+        <f t="shared" ref="I129:O129" si="0">0.0000002*3</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J129" s="83">
         <f t="shared" si="0"/>
         <v>5.9999999999999997E-7</v>
       </c>
+      <c r="K129" s="83">
+        <f t="shared" si="0"/>
+        <v>5.9999999999999997E-7</v>
+      </c>
       <c r="L129" s="83">
         <f t="shared" si="0"/>
         <v>5.9999999999999997E-7</v>
       </c>
-      <c r="M129" s="83">
+      <c r="N129" s="83">
         <f t="shared" si="0"/>
         <v>5.9999999999999997E-7</v>
       </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O129" s="83">
+        <f t="shared" si="0"/>
+        <v>5.9999999999999997E-7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -7894,7 +8695,7 @@
       </c>
       <c r="G130" s="71"/>
       <c r="H130" s="83">
-        <f t="shared" ref="H130:M130" si="1">1000 * 0.000001 / 12</f>
+        <f t="shared" ref="H130:O130" si="1">1000 * 0.000001 / 12</f>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="I130" s="83">
@@ -7905,16 +8706,24 @@
         <f t="shared" si="1"/>
         <v>8.3333333333333331E-5</v>
       </c>
+      <c r="K130" s="83">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
       <c r="L130" s="83">
         <f t="shared" si="1"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M130" s="83">
+      <c r="N130" s="83">
         <f t="shared" si="1"/>
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O130" s="83">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -7945,14 +8754,20 @@
       <c r="J131" s="89" t="s">
         <v>533</v>
       </c>
+      <c r="K131" s="89" t="s">
+        <v>533</v>
+      </c>
       <c r="L131" s="89" t="s">
         <v>533</v>
       </c>
-      <c r="M131" s="89" t="s">
+      <c r="N131" s="89" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O131" s="89" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -7983,14 +8798,20 @@
       <c r="J132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
+      <c r="K132" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
       <c r="L132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="M132" s="83">
+      <c r="N132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O132" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -8021,14 +8842,20 @@
       <c r="J133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
+      <c r="K133" s="83">
+        <v>4.9999999999999999E-13</v>
+      </c>
       <c r="L133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="M133" s="83">
+      <c r="N133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O133" s="83">
+        <v>4.9999999999999999E-13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -8059,14 +8886,20 @@
       <c r="J134" s="77">
         <v>10</v>
       </c>
+      <c r="K134" s="77">
+        <v>10</v>
+      </c>
       <c r="L134" s="77">
         <v>10</v>
       </c>
-      <c r="M134" s="77">
+      <c r="N134" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O134" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -8097,14 +8930,20 @@
       <c r="J135" s="77">
         <v>-0.04</v>
       </c>
+      <c r="K135" s="77">
+        <v>-0.04</v>
+      </c>
       <c r="L135" s="77">
         <v>-0.04</v>
       </c>
-      <c r="M135" s="77">
+      <c r="N135" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O135" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -8135,14 +8974,20 @@
       <c r="J136" s="77">
         <v>2.9</v>
       </c>
+      <c r="K136" s="77">
+        <v>2.9</v>
+      </c>
       <c r="L136" s="77">
         <v>2.9</v>
       </c>
-      <c r="M136" s="77">
+      <c r="N136" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O136" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -8173,14 +9018,20 @@
       <c r="J137" s="77">
         <v>1</v>
       </c>
+      <c r="K137" s="77">
+        <v>1</v>
+      </c>
       <c r="L137" s="77">
         <v>1</v>
       </c>
-      <c r="M137" s="77">
+      <c r="N137" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O137" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="21" t="s">
         <v>68</v>
       </c>
@@ -8211,14 +9062,20 @@
       <c r="J138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
+      <c r="K138" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
       <c r="L138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="M138" s="80">
+      <c r="N138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O138" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -8249,14 +9106,20 @@
       <c r="J139" s="77">
         <v>10</v>
       </c>
+      <c r="K139" s="77">
+        <v>10</v>
+      </c>
       <c r="L139" s="77">
         <v>10</v>
       </c>
-      <c r="M139" s="77">
+      <c r="N139" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O139" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -8287,14 +9150,20 @@
       <c r="J140" s="77">
         <v>-0.04</v>
       </c>
+      <c r="K140" s="77">
+        <v>-0.04</v>
+      </c>
       <c r="L140" s="77">
         <v>-0.04</v>
       </c>
-      <c r="M140" s="77">
+      <c r="N140" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O140" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -8325,14 +9194,20 @@
       <c r="J141" s="77">
         <v>2.9</v>
       </c>
+      <c r="K141" s="77">
+        <v>2.9</v>
+      </c>
       <c r="L141" s="77">
         <v>2.9</v>
       </c>
-      <c r="M141" s="77">
+      <c r="N141" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O141" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -8363,14 +9238,20 @@
       <c r="J142" s="77">
         <v>1</v>
       </c>
+      <c r="K142" s="77">
+        <v>1</v>
+      </c>
       <c r="L142" s="77">
         <v>1</v>
       </c>
-      <c r="M142" s="77">
+      <c r="N142" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O142" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -8401,14 +9282,20 @@
       <c r="J143" s="77">
         <v>0</v>
       </c>
+      <c r="K143" s="77">
+        <v>0</v>
+      </c>
       <c r="L143" s="77">
         <v>0</v>
       </c>
-      <c r="M143" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N143" s="77">
+        <v>0</v>
+      </c>
+      <c r="O143" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -8439,14 +9326,20 @@
       <c r="J144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
+      <c r="K144" s="80">
+        <v>5.0000000000000004E-6</v>
+      </c>
       <c r="L144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="M144" s="80">
+      <c r="N144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O144" s="80">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -8477,14 +9370,20 @@
       <c r="J145" s="77">
         <v>0</v>
       </c>
+      <c r="K145" s="77">
+        <v>0</v>
+      </c>
       <c r="L145" s="77">
         <v>0</v>
       </c>
-      <c r="M145" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N145" s="77">
+        <v>0</v>
+      </c>
+      <c r="O145" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -8515,14 +9414,20 @@
       <c r="J146" s="77">
         <v>2E-3</v>
       </c>
+      <c r="K146" s="77">
+        <v>2E-3</v>
+      </c>
       <c r="L146" s="77">
         <v>2E-3</v>
       </c>
-      <c r="M146" s="77">
+      <c r="N146" s="77">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O146" s="77">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -8553,14 +9458,20 @@
       <c r="J147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
+      <c r="K147" s="80">
+        <v>3.9999999999999998E-6</v>
+      </c>
       <c r="L147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-      <c r="M147" s="80">
+      <c r="N147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O147" s="80">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -8591,14 +9502,20 @@
       <c r="J148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
+      <c r="K148" s="80">
+        <v>3.7699999999999999E-10</v>
+      </c>
       <c r="L148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-      <c r="M148" s="80">
+      <c r="N148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O148" s="80">
+        <v>3.7699999999999999E-10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -8629,14 +9546,20 @@
       <c r="J149" s="77">
         <v>20</v>
       </c>
+      <c r="K149" s="77">
+        <v>20</v>
+      </c>
       <c r="L149" s="77">
         <v>20</v>
       </c>
-      <c r="M149" s="77">
+      <c r="N149" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O149" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -8667,14 +9590,20 @@
       <c r="J150" s="77">
         <v>-0.06</v>
       </c>
+      <c r="K150" s="77">
+        <v>-0.06</v>
+      </c>
       <c r="L150" s="77">
         <v>-0.06</v>
       </c>
-      <c r="M150" s="77">
+      <c r="N150" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O150" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -8705,14 +9634,20 @@
       <c r="J151" s="77">
         <v>0.89100000000000001</v>
       </c>
+      <c r="K151" s="77">
+        <v>0.89100000000000001</v>
+      </c>
       <c r="L151" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="M151" s="77">
+      <c r="N151" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O151" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -8743,14 +9678,20 @@
       <c r="J152" s="77">
         <v>1</v>
       </c>
+      <c r="K152" s="77">
+        <v>1</v>
+      </c>
       <c r="L152" s="77">
         <v>1</v>
       </c>
-      <c r="M152" s="77">
+      <c r="N152" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O152" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -8781,14 +9722,20 @@
       <c r="J153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
+      <c r="K153" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
       <c r="L153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="M153" s="80">
+      <c r="N153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O153" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -8819,14 +9766,20 @@
       <c r="J154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
+      <c r="K154" s="80">
+        <v>5.8333333333333335E-9</v>
+      </c>
       <c r="L154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-      <c r="M154" s="80">
+      <c r="N154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O154" s="80">
+        <v>5.8333333333333335E-9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -8857,14 +9810,20 @@
       <c r="J155" s="77">
         <v>20</v>
       </c>
+      <c r="K155" s="77">
+        <v>20</v>
+      </c>
       <c r="L155" s="77">
         <v>20</v>
       </c>
-      <c r="M155" s="77">
+      <c r="N155" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O155" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -8895,14 +9854,20 @@
       <c r="J156" s="77">
         <v>-0.06</v>
       </c>
+      <c r="K156" s="77">
+        <v>-0.06</v>
+      </c>
       <c r="L156" s="77">
         <v>-0.06</v>
       </c>
-      <c r="M156" s="77">
+      <c r="N156" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O156" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -8933,14 +9898,20 @@
       <c r="J157" s="77">
         <v>0.89100000000000001</v>
       </c>
+      <c r="K157" s="77">
+        <v>0.89100000000000001</v>
+      </c>
       <c r="L157" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="M157" s="77">
+      <c r="N157" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O157" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -8971,14 +9942,20 @@
       <c r="J158" s="77">
         <v>1</v>
       </c>
+      <c r="K158" s="77">
+        <v>1</v>
+      </c>
       <c r="L158" s="77">
         <v>1</v>
       </c>
-      <c r="M158" s="77">
+      <c r="N158" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O158" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -9009,14 +9986,20 @@
       <c r="J159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
+      <c r="K159" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
       <c r="L159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="M159" s="80">
+      <c r="N159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O159" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -9047,14 +10030,20 @@
       <c r="J160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
+      <c r="K160" s="83">
+        <v>4.0000000000000001E-8</v>
+      </c>
       <c r="L160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="M160" s="83">
+      <c r="N160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O160" s="83">
+        <v>4.0000000000000001E-8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -9085,14 +10074,20 @@
       <c r="J161" s="77">
         <v>20</v>
       </c>
+      <c r="K161" s="77">
+        <v>20</v>
+      </c>
       <c r="L161" s="77">
         <v>20</v>
       </c>
-      <c r="M161" s="77">
+      <c r="N161" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O161" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -9123,14 +10118,20 @@
       <c r="J162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
+      <c r="K162" s="77">
+        <v>-4.4200000000000003E-2</v>
+      </c>
       <c r="L162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-      <c r="M162" s="77">
+      <c r="N162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O162" s="77">
+        <v>-4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -9161,14 +10162,20 @@
       <c r="J163" s="77">
         <v>1.55</v>
       </c>
+      <c r="K163" s="77">
+        <v>1.55</v>
+      </c>
       <c r="L163" s="77">
         <v>1.55</v>
       </c>
-      <c r="M163" s="77">
+      <c r="N163" s="77">
         <v>1.55</v>
       </c>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O163" s="77">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -9199,14 +10206,20 @@
       <c r="J164" s="77">
         <v>1</v>
       </c>
+      <c r="K164" s="77">
+        <v>1</v>
+      </c>
       <c r="L164" s="77">
         <v>1</v>
       </c>
-      <c r="M164" s="77">
+      <c r="N164" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O164" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -9237,14 +10250,20 @@
       <c r="J165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
+      <c r="K165" s="77">
+        <v>2.7799999999999998E-4</v>
+      </c>
       <c r="L165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="M165" s="77">
+      <c r="N165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-    </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O165" s="77">
+        <v>2.7799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -9275,14 +10294,20 @@
       <c r="J166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
+      <c r="K166" s="84">
+        <v>2.4999999999999998E-12</v>
+      </c>
       <c r="L166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="M166" s="84">
+      <c r="N166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O166" s="84">
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -9313,14 +10338,20 @@
       <c r="J167" s="77">
         <v>20</v>
       </c>
+      <c r="K167" s="77">
+        <v>20</v>
+      </c>
       <c r="L167" s="77">
         <v>20</v>
       </c>
-      <c r="M167" s="77">
+      <c r="N167" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O167" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -9351,14 +10382,20 @@
       <c r="J168" s="77">
         <v>0</v>
       </c>
+      <c r="K168" s="77">
+        <v>0</v>
+      </c>
       <c r="L168" s="77">
         <v>0</v>
       </c>
-      <c r="M168" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N168" s="77">
+        <v>0</v>
+      </c>
+      <c r="O168" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -9389,14 +10426,20 @@
       <c r="J169" s="77">
         <v>1</v>
       </c>
+      <c r="K169" s="77">
+        <v>1</v>
+      </c>
       <c r="L169" s="77">
         <v>1</v>
       </c>
-      <c r="M169" s="77">
+      <c r="N169" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O169" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -9427,14 +10470,20 @@
       <c r="J170" s="77">
         <v>0</v>
       </c>
+      <c r="K170" s="77">
+        <v>0</v>
+      </c>
       <c r="L170" s="77">
         <v>0</v>
       </c>
-      <c r="M170" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N170" s="77">
+        <v>0</v>
+      </c>
+      <c r="O170" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -9465,14 +10514,20 @@
       <c r="J171" s="77">
         <v>0.4</v>
       </c>
+      <c r="K171" s="77">
+        <v>0.4</v>
+      </c>
       <c r="L171" s="77">
         <v>0.4</v>
       </c>
-      <c r="M171" s="77">
+      <c r="N171" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O171" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -9503,14 +10558,20 @@
       <c r="J172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
+      <c r="K172" s="86">
+        <v>2.0000000000000001E-9</v>
+      </c>
       <c r="L172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-      <c r="M172" s="86">
+      <c r="N172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O172" s="86">
+        <v>2.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -9541,14 +10602,20 @@
       <c r="J173" s="77">
         <v>25</v>
       </c>
+      <c r="K173" s="77">
+        <v>25</v>
+      </c>
       <c r="L173" s="77">
         <v>25</v>
       </c>
-      <c r="M173" s="77">
+      <c r="N173" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O173" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -9579,14 +10646,20 @@
       <c r="J174" s="77">
         <v>0</v>
       </c>
+      <c r="K174" s="77">
+        <v>0</v>
+      </c>
       <c r="L174" s="77">
         <v>0</v>
       </c>
-      <c r="M174" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N174" s="77">
+        <v>0</v>
+      </c>
+      <c r="O174" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -9617,14 +10690,20 @@
       <c r="J175" s="77">
         <v>3.98</v>
       </c>
+      <c r="K175" s="77">
+        <v>3.98</v>
+      </c>
       <c r="L175" s="77">
         <v>3.98</v>
       </c>
-      <c r="M175" s="77">
+      <c r="N175" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O175" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -9655,14 +10734,20 @@
       <c r="J176" s="77">
         <v>1</v>
       </c>
+      <c r="K176" s="77">
+        <v>1</v>
+      </c>
       <c r="L176" s="77">
         <v>1</v>
       </c>
-      <c r="M176" s="77">
+      <c r="N176" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O176" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -9693,14 +10778,20 @@
       <c r="J177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
+      <c r="K177" s="78">
+        <v>1.6666666666666666E-4</v>
+      </c>
       <c r="L177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-      <c r="M177" s="78">
+      <c r="N177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-    </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O177" s="78">
+        <v>1.6666666666666666E-4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -9731,14 +10822,20 @@
       <c r="J178" s="80">
         <v>1E-8</v>
       </c>
+      <c r="K178" s="80">
+        <v>1E-8</v>
+      </c>
       <c r="L178" s="80">
         <v>1E-8</v>
       </c>
-      <c r="M178" s="80">
+      <c r="N178" s="80">
         <v>1E-8</v>
       </c>
-    </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O178" s="80">
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -9769,14 +10866,20 @@
       <c r="J179" s="77">
         <v>20</v>
       </c>
+      <c r="K179" s="77">
+        <v>20</v>
+      </c>
       <c r="L179" s="77">
         <v>20</v>
       </c>
-      <c r="M179" s="77">
+      <c r="N179" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O179" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -9807,14 +10910,20 @@
       <c r="J180" s="77">
         <v>0</v>
       </c>
+      <c r="K180" s="77">
+        <v>0</v>
+      </c>
       <c r="L180" s="77">
         <v>0</v>
       </c>
-      <c r="M180" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N180" s="77">
+        <v>0</v>
+      </c>
+      <c r="O180" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -9845,14 +10954,20 @@
       <c r="J181" s="77">
         <v>2</v>
       </c>
+      <c r="K181" s="77">
+        <v>2</v>
+      </c>
       <c r="L181" s="77">
         <v>2</v>
       </c>
-      <c r="M181" s="77">
+      <c r="N181" s="77">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O181" s="77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -9883,14 +10998,20 @@
       <c r="J182" s="77">
         <v>1</v>
       </c>
+      <c r="K182" s="77">
+        <v>1</v>
+      </c>
       <c r="L182" s="77">
         <v>1</v>
       </c>
-      <c r="M182" s="77">
+      <c r="N182" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O182" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -9921,14 +11042,20 @@
       <c r="J183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
+      <c r="K183" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
       <c r="L183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M183" s="78">
+      <c r="N183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O183" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -9959,14 +11086,20 @@
       <c r="J184" s="77">
         <v>1</v>
       </c>
+      <c r="K184" s="77">
+        <v>1</v>
+      </c>
       <c r="L184" s="77">
         <v>1</v>
       </c>
-      <c r="M184" s="77">
+      <c r="N184" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O184" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -9997,14 +11130,20 @@
       <c r="J185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
+      <c r="K185" s="77">
+        <v>2.3533050791148899E-8</v>
+      </c>
       <c r="L185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-      <c r="M185" s="77">
+      <c r="N185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O185" s="77">
+        <v>2.3533050791148899E-8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -10035,14 +11174,20 @@
       <c r="J186" s="77">
         <v>20</v>
       </c>
+      <c r="K186" s="77">
+        <v>20</v>
+      </c>
       <c r="L186" s="77">
         <v>20</v>
       </c>
-      <c r="M186" s="77">
+      <c r="N186" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O186" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -10073,14 +11218,20 @@
       <c r="J187" s="77">
         <v>-0.187</v>
       </c>
+      <c r="K187" s="77">
+        <v>-0.187</v>
+      </c>
       <c r="L187" s="77">
         <v>-0.187</v>
       </c>
-      <c r="M187" s="77">
+      <c r="N187" s="77">
         <v>-0.187</v>
       </c>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O187" s="77">
+        <v>-0.187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -10111,14 +11262,20 @@
       <c r="J188" s="77">
         <v>2.48</v>
       </c>
+      <c r="K188" s="77">
+        <v>2.48</v>
+      </c>
       <c r="L188" s="77">
         <v>2.48</v>
       </c>
-      <c r="M188" s="77">
+      <c r="N188" s="77">
         <v>2.48</v>
       </c>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O188" s="77">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -10149,14 +11306,20 @@
       <c r="J189" s="77">
         <v>1</v>
       </c>
+      <c r="K189" s="77">
+        <v>1</v>
+      </c>
       <c r="L189" s="77">
         <v>1</v>
       </c>
-      <c r="M189" s="77">
+      <c r="N189" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O189" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -10187,14 +11350,20 @@
       <c r="J190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
+      <c r="K190" s="77">
+        <v>6.1060227588121015E-4</v>
+      </c>
       <c r="L190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-      <c r="M190" s="77">
+      <c r="N190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O190" s="77">
+        <v>6.1060227588121015E-4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -10225,14 +11394,20 @@
       <c r="J191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
+      <c r="K191" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
       <c r="L191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="M191" s="85">
+      <c r="N191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O191" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -10263,14 +11438,20 @@
       <c r="J192" s="77">
         <v>25</v>
       </c>
+      <c r="K192" s="77">
+        <v>25</v>
+      </c>
       <c r="L192" s="77">
         <v>25</v>
       </c>
-      <c r="M192" s="77">
+      <c r="N192" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O192" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -10301,14 +11482,20 @@
       <c r="J193" s="77">
         <v>0</v>
       </c>
+      <c r="K193" s="77">
+        <v>0</v>
+      </c>
       <c r="L193" s="77">
         <v>0</v>
       </c>
-      <c r="M193" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N193" s="77">
+        <v>0</v>
+      </c>
+      <c r="O193" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -10339,14 +11526,20 @@
       <c r="J194" s="77">
         <v>3.98</v>
       </c>
+      <c r="K194" s="77">
+        <v>3.98</v>
+      </c>
       <c r="L194" s="77">
         <v>3.98</v>
       </c>
-      <c r="M194" s="77">
+      <c r="N194" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O194" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -10377,14 +11570,20 @@
       <c r="J195" s="77">
         <v>1</v>
       </c>
+      <c r="K195" s="77">
+        <v>1</v>
+      </c>
       <c r="L195" s="77">
         <v>1</v>
       </c>
-      <c r="M195" s="77">
+      <c r="N195" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O195" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -10415,14 +11614,20 @@
       <c r="J196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
+      <c r="K196" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
       <c r="L196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M196" s="78">
+      <c r="N196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O196" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -10453,14 +11658,20 @@
       <c r="J197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
+      <c r="K197" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
       <c r="L197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="M197" s="85">
+      <c r="N197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O197" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -10491,14 +11702,20 @@
       <c r="J198" s="77">
         <v>25</v>
       </c>
+      <c r="K198" s="77">
+        <v>25</v>
+      </c>
       <c r="L198" s="77">
         <v>25</v>
       </c>
-      <c r="M198" s="77">
+      <c r="N198" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O198" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -10529,14 +11746,20 @@
       <c r="J199" s="77">
         <v>0</v>
       </c>
+      <c r="K199" s="77">
+        <v>0</v>
+      </c>
       <c r="L199" s="77">
         <v>0</v>
       </c>
-      <c r="M199" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N199" s="77">
+        <v>0</v>
+      </c>
+      <c r="O199" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -10567,14 +11790,20 @@
       <c r="J200" s="77">
         <v>3.98</v>
       </c>
+      <c r="K200" s="77">
+        <v>3.98</v>
+      </c>
       <c r="L200" s="77">
         <v>3.98</v>
       </c>
-      <c r="M200" s="77">
+      <c r="N200" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O200" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -10605,14 +11834,20 @@
       <c r="J201" s="77">
         <v>1</v>
       </c>
+      <c r="K201" s="77">
+        <v>1</v>
+      </c>
       <c r="L201" s="77">
         <v>1</v>
       </c>
-      <c r="M201" s="77">
+      <c r="N201" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O201" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -10643,14 +11878,20 @@
       <c r="J202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
+      <c r="K202" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
       <c r="L202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M202" s="78">
+      <c r="N202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O202" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -10681,14 +11922,20 @@
       <c r="J203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
+      <c r="K203" s="85">
+        <v>1.9999999999999999E-7</v>
+      </c>
       <c r="L203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="M203" s="85">
+      <c r="N203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O203" s="85">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -10719,14 +11966,20 @@
       <c r="J204" s="77">
         <v>25</v>
       </c>
+      <c r="K204" s="77">
+        <v>25</v>
+      </c>
       <c r="L204" s="77">
         <v>25</v>
       </c>
-      <c r="M204" s="77">
+      <c r="N204" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O204" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -10757,14 +12010,20 @@
       <c r="J205" s="77">
         <v>0</v>
       </c>
+      <c r="K205" s="77">
+        <v>0</v>
+      </c>
       <c r="L205" s="77">
         <v>0</v>
       </c>
-      <c r="M205" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N205" s="77">
+        <v>0</v>
+      </c>
+      <c r="O205" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -10795,14 +12054,20 @@
       <c r="J206" s="77">
         <v>3.98</v>
       </c>
+      <c r="K206" s="77">
+        <v>3.98</v>
+      </c>
       <c r="L206" s="77">
         <v>3.98</v>
       </c>
-      <c r="M206" s="77">
+      <c r="N206" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O206" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -10833,14 +12098,20 @@
       <c r="J207" s="77">
         <v>1</v>
       </c>
+      <c r="K207" s="77">
+        <v>1</v>
+      </c>
       <c r="L207" s="77">
         <v>1</v>
       </c>
-      <c r="M207" s="77">
+      <c r="N207" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O207" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -10871,14 +12142,20 @@
       <c r="J208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
+      <c r="K208" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
       <c r="L208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M208" s="78">
+      <c r="N208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O208" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -10909,14 +12186,20 @@
       <c r="J209" s="95" t="s">
         <v>90</v>
       </c>
+      <c r="K209" s="95" t="s">
+        <v>90</v>
+      </c>
       <c r="L209" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="M209" s="95" t="s">
+      <c r="N209" s="95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="210" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O209" s="95" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>557</v>
       </c>
@@ -10939,7 +12222,7 @@
         <v>0.5</v>
       </c>
       <c r="H210" s="83">
-        <f t="shared" ref="H210:J210" si="2">0.00002</f>
+        <f t="shared" ref="H210:L210" si="2">0.00002</f>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="I210" s="83">
@@ -10950,15 +12233,23 @@
         <f t="shared" si="2"/>
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="K210" s="1"/>
-      <c r="L210" s="2">
+      <c r="K210" s="83">
+        <f t="shared" si="2"/>
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="L210" s="83">
+        <f t="shared" si="2"/>
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="M210" s="1"/>
+      <c r="N210" s="2">
         <v>0.01</v>
       </c>
-      <c r="M210" s="2">
+      <c r="O210" s="2">
         <v>0.01</v>
       </c>
     </row>
-    <row r="211" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>560</v>
       </c>
@@ -10989,15 +12280,21 @@
       <c r="J211" s="83">
         <v>0.1</v>
       </c>
-      <c r="K211" s="1"/>
-      <c r="L211" s="99">
-        <v>0</v>
-      </c>
-      <c r="M211" s="99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K211" s="83">
+        <v>0.1</v>
+      </c>
+      <c r="L211" s="83">
+        <v>0.1</v>
+      </c>
+      <c r="M211" s="1"/>
+      <c r="N211" s="99">
+        <v>0</v>
+      </c>
+      <c r="O211" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>563</v>
       </c>
@@ -11020,7 +12317,7 @@
         <v>0.5</v>
       </c>
       <c r="H212" s="83">
-        <f t="shared" ref="H212:I212" si="3">0.00002 / 14</f>
+        <f t="shared" ref="H212:L212" si="3">0.00002 / 14</f>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="I212" s="83">
@@ -11030,15 +12327,23 @@
       <c r="J212" s="83">
         <v>2E-3</v>
       </c>
-      <c r="K212" s="1"/>
-      <c r="L212" s="100">
+      <c r="K212" s="83">
+        <f t="shared" si="3"/>
+        <v>1.4285714285714286E-6</v>
+      </c>
+      <c r="L212" s="83">
+        <f t="shared" si="3"/>
+        <v>1.4285714285714286E-6</v>
+      </c>
+      <c r="M212" s="1"/>
+      <c r="N212" s="100">
         <v>1</v>
       </c>
-      <c r="M212" s="100">
+      <c r="O212" s="100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="213" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>507</v>
       </c>
@@ -11069,15 +12374,21 @@
       <c r="J213" s="83">
         <v>0.1</v>
       </c>
-      <c r="K213" s="1"/>
-      <c r="L213" s="98">
+      <c r="K213" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="L213" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="M213" s="1"/>
+      <c r="N213" s="98">
         <v>0.1</v>
       </c>
-      <c r="M213" s="98" t="s">
+      <c r="O213" s="98" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="214" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -11108,15 +12419,21 @@
       <c r="J214" s="83">
         <v>0.04</v>
       </c>
-      <c r="K214" s="1"/>
-      <c r="L214" s="98">
+      <c r="K214" s="83">
+        <v>0</v>
+      </c>
+      <c r="L214" s="83">
+        <v>0</v>
+      </c>
+      <c r="M214" s="1"/>
+      <c r="N214" s="98">
         <v>0.04</v>
       </c>
-      <c r="M214" s="98">
+      <c r="O214" s="98">
         <v>0.04</v>
       </c>
     </row>
-    <row r="215" spans="1:13" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -11147,15 +12464,21 @@
       <c r="J215" s="83">
         <v>1E-3</v>
       </c>
-      <c r="K215" s="1"/>
-      <c r="L215" s="98">
+      <c r="K215" s="83">
         <v>1E-3</v>
       </c>
-      <c r="M215" s="98">
+      <c r="L215" s="83">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M215" s="1"/>
+      <c r="N215" s="98">
+        <v>1E-3</v>
+      </c>
+      <c r="O215" s="98">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>515</v>
       </c>
@@ -11190,14 +12513,22 @@
         <f>1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
+      <c r="K216" s="99">
+        <f>1250*0.000001/5</f>
+        <v>2.5000000000000001E-4</v>
+      </c>
       <c r="L216" s="99">
+        <f>1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="M216" s="99">
+      <c r="N216" s="99">
         <v>2.5000000000000001E-4</v>
       </c>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O216" s="99">
+        <v>2.5000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -11228,14 +12559,20 @@
       <c r="J217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
+      <c r="K217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
       <c r="L217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="M217" s="99">
+      <c r="N217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>534</v>
       </c>
@@ -11261,13 +12598,22 @@
         <v>2.4999999999999999E-13</v>
       </c>
       <c r="I218" s="83">
-        <v>2.4999999999999999E-13</v>
+        <f xml:space="preserve"> 0.0000000000025 * 10</f>
+        <v>2.4999999999999998E-11</v>
       </c>
       <c r="J218" s="83">
         <v>2.4999999999999999E-13</v>
       </c>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K218" s="83">
+        <f xml:space="preserve"> 0.0000000000025</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="L218" s="83">
+        <f xml:space="preserve"> 0.0000000000025</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>535</v>
       </c>
@@ -11294,17 +12640,25 @@
         <v>1.2E-10</v>
       </c>
       <c r="I219" s="83">
-        <f>0.000000012 / 100</f>
-        <v>1.2E-10</v>
+        <f>0.000000012 / 100 / 2</f>
+        <v>6E-11</v>
       </c>
       <c r="J219" s="83">
         <f>0.000000012 / 100</f>
         <v>1.2E-10</v>
       </c>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K219" s="83">
+        <f>0.000000012 / 10 / 5</f>
+        <v>2.4E-10</v>
+      </c>
+      <c r="L219" s="83">
+        <f>0.000000012 / 10 / 5</f>
+        <v>2.4E-10</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>471</v>
@@ -11316,332 +12670,919 @@
         <v>532</v>
       </c>
       <c r="E220" s="96" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F220" s="96" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G220" s="99">
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="H220" s="83">
+      <c r="H220" s="83"/>
+      <c r="I220" s="83"/>
+      <c r="J220" s="83"/>
+      <c r="K220" s="83">
+        <f>0.0000001 / 2</f>
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="L220" s="83">
+        <f>0.0000001 / 2</f>
+        <v>4.9999999999999998E-8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A221" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E221" s="96" t="s">
+        <v>547</v>
+      </c>
+      <c r="F221" s="96" t="s">
+        <v>548</v>
+      </c>
+      <c r="G221" s="99">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="H221" s="83">
         <f>0.000001 / 10000</f>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="I220" s="83">
+      <c r="I221" s="83">
         <f>0.000001 / 10000</f>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="J220" s="83">
+      <c r="J221" s="83">
         <f>0.000001 / 10000</f>
         <v>9.9999999999999991E-11</v>
       </c>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A221" s="2" t="s">
+      <c r="K221" s="83">
+        <f>0.000001 / 10000</f>
+        <v>9.9999999999999991E-11</v>
+      </c>
+      <c r="L221" s="83">
+        <f>0.000001 / 10000</f>
+        <v>9.9999999999999991E-11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="B221" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E221" s="96" t="s">
+      <c r="B222" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E222" s="96" t="s">
         <v>549</v>
       </c>
-      <c r="F221" s="96" t="s">
+      <c r="F222" s="96" t="s">
         <v>550</v>
       </c>
-      <c r="G221" s="99">
+      <c r="G222" s="99">
         <f>2*0.00001</f>
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="H221" s="83">
+      <c r="H222" s="83">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="I221" s="83">
+      <c r="I222" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="J221" s="83">
+      <c r="J222" s="83">
         <v>5.0000000000000002E-5</v>
       </c>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A222" s="2" t="s">
+      <c r="K222" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L222" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B222" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E222" s="96" t="s">
+      <c r="B223" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E223" s="96" t="s">
         <v>551</v>
       </c>
-      <c r="F222" s="96" t="s">
+      <c r="F223" s="96" t="s">
         <v>506</v>
       </c>
-      <c r="G222" s="99">
+      <c r="G223" s="99">
         <f>0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
-      <c r="H222" s="83">
-        <f t="shared" ref="H222:J222" si="4">0.84*(0.36^2)</f>
+      <c r="H223" s="83">
+        <f t="shared" ref="H223:L223" si="4">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
-      <c r="I222" s="83">
+      <c r="I223" s="83">
         <f t="shared" si="4"/>
         <v>0.10886399999999999</v>
       </c>
-      <c r="J222" s="83">
+      <c r="J223" s="83">
         <f t="shared" si="4"/>
         <v>0.10886399999999999</v>
       </c>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A223" s="2" t="s">
+      <c r="K223" s="83">
+        <f t="shared" si="4"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="L223" s="83">
+        <f t="shared" si="4"/>
+        <v>0.10886399999999999</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="B223" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E223" s="96" t="s">
+      <c r="B224" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E224" s="96" t="s">
         <v>552</v>
       </c>
-      <c r="F223" s="96" t="s">
+      <c r="F224" s="96" t="s">
         <v>495</v>
       </c>
-      <c r="G223" s="100">
+      <c r="G224" s="100">
         <v>0.2</v>
       </c>
-      <c r="H223" s="83">
+      <c r="H224" s="83">
         <v>0.2</v>
       </c>
-      <c r="I223" s="83">
+      <c r="I224" s="83">
         <v>0.2</v>
       </c>
-      <c r="J223" s="83">
+      <c r="J224" s="83">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A224" s="2" t="s">
+      <c r="K224" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="L224" s="83">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E224" s="96" t="s">
+      <c r="B225" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E225" s="96" t="s">
         <v>553</v>
-      </c>
-      <c r="F224" s="96" t="s">
-        <v>510</v>
-      </c>
-      <c r="G224" s="100" t="s">
-        <v>476</v>
-      </c>
-      <c r="H224" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="I224" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="J224" s="83" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A225" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E225" s="96" t="s">
-        <v>554</v>
       </c>
       <c r="F225" s="96" t="s">
         <v>510</v>
       </c>
-      <c r="G225" s="100">
+      <c r="G225" s="100" t="s">
+        <v>476</v>
+      </c>
+      <c r="H225" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="I225" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="J225" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="K225" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="L225" s="83" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E226" s="96" t="s">
+        <v>554</v>
+      </c>
+      <c r="F226" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G226" s="100">
         <f>2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="H225" s="83">
-        <f t="shared" ref="H225:J225" si="5">2*0.1</f>
+      <c r="H226" s="83">
+        <f t="shared" ref="H226:L226" si="5">2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="I225" s="83">
+      <c r="I226" s="83">
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
-      <c r="J225" s="83">
+      <c r="J226" s="83">
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A226" s="2" t="s">
+      <c r="K226" s="83">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+      <c r="L226" s="83">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B226" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E226" s="96" t="s">
+      <c r="B227" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E227" s="96" t="s">
         <v>555</v>
-      </c>
-      <c r="F226" s="96" t="s">
-        <v>510</v>
-      </c>
-      <c r="G226" s="100">
-        <v>1E-3</v>
-      </c>
-      <c r="H226" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="I226" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="J226" s="83">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A227" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E227" s="96" t="s">
-        <v>556</v>
       </c>
       <c r="F227" s="96" t="s">
         <v>510</v>
       </c>
-      <c r="G227" s="98">
+      <c r="G227" s="100">
+        <v>1E-3</v>
+      </c>
+      <c r="H227" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="I227" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="J227" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="K227" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="L227" s="83">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E228" s="96" t="s">
+        <v>556</v>
+      </c>
+      <c r="F228" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G228" s="98">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="H227" s="83">
+      <c r="H228" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I227" s="83">
+      <c r="I228" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="J227" s="83">
+      <c r="J228" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A228" s="2" t="s">
+      <c r="K228" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L228" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B228" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="E228" s="30" t="s">
+      <c r="B229" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E229" s="30" t="s">
         <v>558</v>
       </c>
-      <c r="F228" s="30" t="s">
+      <c r="F229" s="30" t="s">
         <v>559</v>
       </c>
-      <c r="G228" s="83">
-        <f t="shared" ref="G228:J228" si="6">0.00002 / 14 / 5</f>
+      <c r="G229" s="83">
+        <f t="shared" ref="G229:J229" si="6">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
-      <c r="H228" s="83">
+      <c r="H229" s="83">
         <f t="shared" si="6"/>
         <v>2.8571428571428575E-7</v>
       </c>
-      <c r="I228" s="83">
-        <v>0</v>
-      </c>
-      <c r="J228" s="83">
+      <c r="I229" s="83">
+        <v>0</v>
+      </c>
+      <c r="J229" s="83">
         <f t="shared" si="6"/>
         <v>2.8571428571428575E-7</v>
       </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A229" s="2" t="s">
+      <c r="K229" s="83">
+        <v>0</v>
+      </c>
+      <c r="L229" s="83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="B229" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="E229" s="30" t="s">
+      <c r="B230" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E230" s="30" t="s">
         <v>558</v>
       </c>
-      <c r="F229" s="30" t="s">
+      <c r="F230" s="30" t="s">
         <v>559</v>
       </c>
-      <c r="G229" s="83">
+      <c r="G230" s="83">
         <f>0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="H229" s="83">
+      <c r="H230" s="83">
         <f>0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="I229" s="83">
-        <v>0</v>
-      </c>
-      <c r="J229" s="83">
+      <c r="I230" s="83">
         <f>0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
+      <c r="J230" s="83">
+        <f>0.00002 / 14 / 5 /10</f>
+        <v>2.8571428571428575E-8</v>
+      </c>
+      <c r="K230" s="83">
+        <f>0.00002 / 14 / 5 /10</f>
+        <v>2.8571428571428575E-8</v>
+      </c>
+      <c r="L230" s="83">
+        <f>0.00002 / 14 / 5 /10</f>
+        <v>2.8571428571428575E-8</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G228:I229">
+  <conditionalFormatting sqref="G229:I230">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G230:L230">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H127:L128">
+    <cfRule type="colorScale" priority="289">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N129:O129 H129:L129">
+    <cfRule type="colorScale" priority="291">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="292">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N130:O130 H130:L130">
+    <cfRule type="colorScale" priority="295">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="296">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N132:O132 H132:L132">
+    <cfRule type="colorScale" priority="299">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="300">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N133:O133 H133:L133">
+    <cfRule type="colorScale" priority="303">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="304">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N138:O138 H138:L138">
+    <cfRule type="colorScale" priority="307">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N144:O144 H144:L144">
+    <cfRule type="colorScale" priority="309">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="310">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="311">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N160:O160 H160:L160">
+    <cfRule type="colorScale" priority="315">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="316">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="317">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H210:L210">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H211:L211">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H212:L212">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H213:L213">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H214:L214">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H215:L215">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H218:L218">
+    <cfRule type="colorScale" priority="327">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="328">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H219:L220">
+    <cfRule type="colorScale" priority="331">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="332">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H221:L221">
+    <cfRule type="colorScale" priority="335">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="336">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H222:L222">
+    <cfRule type="colorScale" priority="339">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="340">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H223:L223">
+    <cfRule type="colorScale" priority="351">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="352">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H224:L228">
+    <cfRule type="colorScale" priority="355">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="356">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J229">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -11663,7 +13604,51 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G229:J229">
+  <conditionalFormatting sqref="N127:O128">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N166:O166 H166:L166">
+    <cfRule type="colorScale" priority="321">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="322">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="323">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K229:L230">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11675,512 +13660,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H127:J128">
-    <cfRule type="colorScale" priority="287">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H129:J129 L129:M129">
-    <cfRule type="colorScale" priority="289">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="290">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H130:J130 L130:M130">
-    <cfRule type="colorScale" priority="293">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="294">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H132:J132 L132:M132">
-    <cfRule type="colorScale" priority="297">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="298">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H133:J133 L133:M133">
-    <cfRule type="colorScale" priority="301">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="302">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H138:J138 L138:M138">
-    <cfRule type="colorScale" priority="305">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H144:J144 L144:M144">
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="309">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H160:J160 L160:M160">
-    <cfRule type="colorScale" priority="313">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="314">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="315">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H210:J210">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H211:J211">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H212:J212">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H213:J213">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H214:J214">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H215:J215">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H218:J218">
-    <cfRule type="colorScale" priority="325">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="326">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H219:J219">
-    <cfRule type="colorScale" priority="329">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="330">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H220:J220">
-    <cfRule type="colorScale" priority="333">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="334">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H221:J221">
-    <cfRule type="colorScale" priority="337">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="338">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H222:J222">
-    <cfRule type="colorScale" priority="349">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="350">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H223:J227">
-    <cfRule type="colorScale" priority="353">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="354">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J228">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L127:M128">
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L166:M166 H166:J166">
-    <cfRule type="colorScale" priority="319">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="320">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="321">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sshfs\torisuten@192.168.12.9\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroparistechfr-my.sharepoint.com/personal/190861_agroparistech_fr/Documents/Thesis/Sujet/Modelling/winscp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3BDE18-D6B2-4B1C-9266-6B7933559CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{DEAA7B16-44C5-44DB-B1E0-9B2F2BF27D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3BF9F43-CB5C-4539-A730-984050407E1A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="575">
   <si>
     <t>input_file</t>
   </si>
@@ -1746,7 +1746,19 @@
     <t>vmax_unloading_AA_phloem</t>
   </si>
   <si>
-    <t>RC_debug</t>
+    <t>previous</t>
+  </si>
+  <si>
+    <t>km_unloading_AA_phloem</t>
+  </si>
+  <si>
+    <t>Affinity parameter for amino acid loading into symplasm from phloem</t>
+  </si>
+  <si>
+    <t>sucrose_input_Swinnen_et_al_1994_interpolated.csv</t>
+  </si>
+  <si>
+    <t>max_loading_rate</t>
   </si>
 </sst>
 </file>
@@ -2404,7 +2416,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2612,6 +2624,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="11" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2668,6 +2681,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2933,7 +2950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O230"/>
+  <dimension ref="A1:N231"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" style="1" customWidth="1"/>
@@ -2941,10 +2958,10 @@
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="22.6640625" customWidth="1"/>
     <col min="7" max="7" width="19.5546875" style="37" customWidth="1"/>
-    <col min="8" max="15" width="39.88671875" style="1" customWidth="1"/>
+    <col min="8" max="14" width="39.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -2978,17 +2995,17 @@
       <c r="K1" s="97" t="s">
         <v>568</v>
       </c>
-      <c r="L1" s="97" t="s">
+      <c r="L1" s="1" t="s">
         <v>570</v>
       </c>
+      <c r="M1" s="97" t="s">
+        <v>522</v>
+      </c>
       <c r="N1" s="97" t="s">
-        <v>522</v>
-      </c>
-      <c r="O1" s="97" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>524</v>
       </c>
@@ -3022,17 +3039,14 @@
       <c r="K2" s="36" t="s">
         <v>476</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="M2" s="36" t="s">
+        <v>528</v>
+      </c>
+      <c r="N2" s="36" t="s">
         <v>476</v>
       </c>
-      <c r="N2" s="36" t="s">
-        <v>528</v>
-      </c>
-      <c r="O2" s="36" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3064,19 +3078,16 @@
         <v>489</v>
       </c>
       <c r="K3" s="36" t="s">
-        <v>489</v>
-      </c>
-      <c r="L3" s="36" t="s">
+        <v>573</v>
+      </c>
+      <c r="M3" s="36" t="s">
         <v>489</v>
       </c>
       <c r="N3" s="36" t="s">
         <v>489</v>
       </c>
-      <c r="O3" s="36" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3110,17 +3121,14 @@
       <c r="K4" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="M4" s="36" t="s">
         <v>482</v>
       </c>
       <c r="N4" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="O4" s="36" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3154,17 +3162,14 @@
       <c r="K5" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="L5" s="36" t="s">
-        <v>482</v>
+      <c r="M5" s="36" t="s">
+        <v>494</v>
       </c>
       <c r="N5" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="O5" s="36" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3196,19 +3201,16 @@
         <v>521</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>521</v>
-      </c>
-      <c r="L6" s="36" t="s">
+        <v>573</v>
+      </c>
+      <c r="M6" s="36" t="s">
         <v>521</v>
       </c>
       <c r="N6" s="36" t="s">
         <v>521</v>
       </c>
-      <c r="O6" s="36" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3242,17 +3244,14 @@
       <c r="K7" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="L7" s="36" t="s">
+      <c r="M7" s="36" t="s">
         <v>494</v>
       </c>
       <c r="N7" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="O7" s="36" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>529</v>
       </c>
@@ -3286,17 +3285,14 @@
       <c r="K8" s="36">
         <v>0</v>
       </c>
-      <c r="L8" s="36">
+      <c r="M8" s="36">
         <v>0</v>
       </c>
       <c r="N8" s="36">
         <v>0</v>
       </c>
-      <c r="O8" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3330,17 +3326,14 @@
       <c r="K9" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="L9" s="77" t="s">
+      <c r="M9" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N9" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O9" s="77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3374,17 +3367,14 @@
       <c r="K10" s="77">
         <v>1</v>
       </c>
-      <c r="L10" s="77">
+      <c r="M10" s="77">
         <v>1</v>
       </c>
       <c r="N10" s="77">
         <v>1</v>
       </c>
-      <c r="O10" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3418,17 +3408,14 @@
       <c r="K11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L11" s="77" t="s">
+      <c r="M11" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O11" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3462,17 +3449,14 @@
       <c r="K12" s="85">
         <v>180</v>
       </c>
-      <c r="L12" s="85">
+      <c r="M12" s="85">
         <v>180</v>
       </c>
       <c r="N12" s="85">
         <v>180</v>
       </c>
-      <c r="O12" s="85">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3506,17 +3490,14 @@
       <c r="K13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="L13" s="78">
+      <c r="M13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
       <c r="N13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="O13" s="78">
-        <v>4.1666666999999998E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3550,17 +3531,14 @@
       <c r="K14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="L14" s="79">
+      <c r="M14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
       <c r="N14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="O14" s="79">
-        <v>4.1666666999999998E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3594,17 +3572,14 @@
       <c r="K15" s="77">
         <v>1</v>
       </c>
-      <c r="L15" s="77">
+      <c r="M15" s="77">
         <v>1</v>
       </c>
       <c r="N15" s="77">
         <v>1</v>
       </c>
-      <c r="O15" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3638,17 +3613,14 @@
       <c r="K16" s="77">
         <v>0</v>
       </c>
-      <c r="L16" s="77">
+      <c r="M16" s="77">
         <v>0</v>
       </c>
       <c r="N16" s="77">
         <v>0</v>
       </c>
-      <c r="O16" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3682,17 +3654,14 @@
       <c r="K17" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L17" s="77" t="s">
+      <c r="M17" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N17" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O17" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3726,17 +3695,14 @@
       <c r="K18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="L18" s="80">
+      <c r="M18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
       <c r="N18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="O18" s="80">
-        <v>5.0000000000000001E-9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -3770,17 +3736,14 @@
       <c r="K19" s="77">
         <v>10</v>
       </c>
-      <c r="L19" s="77">
+      <c r="M19" s="77">
         <v>10</v>
       </c>
       <c r="N19" s="77">
         <v>10</v>
       </c>
-      <c r="O19" s="77">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -3814,17 +3777,14 @@
       <c r="K20" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L20" s="77" t="s">
+      <c r="M20" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N20" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O20" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -3858,17 +3818,14 @@
       <c r="K21" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L21" s="77" t="s">
+      <c r="M21" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N21" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O21" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -3902,17 +3859,14 @@
       <c r="K22" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L22" s="77" t="s">
+      <c r="M22" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N22" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O22" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -3946,17 +3900,14 @@
       <c r="K23" s="77">
         <v>86400</v>
       </c>
-      <c r="L23" s="77">
+      <c r="M23" s="77">
         <v>86400</v>
       </c>
       <c r="N23" s="77">
         <v>86400</v>
       </c>
-      <c r="O23" s="77">
-        <v>86400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -3990,17 +3941,14 @@
       <c r="K24" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="L24" s="77" t="s">
+      <c r="M24" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N24" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O24" s="77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -4034,17 +3982,14 @@
       <c r="K25" s="77">
         <v>3</v>
       </c>
-      <c r="L25" s="77">
+      <c r="M25" s="77">
         <v>3</v>
       </c>
       <c r="N25" s="77">
         <v>3</v>
       </c>
-      <c r="O25" s="77">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -4078,17 +4023,14 @@
       <c r="K26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="L26" s="81" t="s">
+      <c r="M26" s="81" t="s">
         <v>88</v>
       </c>
       <c r="N26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O26" s="81" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -4122,17 +4064,14 @@
       <c r="K27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="L27" s="81" t="s">
+      <c r="M27" s="81" t="s">
         <v>88</v>
       </c>
       <c r="N27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O27" s="81" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -4166,17 +4105,14 @@
       <c r="K28" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L28" s="77" t="s">
+      <c r="M28" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N28" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O28" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4210,17 +4146,14 @@
       <c r="K29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="L29" s="81" t="s">
+      <c r="M29" s="81" t="s">
         <v>88</v>
       </c>
       <c r="N29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O29" s="81" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4254,17 +4187,14 @@
       <c r="K30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="L30" s="81" t="s">
+      <c r="M30" s="81" t="s">
         <v>88</v>
       </c>
       <c r="N30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O30" s="81" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4298,17 +4228,14 @@
       <c r="K31" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L31" s="77" t="s">
+      <c r="M31" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N31" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4342,17 +4269,14 @@
       <c r="K32" s="77">
         <v>0.33</v>
       </c>
-      <c r="L32" s="77">
+      <c r="M32" s="77">
         <v>0.33</v>
       </c>
       <c r="N32" s="77">
         <v>0.33</v>
       </c>
-      <c r="O32" s="77">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4386,17 +4310,14 @@
       <c r="K33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L33" s="77" t="s">
+      <c r="M33" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O33" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4430,17 +4351,14 @@
       <c r="K34" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L34" s="77" t="s">
+      <c r="M34" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N34" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O34" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4474,17 +4392,14 @@
       <c r="K35" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L35" s="77" t="s">
+      <c r="M35" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N35" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O35" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4518,17 +4433,14 @@
       <c r="K36" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="L36" s="77" t="s">
+      <c r="M36" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N36" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O36" s="77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4562,17 +4474,14 @@
       <c r="K37" s="85" t="s">
         <v>433</v>
       </c>
-      <c r="L37" s="85" t="s">
+      <c r="M37" s="85" t="s">
         <v>433</v>
       </c>
       <c r="N37" s="85" t="s">
         <v>433</v>
       </c>
-      <c r="O37" s="85" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -4606,17 +4515,14 @@
       <c r="K38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="L38" s="80">
+      <c r="M38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="N38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="O38" s="80">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -4650,17 +4556,14 @@
       <c r="K39" s="86">
         <v>1E-3</v>
       </c>
-      <c r="L39" s="86">
+      <c r="M39" s="86">
         <v>1E-3</v>
       </c>
       <c r="N39" s="86">
         <v>1E-3</v>
       </c>
-      <c r="O39" s="86">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -4694,17 +4597,14 @@
       <c r="K40" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="L40" s="77" t="s">
+      <c r="M40" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N40" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O40" s="77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -4738,17 +4638,14 @@
       <c r="K41" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="L41" s="77" t="s">
+      <c r="M41" s="77" t="s">
         <v>89</v>
       </c>
       <c r="N41" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="O41" s="77" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -4782,17 +4679,14 @@
       <c r="K42" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="L42" s="77" t="s">
+      <c r="M42" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N42" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O42" s="77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -4826,17 +4720,14 @@
       <c r="K43" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L43" s="77" t="s">
+      <c r="M43" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N43" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O43" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -4870,17 +4761,14 @@
       <c r="K44" s="77">
         <v>120</v>
       </c>
-      <c r="L44" s="77">
+      <c r="M44" s="77">
         <v>120</v>
       </c>
       <c r="N44" s="77">
         <v>120</v>
       </c>
-      <c r="O44" s="77">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -4914,17 +4802,14 @@
       <c r="K45" s="77">
         <v>0</v>
       </c>
-      <c r="L45" s="77">
+      <c r="M45" s="77">
         <v>0</v>
       </c>
       <c r="N45" s="77">
         <v>0</v>
       </c>
-      <c r="O45" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -4958,17 +4843,14 @@
       <c r="K46" s="77">
         <v>0</v>
       </c>
-      <c r="L46" s="77">
+      <c r="M46" s="77">
         <v>0</v>
       </c>
       <c r="N46" s="77">
         <v>0</v>
       </c>
-      <c r="O46" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -5002,17 +4884,14 @@
       <c r="K47" s="77">
         <v>-0.1</v>
       </c>
-      <c r="L47" s="77">
+      <c r="M47" s="77">
         <v>-0.1</v>
       </c>
       <c r="N47" s="77">
         <v>-0.1</v>
       </c>
-      <c r="O47" s="77">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -5046,17 +4925,14 @@
       <c r="K48" s="77">
         <v>-0.2</v>
       </c>
-      <c r="L48" s="77">
+      <c r="M48" s="77">
         <v>-0.2</v>
       </c>
       <c r="N48" s="77">
         <v>-0.2</v>
       </c>
-      <c r="O48" s="77">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -5090,17 +4966,14 @@
       <c r="K49" s="77">
         <v>0.4</v>
       </c>
-      <c r="L49" s="77">
+      <c r="M49" s="77">
         <v>0.4</v>
       </c>
       <c r="N49" s="77">
         <v>0.4</v>
       </c>
-      <c r="O49" s="77">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -5134,17 +5007,14 @@
       <c r="K50" s="77">
         <v>0</v>
       </c>
-      <c r="L50" s="77">
+      <c r="M50" s="77">
         <v>0</v>
       </c>
       <c r="N50" s="77">
         <v>0</v>
       </c>
-      <c r="O50" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -5178,17 +5048,14 @@
       <c r="K51" s="77">
         <v>1200</v>
       </c>
-      <c r="L51" s="77">
+      <c r="M51" s="77">
         <v>1200</v>
       </c>
       <c r="N51" s="77">
         <v>1200</v>
       </c>
-      <c r="O51" s="77">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -5222,17 +5089,14 @@
       <c r="K52" s="77">
         <v>1200</v>
       </c>
-      <c r="L52" s="77">
+      <c r="M52" s="77">
         <v>1200</v>
       </c>
       <c r="N52" s="77">
         <v>1200</v>
       </c>
-      <c r="O52" s="77">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -5266,17 +5130,14 @@
       <c r="K53" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="L53" s="35" t="s">
+      <c r="M53" s="35" t="s">
         <v>460</v>
       </c>
       <c r="N53" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="O53" s="35" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -5310,17 +5171,14 @@
       <c r="K54" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="L54" s="77" t="s">
+      <c r="M54" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N54" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O54" s="77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5354,17 +5212,14 @@
       <c r="K55" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="L55" s="77" t="s">
+      <c r="M55" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N55" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O55" s="77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -5398,17 +5253,14 @@
       <c r="K56" s="77">
         <v>0</v>
       </c>
-      <c r="L56" s="77">
+      <c r="M56" s="77">
         <v>0</v>
       </c>
       <c r="N56" s="77">
         <v>0</v>
       </c>
-      <c r="O56" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -5442,17 +5294,14 @@
       <c r="K57" s="77">
         <v>0.5</v>
       </c>
-      <c r="L57" s="77">
+      <c r="M57" s="77">
         <v>0.5</v>
       </c>
       <c r="N57" s="77">
         <v>0.5</v>
       </c>
-      <c r="O57" s="77">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -5486,17 +5335,14 @@
       <c r="K58" s="77">
         <v>0.05</v>
       </c>
-      <c r="L58" s="77">
+      <c r="M58" s="77">
         <v>0.05</v>
       </c>
       <c r="N58" s="77">
         <v>0.05</v>
       </c>
-      <c r="O58" s="77">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -5530,17 +5376,14 @@
       <c r="K59" s="80">
         <v>1E-3</v>
       </c>
-      <c r="L59" s="80">
+      <c r="M59" s="80">
         <v>1E-3</v>
       </c>
       <c r="N59" s="80">
         <v>1E-3</v>
       </c>
-      <c r="O59" s="80">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -5574,17 +5417,14 @@
       <c r="K60" s="77">
         <v>0</v>
       </c>
-      <c r="L60" s="77">
+      <c r="M60" s="77">
         <v>0</v>
       </c>
       <c r="N60" s="77">
         <v>0</v>
       </c>
-      <c r="O60" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -5618,17 +5458,14 @@
       <c r="K61" s="77">
         <v>1E-4</v>
       </c>
-      <c r="L61" s="77">
+      <c r="M61" s="77">
         <v>1E-4</v>
       </c>
       <c r="N61" s="77">
         <v>1E-4</v>
       </c>
-      <c r="O61" s="77">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -5662,17 +5499,14 @@
       <c r="K62" s="77">
         <v>1E-4</v>
       </c>
-      <c r="L62" s="77">
+      <c r="M62" s="77">
         <v>1E-4</v>
       </c>
       <c r="N62" s="77">
         <v>1E-4</v>
       </c>
-      <c r="O62" s="77">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -5706,17 +5540,14 @@
       <c r="K63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="L63" s="77">
+      <c r="M63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="N63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="O63" s="77">
-        <v>6.9999999999999999E-4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -5750,17 +5581,14 @@
       <c r="K64" s="77">
         <v>1.22E-4</v>
       </c>
-      <c r="L64" s="77">
+      <c r="M64" s="77">
         <v>1.22E-4</v>
       </c>
       <c r="N64" s="77">
         <v>1.22E-4</v>
       </c>
-      <c r="O64" s="77">
-        <v>1.22E-4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -5794,17 +5622,14 @@
       <c r="K65" s="77">
         <v>1</v>
       </c>
-      <c r="L65" s="77">
+      <c r="M65" s="77">
         <v>1</v>
       </c>
       <c r="N65" s="77">
         <v>1</v>
       </c>
-      <c r="O65" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -5838,17 +5663,14 @@
       <c r="K66" s="77">
         <v>0.95</v>
       </c>
-      <c r="L66" s="77">
+      <c r="M66" s="77">
         <v>0.95</v>
       </c>
       <c r="N66" s="77">
         <v>0.95</v>
       </c>
-      <c r="O66" s="77">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -5882,17 +5704,14 @@
       <c r="K67" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L67" s="77" t="s">
+      <c r="M67" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N67" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O67" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -5926,17 +5745,14 @@
       <c r="K68" s="77">
         <v>5</v>
       </c>
-      <c r="L68" s="77">
+      <c r="M68" s="77">
         <v>5</v>
       </c>
       <c r="N68" s="77">
         <v>5</v>
       </c>
-      <c r="O68" s="77">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -5970,17 +5786,14 @@
       <c r="K69" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L69" s="77" t="s">
+      <c r="M69" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N69" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O69" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -6014,17 +5827,14 @@
       <c r="K70" s="77">
         <v>50</v>
       </c>
-      <c r="L70" s="77">
+      <c r="M70" s="77">
         <v>50</v>
       </c>
       <c r="N70" s="77">
         <v>50</v>
       </c>
-      <c r="O70" s="77">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -6058,17 +5868,14 @@
       <c r="K71" s="78">
         <v>1453890.8941884842</v>
       </c>
-      <c r="L71" s="78">
+      <c r="M71" s="78">
         <v>1453890.8941884842</v>
       </c>
       <c r="N71" s="78">
         <v>1453890.8941884842</v>
       </c>
-      <c r="O71" s="78">
-        <v>1453890.8941884842</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -6102,17 +5909,14 @@
       <c r="K72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-      <c r="L72" s="78">
+      <c r="M72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
       <c r="N72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-      <c r="O72" s="78">
-        <v>1.3888888888888888E-5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -6146,17 +5950,14 @@
       <c r="K73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-      <c r="L73" s="79">
+      <c r="M73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
       <c r="N73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-      <c r="O73" s="79">
-        <v>6.5011574074074071E-4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -6190,17 +5991,14 @@
       <c r="K74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-      <c r="L74" s="85">
+      <c r="M74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
       <c r="N74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-      <c r="O74" s="85">
-        <v>4.7400000000000003E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -6234,17 +6032,14 @@
       <c r="K75" s="79">
         <v>282528</v>
       </c>
-      <c r="L75" s="79">
+      <c r="M75" s="79">
         <v>282528</v>
       </c>
       <c r="N75" s="79">
         <v>282528</v>
       </c>
-      <c r="O75" s="79">
-        <v>282528</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -6278,17 +6073,14 @@
       <c r="K76" s="85">
         <v>0.56999999999999995</v>
       </c>
-      <c r="L76" s="85">
+      <c r="M76" s="85">
         <v>0.56999999999999995</v>
       </c>
       <c r="N76" s="85">
         <v>0.56999999999999995</v>
       </c>
-      <c r="O76" s="85">
-        <v>0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -6322,17 +6114,14 @@
       <c r="K77" s="87">
         <v>0.16</v>
       </c>
-      <c r="L77" s="87">
+      <c r="M77" s="87">
         <v>0.16</v>
       </c>
       <c r="N77" s="87">
         <v>0.16</v>
       </c>
-      <c r="O77" s="87">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -6366,17 +6155,14 @@
       <c r="K78" s="77">
         <v>0</v>
       </c>
-      <c r="L78" s="77">
+      <c r="M78" s="77">
         <v>0</v>
       </c>
       <c r="N78" s="77">
         <v>0</v>
       </c>
-      <c r="O78" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -6410,17 +6196,14 @@
       <c r="K79" s="78">
         <v>745476480000</v>
       </c>
-      <c r="L79" s="78">
+      <c r="M79" s="78">
         <v>745476480000</v>
       </c>
       <c r="N79" s="78">
         <v>745476480000</v>
       </c>
-      <c r="O79" s="78">
-        <v>745476480000</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -6454,17 +6237,14 @@
       <c r="K80" s="77">
         <v>100</v>
       </c>
-      <c r="L80" s="77">
+      <c r="M80" s="77">
         <v>100</v>
       </c>
       <c r="N80" s="77">
         <v>100</v>
       </c>
-      <c r="O80" s="77">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -6498,17 +6278,14 @@
       <c r="K81" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="L81" s="77" t="s">
+      <c r="M81" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N81" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O81" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -6542,17 +6319,14 @@
       <c r="K82" s="85">
         <v>21600</v>
       </c>
-      <c r="L82" s="85">
+      <c r="M82" s="85">
         <v>21600</v>
       </c>
       <c r="N82" s="85">
         <v>21600</v>
       </c>
-      <c r="O82" s="85">
-        <v>21600</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -6586,17 +6360,14 @@
       <c r="K83" s="77">
         <v>0.5</v>
       </c>
-      <c r="L83" s="77">
+      <c r="M83" s="77">
         <v>0.5</v>
       </c>
       <c r="N83" s="77">
         <v>0.5</v>
       </c>
-      <c r="O83" s="77">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -6630,17 +6401,14 @@
       <c r="K84" s="85">
         <v>60479.999999999993</v>
       </c>
-      <c r="L84" s="85">
+      <c r="M84" s="85">
         <v>60479.999999999993</v>
       </c>
       <c r="N84" s="85">
         <v>60479.999999999993</v>
       </c>
-      <c r="O84" s="85">
-        <v>60479.999999999993</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -6674,17 +6442,14 @@
       <c r="K85" s="77">
         <v>0.85</v>
       </c>
-      <c r="L85" s="77">
+      <c r="M85" s="77">
         <v>0.85</v>
       </c>
       <c r="N85" s="77">
         <v>0.85</v>
       </c>
-      <c r="O85" s="77">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -6718,17 +6483,14 @@
       <c r="K86" s="77">
         <v>518400</v>
       </c>
-      <c r="L86" s="77">
+      <c r="M86" s="77">
         <v>518400</v>
       </c>
       <c r="N86" s="77">
         <v>518400</v>
       </c>
-      <c r="O86" s="77">
-        <v>518400</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -6762,17 +6524,14 @@
       <c r="K87" s="77">
         <v>5184000</v>
       </c>
-      <c r="L87" s="77">
+      <c r="M87" s="77">
         <v>5184000</v>
       </c>
       <c r="N87" s="77">
         <v>5184000</v>
       </c>
-      <c r="O87" s="77">
-        <v>5184000</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -6806,17 +6565,14 @@
       <c r="K88" s="86">
         <v>50000</v>
       </c>
-      <c r="L88" s="86">
+      <c r="M88" s="86">
         <v>50000</v>
       </c>
       <c r="N88" s="86">
         <v>50000</v>
       </c>
-      <c r="O88" s="86">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -6850,17 +6606,14 @@
       <c r="K89" s="77">
         <v>140000</v>
       </c>
-      <c r="L89" s="77">
+      <c r="M89" s="77">
         <v>140000</v>
       </c>
       <c r="N89" s="77">
         <v>140000</v>
       </c>
-      <c r="O89" s="77">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -6894,17 +6647,14 @@
       <c r="K90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-      <c r="L90" s="78">
+      <c r="M90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
       <c r="N90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-      <c r="O90" s="78">
-        <v>3.6636136999999999E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -6938,17 +6688,14 @@
       <c r="K91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="L91" s="77">
+      <c r="M91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="N91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="O91" s="77">
-        <v>4.4999999999999997E-3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -6982,17 +6729,14 @@
       <c r="K92" s="77">
         <v>0.05</v>
       </c>
-      <c r="L92" s="77">
+      <c r="M92" s="77">
         <v>0.05</v>
       </c>
       <c r="N92" s="77">
         <v>0.05</v>
       </c>
-      <c r="O92" s="77">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -7026,17 +6770,14 @@
       <c r="K93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="L93" s="77">
+      <c r="M93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
       <c r="N93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="O93" s="77">
-        <v>6.0000000000000002E-6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -7070,17 +6811,14 @@
       <c r="K94" s="77">
         <v>1E-3</v>
       </c>
-      <c r="L94" s="77">
-        <v>1E-3</v>
+      <c r="M94" s="77">
+        <v>0</v>
       </c>
       <c r="N94" s="77">
         <v>0</v>
       </c>
-      <c r="O94" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -7114,17 +6852,14 @@
       <c r="K95" s="77">
         <v>374999999.99999994</v>
       </c>
-      <c r="L95" s="77">
+      <c r="M95" s="77">
         <v>374999999.99999994</v>
       </c>
       <c r="N95" s="77">
         <v>374999999.99999994</v>
       </c>
-      <c r="O95" s="77">
-        <v>374999999.99999994</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -7158,17 +6893,14 @@
       <c r="K96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="L96" s="78">
+      <c r="M96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
       <c r="N96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="O96" s="78">
-        <v>3.7037037037037038E-3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -7202,17 +6934,14 @@
       <c r="K97" s="77">
         <v>165600</v>
       </c>
-      <c r="L97" s="77">
+      <c r="M97" s="77">
         <v>165600</v>
       </c>
       <c r="N97" s="77">
         <v>165600</v>
       </c>
-      <c r="O97" s="77">
-        <v>165600</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -7246,17 +6975,14 @@
       <c r="K98" s="77">
         <v>20</v>
       </c>
-      <c r="L98" s="77">
+      <c r="M98" s="77">
         <v>20</v>
       </c>
       <c r="N98" s="77">
         <v>20</v>
       </c>
-      <c r="O98" s="77">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -7290,17 +7016,14 @@
       <c r="K99" s="77">
         <v>1</v>
       </c>
-      <c r="L99" s="77">
+      <c r="M99" s="77">
         <v>1</v>
       </c>
       <c r="N99" s="77">
         <v>1</v>
       </c>
-      <c r="O99" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -7334,17 +7057,14 @@
       <c r="K100" s="77">
         <v>21</v>
       </c>
-      <c r="L100" s="77">
+      <c r="M100" s="77">
         <v>21</v>
       </c>
       <c r="N100" s="77">
         <v>21</v>
       </c>
-      <c r="O100" s="77">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -7378,17 +7098,14 @@
       <c r="K101" s="77">
         <v>0.64</v>
       </c>
-      <c r="L101" s="77">
+      <c r="M101" s="77">
         <v>0.64</v>
       </c>
       <c r="N101" s="77">
         <v>0.64</v>
       </c>
-      <c r="O101" s="77">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -7422,17 +7139,14 @@
       <c r="K102" s="77">
         <v>8</v>
       </c>
-      <c r="L102" s="77">
+      <c r="M102" s="77">
         <v>8</v>
       </c>
       <c r="N102" s="77">
         <v>8</v>
       </c>
-      <c r="O102" s="77">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -7466,17 +7180,14 @@
       <c r="K103" s="77">
         <v>10</v>
       </c>
-      <c r="L103" s="77">
+      <c r="M103" s="77">
         <v>10</v>
       </c>
       <c r="N103" s="77">
         <v>10</v>
       </c>
-      <c r="O103" s="77">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -7510,17 +7221,14 @@
       <c r="K104" s="77">
         <v>8</v>
       </c>
-      <c r="L104" s="77">
+      <c r="M104" s="77">
         <v>8</v>
       </c>
       <c r="N104" s="77">
         <v>8</v>
       </c>
-      <c r="O104" s="77">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>500</v>
       </c>
@@ -7554,17 +7262,14 @@
       <c r="K105" s="77">
         <v>1</v>
       </c>
-      <c r="L105" s="77">
+      <c r="M105" s="77">
         <v>1</v>
       </c>
       <c r="N105" s="77">
         <v>1</v>
       </c>
-      <c r="O105" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -7598,17 +7303,14 @@
       <c r="K106" s="77">
         <v>0.5</v>
       </c>
-      <c r="L106" s="77">
+      <c r="M106" s="77">
         <v>0.5</v>
       </c>
       <c r="N106" s="77">
         <v>0.5</v>
       </c>
-      <c r="O106" s="77">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>501</v>
       </c>
@@ -7628,37 +7330,33 @@
         <v>506</v>
       </c>
       <c r="G107" s="58">
-        <f>G105</f>
+        <f t="shared" ref="G107:K107" si="0">G105</f>
         <v>1</v>
       </c>
       <c r="H107" s="58">
-        <f>H105</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I107" s="58">
-        <f>I105</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J107" s="58">
-        <f>J105</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K107" s="58">
-        <f>K105</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L107" s="58">
-        <f>L105</f>
+      <c r="M107" s="58">
         <v>1</v>
       </c>
       <c r="N107" s="58">
         <v>1</v>
       </c>
-      <c r="O107" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
         <v>502</v>
       </c>
@@ -7697,18 +7395,14 @@
         <f>150*K105</f>
         <v>150</v>
       </c>
-      <c r="L108" s="58">
-        <f>150*L105</f>
+      <c r="M108" s="58">
         <v>150</v>
       </c>
       <c r="N108" s="58">
         <v>150</v>
       </c>
-      <c r="O108" s="58">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>503</v>
       </c>
@@ -7728,37 +7422,33 @@
         <v>506</v>
       </c>
       <c r="G109" s="58">
-        <f>G100</f>
+        <f t="shared" ref="G109:K109" si="1">G100</f>
         <v>21</v>
       </c>
       <c r="H109" s="58">
-        <f>H100</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="I109" s="58">
-        <f>I100</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="J109" s="58">
-        <f>J100</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="K109" s="58">
-        <f>K100</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="L109" s="58">
-        <f>L100</f>
+      <c r="M109" s="58">
         <v>21</v>
       </c>
       <c r="N109" s="58">
         <v>21</v>
       </c>
-      <c r="O109" s="58">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
         <v>504</v>
       </c>
@@ -7797,18 +7487,14 @@
         <f>70*K100</f>
         <v>1470</v>
       </c>
-      <c r="L110" s="58">
-        <f>70*L100</f>
+      <c r="M110" s="58">
         <v>1470</v>
       </c>
       <c r="N110" s="58">
         <v>1470</v>
       </c>
-      <c r="O110" s="58">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -7842,17 +7528,14 @@
       <c r="K111" s="77">
         <v>0</v>
       </c>
-      <c r="L111" s="77">
+      <c r="M111" s="77">
         <v>0</v>
       </c>
       <c r="N111" s="77">
         <v>0</v>
       </c>
-      <c r="O111" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -7886,17 +7569,14 @@
       <c r="K112" s="82">
         <v>1589759.9999999998</v>
       </c>
-      <c r="L112" s="82">
+      <c r="M112" s="82">
         <v>1589759.9999999998</v>
       </c>
       <c r="N112" s="82">
         <v>1589759.9999999998</v>
       </c>
-      <c r="O112" s="82">
-        <v>1589759.9999999998</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -7930,17 +7610,14 @@
       <c r="K113" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="L113" s="82">
+      <c r="M113" s="82">
         <v>6171428.5714285718</v>
       </c>
       <c r="N113" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="O113" s="82">
-        <v>6171428.5714285718</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -7974,17 +7651,14 @@
       <c r="K114" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="L114" s="82">
+      <c r="M114" s="82">
         <v>6171428.5714285718</v>
       </c>
       <c r="N114" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="O114" s="82">
-        <v>6171428.5714285718</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -8018,17 +7692,14 @@
       <c r="K115" s="82">
         <v>100</v>
       </c>
-      <c r="L115" s="82">
+      <c r="M115" s="82">
         <v>100</v>
       </c>
       <c r="N115" s="82">
         <v>100</v>
       </c>
-      <c r="O115" s="82">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -8067,18 +7738,14 @@
         <f>0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
-      <c r="L116" s="67">
-        <f>0.1 * 3.25 * (60*60*24)</f>
+      <c r="M116" s="67">
         <v>28080</v>
       </c>
       <c r="N116" s="67">
         <v>28080</v>
       </c>
-      <c r="O116" s="67">
-        <v>28080</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -8117,18 +7784,14 @@
         <f>1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
-      <c r="L117" s="67">
-        <f>1.11 / 10</f>
+      <c r="M117" s="67">
         <v>0.11100000000000002</v>
       </c>
       <c r="N117" s="67">
         <v>0.11100000000000002</v>
       </c>
-      <c r="O117" s="67">
-        <v>0.11100000000000002</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
         <v>497</v>
       </c>
@@ -8162,17 +7825,14 @@
       <c r="K118" s="82">
         <v>100</v>
       </c>
-      <c r="L118" s="82">
+      <c r="M118" s="82">
         <v>100</v>
       </c>
       <c r="N118" s="82">
         <v>100</v>
       </c>
-      <c r="O118" s="82">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>498</v>
       </c>
@@ -8192,37 +7852,33 @@
         <v>431</v>
       </c>
       <c r="G119" s="67">
-        <f>5.32 * (60*60*24)</f>
+        <f t="shared" ref="G119:K119" si="2">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H119" s="67">
-        <f>5.32 * (60*60*24)</f>
+        <f t="shared" si="2"/>
         <v>459648</v>
       </c>
       <c r="I119" s="67">
-        <f>5.32 * (60*60*24)</f>
+        <f t="shared" si="2"/>
         <v>459648</v>
       </c>
       <c r="J119" s="67">
-        <f>5.32 * (60*60*24)</f>
+        <f t="shared" si="2"/>
         <v>459648</v>
       </c>
       <c r="K119" s="67">
-        <f>5.32 * (60*60*24)</f>
+        <f t="shared" si="2"/>
         <v>459648</v>
       </c>
-      <c r="L119" s="67">
-        <f>5.32 * (60*60*24)</f>
+      <c r="M119" s="67">
         <v>459648</v>
       </c>
       <c r="N119" s="67">
         <v>459648</v>
       </c>
-      <c r="O119" s="67">
-        <v>459648</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
         <v>499</v>
       </c>
@@ -8261,18 +7917,14 @@
         <f>1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
-      <c r="L120" s="67">
-        <f>1.11/8</f>
+      <c r="M120" s="67">
         <v>0.13875000000000001</v>
       </c>
       <c r="N120" s="67">
         <v>0.13875000000000001</v>
       </c>
-      <c r="O120" s="67">
-        <v>0.13875000000000001</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -8306,17 +7958,14 @@
       <c r="K121" s="82">
         <v>21600</v>
       </c>
-      <c r="L121" s="82">
+      <c r="M121" s="82">
         <v>21600</v>
       </c>
       <c r="N121" s="82">
         <v>21600</v>
       </c>
-      <c r="O121" s="82">
-        <v>21600</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -8350,17 +7999,14 @@
       <c r="K122" s="88">
         <v>43200</v>
       </c>
-      <c r="L122" s="88">
+      <c r="M122" s="88">
         <v>43200</v>
       </c>
       <c r="N122" s="88">
         <v>43200</v>
       </c>
-      <c r="O122" s="88">
-        <v>43200</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -8394,17 +8040,14 @@
       <c r="K123" s="77">
         <v>0.8</v>
       </c>
-      <c r="L123" s="77">
+      <c r="M123" s="77">
         <v>0.8</v>
       </c>
       <c r="N123" s="77">
         <v>0.8</v>
       </c>
-      <c r="O123" s="77">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -8439,17 +8082,14 @@
       <c r="K124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="L124" s="78">
+      <c r="M124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
       <c r="N124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="O124" s="78">
-        <v>2.0833333333333335E-4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -8483,17 +8123,14 @@
       <c r="K125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-      <c r="L125" s="77">
+      <c r="M125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
       <c r="N125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-      <c r="O125" s="77">
-        <v>5.7899999999999998E-7</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -8527,17 +8164,14 @@
       <c r="K126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="L126" s="78">
+      <c r="M126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
       <c r="N126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="O126" s="78">
-        <v>2.0833333333333335E-4</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -8571,17 +8205,14 @@
       <c r="K127" s="78">
         <v>0</v>
       </c>
-      <c r="L127" s="78">
+      <c r="M127" s="78">
         <v>0</v>
       </c>
       <c r="N127" s="78">
         <v>0</v>
       </c>
-      <c r="O127" s="78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -8615,17 +8246,14 @@
       <c r="K128" s="78">
         <v>0</v>
       </c>
-      <c r="L128" s="78">
+      <c r="M128" s="78">
         <v>0</v>
       </c>
       <c r="N128" s="78">
         <v>0</v>
       </c>
-      <c r="O128" s="78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -8650,31 +8278,31 @@
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="I129" s="83">
-        <f t="shared" ref="I129:O129" si="0">0.0000002*3</f>
+        <f t="shared" ref="I129:N129" si="3">0.0000002*3</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J129" s="83">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="K129" s="83">
-        <f t="shared" si="0"/>
+        <f>0.0000002 * 2 / 10</f>
+        <v>4.0000000000000001E-8</v>
+      </c>
+      <c r="L129" s="83">
+        <f t="shared" si="3"/>
         <v>5.9999999999999997E-7</v>
       </c>
-      <c r="L129" s="83">
-        <f t="shared" si="0"/>
+      <c r="M129" s="83">
+        <f t="shared" si="3"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="N129" s="83">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5.9999999999999997E-7</v>
       </c>
-      <c r="O129" s="83">
-        <f t="shared" si="0"/>
-        <v>5.9999999999999997E-7</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -8695,35 +8323,31 @@
       </c>
       <c r="G130" s="71"/>
       <c r="H130" s="83">
-        <f t="shared" ref="H130:O130" si="1">1000 * 0.000001 / 12</f>
+        <f t="shared" ref="H130:N130" si="4">1000 * 0.000001 / 12</f>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="I130" s="83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="J130" s="83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="K130" s="83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="L130" s="83">
-        <f t="shared" si="1"/>
+      <c r="M130" s="83">
+        <f t="shared" si="4"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N130" s="83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O130" s="83">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333331E-5</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -8757,17 +8381,14 @@
       <c r="K131" s="89" t="s">
         <v>533</v>
       </c>
-      <c r="L131" s="89" t="s">
+      <c r="M131" s="89" t="s">
         <v>533</v>
       </c>
       <c r="N131" s="89" t="s">
         <v>533</v>
       </c>
-      <c r="O131" s="89" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -8799,19 +8420,20 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="K132" s="83">
+        <f>0.0005</f>
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="L132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
+      <c r="M132" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
       <c r="N132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="O132" s="83">
-        <v>5.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -8845,17 +8467,14 @@
       <c r="K133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="L133" s="83">
+      <c r="M133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
       <c r="N133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="O133" s="83">
-        <v>4.9999999999999999E-13</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -8889,17 +8508,14 @@
       <c r="K134" s="77">
         <v>10</v>
       </c>
-      <c r="L134" s="77">
+      <c r="M134" s="77">
         <v>10</v>
       </c>
       <c r="N134" s="77">
         <v>10</v>
       </c>
-      <c r="O134" s="77">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -8933,17 +8549,14 @@
       <c r="K135" s="77">
         <v>-0.04</v>
       </c>
-      <c r="L135" s="77">
+      <c r="M135" s="77">
         <v>-0.04</v>
       </c>
       <c r="N135" s="77">
         <v>-0.04</v>
       </c>
-      <c r="O135" s="77">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -8977,17 +8590,14 @@
       <c r="K136" s="77">
         <v>2.9</v>
       </c>
-      <c r="L136" s="77">
+      <c r="M136" s="77">
         <v>2.9</v>
       </c>
       <c r="N136" s="77">
         <v>2.9</v>
       </c>
-      <c r="O136" s="77">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -9021,19 +8631,16 @@
       <c r="K137" s="77">
         <v>1</v>
       </c>
-      <c r="L137" s="77">
+      <c r="M137" s="77">
         <v>1</v>
       </c>
       <c r="N137" s="77">
         <v>1</v>
       </c>
-      <c r="O137" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="21" t="s">
-        <v>68</v>
+        <v>574</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>471</v>
@@ -9063,19 +8670,20 @@
         <v>1.9999999999999999E-7</v>
       </c>
       <c r="K138" s="80">
-        <v>1.9999999999999999E-7</v>
+        <f>0.0000002 * 2 / 10</f>
+        <v>4.0000000000000001E-8</v>
       </c>
       <c r="L138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
+      <c r="M138" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
       <c r="N138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="O138" s="80">
-        <v>1.9999999999999999E-7</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -9109,17 +8717,14 @@
       <c r="K139" s="77">
         <v>10</v>
       </c>
-      <c r="L139" s="77">
+      <c r="M139" s="77">
         <v>10</v>
       </c>
       <c r="N139" s="77">
         <v>10</v>
       </c>
-      <c r="O139" s="77">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -9153,17 +8758,14 @@
       <c r="K140" s="77">
         <v>-0.04</v>
       </c>
-      <c r="L140" s="77">
+      <c r="M140" s="77">
         <v>-0.04</v>
       </c>
       <c r="N140" s="77">
         <v>-0.04</v>
       </c>
-      <c r="O140" s="77">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -9197,17 +8799,14 @@
       <c r="K141" s="77">
         <v>2.9</v>
       </c>
-      <c r="L141" s="77">
+      <c r="M141" s="77">
         <v>2.9</v>
       </c>
       <c r="N141" s="77">
         <v>2.9</v>
       </c>
-      <c r="O141" s="77">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -9241,17 +8840,14 @@
       <c r="K142" s="77">
         <v>1</v>
       </c>
-      <c r="L142" s="77">
+      <c r="M142" s="77">
         <v>1</v>
       </c>
       <c r="N142" s="77">
         <v>1</v>
       </c>
-      <c r="O142" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -9285,17 +8881,14 @@
       <c r="K143" s="77">
         <v>0</v>
       </c>
-      <c r="L143" s="77">
+      <c r="M143" s="77">
         <v>0</v>
       </c>
       <c r="N143" s="77">
         <v>0</v>
       </c>
-      <c r="O143" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -9329,17 +8922,14 @@
       <c r="K144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="L144" s="80">
+      <c r="M144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="N144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="O144" s="80">
-        <v>5.0000000000000004E-6</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -9373,17 +8963,14 @@
       <c r="K145" s="77">
         <v>0</v>
       </c>
-      <c r="L145" s="77">
+      <c r="M145" s="77">
         <v>0</v>
       </c>
       <c r="N145" s="77">
         <v>0</v>
       </c>
-      <c r="O145" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -9417,17 +9004,14 @@
       <c r="K146" s="77">
         <v>2E-3</v>
       </c>
-      <c r="L146" s="77">
+      <c r="M146" s="77">
         <v>2E-3</v>
       </c>
       <c r="N146" s="77">
         <v>2E-3</v>
       </c>
-      <c r="O146" s="77">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -9461,17 +9045,14 @@
       <c r="K147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-      <c r="L147" s="80">
+      <c r="M147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
       <c r="N147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-      <c r="O147" s="80">
-        <v>3.9999999999999998E-6</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -9505,17 +9086,14 @@
       <c r="K148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-      <c r="L148" s="80">
+      <c r="M148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
       <c r="N148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-      <c r="O148" s="80">
-        <v>3.7699999999999999E-10</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -9549,17 +9127,14 @@
       <c r="K149" s="77">
         <v>20</v>
       </c>
-      <c r="L149" s="77">
+      <c r="M149" s="77">
         <v>20</v>
       </c>
       <c r="N149" s="77">
         <v>20</v>
       </c>
-      <c r="O149" s="77">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -9593,17 +9168,14 @@
       <c r="K150" s="77">
         <v>-0.06</v>
       </c>
-      <c r="L150" s="77">
+      <c r="M150" s="77">
         <v>-0.06</v>
       </c>
       <c r="N150" s="77">
         <v>-0.06</v>
       </c>
-      <c r="O150" s="77">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -9637,17 +9209,14 @@
       <c r="K151" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="L151" s="77">
+      <c r="M151" s="77">
         <v>0.89100000000000001</v>
       </c>
       <c r="N151" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="O151" s="77">
-        <v>0.89100000000000001</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -9681,17 +9250,14 @@
       <c r="K152" s="77">
         <v>1</v>
       </c>
-      <c r="L152" s="77">
+      <c r="M152" s="77">
         <v>1</v>
       </c>
       <c r="N152" s="77">
         <v>1</v>
       </c>
-      <c r="O152" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -9725,17 +9291,14 @@
       <c r="K153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="L153" s="80">
+      <c r="M153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="N153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="O153" s="80">
-        <v>4.0000000000000003E-5</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -9769,17 +9332,14 @@
       <c r="K154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-      <c r="L154" s="80">
+      <c r="M154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
       <c r="N154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-      <c r="O154" s="80">
-        <v>5.8333333333333335E-9</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -9813,17 +9373,14 @@
       <c r="K155" s="77">
         <v>20</v>
       </c>
-      <c r="L155" s="77">
+      <c r="M155" s="77">
         <v>20</v>
       </c>
       <c r="N155" s="77">
         <v>20</v>
       </c>
-      <c r="O155" s="77">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -9857,17 +9414,14 @@
       <c r="K156" s="77">
         <v>-0.06</v>
       </c>
-      <c r="L156" s="77">
+      <c r="M156" s="77">
         <v>-0.06</v>
       </c>
       <c r="N156" s="77">
         <v>-0.06</v>
       </c>
-      <c r="O156" s="77">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -9901,17 +9455,14 @@
       <c r="K157" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="L157" s="77">
+      <c r="M157" s="77">
         <v>0.89100000000000001</v>
       </c>
       <c r="N157" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="O157" s="77">
-        <v>0.89100000000000001</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -9945,17 +9496,14 @@
       <c r="K158" s="77">
         <v>1</v>
       </c>
-      <c r="L158" s="77">
+      <c r="M158" s="77">
         <v>1</v>
       </c>
       <c r="N158" s="77">
         <v>1</v>
       </c>
-      <c r="O158" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -9989,17 +9537,14 @@
       <c r="K159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="L159" s="80">
+      <c r="M159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="N159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="O159" s="80">
-        <v>4.0000000000000003E-5</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -10033,17 +9578,14 @@
       <c r="K160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="L160" s="83">
+      <c r="M160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="N160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="O160" s="83">
-        <v>4.0000000000000001E-8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -10077,17 +9619,14 @@
       <c r="K161" s="77">
         <v>20</v>
       </c>
-      <c r="L161" s="77">
+      <c r="M161" s="77">
         <v>20</v>
       </c>
       <c r="N161" s="77">
         <v>20</v>
       </c>
-      <c r="O161" s="77">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -10121,17 +9660,14 @@
       <c r="K162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-      <c r="L162" s="77">
+      <c r="M162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
       <c r="N162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-      <c r="O162" s="77">
-        <v>-4.4200000000000003E-2</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -10165,17 +9701,14 @@
       <c r="K163" s="77">
         <v>1.55</v>
       </c>
-      <c r="L163" s="77">
+      <c r="M163" s="77">
         <v>1.55</v>
       </c>
       <c r="N163" s="77">
         <v>1.55</v>
       </c>
-      <c r="O163" s="77">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -10209,17 +9742,14 @@
       <c r="K164" s="77">
         <v>1</v>
       </c>
-      <c r="L164" s="77">
+      <c r="M164" s="77">
         <v>1</v>
       </c>
       <c r="N164" s="77">
         <v>1</v>
       </c>
-      <c r="O164" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -10253,17 +9783,14 @@
       <c r="K165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="L165" s="77">
+      <c r="M165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
       <c r="N165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="O165" s="77">
-        <v>2.7799999999999998E-4</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -10297,17 +9824,14 @@
       <c r="K166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="L166" s="84">
+      <c r="M166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="N166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="O166" s="84">
-        <v>2.4999999999999998E-12</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -10341,17 +9865,14 @@
       <c r="K167" s="77">
         <v>20</v>
       </c>
-      <c r="L167" s="77">
+      <c r="M167" s="77">
         <v>20</v>
       </c>
       <c r="N167" s="77">
         <v>20</v>
       </c>
-      <c r="O167" s="77">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -10385,17 +9906,14 @@
       <c r="K168" s="77">
         <v>0</v>
       </c>
-      <c r="L168" s="77">
+      <c r="M168" s="77">
         <v>0</v>
       </c>
       <c r="N168" s="77">
         <v>0</v>
       </c>
-      <c r="O168" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -10429,17 +9947,14 @@
       <c r="K169" s="77">
         <v>1</v>
       </c>
-      <c r="L169" s="77">
+      <c r="M169" s="77">
         <v>1</v>
       </c>
       <c r="N169" s="77">
         <v>1</v>
       </c>
-      <c r="O169" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -10473,17 +9988,14 @@
       <c r="K170" s="77">
         <v>0</v>
       </c>
-      <c r="L170" s="77">
+      <c r="M170" s="77">
         <v>0</v>
       </c>
       <c r="N170" s="77">
         <v>0</v>
       </c>
-      <c r="O170" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -10517,17 +10029,14 @@
       <c r="K171" s="77">
         <v>0.4</v>
       </c>
-      <c r="L171" s="77">
+      <c r="M171" s="77">
         <v>0.4</v>
       </c>
       <c r="N171" s="77">
         <v>0.4</v>
       </c>
-      <c r="O171" s="77">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -10561,17 +10070,14 @@
       <c r="K172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-      <c r="L172" s="86">
+      <c r="M172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
       <c r="N172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-      <c r="O172" s="86">
-        <v>2.0000000000000001E-9</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -10605,17 +10111,14 @@
       <c r="K173" s="77">
         <v>25</v>
       </c>
-      <c r="L173" s="77">
+      <c r="M173" s="77">
         <v>25</v>
       </c>
       <c r="N173" s="77">
         <v>25</v>
       </c>
-      <c r="O173" s="77">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -10649,17 +10152,14 @@
       <c r="K174" s="77">
         <v>0</v>
       </c>
-      <c r="L174" s="77">
+      <c r="M174" s="77">
         <v>0</v>
       </c>
       <c r="N174" s="77">
         <v>0</v>
       </c>
-      <c r="O174" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -10693,17 +10193,14 @@
       <c r="K175" s="77">
         <v>3.98</v>
       </c>
-      <c r="L175" s="77">
+      <c r="M175" s="77">
         <v>3.98</v>
       </c>
       <c r="N175" s="77">
         <v>3.98</v>
       </c>
-      <c r="O175" s="77">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -10737,17 +10234,14 @@
       <c r="K176" s="77">
         <v>1</v>
       </c>
-      <c r="L176" s="77">
+      <c r="M176" s="77">
         <v>1</v>
       </c>
       <c r="N176" s="77">
         <v>1</v>
       </c>
-      <c r="O176" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -10781,17 +10275,14 @@
       <c r="K177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-      <c r="L177" s="78">
+      <c r="M177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
       <c r="N177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-      <c r="O177" s="78">
-        <v>1.6666666666666666E-4</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -10825,17 +10316,14 @@
       <c r="K178" s="80">
         <v>1E-8</v>
       </c>
-      <c r="L178" s="80">
+      <c r="M178" s="80">
         <v>1E-8</v>
       </c>
       <c r="N178" s="80">
         <v>1E-8</v>
       </c>
-      <c r="O178" s="80">
-        <v>1E-8</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -10869,17 +10357,14 @@
       <c r="K179" s="77">
         <v>20</v>
       </c>
-      <c r="L179" s="77">
+      <c r="M179" s="77">
         <v>20</v>
       </c>
       <c r="N179" s="77">
         <v>20</v>
       </c>
-      <c r="O179" s="77">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -10913,17 +10398,14 @@
       <c r="K180" s="77">
         <v>0</v>
       </c>
-      <c r="L180" s="77">
+      <c r="M180" s="77">
         <v>0</v>
       </c>
       <c r="N180" s="77">
         <v>0</v>
       </c>
-      <c r="O180" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -10957,17 +10439,14 @@
       <c r="K181" s="77">
         <v>2</v>
       </c>
-      <c r="L181" s="77">
+      <c r="M181" s="77">
         <v>2</v>
       </c>
       <c r="N181" s="77">
         <v>2</v>
       </c>
-      <c r="O181" s="77">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -11001,17 +10480,14 @@
       <c r="K182" s="77">
         <v>1</v>
       </c>
-      <c r="L182" s="77">
+      <c r="M182" s="77">
         <v>1</v>
       </c>
       <c r="N182" s="77">
         <v>1</v>
       </c>
-      <c r="O182" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -11045,17 +10521,14 @@
       <c r="K183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="L183" s="78">
+      <c r="M183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O183" s="78">
-        <v>8.3333333333333331E-5</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -11089,17 +10562,14 @@
       <c r="K184" s="77">
         <v>1</v>
       </c>
-      <c r="L184" s="77">
+      <c r="M184" s="77">
         <v>1</v>
       </c>
       <c r="N184" s="77">
         <v>1</v>
       </c>
-      <c r="O184" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -11133,17 +10603,14 @@
       <c r="K185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-      <c r="L185" s="77">
+      <c r="M185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
       <c r="N185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-      <c r="O185" s="77">
-        <v>2.3533050791148899E-8</v>
-      </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -11177,17 +10644,14 @@
       <c r="K186" s="77">
         <v>20</v>
       </c>
-      <c r="L186" s="77">
+      <c r="M186" s="77">
         <v>20</v>
       </c>
       <c r="N186" s="77">
         <v>20</v>
       </c>
-      <c r="O186" s="77">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -11221,17 +10685,14 @@
       <c r="K187" s="77">
         <v>-0.187</v>
       </c>
-      <c r="L187" s="77">
+      <c r="M187" s="77">
         <v>-0.187</v>
       </c>
       <c r="N187" s="77">
         <v>-0.187</v>
       </c>
-      <c r="O187" s="77">
-        <v>-0.187</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -11265,17 +10726,14 @@
       <c r="K188" s="77">
         <v>2.48</v>
       </c>
-      <c r="L188" s="77">
+      <c r="M188" s="77">
         <v>2.48</v>
       </c>
       <c r="N188" s="77">
         <v>2.48</v>
       </c>
-      <c r="O188" s="77">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -11309,17 +10767,14 @@
       <c r="K189" s="77">
         <v>1</v>
       </c>
-      <c r="L189" s="77">
+      <c r="M189" s="77">
         <v>1</v>
       </c>
       <c r="N189" s="77">
         <v>1</v>
       </c>
-      <c r="O189" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -11353,17 +10808,14 @@
       <c r="K190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-      <c r="L190" s="77">
+      <c r="M190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
       <c r="N190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-      <c r="O190" s="77">
-        <v>6.1060227588121015E-4</v>
-      </c>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -11397,17 +10849,14 @@
       <c r="K191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="L191" s="85">
+      <c r="M191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
       <c r="N191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="O191" s="85">
-        <v>3.9999999999999998E-7</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -11441,17 +10890,14 @@
       <c r="K192" s="77">
         <v>25</v>
       </c>
-      <c r="L192" s="77">
+      <c r="M192" s="77">
         <v>25</v>
       </c>
       <c r="N192" s="77">
         <v>25</v>
       </c>
-      <c r="O192" s="77">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -11485,17 +10931,14 @@
       <c r="K193" s="77">
         <v>0</v>
       </c>
-      <c r="L193" s="77">
+      <c r="M193" s="77">
         <v>0</v>
       </c>
       <c r="N193" s="77">
         <v>0</v>
       </c>
-      <c r="O193" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -11529,17 +10972,14 @@
       <c r="K194" s="77">
         <v>3.98</v>
       </c>
-      <c r="L194" s="77">
+      <c r="M194" s="77">
         <v>3.98</v>
       </c>
       <c r="N194" s="77">
         <v>3.98</v>
       </c>
-      <c r="O194" s="77">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -11573,17 +11013,14 @@
       <c r="K195" s="77">
         <v>1</v>
       </c>
-      <c r="L195" s="77">
+      <c r="M195" s="77">
         <v>1</v>
       </c>
       <c r="N195" s="77">
         <v>1</v>
       </c>
-      <c r="O195" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -11617,17 +11054,14 @@
       <c r="K196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="L196" s="78">
+      <c r="M196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O196" s="78">
-        <v>8.3333333333333331E-5</v>
-      </c>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -11661,17 +11095,14 @@
       <c r="K197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="L197" s="85">
+      <c r="M197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
       <c r="N197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="O197" s="85">
-        <v>3.9999999999999998E-7</v>
-      </c>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -11705,17 +11136,14 @@
       <c r="K198" s="77">
         <v>25</v>
       </c>
-      <c r="L198" s="77">
+      <c r="M198" s="77">
         <v>25</v>
       </c>
       <c r="N198" s="77">
         <v>25</v>
       </c>
-      <c r="O198" s="77">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -11749,17 +11177,14 @@
       <c r="K199" s="77">
         <v>0</v>
       </c>
-      <c r="L199" s="77">
+      <c r="M199" s="77">
         <v>0</v>
       </c>
       <c r="N199" s="77">
         <v>0</v>
       </c>
-      <c r="O199" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -11793,17 +11218,14 @@
       <c r="K200" s="77">
         <v>3.98</v>
       </c>
-      <c r="L200" s="77">
+      <c r="M200" s="77">
         <v>3.98</v>
       </c>
       <c r="N200" s="77">
         <v>3.98</v>
       </c>
-      <c r="O200" s="77">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -11837,17 +11259,14 @@
       <c r="K201" s="77">
         <v>1</v>
       </c>
-      <c r="L201" s="77">
+      <c r="M201" s="77">
         <v>1</v>
       </c>
       <c r="N201" s="77">
         <v>1</v>
       </c>
-      <c r="O201" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -11881,17 +11300,14 @@
       <c r="K202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="L202" s="78">
+      <c r="M202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O202" s="78">
-        <v>8.3333333333333331E-5</v>
-      </c>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -11925,17 +11341,14 @@
       <c r="K203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="L203" s="85">
+      <c r="M203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
       <c r="N203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="O203" s="85">
-        <v>1.9999999999999999E-7</v>
-      </c>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -11969,17 +11382,14 @@
       <c r="K204" s="77">
         <v>25</v>
       </c>
-      <c r="L204" s="77">
+      <c r="M204" s="77">
         <v>25</v>
       </c>
       <c r="N204" s="77">
         <v>25</v>
       </c>
-      <c r="O204" s="77">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -12013,17 +11423,14 @@
       <c r="K205" s="77">
         <v>0</v>
       </c>
-      <c r="L205" s="77">
+      <c r="M205" s="77">
         <v>0</v>
       </c>
       <c r="N205" s="77">
         <v>0</v>
       </c>
-      <c r="O205" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -12057,17 +11464,14 @@
       <c r="K206" s="77">
         <v>3.98</v>
       </c>
-      <c r="L206" s="77">
+      <c r="M206" s="77">
         <v>3.98</v>
       </c>
       <c r="N206" s="77">
         <v>3.98</v>
       </c>
-      <c r="O206" s="77">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -12101,17 +11505,14 @@
       <c r="K207" s="77">
         <v>1</v>
       </c>
-      <c r="L207" s="77">
+      <c r="M207" s="77">
         <v>1</v>
       </c>
       <c r="N207" s="77">
         <v>1</v>
       </c>
-      <c r="O207" s="77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -12145,17 +11546,14 @@
       <c r="K208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="L208" s="78">
+      <c r="M208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O208" s="78">
-        <v>8.3333333333333331E-5</v>
-      </c>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -12189,17 +11587,14 @@
       <c r="K209" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="L209" s="95" t="s">
+      <c r="M209" s="95" t="s">
         <v>90</v>
       </c>
       <c r="N209" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="O209" s="95" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="210" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>557</v>
       </c>
@@ -12222,34 +11617,30 @@
         <v>0.5</v>
       </c>
       <c r="H210" s="83">
-        <f t="shared" ref="H210:L210" si="2">0.00002</f>
+        <f t="shared" ref="H210:J210" si="5">0.00002</f>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="I210" s="83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="J210" s="83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="K210" s="83">
-        <f t="shared" si="2"/>
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="L210" s="83">
-        <f t="shared" si="2"/>
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="M210" s="1"/>
+        <f>0.00005 / 100</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="L210" s="1"/>
+      <c r="M210" s="2">
+        <v>0.01</v>
+      </c>
       <c r="N210" s="2">
         <v>0.01</v>
       </c>
-      <c r="O210" s="2">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="211" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>560</v>
       </c>
@@ -12283,18 +11674,15 @@
       <c r="K211" s="83">
         <v>0.1</v>
       </c>
-      <c r="L211" s="83">
-        <v>0.1</v>
-      </c>
-      <c r="M211" s="1"/>
+      <c r="L211" s="1"/>
+      <c r="M211" s="99">
+        <v>0</v>
+      </c>
       <c r="N211" s="99">
         <v>0</v>
       </c>
-      <c r="O211" s="99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="212" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>563</v>
       </c>
@@ -12317,33 +11705,29 @@
         <v>0.5</v>
       </c>
       <c r="H212" s="83">
-        <f t="shared" ref="H212:L212" si="3">0.00002 / 14</f>
+        <f t="shared" ref="H212:K212" si="6">0.00002 / 14</f>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="I212" s="83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="J212" s="83">
         <v>2E-3</v>
       </c>
       <c r="K212" s="83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.4285714285714286E-6</v>
       </c>
-      <c r="L212" s="83">
-        <f t="shared" si="3"/>
-        <v>1.4285714285714286E-6</v>
-      </c>
-      <c r="M212" s="1"/>
+      <c r="L212" s="1"/>
+      <c r="M212" s="100">
+        <v>1</v>
+      </c>
       <c r="N212" s="100">
-        <v>1</v>
-      </c>
-      <c r="O212" s="100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="213" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>507</v>
       </c>
@@ -12377,18 +11761,15 @@
       <c r="K213" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="L213" s="83" t="s">
+      <c r="L213" s="1"/>
+      <c r="M213" s="98">
+        <v>0.1</v>
+      </c>
+      <c r="N213" s="98" t="s">
         <v>476</v>
       </c>
-      <c r="M213" s="1"/>
-      <c r="N213" s="98">
-        <v>0.1</v>
-      </c>
-      <c r="O213" s="98" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="214" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -12422,18 +11803,15 @@
       <c r="K214" s="83">
         <v>0</v>
       </c>
-      <c r="L214" s="83">
-        <v>0</v>
-      </c>
-      <c r="M214" s="1"/>
+      <c r="L214" s="1"/>
+      <c r="M214" s="98">
+        <v>0.04</v>
+      </c>
       <c r="N214" s="98">
         <v>0.04</v>
       </c>
-      <c r="O214" s="98">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="215" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="215" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -12467,18 +11845,15 @@
       <c r="K215" s="83">
         <v>1E-3</v>
       </c>
-      <c r="L215" s="83">
+      <c r="L215" s="1"/>
+      <c r="M215" s="98">
         <v>1E-3</v>
       </c>
-      <c r="M215" s="1"/>
       <c r="N215" s="98">
         <v>1E-3</v>
       </c>
-      <c r="O215" s="98">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>515</v>
       </c>
@@ -12517,18 +11892,14 @@
         <f>1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="L216" s="99">
-        <f>1250*0.000001/5</f>
+      <c r="M216" s="99">
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="N216" s="99">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="O216" s="99">
-        <v>2.5000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -12562,17 +11933,14 @@
       <c r="K217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="L217" s="99">
+      <c r="M217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="N217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="O217" s="99">
-        <v>2.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>534</v>
       </c>
@@ -12608,12 +11976,8 @@
         <f xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="L218" s="83">
-        <f xml:space="preserve"> 0.0000000000025</f>
-        <v>2.4999999999999998E-12</v>
-      </c>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>535</v>
       </c>
@@ -12648,15 +12012,14 @@
         <v>1.2E-10</v>
       </c>
       <c r="K219" s="83">
-        <f>0.000000012 / 10 / 5</f>
-        <v>2.4E-10</v>
-      </c>
-      <c r="L219" s="83">
-        <f>0.000000012 / 10 / 5</f>
-        <v>2.4E-10</v>
-      </c>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+        <f>0.00000000005</f>
+        <v>5.0000000000000002E-11</v>
+      </c>
+      <c r="L219" s="101">
+        <v>5.0000000000000002E-11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>569</v>
       </c>
@@ -12673,7 +12036,7 @@
         <v>546</v>
       </c>
       <c r="F220" s="96" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="G220" s="99">
         <v>9.9999999999999995E-8</v>
@@ -12682,380 +12045,345 @@
       <c r="I220" s="83"/>
       <c r="J220" s="83"/>
       <c r="K220" s="83">
-        <f>0.0000001 / 2</f>
-        <v>4.9999999999999998E-8</v>
-      </c>
-      <c r="L220" s="83">
-        <f>0.0000001 / 2</f>
-        <v>4.9999999999999998E-8</v>
-      </c>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+        <f>0.0000001 * 10</f>
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="L220" s="101">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E221" s="96" t="s">
+        <v>572</v>
+      </c>
+      <c r="F221" s="96" t="s">
+        <v>495</v>
+      </c>
+      <c r="G221" s="99">
+        <v>100</v>
+      </c>
+      <c r="H221" s="83"/>
+      <c r="I221" s="83"/>
+      <c r="J221" s="83"/>
+      <c r="K221" s="83">
+        <f>100</f>
+        <v>100</v>
+      </c>
+      <c r="L221" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="B221" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E221" s="96" t="s">
+      <c r="B222" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E222" s="96" t="s">
         <v>547</v>
       </c>
-      <c r="F221" s="96" t="s">
+      <c r="F222" s="96" t="s">
         <v>548</v>
       </c>
-      <c r="G221" s="99">
+      <c r="G222" s="99">
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="H221" s="83">
+      <c r="H222" s="83">
         <f>0.000001 / 10000</f>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="I221" s="83">
+      <c r="I222" s="83">
         <f>0.000001 / 10000</f>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="J221" s="83">
+      <c r="J222" s="83">
         <f>0.000001 / 10000</f>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="K221" s="83">
-        <f>0.000001 / 10000</f>
-        <v>9.9999999999999991E-11</v>
-      </c>
-      <c r="L221" s="83">
-        <f>0.000001 / 10000</f>
-        <v>9.9999999999999991E-11</v>
-      </c>
-    </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A222" s="2" t="s">
+      <c r="K222" s="83">
+        <f>0.000001 / 10000 / 4</f>
+        <v>2.4999999999999998E-11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="B222" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E222" s="96" t="s">
+      <c r="B223" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E223" s="96" t="s">
         <v>549</v>
       </c>
-      <c r="F222" s="96" t="s">
+      <c r="F223" s="96" t="s">
         <v>550</v>
       </c>
-      <c r="G222" s="99">
+      <c r="G223" s="99">
         <f>2*0.00001</f>
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="H222" s="83">
+      <c r="H223" s="83">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="I222" s="83">
+      <c r="I223" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="J222" s="83">
+      <c r="J223" s="83">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="K222" s="83">
+      <c r="K223" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="L222" s="83">
-        <v>1.0000000000000001E-5</v>
-      </c>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A223" s="2" t="s">
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B223" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E223" s="96" t="s">
+      <c r="B224" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E224" s="96" t="s">
         <v>551</v>
       </c>
-      <c r="F223" s="96" t="s">
+      <c r="F224" s="96" t="s">
         <v>506</v>
       </c>
-      <c r="G223" s="99">
+      <c r="G224" s="99">
         <f>0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
-      <c r="H223" s="83">
-        <f t="shared" ref="H223:L223" si="4">0.84*(0.36^2)</f>
+      <c r="H224" s="83">
+        <f t="shared" ref="H224:K224" si="7">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
-      <c r="I223" s="83">
-        <f t="shared" si="4"/>
+      <c r="I224" s="83">
+        <f t="shared" si="7"/>
         <v>0.10886399999999999</v>
       </c>
-      <c r="J223" s="83">
-        <f t="shared" si="4"/>
+      <c r="J224" s="83">
+        <f t="shared" si="7"/>
         <v>0.10886399999999999</v>
       </c>
-      <c r="K223" s="83">
-        <f t="shared" si="4"/>
+      <c r="K224" s="83">
+        <f t="shared" si="7"/>
         <v>0.10886399999999999</v>
       </c>
-      <c r="L223" s="83">
-        <f t="shared" si="4"/>
-        <v>0.10886399999999999</v>
-      </c>
-    </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A224" s="2" t="s">
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E224" s="96" t="s">
+      <c r="B225" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E225" s="96" t="s">
         <v>552</v>
       </c>
-      <c r="F224" s="96" t="s">
+      <c r="F225" s="96" t="s">
         <v>495</v>
       </c>
-      <c r="G224" s="100">
+      <c r="G225" s="100">
         <v>0.2</v>
       </c>
-      <c r="H224" s="83">
+      <c r="H225" s="83">
         <v>0.2</v>
       </c>
-      <c r="I224" s="83">
+      <c r="I225" s="83">
         <v>0.2</v>
       </c>
-      <c r="J224" s="83">
+      <c r="J225" s="83">
         <v>0.2</v>
       </c>
-      <c r="K224" s="83">
+      <c r="K225" s="83">
         <v>0.2</v>
       </c>
-      <c r="L224" s="83">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A225" s="2" t="s">
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B225" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E225" s="96" t="s">
+      <c r="B226" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E226" s="96" t="s">
         <v>553</v>
-      </c>
-      <c r="F225" s="96" t="s">
-        <v>510</v>
-      </c>
-      <c r="G225" s="100" t="s">
-        <v>476</v>
-      </c>
-      <c r="H225" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="I225" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="J225" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="K225" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="L225" s="83" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A226" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E226" s="96" t="s">
-        <v>554</v>
       </c>
       <c r="F226" s="96" t="s">
         <v>510</v>
       </c>
-      <c r="G226" s="100">
+      <c r="G226" s="100" t="s">
+        <v>476</v>
+      </c>
+      <c r="H226" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="I226" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="J226" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="K226" s="83" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E227" s="96" t="s">
+        <v>554</v>
+      </c>
+      <c r="F227" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G227" s="100">
         <f>2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="H226" s="83">
-        <f t="shared" ref="H226:L226" si="5">2*0.1</f>
+      <c r="H227" s="83">
+        <f t="shared" ref="H227:K227" si="8">2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="I226" s="83">
-        <f t="shared" si="5"/>
+      <c r="I227" s="83">
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
-      <c r="J226" s="83">
-        <f t="shared" si="5"/>
+      <c r="J227" s="83">
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
-      <c r="K226" s="83">
-        <f t="shared" si="5"/>
+      <c r="K227" s="83">
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
-      <c r="L226" s="83">
-        <f t="shared" si="5"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A227" s="2" t="s">
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B227" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E227" s="96" t="s">
+      <c r="B228" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E228" s="96" t="s">
         <v>555</v>
-      </c>
-      <c r="F227" s="96" t="s">
-        <v>510</v>
-      </c>
-      <c r="G227" s="100">
-        <v>1E-3</v>
-      </c>
-      <c r="H227" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="I227" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="J227" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="K227" s="83">
-        <v>1E-3</v>
-      </c>
-      <c r="L227" s="83">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A228" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E228" s="96" t="s">
-        <v>556</v>
       </c>
       <c r="F228" s="96" t="s">
         <v>510</v>
       </c>
-      <c r="G228" s="98">
+      <c r="G228" s="100">
+        <v>1E-3</v>
+      </c>
+      <c r="H228" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="I228" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="J228" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="K228" s="83">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E229" s="96" t="s">
+        <v>556</v>
+      </c>
+      <c r="F229" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G229" s="98">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="H228" s="83">
+      <c r="H229" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I228" s="83">
+      <c r="I229" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="J228" s="83">
+      <c r="J229" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="K228" s="83">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="L228" s="83">
-        <v>1.0000000000000001E-5</v>
-      </c>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A229" s="2" t="s">
+      <c r="K229" s="83">
+        <f>0.00001 / 2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="E229" s="30" t="s">
-        <v>558</v>
-      </c>
-      <c r="F229" s="30" t="s">
-        <v>559</v>
-      </c>
-      <c r="G229" s="83">
-        <f t="shared" ref="G229:J229" si="6">0.00002 / 14 / 5</f>
-        <v>2.8571428571428575E-7</v>
-      </c>
-      <c r="H229" s="83">
-        <f t="shared" si="6"/>
-        <v>2.8571428571428575E-7</v>
-      </c>
-      <c r="I229" s="83">
-        <v>0</v>
-      </c>
-      <c r="J229" s="83">
-        <f t="shared" si="6"/>
-        <v>2.8571428571428575E-7</v>
-      </c>
-      <c r="K229" s="83">
-        <v>0</v>
-      </c>
-      <c r="L229" s="83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A230" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>471</v>
@@ -13073,32 +12401,66 @@
         <v>559</v>
       </c>
       <c r="G230" s="83">
-        <f>0.00002 / 14 / 5 /10</f>
+        <f t="shared" ref="G230:J230" si="9">0.00002 / 14 / 5</f>
+        <v>2.8571428571428575E-7</v>
+      </c>
+      <c r="H230" s="83">
+        <f t="shared" si="9"/>
+        <v>2.8571428571428575E-7</v>
+      </c>
+      <c r="I230" s="83">
+        <v>0</v>
+      </c>
+      <c r="J230" s="83">
+        <f t="shared" si="9"/>
+        <v>2.8571428571428575E-7</v>
+      </c>
+      <c r="K230" s="83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A231" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E231" s="30" t="s">
+        <v>558</v>
+      </c>
+      <c r="F231" s="30" t="s">
+        <v>559</v>
+      </c>
+      <c r="G231" s="83">
+        <f t="shared" ref="G231:K231" si="10">0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="H230" s="83">
-        <f>0.00002 / 14 / 5 /10</f>
+      <c r="H231" s="83">
+        <f t="shared" si="10"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="I230" s="83">
-        <f>0.00002 / 14 / 5 /10</f>
+      <c r="I231" s="83">
+        <f t="shared" si="10"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="J230" s="83">
-        <f>0.00002 / 14 / 5 /10</f>
+      <c r="J231" s="83">
+        <f t="shared" si="10"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="K230" s="83">
-        <f>0.00002 / 14 / 5 /10</f>
+      <c r="K231" s="83">
+        <f t="shared" si="10"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="L230" s="83">
-        <f>0.00002 / 14 / 5 /10</f>
-        <v>2.8571428571428575E-8</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G229:I230">
+  <conditionalFormatting sqref="G230:I231">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -13120,8 +12482,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G230:L230">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="G231:K231">
+    <cfRule type="colorScale" priority="357">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13131,7 +12493,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="358">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13142,8 +12504,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H127:L128">
-    <cfRule type="colorScale" priority="289">
+  <conditionalFormatting sqref="H127:K128">
+    <cfRule type="colorScale" priority="359">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13154,7 +12516,281 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N129:O129 H129:L129">
+  <conditionalFormatting sqref="H210:K210">
+    <cfRule type="colorScale" priority="360">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="361">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H211:K211">
+    <cfRule type="colorScale" priority="363">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="362">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H212:K212">
+    <cfRule type="colorScale" priority="365">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="364">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H213:K213">
+    <cfRule type="colorScale" priority="366">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="367">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H214:K214">
+    <cfRule type="colorScale" priority="369">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="368">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H215:K215">
+    <cfRule type="colorScale" priority="371">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="370">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H218:K218">
+    <cfRule type="colorScale" priority="373">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="372">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H219:K221">
+    <cfRule type="colorScale" priority="386">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="387">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H222:K222">
+    <cfRule type="colorScale" priority="376">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="377">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H223:K223">
+    <cfRule type="colorScale" priority="378">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="379">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H224:K224">
+    <cfRule type="colorScale" priority="380">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="381">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H225:K229">
+    <cfRule type="colorScale" priority="382">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="383">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H129:N129">
+    <cfRule type="colorScale" priority="292">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="291">
       <colorScale>
         <cfvo type="min"/>
@@ -13165,7 +12801,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="292">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H132:N132">
+    <cfRule type="colorScale" priority="299">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="300">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13176,7 +12824,75 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N130:O130 H130:L130">
+  <conditionalFormatting sqref="H138:N138">
+    <cfRule type="colorScale" priority="307">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J230">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K230:K231">
+    <cfRule type="colorScale" priority="384">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="385">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M127:N128">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M130:N130 H130:K130">
     <cfRule type="colorScale" priority="295">
       <colorScale>
         <cfvo type="min"/>
@@ -13198,8 +12914,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N132:O132 H132:L132">
-    <cfRule type="colorScale" priority="299">
+  <conditionalFormatting sqref="M133:N133 H133:K133">
+    <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13209,7 +12925,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="300">
+    <cfRule type="colorScale" priority="303">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13220,42 +12936,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N133:O133 H133:L133">
-    <cfRule type="colorScale" priority="303">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="304">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N138:O138 H138:L138">
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N144:O144 H144:L144">
-    <cfRule type="colorScale" priority="309">
+  <conditionalFormatting sqref="M144:N144 H144:K144">
+    <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13275,7 +12957,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="311">
+    <cfRule type="colorScale" priority="309">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13286,8 +12968,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N160:O160 H160:L160">
-    <cfRule type="colorScale" priority="315">
+  <conditionalFormatting sqref="M160:N160 H160:K160">
+    <cfRule type="colorScale" priority="317">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13307,7 +12989,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="317">
+    <cfRule type="colorScale" priority="315">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13318,8 +13000,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H210:L210">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="M166:N166 H166:K166">
+    <cfRule type="colorScale" priority="322">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13329,294 +13011,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H211:L211">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H212:L212">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H213:L213">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H214:L214">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H215:L215">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H218:L218">
-    <cfRule type="colorScale" priority="327">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="328">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H219:L220">
-    <cfRule type="colorScale" priority="331">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="332">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H221:L221">
-    <cfRule type="colorScale" priority="335">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="336">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H222:L222">
-    <cfRule type="colorScale" priority="339">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="340">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H223:L223">
-    <cfRule type="colorScale" priority="351">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="352">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H224:L228">
-    <cfRule type="colorScale" priority="355">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="356">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J229">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N127:O128">
-    <cfRule type="colorScale" priority="47">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N166:O166 H166:L166">
     <cfRule type="colorScale" priority="321">
       <colorScale>
         <cfvo type="min"/>
@@ -13627,39 +13021,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="322">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="323">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K229:L230">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroparistechfr-my.sharepoint.com/personal/190861_agroparistech_fr/Documents/Thesis/Sujet/Modelling/winscp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{DEAA7B16-44C5-44DB-B1E0-9B2F2BF27D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3BF9F43-CB5C-4539-A730-984050407E1A}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{DEAA7B16-44C5-44DB-B1E0-9B2F2BF27D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B4AAEC3-AEAB-4B06-A772-79D0A4E38EF3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2416,7 +2416,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2624,7 +2624,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -8289,10 +8288,6 @@
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="L129" s="83">
-        <f t="shared" si="3"/>
-        <v>5.9999999999999997E-7</v>
-      </c>
       <c r="M129" s="83">
         <f t="shared" si="3"/>
         <v>5.9999999999999997E-7</v>
@@ -8420,11 +8415,8 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="K132" s="83">
-        <f>0.0005</f>
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="L132" s="83">
-        <v>5.0000000000000001E-4</v>
+        <f>0.0005 * 1.2</f>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="M132" s="83">
         <v>5.0000000000000001E-4</v>
@@ -8673,9 +8665,6 @@
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="L138" s="80">
-        <v>1.9999999999999999E-7</v>
-      </c>
       <c r="M138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
@@ -12013,9 +12002,6 @@
       </c>
       <c r="K219" s="83">
         <f>0.00000000005</f>
-        <v>5.0000000000000002E-11</v>
-      </c>
-      <c r="L219" s="101">
         <v>5.0000000000000002E-11</v>
       </c>
     </row>
@@ -12045,10 +12031,11 @@
       <c r="I220" s="83"/>
       <c r="J220" s="83"/>
       <c r="K220" s="83">
+        <f>0.0000001 * 10 /2</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="L220" s="83">
         <f>0.0000001 * 10</f>
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="L220" s="101">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
@@ -12081,9 +12068,6 @@
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="L221" s="1">
-        <v>100</v>
-      </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
@@ -12461,7 +12445,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G230:I231">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12471,7 +12455,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12483,7 +12467,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G231:K231">
-    <cfRule type="colorScale" priority="357">
+    <cfRule type="colorScale" priority="359">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12493,7 +12477,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="358">
+    <cfRule type="colorScale" priority="360">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12505,7 +12489,41 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H127:K128">
-    <cfRule type="colorScale" priority="359">
+    <cfRule type="colorScale" priority="361">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H129:K129 M129:N129">
+    <cfRule type="colorScale" priority="294">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="293">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H138:K138 M138:N138">
+    <cfRule type="colorScale" priority="309">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12517,28 +12535,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H210:K210">
-    <cfRule type="colorScale" priority="360">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="361">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H211:K211">
     <cfRule type="colorScale" priority="363">
       <colorScale>
         <cfvo type="min"/>
@@ -12560,7 +12556,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H212:K212">
+  <conditionalFormatting sqref="H211:K211">
     <cfRule type="colorScale" priority="365">
       <colorScale>
         <cfvo type="min"/>
@@ -12582,7 +12578,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H213:K213">
+  <conditionalFormatting sqref="H212:K212">
+    <cfRule type="colorScale" priority="367">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="366">
       <colorScale>
         <cfvo type="min"/>
@@ -12593,7 +12599,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="367">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H213:K213">
+    <cfRule type="colorScale" priority="368">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="369">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12605,28 +12623,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H214:K214">
-    <cfRule type="colorScale" priority="369">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="368">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H215:K215">
     <cfRule type="colorScale" priority="371">
       <colorScale>
         <cfvo type="min"/>
@@ -12648,7 +12644,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H218:K218">
+  <conditionalFormatting sqref="H215:K215">
     <cfRule type="colorScale" priority="373">
       <colorScale>
         <cfvo type="min"/>
@@ -12670,7 +12666,183 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H218:K218">
+    <cfRule type="colorScale" priority="375">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="374">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H219:K221">
+    <cfRule type="colorScale" priority="389">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="388">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H222:K222">
+    <cfRule type="colorScale" priority="378">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="379">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H223:K223">
+    <cfRule type="colorScale" priority="380">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="381">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H224:K224">
+    <cfRule type="colorScale" priority="382">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="383">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H225:K229">
+    <cfRule type="colorScale" priority="384">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="385">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H132:K132 M132:N132">
+    <cfRule type="colorScale" priority="302">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="301">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J230">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K230:K231">
     <cfRule type="colorScale" priority="386">
       <colorScale>
         <cfvo type="min"/>
@@ -12692,196 +12864,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H222:K222">
-    <cfRule type="colorScale" priority="376">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="377">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H223:K223">
-    <cfRule type="colorScale" priority="378">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="379">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H224:K224">
-    <cfRule type="colorScale" priority="380">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="381">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H225:K229">
-    <cfRule type="colorScale" priority="382">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="383">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H129:N129">
-    <cfRule type="colorScale" priority="292">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="291">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H132:N132">
-    <cfRule type="colorScale" priority="299">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="300">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H138:N138">
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J230">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K230:K231">
-    <cfRule type="colorScale" priority="384">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="385">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="M127:N128">
-    <cfRule type="colorScale" priority="47">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12893,7 +12877,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M130:N130 H130:K130">
-    <cfRule type="colorScale" priority="295">
+    <cfRule type="colorScale" priority="297">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12903,7 +12887,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="296">
+    <cfRule type="colorScale" priority="298">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12915,7 +12899,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M133:N133 H133:K133">
-    <cfRule type="colorScale" priority="304">
+    <cfRule type="colorScale" priority="306">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12925,7 +12909,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="303">
+    <cfRule type="colorScale" priority="305">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12937,7 +12921,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M144:N144 H144:K144">
-    <cfRule type="colorScale" priority="311">
+    <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12947,7 +12931,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="310">
+    <cfRule type="colorScale" priority="312">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12957,7 +12941,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="309">
+    <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12969,7 +12953,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M160:N160 H160:K160">
-    <cfRule type="colorScale" priority="317">
+    <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12979,7 +12963,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="316">
+    <cfRule type="colorScale" priority="318">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12989,7 +12973,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="315">
+    <cfRule type="colorScale" priority="317">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13001,17 +12985,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M166:N166 H166:K166">
-    <cfRule type="colorScale" priority="322">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="321">
+    <cfRule type="colorScale" priority="324">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13022,6 +12996,38 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="323">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="325">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L220">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroparistechfr-my.sharepoint.com/personal/190861_agroparistech_fr/Documents/Thesis/Sujet/Modelling/winscp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp15581\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{DEAA7B16-44C5-44DB-B1E0-9B2F2BF27D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B4AAEC3-AEAB-4B06-A772-79D0A4E38EF3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7010F0-625C-4947-BDF6-86F87F05EA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="576">
   <si>
     <t>input_file</t>
   </si>
@@ -1759,6 +1759,9 @@
   </si>
   <si>
     <t>max_loading_rate</t>
+  </si>
+  <si>
+    <t>RC_no_deficit</t>
   </si>
 </sst>
 </file>
@@ -2682,10 +2685,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -2949,7 +2948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N231"/>
+  <dimension ref="A1:O231"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" style="1" customWidth="1"/>
@@ -2957,10 +2956,10 @@
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="22.6640625" customWidth="1"/>
     <col min="7" max="7" width="19.5546875" style="37" customWidth="1"/>
-    <col min="8" max="14" width="39.88671875" style="1" customWidth="1"/>
+    <col min="8" max="15" width="39.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -2992,19 +2991,22 @@
         <v>565</v>
       </c>
       <c r="K1" s="97" t="s">
+        <v>575</v>
+      </c>
+      <c r="L1" s="97" t="s">
         <v>568</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="M1" s="97" t="s">
+      <c r="N1" s="97" t="s">
         <v>522</v>
       </c>
-      <c r="N1" s="97" t="s">
+      <c r="O1" s="97" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>524</v>
       </c>
@@ -3038,14 +3040,17 @@
       <c r="K2" s="36" t="s">
         <v>476</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="L2" s="36" t="s">
+        <v>476</v>
+      </c>
+      <c r="N2" s="36" t="s">
         <v>528</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="O2" s="36" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3079,14 +3084,17 @@
       <c r="K3" s="36" t="s">
         <v>573</v>
       </c>
-      <c r="M3" s="36" t="s">
-        <v>489</v>
+      <c r="L3" s="36" t="s">
+        <v>573</v>
       </c>
       <c r="N3" s="36" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="36" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3120,14 +3128,17 @@
       <c r="K4" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="L4" s="36" t="s">
         <v>482</v>
       </c>
       <c r="N4" s="36" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O4" s="36" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3161,14 +3172,17 @@
       <c r="K5" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="M5" s="36" t="s">
-        <v>494</v>
+      <c r="L5" s="36" t="s">
+        <v>482</v>
       </c>
       <c r="N5" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O5" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3202,14 +3216,17 @@
       <c r="K6" s="36" t="s">
         <v>573</v>
       </c>
-      <c r="M6" s="36" t="s">
-        <v>521</v>
+      <c r="L6" s="36" t="s">
+        <v>573</v>
       </c>
       <c r="N6" s="36" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O6" s="36" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3243,14 +3260,17 @@
       <c r="K7" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="M7" s="36" t="s">
+      <c r="L7" s="36" t="s">
         <v>494</v>
       </c>
       <c r="N7" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O7" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>529</v>
       </c>
@@ -3284,14 +3304,17 @@
       <c r="K8" s="36">
         <v>0</v>
       </c>
-      <c r="M8" s="36">
+      <c r="L8" s="36">
         <v>0</v>
       </c>
       <c r="N8" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3325,14 +3348,17 @@
       <c r="K9" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="77" t="s">
+      <c r="L9" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N9" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3366,14 +3392,17 @@
       <c r="K10" s="77">
         <v>1</v>
       </c>
-      <c r="M10" s="77">
+      <c r="L10" s="77">
         <v>1</v>
       </c>
       <c r="N10" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3407,14 +3436,17 @@
       <c r="K11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="77" t="s">
+      <c r="L11" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N11" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3448,14 +3480,17 @@
       <c r="K12" s="85">
         <v>180</v>
       </c>
-      <c r="M12" s="85">
+      <c r="L12" s="85">
         <v>180</v>
       </c>
       <c r="N12" s="85">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" s="85">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3489,14 +3524,17 @@
       <c r="K13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="M13" s="78">
+      <c r="L13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
       <c r="N13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3530,14 +3568,17 @@
       <c r="K14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="M14" s="79">
+      <c r="L14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
       <c r="N14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3571,14 +3612,17 @@
       <c r="K15" s="77">
         <v>1</v>
       </c>
-      <c r="M15" s="77">
+      <c r="L15" s="77">
         <v>1</v>
       </c>
       <c r="N15" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3612,14 +3656,17 @@
       <c r="K16" s="77">
         <v>0</v>
       </c>
-      <c r="M16" s="77">
+      <c r="L16" s="77">
         <v>0</v>
       </c>
       <c r="N16" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3653,14 +3700,17 @@
       <c r="K17" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M17" s="77" t="s">
+      <c r="L17" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N17" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3694,14 +3744,17 @@
       <c r="K18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="M18" s="80">
+      <c r="L18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
       <c r="N18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -3735,14 +3788,17 @@
       <c r="K19" s="77">
         <v>10</v>
       </c>
-      <c r="M19" s="77">
+      <c r="L19" s="77">
         <v>10</v>
       </c>
       <c r="N19" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -3776,14 +3832,17 @@
       <c r="K20" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M20" s="77" t="s">
+      <c r="L20" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N20" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -3817,14 +3876,17 @@
       <c r="K21" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M21" s="77" t="s">
+      <c r="L21" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N21" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -3858,14 +3920,17 @@
       <c r="K22" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M22" s="77" t="s">
+      <c r="L22" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N22" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O22" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -3899,14 +3964,17 @@
       <c r="K23" s="77">
         <v>86400</v>
       </c>
-      <c r="M23" s="77">
+      <c r="L23" s="77">
         <v>86400</v>
       </c>
       <c r="N23" s="77">
         <v>86400</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O23" s="77">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -3940,14 +4008,17 @@
       <c r="K24" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M24" s="77" t="s">
+      <c r="L24" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N24" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O24" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -3981,14 +4052,17 @@
       <c r="K25" s="77">
         <v>3</v>
       </c>
-      <c r="M25" s="77">
+      <c r="L25" s="77">
         <v>3</v>
       </c>
       <c r="N25" s="77">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O25" s="77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -4022,14 +4096,17 @@
       <c r="K26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="M26" s="81" t="s">
+      <c r="L26" s="81" t="s">
         <v>88</v>
       </c>
       <c r="N26" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -4063,14 +4140,17 @@
       <c r="K27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="M27" s="81" t="s">
+      <c r="L27" s="81" t="s">
         <v>88</v>
       </c>
       <c r="N27" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -4104,14 +4184,17 @@
       <c r="K28" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M28" s="77" t="s">
+      <c r="L28" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N28" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O28" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4145,14 +4228,17 @@
       <c r="K29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="M29" s="81" t="s">
+      <c r="L29" s="81" t="s">
         <v>88</v>
       </c>
       <c r="N29" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O29" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4186,14 +4272,17 @@
       <c r="K30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="M30" s="81" t="s">
+      <c r="L30" s="81" t="s">
         <v>88</v>
       </c>
       <c r="N30" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O30" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4227,14 +4316,17 @@
       <c r="K31" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M31" s="77" t="s">
+      <c r="L31" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N31" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O31" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4268,14 +4360,17 @@
       <c r="K32" s="77">
         <v>0.33</v>
       </c>
-      <c r="M32" s="77">
+      <c r="L32" s="77">
         <v>0.33</v>
       </c>
       <c r="N32" s="77">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O32" s="77">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4309,14 +4404,17 @@
       <c r="K33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M33" s="77" t="s">
+      <c r="L33" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N33" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4350,14 +4448,17 @@
       <c r="K34" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M34" s="77" t="s">
+      <c r="L34" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N34" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4391,14 +4492,17 @@
       <c r="K35" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M35" s="77" t="s">
+      <c r="L35" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N35" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O35" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4432,14 +4536,17 @@
       <c r="K36" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M36" s="77" t="s">
+      <c r="L36" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N36" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4473,14 +4580,17 @@
       <c r="K37" s="85" t="s">
         <v>433</v>
       </c>
-      <c r="M37" s="85" t="s">
+      <c r="L37" s="85" t="s">
         <v>433</v>
       </c>
       <c r="N37" s="85" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O37" s="85" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -4514,14 +4624,17 @@
       <c r="K38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="M38" s="80">
+      <c r="L38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="N38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -4555,14 +4668,17 @@
       <c r="K39" s="86">
         <v>1E-3</v>
       </c>
-      <c r="M39" s="86">
+      <c r="L39" s="86">
         <v>1E-3</v>
       </c>
       <c r="N39" s="86">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O39" s="86">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -4596,14 +4712,17 @@
       <c r="K40" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M40" s="77" t="s">
+      <c r="L40" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N40" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -4637,14 +4756,17 @@
       <c r="K41" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="M41" s="77" t="s">
+      <c r="L41" s="77" t="s">
         <v>89</v>
       </c>
       <c r="N41" s="77" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O41" s="77" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -4678,14 +4800,17 @@
       <c r="K42" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M42" s="77" t="s">
+      <c r="L42" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N42" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O42" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -4719,14 +4844,17 @@
       <c r="K43" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M43" s="77" t="s">
+      <c r="L43" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N43" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O43" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -4760,14 +4888,17 @@
       <c r="K44" s="77">
         <v>120</v>
       </c>
-      <c r="M44" s="77">
+      <c r="L44" s="77">
         <v>120</v>
       </c>
       <c r="N44" s="77">
         <v>120</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O44" s="77">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -4801,14 +4932,17 @@
       <c r="K45" s="77">
         <v>0</v>
       </c>
-      <c r="M45" s="77">
+      <c r="L45" s="77">
         <v>0</v>
       </c>
       <c r="N45" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O45" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -4842,14 +4976,17 @@
       <c r="K46" s="77">
         <v>0</v>
       </c>
-      <c r="M46" s="77">
+      <c r="L46" s="77">
         <v>0</v>
       </c>
       <c r="N46" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O46" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -4883,14 +5020,17 @@
       <c r="K47" s="77">
         <v>-0.1</v>
       </c>
-      <c r="M47" s="77">
+      <c r="L47" s="77">
         <v>-0.1</v>
       </c>
       <c r="N47" s="77">
         <v>-0.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O47" s="77">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -4924,14 +5064,17 @@
       <c r="K48" s="77">
         <v>-0.2</v>
       </c>
-      <c r="M48" s="77">
+      <c r="L48" s="77">
         <v>-0.2</v>
       </c>
       <c r="N48" s="77">
         <v>-0.2</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O48" s="77">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -4965,14 +5108,17 @@
       <c r="K49" s="77">
         <v>0.4</v>
       </c>
-      <c r="M49" s="77">
+      <c r="L49" s="77">
         <v>0.4</v>
       </c>
       <c r="N49" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O49" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -5006,14 +5152,17 @@
       <c r="K50" s="77">
         <v>0</v>
       </c>
-      <c r="M50" s="77">
+      <c r="L50" s="77">
         <v>0</v>
       </c>
       <c r="N50" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O50" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -5047,14 +5196,17 @@
       <c r="K51" s="77">
         <v>1200</v>
       </c>
-      <c r="M51" s="77">
+      <c r="L51" s="77">
         <v>1200</v>
       </c>
       <c r="N51" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O51" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -5088,14 +5240,17 @@
       <c r="K52" s="77">
         <v>1200</v>
       </c>
-      <c r="M52" s="77">
+      <c r="L52" s="77">
         <v>1200</v>
       </c>
       <c r="N52" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O52" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -5129,14 +5284,17 @@
       <c r="K53" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="M53" s="35" t="s">
+      <c r="L53" s="35" t="s">
         <v>460</v>
       </c>
       <c r="N53" s="35" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O53" s="35" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -5170,14 +5328,17 @@
       <c r="K54" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M54" s="77" t="s">
+      <c r="L54" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N54" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O54" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5211,14 +5372,17 @@
       <c r="K55" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="M55" s="77" t="s">
+      <c r="L55" s="77" t="s">
         <v>87</v>
       </c>
       <c r="N55" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O55" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -5252,14 +5416,17 @@
       <c r="K56" s="77">
         <v>0</v>
       </c>
-      <c r="M56" s="77">
+      <c r="L56" s="77">
         <v>0</v>
       </c>
       <c r="N56" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O56" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -5293,14 +5460,17 @@
       <c r="K57" s="77">
         <v>0.5</v>
       </c>
-      <c r="M57" s="77">
+      <c r="L57" s="77">
         <v>0.5</v>
       </c>
       <c r="N57" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O57" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -5334,14 +5504,17 @@
       <c r="K58" s="77">
         <v>0.05</v>
       </c>
-      <c r="M58" s="77">
+      <c r="L58" s="77">
         <v>0.05</v>
       </c>
       <c r="N58" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O58" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -5375,14 +5548,17 @@
       <c r="K59" s="80">
         <v>1E-3</v>
       </c>
-      <c r="M59" s="80">
+      <c r="L59" s="80">
         <v>1E-3</v>
       </c>
       <c r="N59" s="80">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O59" s="80">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -5416,14 +5592,17 @@
       <c r="K60" s="77">
         <v>0</v>
       </c>
-      <c r="M60" s="77">
+      <c r="L60" s="77">
         <v>0</v>
       </c>
       <c r="N60" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O60" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -5457,14 +5636,17 @@
       <c r="K61" s="77">
         <v>1E-4</v>
       </c>
-      <c r="M61" s="77">
+      <c r="L61" s="77">
         <v>1E-4</v>
       </c>
       <c r="N61" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O61" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -5498,14 +5680,17 @@
       <c r="K62" s="77">
         <v>1E-4</v>
       </c>
-      <c r="M62" s="77">
+      <c r="L62" s="77">
         <v>1E-4</v>
       </c>
       <c r="N62" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O62" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -5539,14 +5724,17 @@
       <c r="K63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="M63" s="77">
+      <c r="L63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="N63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -5580,14 +5768,17 @@
       <c r="K64" s="77">
         <v>1.22E-4</v>
       </c>
-      <c r="M64" s="77">
+      <c r="L64" s="77">
         <v>1.22E-4</v>
       </c>
       <c r="N64" s="77">
         <v>1.22E-4</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O64" s="77">
+        <v>1.22E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -5621,14 +5812,17 @@
       <c r="K65" s="77">
         <v>1</v>
       </c>
-      <c r="M65" s="77">
+      <c r="L65" s="77">
         <v>1</v>
       </c>
       <c r="N65" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O65" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -5662,14 +5856,17 @@
       <c r="K66" s="77">
         <v>0.95</v>
       </c>
-      <c r="M66" s="77">
+      <c r="L66" s="77">
         <v>0.95</v>
       </c>
       <c r="N66" s="77">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O66" s="77">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -5703,14 +5900,17 @@
       <c r="K67" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M67" s="77" t="s">
+      <c r="L67" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N67" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O67" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -5744,14 +5944,17 @@
       <c r="K68" s="77">
         <v>5</v>
       </c>
-      <c r="M68" s="77">
+      <c r="L68" s="77">
         <v>5</v>
       </c>
       <c r="N68" s="77">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O68" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -5785,14 +5988,17 @@
       <c r="K69" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M69" s="77" t="s">
+      <c r="L69" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N69" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O69" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -5826,14 +6032,17 @@
       <c r="K70" s="77">
         <v>50</v>
       </c>
-      <c r="M70" s="77">
+      <c r="L70" s="77">
         <v>50</v>
       </c>
       <c r="N70" s="77">
         <v>50</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O70" s="77">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -5867,14 +6076,17 @@
       <c r="K71" s="78">
         <v>1453890.8941884842</v>
       </c>
-      <c r="M71" s="78">
+      <c r="L71" s="78">
         <v>1453890.8941884842</v>
       </c>
       <c r="N71" s="78">
         <v>1453890.8941884842</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -5908,14 +6120,17 @@
       <c r="K72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-      <c r="M72" s="78">
+      <c r="L72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
       <c r="N72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -5949,14 +6164,17 @@
       <c r="K73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-      <c r="M73" s="79">
+      <c r="L73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
       <c r="N73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -5990,14 +6208,17 @@
       <c r="K74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-      <c r="M74" s="85">
+      <c r="L74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
       <c r="N74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -6031,14 +6252,17 @@
       <c r="K75" s="79">
         <v>282528</v>
       </c>
-      <c r="M75" s="79">
+      <c r="L75" s="79">
         <v>282528</v>
       </c>
       <c r="N75" s="79">
         <v>282528</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O75" s="79">
+        <v>282528</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -6072,14 +6296,17 @@
       <c r="K76" s="85">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M76" s="85">
+      <c r="L76" s="85">
         <v>0.56999999999999995</v>
       </c>
       <c r="N76" s="85">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -6113,14 +6340,17 @@
       <c r="K77" s="87">
         <v>0.16</v>
       </c>
-      <c r="M77" s="87">
+      <c r="L77" s="87">
         <v>0.16</v>
       </c>
       <c r="N77" s="87">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O77" s="87">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -6154,14 +6384,17 @@
       <c r="K78" s="77">
         <v>0</v>
       </c>
-      <c r="M78" s="77">
+      <c r="L78" s="77">
         <v>0</v>
       </c>
       <c r="N78" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O78" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -6195,14 +6428,17 @@
       <c r="K79" s="78">
         <v>745476480000</v>
       </c>
-      <c r="M79" s="78">
+      <c r="L79" s="78">
         <v>745476480000</v>
       </c>
       <c r="N79" s="78">
         <v>745476480000</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O79" s="78">
+        <v>745476480000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -6236,14 +6472,17 @@
       <c r="K80" s="77">
         <v>100</v>
       </c>
-      <c r="M80" s="77">
+      <c r="L80" s="77">
         <v>100</v>
       </c>
       <c r="N80" s="77">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O80" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -6277,14 +6516,17 @@
       <c r="K81" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="M81" s="77" t="s">
+      <c r="L81" s="77" t="s">
         <v>88</v>
       </c>
       <c r="N81" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O81" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -6318,14 +6560,17 @@
       <c r="K82" s="85">
         <v>21600</v>
       </c>
-      <c r="M82" s="85">
+      <c r="L82" s="85">
         <v>21600</v>
       </c>
       <c r="N82" s="85">
         <v>21600</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O82" s="85">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -6359,14 +6604,17 @@
       <c r="K83" s="77">
         <v>0.5</v>
       </c>
-      <c r="M83" s="77">
+      <c r="L83" s="77">
         <v>0.5</v>
       </c>
       <c r="N83" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O83" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -6400,14 +6648,17 @@
       <c r="K84" s="85">
         <v>60479.999999999993</v>
       </c>
-      <c r="M84" s="85">
+      <c r="L84" s="85">
         <v>60479.999999999993</v>
       </c>
       <c r="N84" s="85">
         <v>60479.999999999993</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -6441,14 +6692,17 @@
       <c r="K85" s="77">
         <v>0.85</v>
       </c>
-      <c r="M85" s="77">
+      <c r="L85" s="77">
         <v>0.85</v>
       </c>
       <c r="N85" s="77">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O85" s="77">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -6482,14 +6736,17 @@
       <c r="K86" s="77">
         <v>518400</v>
       </c>
-      <c r="M86" s="77">
+      <c r="L86" s="77">
         <v>518400</v>
       </c>
       <c r="N86" s="77">
         <v>518400</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O86" s="77">
+        <v>518400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -6523,14 +6780,17 @@
       <c r="K87" s="77">
         <v>5184000</v>
       </c>
-      <c r="M87" s="77">
+      <c r="L87" s="77">
         <v>5184000</v>
       </c>
       <c r="N87" s="77">
         <v>5184000</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O87" s="77">
+        <v>5184000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -6564,14 +6824,17 @@
       <c r="K88" s="86">
         <v>50000</v>
       </c>
-      <c r="M88" s="86">
+      <c r="L88" s="86">
         <v>50000</v>
       </c>
       <c r="N88" s="86">
         <v>50000</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O88" s="86">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -6605,14 +6868,17 @@
       <c r="K89" s="77">
         <v>140000</v>
       </c>
-      <c r="M89" s="77">
+      <c r="L89" s="77">
         <v>140000</v>
       </c>
       <c r="N89" s="77">
         <v>140000</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O89" s="77">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -6646,14 +6912,17 @@
       <c r="K90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-      <c r="M90" s="78">
+      <c r="L90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
       <c r="N90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -6687,14 +6956,17 @@
       <c r="K91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="M91" s="77">
+      <c r="L91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="N91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -6728,14 +7000,17 @@
       <c r="K92" s="77">
         <v>0.05</v>
       </c>
-      <c r="M92" s="77">
+      <c r="L92" s="77">
         <v>0.05</v>
       </c>
       <c r="N92" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O92" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -6769,14 +7044,17 @@
       <c r="K93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="M93" s="77">
+      <c r="L93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
       <c r="N93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -6810,14 +7088,17 @@
       <c r="K94" s="77">
         <v>1E-3</v>
       </c>
-      <c r="M94" s="77">
-        <v>0</v>
+      <c r="L94" s="77">
+        <v>1E-3</v>
       </c>
       <c r="N94" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O94" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -6851,14 +7132,17 @@
       <c r="K95" s="77">
         <v>374999999.99999994</v>
       </c>
-      <c r="M95" s="77">
+      <c r="L95" s="77">
         <v>374999999.99999994</v>
       </c>
       <c r="N95" s="77">
         <v>374999999.99999994</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -6892,14 +7176,17 @@
       <c r="K96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="M96" s="78">
+      <c r="L96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
       <c r="N96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -6933,14 +7220,17 @@
       <c r="K97" s="77">
         <v>165600</v>
       </c>
-      <c r="M97" s="77">
+      <c r="L97" s="77">
         <v>165600</v>
       </c>
       <c r="N97" s="77">
         <v>165600</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O97" s="77">
+        <v>165600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -6974,14 +7264,17 @@
       <c r="K98" s="77">
         <v>20</v>
       </c>
-      <c r="M98" s="77">
+      <c r="L98" s="77">
         <v>20</v>
       </c>
       <c r="N98" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O98" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -7015,14 +7308,17 @@
       <c r="K99" s="77">
         <v>1</v>
       </c>
-      <c r="M99" s="77">
+      <c r="L99" s="77">
         <v>1</v>
       </c>
       <c r="N99" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O99" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -7056,14 +7352,17 @@
       <c r="K100" s="77">
         <v>21</v>
       </c>
-      <c r="M100" s="77">
+      <c r="L100" s="77">
         <v>21</v>
       </c>
       <c r="N100" s="77">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O100" s="77">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -7097,14 +7396,17 @@
       <c r="K101" s="77">
         <v>0.64</v>
       </c>
-      <c r="M101" s="77">
+      <c r="L101" s="77">
         <v>0.64</v>
       </c>
       <c r="N101" s="77">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O101" s="77">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -7138,14 +7440,17 @@
       <c r="K102" s="77">
         <v>8</v>
       </c>
-      <c r="M102" s="77">
+      <c r="L102" s="77">
         <v>8</v>
       </c>
       <c r="N102" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O102" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -7179,14 +7484,17 @@
       <c r="K103" s="77">
         <v>10</v>
       </c>
-      <c r="M103" s="77">
+      <c r="L103" s="77">
         <v>10</v>
       </c>
       <c r="N103" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O103" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -7220,14 +7528,17 @@
       <c r="K104" s="77">
         <v>8</v>
       </c>
-      <c r="M104" s="77">
+      <c r="L104" s="77">
         <v>8</v>
       </c>
       <c r="N104" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O104" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>500</v>
       </c>
@@ -7261,14 +7572,17 @@
       <c r="K105" s="77">
         <v>1</v>
       </c>
-      <c r="M105" s="77">
+      <c r="L105" s="77">
         <v>1</v>
       </c>
       <c r="N105" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O105" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -7302,14 +7616,17 @@
       <c r="K106" s="77">
         <v>0.5</v>
       </c>
-      <c r="M106" s="77">
+      <c r="L106" s="77">
         <v>0.5</v>
       </c>
       <c r="N106" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O106" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>501</v>
       </c>
@@ -7329,7 +7646,7 @@
         <v>506</v>
       </c>
       <c r="G107" s="58">
-        <f t="shared" ref="G107:K107" si="0">G105</f>
+        <f t="shared" ref="G107:L107" si="0">G105</f>
         <v>1</v>
       </c>
       <c r="H107" s="58">
@@ -7345,17 +7662,21 @@
         <v>1</v>
       </c>
       <c r="K107" s="58">
+        <f t="shared" ref="K107" si="1">K105</f>
+        <v>1</v>
+      </c>
+      <c r="L107" s="58">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M107" s="58">
-        <v>1</v>
-      </c>
       <c r="N107" s="58">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O107" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
         <v>502</v>
       </c>
@@ -7394,14 +7715,18 @@
         <f>150*K105</f>
         <v>150</v>
       </c>
-      <c r="M108" s="58">
+      <c r="L108" s="58">
+        <f>150*L105</f>
         <v>150</v>
       </c>
       <c r="N108" s="58">
         <v>150</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O108" s="58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>503</v>
       </c>
@@ -7421,33 +7746,37 @@
         <v>506</v>
       </c>
       <c r="G109" s="58">
-        <f t="shared" ref="G109:K109" si="1">G100</f>
+        <f t="shared" ref="G109:L109" si="2">G100</f>
         <v>21</v>
       </c>
       <c r="H109" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="I109" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="J109" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="K109" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K109" si="3">K100</f>
         <v>21</v>
       </c>
-      <c r="M109" s="58">
+      <c r="L109" s="58">
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="N109" s="58">
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O109" s="58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
         <v>504</v>
       </c>
@@ -7486,14 +7815,18 @@
         <f>70*K100</f>
         <v>1470</v>
       </c>
-      <c r="M110" s="58">
+      <c r="L110" s="58">
+        <f>70*L100</f>
         <v>1470</v>
       </c>
       <c r="N110" s="58">
         <v>1470</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O110" s="58">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -7527,14 +7860,17 @@
       <c r="K111" s="77">
         <v>0</v>
       </c>
-      <c r="M111" s="77">
+      <c r="L111" s="77">
         <v>0</v>
       </c>
       <c r="N111" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O111" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -7568,14 +7904,17 @@
       <c r="K112" s="82">
         <v>1589759.9999999998</v>
       </c>
-      <c r="M112" s="82">
+      <c r="L112" s="82">
         <v>1589759.9999999998</v>
       </c>
       <c r="N112" s="82">
         <v>1589759.9999999998</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -7609,14 +7948,17 @@
       <c r="K113" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="M113" s="82">
+      <c r="L113" s="82">
         <v>6171428.5714285718</v>
       </c>
       <c r="N113" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -7650,14 +7992,17 @@
       <c r="K114" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="M114" s="82">
+      <c r="L114" s="82">
         <v>6171428.5714285718</v>
       </c>
       <c r="N114" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -7691,14 +8036,17 @@
       <c r="K115" s="82">
         <v>100</v>
       </c>
-      <c r="M115" s="82">
+      <c r="L115" s="82">
         <v>100</v>
       </c>
       <c r="N115" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O115" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -7737,14 +8085,18 @@
         <f>0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
-      <c r="M116" s="67">
+      <c r="L116" s="67">
+        <f>0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
       <c r="N116" s="67">
         <v>28080</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O116" s="67">
+        <v>28080</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -7783,14 +8135,18 @@
         <f>1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
-      <c r="M117" s="67">
+      <c r="L117" s="67">
+        <f>1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
       <c r="N117" s="67">
         <v>0.11100000000000002</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O117" s="67">
+        <v>0.11100000000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
         <v>497</v>
       </c>
@@ -7824,14 +8180,17 @@
       <c r="K118" s="82">
         <v>100</v>
       </c>
-      <c r="M118" s="82">
+      <c r="L118" s="82">
         <v>100</v>
       </c>
       <c r="N118" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O118" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>498</v>
       </c>
@@ -7851,33 +8210,37 @@
         <v>431</v>
       </c>
       <c r="G119" s="67">
-        <f t="shared" ref="G119:K119" si="2">5.32 * (60*60*24)</f>
+        <f t="shared" ref="G119:L119" si="4">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H119" s="67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>459648</v>
       </c>
       <c r="I119" s="67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>459648</v>
       </c>
       <c r="J119" s="67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>459648</v>
       </c>
       <c r="K119" s="67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>459648</v>
       </c>
-      <c r="M119" s="67">
+      <c r="L119" s="67">
+        <f t="shared" si="4"/>
         <v>459648</v>
       </c>
       <c r="N119" s="67">
         <v>459648</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O119" s="67">
+        <v>459648</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
         <v>499</v>
       </c>
@@ -7916,14 +8279,18 @@
         <f>1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
-      <c r="M120" s="67">
+      <c r="L120" s="67">
+        <f>1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
       <c r="N120" s="67">
         <v>0.13875000000000001</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O120" s="67">
+        <v>0.13875000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -7957,14 +8324,17 @@
       <c r="K121" s="82">
         <v>21600</v>
       </c>
-      <c r="M121" s="82">
+      <c r="L121" s="82">
         <v>21600</v>
       </c>
       <c r="N121" s="82">
         <v>21600</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O121" s="82">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -7998,14 +8368,17 @@
       <c r="K122" s="88">
         <v>43200</v>
       </c>
-      <c r="M122" s="88">
+      <c r="L122" s="88">
         <v>43200</v>
       </c>
       <c r="N122" s="88">
         <v>43200</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O122" s="88">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -8039,14 +8412,17 @@
       <c r="K123" s="77">
         <v>0.8</v>
       </c>
-      <c r="M123" s="77">
+      <c r="L123" s="77">
         <v>0.8</v>
       </c>
       <c r="N123" s="77">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O123" s="77">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -8081,14 +8457,17 @@
       <c r="K124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="M124" s="78">
+      <c r="L124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
       <c r="N124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O124" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -8122,14 +8501,17 @@
       <c r="K125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-      <c r="M125" s="77">
+      <c r="L125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
       <c r="N125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O125" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -8163,14 +8545,17 @@
       <c r="K126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="M126" s="78">
+      <c r="L126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
       <c r="N126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O126" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -8204,14 +8589,17 @@
       <c r="K127" s="78">
         <v>0</v>
       </c>
-      <c r="M127" s="78">
+      <c r="L127" s="78">
         <v>0</v>
       </c>
       <c r="N127" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O127" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -8245,14 +8633,17 @@
       <c r="K128" s="78">
         <v>0</v>
       </c>
-      <c r="M128" s="78">
+      <c r="L128" s="78">
         <v>0</v>
       </c>
       <c r="N128" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O128" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -8277,27 +8668,31 @@
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="I129" s="83">
-        <f t="shared" ref="I129:N129" si="3">0.0000002*3</f>
+        <f t="shared" ref="I129:O129" si="5">0.0000002*3</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J129" s="83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="K129" s="83">
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="M129" s="83">
-        <f t="shared" si="3"/>
+      <c r="L129" s="83">
+        <f>0.0000002 * 2 / 10</f>
+        <v>4.0000000000000001E-8</v>
+      </c>
+      <c r="N129" s="83">
+        <f t="shared" si="5"/>
         <v>5.9999999999999997E-7</v>
       </c>
-      <c r="N129" s="83">
-        <f t="shared" si="3"/>
+      <c r="O129" s="83">
+        <f t="shared" si="5"/>
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -8318,31 +8713,35 @@
       </c>
       <c r="G130" s="71"/>
       <c r="H130" s="83">
-        <f t="shared" ref="H130:N130" si="4">1000 * 0.000001 / 12</f>
+        <f t="shared" ref="H130:O130" si="6">1000 * 0.000001 / 12</f>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="I130" s="83">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="J130" s="83">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="K130" s="83">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M130" s="83">
-        <f t="shared" si="4"/>
+      <c r="L130" s="83">
+        <f t="shared" si="6"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N130" s="83">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O130" s="83">
+        <f t="shared" si="6"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -8376,14 +8775,17 @@
       <c r="K131" s="89" t="s">
         <v>533</v>
       </c>
-      <c r="M131" s="89" t="s">
+      <c r="L131" s="89" t="s">
         <v>533</v>
       </c>
       <c r="N131" s="89" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O131" s="89" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -8418,14 +8820,18 @@
         <f>0.0005 * 1.2</f>
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="M132" s="83">
-        <v>5.0000000000000001E-4</v>
+      <c r="L132" s="83">
+        <f>0.0005 * 1.2</f>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="N132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O132" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -8459,14 +8865,17 @@
       <c r="K133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="M133" s="83">
+      <c r="L133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
       <c r="N133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O133" s="83">
+        <v>4.9999999999999999E-13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -8500,14 +8909,17 @@
       <c r="K134" s="77">
         <v>10</v>
       </c>
-      <c r="M134" s="77">
+      <c r="L134" s="77">
         <v>10</v>
       </c>
       <c r="N134" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O134" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -8541,14 +8953,17 @@
       <c r="K135" s="77">
         <v>-0.04</v>
       </c>
-      <c r="M135" s="77">
+      <c r="L135" s="77">
         <v>-0.04</v>
       </c>
       <c r="N135" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O135" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -8582,14 +8997,17 @@
       <c r="K136" s="77">
         <v>2.9</v>
       </c>
-      <c r="M136" s="77">
+      <c r="L136" s="77">
         <v>2.9</v>
       </c>
       <c r="N136" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O136" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -8623,14 +9041,17 @@
       <c r="K137" s="77">
         <v>1</v>
       </c>
-      <c r="M137" s="77">
+      <c r="L137" s="77">
         <v>1</v>
       </c>
       <c r="N137" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O137" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="21" t="s">
         <v>574</v>
       </c>
@@ -8665,14 +9086,18 @@
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="M138" s="80">
-        <v>1.9999999999999999E-7</v>
+      <c r="L138" s="80">
+        <f>0.0000002 * 2 / 10</f>
+        <v>4.0000000000000001E-8</v>
       </c>
       <c r="N138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O138" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -8706,14 +9131,17 @@
       <c r="K139" s="77">
         <v>10</v>
       </c>
-      <c r="M139" s="77">
+      <c r="L139" s="77">
         <v>10</v>
       </c>
       <c r="N139" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O139" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -8747,14 +9175,17 @@
       <c r="K140" s="77">
         <v>-0.04</v>
       </c>
-      <c r="M140" s="77">
+      <c r="L140" s="77">
         <v>-0.04</v>
       </c>
       <c r="N140" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O140" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -8788,14 +9219,17 @@
       <c r="K141" s="77">
         <v>2.9</v>
       </c>
-      <c r="M141" s="77">
+      <c r="L141" s="77">
         <v>2.9</v>
       </c>
       <c r="N141" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O141" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -8829,14 +9263,17 @@
       <c r="K142" s="77">
         <v>1</v>
       </c>
-      <c r="M142" s="77">
+      <c r="L142" s="77">
         <v>1</v>
       </c>
       <c r="N142" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O142" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -8870,14 +9307,17 @@
       <c r="K143" s="77">
         <v>0</v>
       </c>
-      <c r="M143" s="77">
+      <c r="L143" s="77">
         <v>0</v>
       </c>
       <c r="N143" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O143" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -8911,14 +9351,17 @@
       <c r="K144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="M144" s="80">
+      <c r="L144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="N144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O144" s="80">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -8952,14 +9395,17 @@
       <c r="K145" s="77">
         <v>0</v>
       </c>
-      <c r="M145" s="77">
+      <c r="L145" s="77">
         <v>0</v>
       </c>
       <c r="N145" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O145" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -8993,14 +9439,17 @@
       <c r="K146" s="77">
         <v>2E-3</v>
       </c>
-      <c r="M146" s="77">
+      <c r="L146" s="77">
         <v>2E-3</v>
       </c>
       <c r="N146" s="77">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O146" s="77">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -9034,14 +9483,17 @@
       <c r="K147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-      <c r="M147" s="80">
+      <c r="L147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
       <c r="N147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O147" s="80">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -9075,14 +9527,17 @@
       <c r="K148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-      <c r="M148" s="80">
+      <c r="L148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
       <c r="N148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O148" s="80">
+        <v>3.7699999999999999E-10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -9116,14 +9571,17 @@
       <c r="K149" s="77">
         <v>20</v>
       </c>
-      <c r="M149" s="77">
+      <c r="L149" s="77">
         <v>20</v>
       </c>
       <c r="N149" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O149" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -9157,14 +9615,17 @@
       <c r="K150" s="77">
         <v>-0.06</v>
       </c>
-      <c r="M150" s="77">
+      <c r="L150" s="77">
         <v>-0.06</v>
       </c>
       <c r="N150" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O150" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -9198,14 +9659,17 @@
       <c r="K151" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="M151" s="77">
+      <c r="L151" s="77">
         <v>0.89100000000000001</v>
       </c>
       <c r="N151" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O151" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -9239,14 +9703,17 @@
       <c r="K152" s="77">
         <v>1</v>
       </c>
-      <c r="M152" s="77">
+      <c r="L152" s="77">
         <v>1</v>
       </c>
       <c r="N152" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O152" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -9280,14 +9747,17 @@
       <c r="K153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="M153" s="80">
+      <c r="L153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="N153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O153" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -9321,14 +9791,17 @@
       <c r="K154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-      <c r="M154" s="80">
+      <c r="L154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
       <c r="N154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O154" s="80">
+        <v>5.8333333333333335E-9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -9362,14 +9835,17 @@
       <c r="K155" s="77">
         <v>20</v>
       </c>
-      <c r="M155" s="77">
+      <c r="L155" s="77">
         <v>20</v>
       </c>
       <c r="N155" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O155" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -9403,14 +9879,17 @@
       <c r="K156" s="77">
         <v>-0.06</v>
       </c>
-      <c r="M156" s="77">
+      <c r="L156" s="77">
         <v>-0.06</v>
       </c>
       <c r="N156" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O156" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -9444,14 +9923,17 @@
       <c r="K157" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="M157" s="77">
+      <c r="L157" s="77">
         <v>0.89100000000000001</v>
       </c>
       <c r="N157" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O157" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -9485,14 +9967,17 @@
       <c r="K158" s="77">
         <v>1</v>
       </c>
-      <c r="M158" s="77">
+      <c r="L158" s="77">
         <v>1</v>
       </c>
       <c r="N158" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O158" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -9526,14 +10011,17 @@
       <c r="K159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="M159" s="80">
+      <c r="L159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="N159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O159" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -9567,14 +10055,17 @@
       <c r="K160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="M160" s="83">
+      <c r="L160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="N160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O160" s="83">
+        <v>4.0000000000000001E-8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -9608,14 +10099,17 @@
       <c r="K161" s="77">
         <v>20</v>
       </c>
-      <c r="M161" s="77">
+      <c r="L161" s="77">
         <v>20</v>
       </c>
       <c r="N161" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O161" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -9649,14 +10143,17 @@
       <c r="K162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-      <c r="M162" s="77">
+      <c r="L162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
       <c r="N162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O162" s="77">
+        <v>-4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -9690,14 +10187,17 @@
       <c r="K163" s="77">
         <v>1.55</v>
       </c>
-      <c r="M163" s="77">
+      <c r="L163" s="77">
         <v>1.55</v>
       </c>
       <c r="N163" s="77">
         <v>1.55</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O163" s="77">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -9731,14 +10231,17 @@
       <c r="K164" s="77">
         <v>1</v>
       </c>
-      <c r="M164" s="77">
+      <c r="L164" s="77">
         <v>1</v>
       </c>
       <c r="N164" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O164" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -9772,14 +10275,17 @@
       <c r="K165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="M165" s="77">
+      <c r="L165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
       <c r="N165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O165" s="77">
+        <v>2.7799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -9813,14 +10319,17 @@
       <c r="K166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="M166" s="84">
+      <c r="L166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="N166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O166" s="84">
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -9854,14 +10363,17 @@
       <c r="K167" s="77">
         <v>20</v>
       </c>
-      <c r="M167" s="77">
+      <c r="L167" s="77">
         <v>20</v>
       </c>
       <c r="N167" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O167" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -9895,14 +10407,17 @@
       <c r="K168" s="77">
         <v>0</v>
       </c>
-      <c r="M168" s="77">
+      <c r="L168" s="77">
         <v>0</v>
       </c>
       <c r="N168" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O168" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -9936,14 +10451,17 @@
       <c r="K169" s="77">
         <v>1</v>
       </c>
-      <c r="M169" s="77">
+      <c r="L169" s="77">
         <v>1</v>
       </c>
       <c r="N169" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O169" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -9977,14 +10495,17 @@
       <c r="K170" s="77">
         <v>0</v>
       </c>
-      <c r="M170" s="77">
+      <c r="L170" s="77">
         <v>0</v>
       </c>
       <c r="N170" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O170" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -10018,14 +10539,17 @@
       <c r="K171" s="77">
         <v>0.4</v>
       </c>
-      <c r="M171" s="77">
+      <c r="L171" s="77">
         <v>0.4</v>
       </c>
       <c r="N171" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O171" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -10059,14 +10583,17 @@
       <c r="K172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-      <c r="M172" s="86">
+      <c r="L172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
       <c r="N172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O172" s="86">
+        <v>2.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -10100,14 +10627,17 @@
       <c r="K173" s="77">
         <v>25</v>
       </c>
-      <c r="M173" s="77">
+      <c r="L173" s="77">
         <v>25</v>
       </c>
       <c r="N173" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O173" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -10141,14 +10671,17 @@
       <c r="K174" s="77">
         <v>0</v>
       </c>
-      <c r="M174" s="77">
+      <c r="L174" s="77">
         <v>0</v>
       </c>
       <c r="N174" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O174" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -10182,14 +10715,17 @@
       <c r="K175" s="77">
         <v>3.98</v>
       </c>
-      <c r="M175" s="77">
+      <c r="L175" s="77">
         <v>3.98</v>
       </c>
       <c r="N175" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O175" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -10223,14 +10759,17 @@
       <c r="K176" s="77">
         <v>1</v>
       </c>
-      <c r="M176" s="77">
+      <c r="L176" s="77">
         <v>1</v>
       </c>
       <c r="N176" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O176" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -10264,14 +10803,17 @@
       <c r="K177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-      <c r="M177" s="78">
+      <c r="L177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
       <c r="N177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O177" s="78">
+        <v>1.6666666666666666E-4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -10305,14 +10847,17 @@
       <c r="K178" s="80">
         <v>1E-8</v>
       </c>
-      <c r="M178" s="80">
+      <c r="L178" s="80">
         <v>1E-8</v>
       </c>
       <c r="N178" s="80">
         <v>1E-8</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O178" s="80">
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -10346,14 +10891,17 @@
       <c r="K179" s="77">
         <v>20</v>
       </c>
-      <c r="M179" s="77">
+      <c r="L179" s="77">
         <v>20</v>
       </c>
       <c r="N179" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O179" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -10387,14 +10935,17 @@
       <c r="K180" s="77">
         <v>0</v>
       </c>
-      <c r="M180" s="77">
+      <c r="L180" s="77">
         <v>0</v>
       </c>
       <c r="N180" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O180" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -10428,14 +10979,17 @@
       <c r="K181" s="77">
         <v>2</v>
       </c>
-      <c r="M181" s="77">
+      <c r="L181" s="77">
         <v>2</v>
       </c>
       <c r="N181" s="77">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O181" s="77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -10469,14 +11023,17 @@
       <c r="K182" s="77">
         <v>1</v>
       </c>
-      <c r="M182" s="77">
+      <c r="L182" s="77">
         <v>1</v>
       </c>
       <c r="N182" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O182" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -10510,14 +11067,17 @@
       <c r="K183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M183" s="78">
+      <c r="L183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O183" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -10551,14 +11111,17 @@
       <c r="K184" s="77">
         <v>1</v>
       </c>
-      <c r="M184" s="77">
+      <c r="L184" s="77">
         <v>1</v>
       </c>
       <c r="N184" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O184" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -10592,14 +11155,17 @@
       <c r="K185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-      <c r="M185" s="77">
+      <c r="L185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
       <c r="N185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O185" s="77">
+        <v>2.3533050791148899E-8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -10633,14 +11199,17 @@
       <c r="K186" s="77">
         <v>20</v>
       </c>
-      <c r="M186" s="77">
+      <c r="L186" s="77">
         <v>20</v>
       </c>
       <c r="N186" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O186" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -10674,14 +11243,17 @@
       <c r="K187" s="77">
         <v>-0.187</v>
       </c>
-      <c r="M187" s="77">
+      <c r="L187" s="77">
         <v>-0.187</v>
       </c>
       <c r="N187" s="77">
         <v>-0.187</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O187" s="77">
+        <v>-0.187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -10715,14 +11287,17 @@
       <c r="K188" s="77">
         <v>2.48</v>
       </c>
-      <c r="M188" s="77">
+      <c r="L188" s="77">
         <v>2.48</v>
       </c>
       <c r="N188" s="77">
         <v>2.48</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O188" s="77">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -10756,14 +11331,17 @@
       <c r="K189" s="77">
         <v>1</v>
       </c>
-      <c r="M189" s="77">
+      <c r="L189" s="77">
         <v>1</v>
       </c>
       <c r="N189" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O189" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -10797,14 +11375,17 @@
       <c r="K190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-      <c r="M190" s="77">
+      <c r="L190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
       <c r="N190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O190" s="77">
+        <v>6.1060227588121015E-4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -10838,14 +11419,17 @@
       <c r="K191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="M191" s="85">
+      <c r="L191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
       <c r="N191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O191" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -10879,14 +11463,17 @@
       <c r="K192" s="77">
         <v>25</v>
       </c>
-      <c r="M192" s="77">
+      <c r="L192" s="77">
         <v>25</v>
       </c>
       <c r="N192" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O192" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -10920,14 +11507,17 @@
       <c r="K193" s="77">
         <v>0</v>
       </c>
-      <c r="M193" s="77">
+      <c r="L193" s="77">
         <v>0</v>
       </c>
       <c r="N193" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O193" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -10961,14 +11551,17 @@
       <c r="K194" s="77">
         <v>3.98</v>
       </c>
-      <c r="M194" s="77">
+      <c r="L194" s="77">
         <v>3.98</v>
       </c>
       <c r="N194" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O194" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -11002,14 +11595,17 @@
       <c r="K195" s="77">
         <v>1</v>
       </c>
-      <c r="M195" s="77">
+      <c r="L195" s="77">
         <v>1</v>
       </c>
       <c r="N195" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O195" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -11043,14 +11639,17 @@
       <c r="K196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M196" s="78">
+      <c r="L196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O196" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -11084,14 +11683,17 @@
       <c r="K197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="M197" s="85">
+      <c r="L197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
       <c r="N197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O197" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -11125,14 +11727,17 @@
       <c r="K198" s="77">
         <v>25</v>
       </c>
-      <c r="M198" s="77">
+      <c r="L198" s="77">
         <v>25</v>
       </c>
       <c r="N198" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O198" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -11166,14 +11771,17 @@
       <c r="K199" s="77">
         <v>0</v>
       </c>
-      <c r="M199" s="77">
+      <c r="L199" s="77">
         <v>0</v>
       </c>
       <c r="N199" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O199" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -11207,14 +11815,17 @@
       <c r="K200" s="77">
         <v>3.98</v>
       </c>
-      <c r="M200" s="77">
+      <c r="L200" s="77">
         <v>3.98</v>
       </c>
       <c r="N200" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O200" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -11248,14 +11859,17 @@
       <c r="K201" s="77">
         <v>1</v>
       </c>
-      <c r="M201" s="77">
+      <c r="L201" s="77">
         <v>1</v>
       </c>
       <c r="N201" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O201" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -11289,14 +11903,17 @@
       <c r="K202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M202" s="78">
+      <c r="L202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O202" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -11330,14 +11947,17 @@
       <c r="K203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="M203" s="85">
+      <c r="L203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
       <c r="N203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O203" s="85">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -11371,14 +11991,17 @@
       <c r="K204" s="77">
         <v>25</v>
       </c>
-      <c r="M204" s="77">
+      <c r="L204" s="77">
         <v>25</v>
       </c>
       <c r="N204" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O204" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -11412,14 +12035,17 @@
       <c r="K205" s="77">
         <v>0</v>
       </c>
-      <c r="M205" s="77">
+      <c r="L205" s="77">
         <v>0</v>
       </c>
       <c r="N205" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O205" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -11453,14 +12079,17 @@
       <c r="K206" s="77">
         <v>3.98</v>
       </c>
-      <c r="M206" s="77">
+      <c r="L206" s="77">
         <v>3.98</v>
       </c>
       <c r="N206" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O206" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -11494,14 +12123,17 @@
       <c r="K207" s="77">
         <v>1</v>
       </c>
-      <c r="M207" s="77">
+      <c r="L207" s="77">
         <v>1</v>
       </c>
       <c r="N207" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O207" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -11535,14 +12167,17 @@
       <c r="K208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="M208" s="78">
+      <c r="L208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O208" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -11576,14 +12211,17 @@
       <c r="K209" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="M209" s="95" t="s">
+      <c r="L209" s="95" t="s">
         <v>90</v>
       </c>
       <c r="N209" s="95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O209" s="95" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>557</v>
       </c>
@@ -11606,30 +12244,34 @@
         <v>0.5</v>
       </c>
       <c r="H210" s="83">
-        <f t="shared" ref="H210:J210" si="5">0.00002</f>
+        <f t="shared" ref="H210:J210" si="7">0.00002</f>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="I210" s="83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="J210" s="83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="K210" s="83">
         <f>0.00005 / 100</f>
         <v>4.9999999999999998E-7</v>
       </c>
-      <c r="L210" s="1"/>
-      <c r="M210" s="2">
-        <v>0.01</v>
-      </c>
+      <c r="L210" s="83">
+        <f>0.00005 / 100</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="M210" s="1"/>
       <c r="N210" s="2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O210" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>560</v>
       </c>
@@ -11663,15 +12305,18 @@
       <c r="K211" s="83">
         <v>0.1</v>
       </c>
-      <c r="L211" s="1"/>
-      <c r="M211" s="99">
-        <v>0</v>
-      </c>
+      <c r="L211" s="83">
+        <v>0.1</v>
+      </c>
+      <c r="M211" s="1"/>
       <c r="N211" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O211" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>563</v>
       </c>
@@ -11694,29 +12339,33 @@
         <v>0.5</v>
       </c>
       <c r="H212" s="83">
-        <f t="shared" ref="H212:K212" si="6">0.00002 / 14</f>
+        <f t="shared" ref="H212:L212" si="8">0.00002 / 14</f>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="I212" s="83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="J212" s="83">
         <v>2E-3</v>
       </c>
       <c r="K212" s="83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.4285714285714286E-6</v>
       </c>
-      <c r="L212" s="1"/>
-      <c r="M212" s="100">
+      <c r="L212" s="83">
+        <f t="shared" si="8"/>
+        <v>1.4285714285714286E-6</v>
+      </c>
+      <c r="M212" s="1"/>
+      <c r="N212" s="100">
         <v>1</v>
       </c>
-      <c r="N212" s="100">
+      <c r="O212" s="100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="213" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>507</v>
       </c>
@@ -11750,15 +12399,18 @@
       <c r="K213" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="L213" s="1"/>
-      <c r="M213" s="98">
+      <c r="L213" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="M213" s="1"/>
+      <c r="N213" s="98">
         <v>0.1</v>
       </c>
-      <c r="N213" s="98" t="s">
+      <c r="O213" s="98" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="214" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -11792,15 +12444,18 @@
       <c r="K214" s="83">
         <v>0</v>
       </c>
-      <c r="L214" s="1"/>
-      <c r="M214" s="98">
-        <v>0.04</v>
-      </c>
+      <c r="L214" s="83">
+        <v>0</v>
+      </c>
+      <c r="M214" s="1"/>
       <c r="N214" s="98">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="215" spans="1:14" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O214" s="98">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -11834,15 +12489,18 @@
       <c r="K215" s="83">
         <v>1E-3</v>
       </c>
-      <c r="L215" s="1"/>
-      <c r="M215" s="98">
+      <c r="L215" s="83">
         <v>1E-3</v>
       </c>
+      <c r="M215" s="1"/>
       <c r="N215" s="98">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O215" s="98">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>515</v>
       </c>
@@ -11881,14 +12539,18 @@
         <f>1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="M216" s="99">
+      <c r="L216" s="99">
+        <f>1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="N216" s="99">
         <v>2.5000000000000001E-4</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O216" s="99">
+        <v>2.5000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -11922,14 +12584,17 @@
       <c r="K217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="M217" s="99">
+      <c r="L217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="N217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>534</v>
       </c>
@@ -11965,8 +12630,12 @@
         <f xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L218" s="83">
+        <f xml:space="preserve"> 0.0000000000025</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>535</v>
       </c>
@@ -12004,8 +12673,12 @@
         <f>0.00000000005</f>
         <v>5.0000000000000002E-11</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L219" s="83">
+        <f>0.00000000005</f>
+        <v>5.0000000000000002E-11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>569</v>
       </c>
@@ -12035,11 +12708,11 @@
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="L220" s="83">
-        <f>0.0000001 * 10</f>
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+        <f>0.0000001 * 10 /2</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>571</v>
       </c>
@@ -12068,8 +12741,12 @@
         <f>100</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L221" s="83">
+        <f>100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>536</v>
       </c>
@@ -12107,8 +12784,12 @@
         <f>0.000001 / 10000 / 4</f>
         <v>2.4999999999999998E-11</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L222" s="83">
+        <f>0.000001 / 10000 / 4</f>
+        <v>2.4999999999999998E-11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>537</v>
       </c>
@@ -12143,8 +12824,15 @@
       <c r="K223" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L223" s="83">
+        <f>0.00001 * 10</f>
+        <v>1E-4</v>
+      </c>
+      <c r="M223" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>538</v>
       </c>
@@ -12168,23 +12856,27 @@
         <v>0.10886399999999999</v>
       </c>
       <c r="H224" s="83">
-        <f t="shared" ref="H224:K224" si="7">0.84*(0.36^2)</f>
+        <f t="shared" ref="H224:L224" si="9">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
       <c r="I224" s="83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="J224" s="83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="K224" s="83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.10886399999999999</v>
       </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L224" s="83">
+        <f t="shared" si="9"/>
+        <v>0.10886399999999999</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>539</v>
       </c>
@@ -12218,8 +12910,11 @@
       <c r="K225" s="83">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L225" s="83">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>540</v>
       </c>
@@ -12253,8 +12948,11 @@
       <c r="K226" s="83" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L226" s="83" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>541</v>
       </c>
@@ -12278,23 +12976,27 @@
         <v>0.2</v>
       </c>
       <c r="H227" s="83">
-        <f t="shared" ref="H227:K227" si="8">2*0.1</f>
+        <f t="shared" ref="H227:L227" si="10">2*0.1</f>
         <v>0.2</v>
       </c>
       <c r="I227" s="83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J227" s="83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="K227" s="83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L227" s="83">
+        <f t="shared" si="10"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>542</v>
       </c>
@@ -12328,8 +13030,11 @@
       <c r="K228" s="83">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L228" s="83">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>543</v>
       </c>
@@ -12364,8 +13069,12 @@
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L229" s="83">
+        <f>0.00001 / 2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>566</v>
       </c>
@@ -12385,25 +13094,28 @@
         <v>559</v>
       </c>
       <c r="G230" s="83">
-        <f t="shared" ref="G230:J230" si="9">0.00002 / 14 / 5</f>
+        <f t="shared" ref="G230:J230" si="11">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="H230" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="I230" s="83">
         <v>0</v>
       </c>
       <c r="J230" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="K230" s="83">
         <v>0</v>
       </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L230" s="83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>567</v>
       </c>
@@ -12423,28 +13135,352 @@
         <v>559</v>
       </c>
       <c r="G231" s="83">
-        <f t="shared" ref="G231:K231" si="10">0.00002 / 14 / 5 /10</f>
+        <f t="shared" ref="G231:L231" si="12">0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="H231" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="I231" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="J231" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="K231" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
+        <v>2.8571428571428575E-8</v>
+      </c>
+      <c r="L231" s="83">
+        <f t="shared" si="12"/>
         <v>2.8571428571428575E-8</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G230:I231">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G231:L231">
+    <cfRule type="colorScale" priority="361">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="362">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H127:L128">
+    <cfRule type="colorScale" priority="363">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H210:L210">
+    <cfRule type="colorScale" priority="365">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="364">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H211:L211">
+    <cfRule type="colorScale" priority="367">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="366">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H212:L212">
+    <cfRule type="colorScale" priority="368">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="369">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H213:L213">
+    <cfRule type="colorScale" priority="371">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="370">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H214:L214">
+    <cfRule type="colorScale" priority="373">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="372">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H215:L215">
+    <cfRule type="colorScale" priority="375">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="374">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H218:L218">
+    <cfRule type="colorScale" priority="377">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="376">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H219:L221">
+    <cfRule type="colorScale" priority="391">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="390">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H222:L222">
+    <cfRule type="colorScale" priority="381">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="380">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H223:M223">
+    <cfRule type="colorScale" priority="383">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="382">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H224:L224">
+    <cfRule type="colorScale" priority="385">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="384">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H225:L229">
+    <cfRule type="colorScale" priority="386">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="387">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J230">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -12466,8 +13502,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G231:K231">
-    <cfRule type="colorScale" priority="359">
+  <conditionalFormatting sqref="K230:K231">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12477,7 +13513,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="360">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12488,8 +13524,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H127:K128">
-    <cfRule type="colorScale" priority="361">
+  <conditionalFormatting sqref="L230:L231">
+    <cfRule type="colorScale" priority="388">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="389">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12500,18 +13546,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H129:K129 M129:N129">
-    <cfRule type="colorScale" priority="294">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="293">
+  <conditionalFormatting sqref="N127:O128">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12522,8 +13558,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H138:K138 M138:N138">
-    <cfRule type="colorScale" priority="309">
+  <conditionalFormatting sqref="N129:O129 H129:L129">
+    <cfRule type="colorScale" priority="295">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="296">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12534,8 +13580,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H210:K210">
-    <cfRule type="colorScale" priority="363">
+  <conditionalFormatting sqref="N130:O130 H130:L130">
+    <cfRule type="colorScale" priority="299">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12545,7 +13591,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="362">
+    <cfRule type="colorScale" priority="300">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12556,8 +13602,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H211:K211">
-    <cfRule type="colorScale" priority="365">
+  <conditionalFormatting sqref="N132:O132 H132:L132">
+    <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12567,7 +13613,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="364">
+    <cfRule type="colorScale" priority="303">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12578,8 +13624,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H212:K212">
-    <cfRule type="colorScale" priority="367">
+  <conditionalFormatting sqref="N133:O133 H133:L133">
+    <cfRule type="colorScale" priority="308">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12589,7 +13635,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="366">
+    <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12600,347 +13646,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H213:K213">
-    <cfRule type="colorScale" priority="368">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="369">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H214:K214">
-    <cfRule type="colorScale" priority="371">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="370">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H215:K215">
-    <cfRule type="colorScale" priority="373">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="372">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H218:K218">
-    <cfRule type="colorScale" priority="375">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="374">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H219:K221">
-    <cfRule type="colorScale" priority="389">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="388">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H222:K222">
-    <cfRule type="colorScale" priority="378">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="379">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H223:K223">
-    <cfRule type="colorScale" priority="380">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="381">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H224:K224">
-    <cfRule type="colorScale" priority="382">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="383">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H225:K229">
-    <cfRule type="colorScale" priority="384">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="385">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H132:K132 M132:N132">
-    <cfRule type="colorScale" priority="302">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="301">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J230">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K230:K231">
-    <cfRule type="colorScale" priority="386">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="387">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M127:N128">
-    <cfRule type="colorScale" priority="49">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M130:N130 H130:K130">
-    <cfRule type="colorScale" priority="297">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="298">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M133:N133 H133:K133">
-    <cfRule type="colorScale" priority="306">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="305">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M144:N144 H144:K144">
-    <cfRule type="colorScale" priority="313">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="312">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
+  <conditionalFormatting sqref="N138:O138 H138:L138">
     <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min"/>
@@ -12952,7 +13658,49 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M160:N160 H160:K160">
+  <conditionalFormatting sqref="N144:O144 H144:L144">
+    <cfRule type="colorScale" priority="313">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="314">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="315">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N160:O160 H160:L160">
+    <cfRule type="colorScale" priority="321">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min"/>
@@ -12963,17 +13711,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="318">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="317">
+    <cfRule type="colorScale" priority="320">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12984,18 +13722,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M166:N166 H166:K166">
-    <cfRule type="colorScale" priority="324">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="323">
+  <conditionalFormatting sqref="N166:O166 H166:L166">
+    <cfRule type="colorScale" priority="326">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13015,19 +13743,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L220">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="327">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp15581\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp30714\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7010F0-625C-4947-BDF6-86F87F05EA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5E05B9-D7BF-4622-B7BF-7DCD11BD30F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="578">
   <si>
     <t>input_file</t>
   </si>
@@ -1762,6 +1762,12 @@
   </si>
   <si>
     <t>RC_no_deficit</t>
+  </si>
+  <si>
+    <t>Rhizodep_ref</t>
+  </si>
+  <si>
+    <t>sucrose_input_Swinnen_et_al_1994_20degrees_interpolated.csv</t>
   </si>
 </sst>
 </file>
@@ -2419,7 +2425,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2627,6 +2633,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="11" fontId="16" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2948,18 +2956,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O231"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P231"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="37" customWidth="1"/>
-    <col min="8" max="15" width="39.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="37" customWidth="1"/>
+    <col min="8" max="16" width="39.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -2996,17 +3004,20 @@
       <c r="L1" s="97" t="s">
         <v>568</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="97" t="s">
+        <v>576</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="N1" s="97" t="s">
+      <c r="O1" s="97" t="s">
         <v>522</v>
       </c>
-      <c r="O1" s="97" t="s">
+      <c r="P1" s="97" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>524</v>
       </c>
@@ -3043,14 +3054,17 @@
       <c r="L2" s="36" t="s">
         <v>476</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="M2" s="36" t="s">
+        <v>476</v>
+      </c>
+      <c r="O2" s="36" t="s">
         <v>528</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="P2" s="36" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" s="1" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3085,16 +3099,19 @@
         <v>573</v>
       </c>
       <c r="L3" s="36" t="s">
-        <v>573</v>
-      </c>
-      <c r="N3" s="36" t="s">
-        <v>489</v>
+        <v>577</v>
+      </c>
+      <c r="M3" s="36" t="s">
+        <v>577</v>
       </c>
       <c r="O3" s="36" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P3" s="36" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3131,14 +3148,17 @@
       <c r="L4" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="M4" s="36" t="s">
         <v>482</v>
       </c>
       <c r="O4" s="36" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P4" s="36" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3175,14 +3195,17 @@
       <c r="L5" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="N5" s="36" t="s">
-        <v>494</v>
+      <c r="M5" s="36" t="s">
+        <v>482</v>
       </c>
       <c r="O5" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3217,16 +3240,19 @@
         <v>573</v>
       </c>
       <c r="L6" s="36" t="s">
-        <v>573</v>
-      </c>
-      <c r="N6" s="36" t="s">
-        <v>521</v>
+        <v>577</v>
+      </c>
+      <c r="M6" s="36" t="s">
+        <v>577</v>
       </c>
       <c r="O6" s="36" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P6" s="36" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3263,14 +3289,17 @@
       <c r="L7" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="N7" s="36" t="s">
+      <c r="M7" s="36" t="s">
         <v>494</v>
       </c>
       <c r="O7" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P7" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>529</v>
       </c>
@@ -3307,14 +3336,17 @@
       <c r="L8" s="36">
         <v>0</v>
       </c>
-      <c r="N8" s="36">
+      <c r="M8" s="36">
         <v>0</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3351,14 +3383,17 @@
       <c r="L9" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="N9" s="77" t="s">
+      <c r="M9" s="77" t="s">
         <v>87</v>
       </c>
       <c r="O9" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3395,14 +3430,17 @@
       <c r="L10" s="77">
         <v>1</v>
       </c>
-      <c r="N10" s="77">
+      <c r="M10" s="77">
         <v>1</v>
       </c>
       <c r="O10" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3439,14 +3477,17 @@
       <c r="L11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N11" s="77" t="s">
+      <c r="M11" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O11" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3483,14 +3524,17 @@
       <c r="L12" s="85">
         <v>180</v>
       </c>
-      <c r="N12" s="85">
+      <c r="M12" s="85">
         <v>180</v>
       </c>
       <c r="O12" s="85">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12" s="85">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3527,14 +3571,17 @@
       <c r="L13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="N13" s="78">
+      <c r="M13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
       <c r="O13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3571,14 +3618,17 @@
       <c r="L14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="N14" s="79">
+      <c r="M14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
       <c r="O14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3615,14 +3665,17 @@
       <c r="L15" s="77">
         <v>1</v>
       </c>
-      <c r="N15" s="77">
+      <c r="M15" s="77">
         <v>1</v>
       </c>
       <c r="O15" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3659,14 +3712,17 @@
       <c r="L16" s="77">
         <v>0</v>
       </c>
-      <c r="N16" s="77">
+      <c r="M16" s="77">
         <v>0</v>
       </c>
       <c r="O16" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3703,14 +3759,17 @@
       <c r="L17" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N17" s="77" t="s">
+      <c r="M17" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O17" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3747,14 +3806,17 @@
       <c r="L18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="N18" s="80">
+      <c r="M18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
       <c r="O18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -3791,14 +3853,17 @@
       <c r="L19" s="77">
         <v>10</v>
       </c>
-      <c r="N19" s="77">
+      <c r="M19" s="77">
         <v>10</v>
       </c>
       <c r="O19" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P19" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -3835,14 +3900,17 @@
       <c r="L20" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N20" s="77" t="s">
+      <c r="M20" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O20" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P20" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -3879,14 +3947,17 @@
       <c r="L21" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N21" s="77" t="s">
+      <c r="M21" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O21" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P21" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -3923,14 +3994,17 @@
       <c r="L22" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N22" s="77" t="s">
+      <c r="M22" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O22" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P22" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -3967,14 +4041,17 @@
       <c r="L23" s="77">
         <v>86400</v>
       </c>
-      <c r="N23" s="77">
+      <c r="M23" s="77">
         <v>86400</v>
       </c>
       <c r="O23" s="77">
         <v>86400</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P23" s="77">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -4011,14 +4088,17 @@
       <c r="L24" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="N24" s="77" t="s">
+      <c r="M24" s="77" t="s">
         <v>87</v>
       </c>
       <c r="O24" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P24" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -4055,14 +4135,17 @@
       <c r="L25" s="77">
         <v>3</v>
       </c>
-      <c r="N25" s="77">
+      <c r="M25" s="77">
         <v>3</v>
       </c>
       <c r="O25" s="77">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P25" s="77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -4099,14 +4182,17 @@
       <c r="L26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="N26" s="81" t="s">
+      <c r="M26" s="81" t="s">
         <v>88</v>
       </c>
       <c r="O26" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P26" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -4143,14 +4229,17 @@
       <c r="L27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="N27" s="81" t="s">
+      <c r="M27" s="81" t="s">
         <v>88</v>
       </c>
       <c r="O27" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P27" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -4187,14 +4276,17 @@
       <c r="L28" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N28" s="77" t="s">
+      <c r="M28" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O28" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P28" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4231,14 +4323,17 @@
       <c r="L29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="N29" s="81" t="s">
+      <c r="M29" s="81" t="s">
         <v>88</v>
       </c>
       <c r="O29" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P29" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4275,14 +4370,17 @@
       <c r="L30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="N30" s="81" t="s">
+      <c r="M30" s="81" t="s">
         <v>88</v>
       </c>
       <c r="O30" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P30" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4319,14 +4417,17 @@
       <c r="L31" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N31" s="77" t="s">
+      <c r="M31" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O31" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P31" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4363,14 +4464,17 @@
       <c r="L32" s="77">
         <v>0.33</v>
       </c>
-      <c r="N32" s="77">
+      <c r="M32" s="77">
         <v>0.33</v>
       </c>
       <c r="O32" s="77">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P32" s="77">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4407,14 +4511,17 @@
       <c r="L33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N33" s="77" t="s">
+      <c r="M33" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O33" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P33" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4451,14 +4558,17 @@
       <c r="L34" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N34" s="77" t="s">
+      <c r="M34" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O34" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P34" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4495,14 +4605,17 @@
       <c r="L35" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N35" s="77" t="s">
+      <c r="M35" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O35" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P35" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4539,14 +4652,17 @@
       <c r="L36" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="N36" s="77" t="s">
+      <c r="M36" s="77" t="s">
         <v>87</v>
       </c>
       <c r="O36" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P36" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4583,14 +4699,17 @@
       <c r="L37" s="85" t="s">
         <v>433</v>
       </c>
-      <c r="N37" s="85" t="s">
+      <c r="M37" s="85" t="s">
         <v>433</v>
       </c>
       <c r="O37" s="85" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P37" s="85" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -4627,14 +4746,17 @@
       <c r="L38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="N38" s="80">
+      <c r="M38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="O38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -4671,14 +4793,17 @@
       <c r="L39" s="86">
         <v>1E-3</v>
       </c>
-      <c r="N39" s="86">
+      <c r="M39" s="86">
         <v>1E-3</v>
       </c>
       <c r="O39" s="86">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P39" s="86">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -4715,14 +4840,17 @@
       <c r="L40" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="N40" s="77" t="s">
+      <c r="M40" s="77" t="s">
         <v>87</v>
       </c>
       <c r="O40" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P40" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -4759,14 +4887,17 @@
       <c r="L41" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="N41" s="77" t="s">
+      <c r="M41" s="77" t="s">
         <v>89</v>
       </c>
       <c r="O41" s="77" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P41" s="77" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -4803,14 +4934,17 @@
       <c r="L42" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="N42" s="77" t="s">
+      <c r="M42" s="77" t="s">
         <v>87</v>
       </c>
       <c r="O42" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P42" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -4847,14 +4981,17 @@
       <c r="L43" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N43" s="77" t="s">
+      <c r="M43" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O43" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P43" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -4891,14 +5028,17 @@
       <c r="L44" s="77">
         <v>120</v>
       </c>
-      <c r="N44" s="77">
+      <c r="M44" s="77">
         <v>120</v>
       </c>
       <c r="O44" s="77">
         <v>120</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P44" s="77">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -4935,14 +5075,17 @@
       <c r="L45" s="77">
         <v>0</v>
       </c>
-      <c r="N45" s="77">
+      <c r="M45" s="77">
         <v>0</v>
       </c>
       <c r="O45" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P45" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -4979,14 +5122,17 @@
       <c r="L46" s="77">
         <v>0</v>
       </c>
-      <c r="N46" s="77">
+      <c r="M46" s="77">
         <v>0</v>
       </c>
       <c r="O46" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P46" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -5023,14 +5169,17 @@
       <c r="L47" s="77">
         <v>-0.1</v>
       </c>
-      <c r="N47" s="77">
+      <c r="M47" s="77">
         <v>-0.1</v>
       </c>
       <c r="O47" s="77">
         <v>-0.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P47" s="77">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -5067,14 +5216,17 @@
       <c r="L48" s="77">
         <v>-0.2</v>
       </c>
-      <c r="N48" s="77">
+      <c r="M48" s="77">
         <v>-0.2</v>
       </c>
       <c r="O48" s="77">
         <v>-0.2</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P48" s="77">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -5111,14 +5263,17 @@
       <c r="L49" s="77">
         <v>0.4</v>
       </c>
-      <c r="N49" s="77">
+      <c r="M49" s="77">
         <v>0.4</v>
       </c>
       <c r="O49" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P49" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -5155,14 +5310,17 @@
       <c r="L50" s="77">
         <v>0</v>
       </c>
-      <c r="N50" s="77">
+      <c r="M50" s="77">
         <v>0</v>
       </c>
       <c r="O50" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P50" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -5199,14 +5357,17 @@
       <c r="L51" s="77">
         <v>1200</v>
       </c>
-      <c r="N51" s="77">
+      <c r="M51" s="77">
         <v>1200</v>
       </c>
       <c r="O51" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P51" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -5243,14 +5404,17 @@
       <c r="L52" s="77">
         <v>1200</v>
       </c>
-      <c r="N52" s="77">
+      <c r="M52" s="77">
         <v>1200</v>
       </c>
       <c r="O52" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P52" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -5287,14 +5451,17 @@
       <c r="L53" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="N53" s="35" t="s">
+      <c r="M53" s="35" t="s">
         <v>460</v>
       </c>
       <c r="O53" s="35" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P53" s="35" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -5331,14 +5498,17 @@
       <c r="L54" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="N54" s="77" t="s">
+      <c r="M54" s="77" t="s">
         <v>87</v>
       </c>
       <c r="O54" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P54" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5375,14 +5545,17 @@
       <c r="L55" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="N55" s="77" t="s">
+      <c r="M55" s="77" t="s">
         <v>87</v>
       </c>
       <c r="O55" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P55" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -5419,14 +5592,17 @@
       <c r="L56" s="77">
         <v>0</v>
       </c>
-      <c r="N56" s="77">
+      <c r="M56" s="77">
         <v>0</v>
       </c>
       <c r="O56" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P56" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -5463,14 +5639,17 @@
       <c r="L57" s="77">
         <v>0.5</v>
       </c>
-      <c r="N57" s="77">
+      <c r="M57" s="77">
         <v>0.5</v>
       </c>
       <c r="O57" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P57" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -5507,14 +5686,17 @@
       <c r="L58" s="77">
         <v>0.05</v>
       </c>
-      <c r="N58" s="77">
+      <c r="M58" s="77">
         <v>0.05</v>
       </c>
       <c r="O58" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P58" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -5551,14 +5733,17 @@
       <c r="L59" s="80">
         <v>1E-3</v>
       </c>
-      <c r="N59" s="80">
+      <c r="M59" s="80">
         <v>1E-3</v>
       </c>
       <c r="O59" s="80">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P59" s="80">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -5595,14 +5780,17 @@
       <c r="L60" s="77">
         <v>0</v>
       </c>
-      <c r="N60" s="77">
+      <c r="M60" s="77">
         <v>0</v>
       </c>
       <c r="O60" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P60" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -5639,14 +5827,17 @@
       <c r="L61" s="77">
         <v>1E-4</v>
       </c>
-      <c r="N61" s="77">
+      <c r="M61" s="77">
         <v>1E-4</v>
       </c>
       <c r="O61" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P61" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -5683,14 +5874,17 @@
       <c r="L62" s="77">
         <v>1E-4</v>
       </c>
-      <c r="N62" s="77">
+      <c r="M62" s="77">
         <v>1E-4</v>
       </c>
       <c r="O62" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P62" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -5727,14 +5921,17 @@
       <c r="L63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="N63" s="77">
+      <c r="M63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="O63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -5771,14 +5968,17 @@
       <c r="L64" s="77">
         <v>1.22E-4</v>
       </c>
-      <c r="N64" s="77">
+      <c r="M64" s="77">
         <v>1.22E-4</v>
       </c>
       <c r="O64" s="77">
         <v>1.22E-4</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P64" s="77">
+        <v>1.22E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -5815,14 +6015,17 @@
       <c r="L65" s="77">
         <v>1</v>
       </c>
-      <c r="N65" s="77">
+      <c r="M65" s="77">
         <v>1</v>
       </c>
       <c r="O65" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P65" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -5859,14 +6062,17 @@
       <c r="L66" s="77">
         <v>0.95</v>
       </c>
-      <c r="N66" s="77">
+      <c r="M66" s="77">
         <v>0.95</v>
       </c>
       <c r="O66" s="77">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P66" s="77">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -5903,14 +6109,17 @@
       <c r="L67" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N67" s="77" t="s">
+      <c r="M67" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O67" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P67" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -5947,14 +6156,17 @@
       <c r="L68" s="77">
         <v>5</v>
       </c>
-      <c r="N68" s="77">
+      <c r="M68" s="77">
         <v>5</v>
       </c>
       <c r="O68" s="77">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P68" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -5991,14 +6203,17 @@
       <c r="L69" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="N69" s="77" t="s">
+      <c r="M69" s="77" t="s">
         <v>88</v>
       </c>
       <c r="O69" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P69" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -6035,14 +6250,17 @@
       <c r="L70" s="77">
         <v>50</v>
       </c>
-      <c r="N70" s="77">
+      <c r="M70" s="77">
         <v>50</v>
       </c>
       <c r="O70" s="77">
         <v>50</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P70" s="77">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -6079,14 +6297,17 @@
       <c r="L71" s="78">
         <v>1453890.8941884842</v>
       </c>
-      <c r="N71" s="78">
+      <c r="M71" s="78">
         <v>1453890.8941884842</v>
       </c>
       <c r="O71" s="78">
         <v>1453890.8941884842</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -6123,14 +6344,17 @@
       <c r="L72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-      <c r="N72" s="78">
+      <c r="M72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
       <c r="O72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -6167,14 +6391,17 @@
       <c r="L73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-      <c r="N73" s="79">
+      <c r="M73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
       <c r="O73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -6211,14 +6438,17 @@
       <c r="L74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-      <c r="N74" s="85">
+      <c r="M74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
       <c r="O74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -6253,16 +6483,20 @@
         <v>282528</v>
       </c>
       <c r="L75" s="79">
+        <f>282528</f>
         <v>282528</v>
       </c>
-      <c r="N75" s="79">
+      <c r="M75" s="79">
         <v>282528</v>
       </c>
       <c r="O75" s="79">
         <v>282528</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P75" s="79">
+        <v>282528</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -6299,14 +6533,17 @@
       <c r="L76" s="85">
         <v>0.56999999999999995</v>
       </c>
-      <c r="N76" s="85">
+      <c r="M76" s="85">
         <v>0.56999999999999995</v>
       </c>
       <c r="O76" s="85">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -6343,14 +6580,17 @@
       <c r="L77" s="87">
         <v>0.16</v>
       </c>
-      <c r="N77" s="87">
+      <c r="M77" s="87">
         <v>0.16</v>
       </c>
       <c r="O77" s="87">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P77" s="87">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -6387,14 +6627,17 @@
       <c r="L78" s="77">
         <v>0</v>
       </c>
-      <c r="N78" s="77">
+      <c r="M78" s="77">
         <v>0</v>
       </c>
       <c r="O78" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P78" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -6431,14 +6674,17 @@
       <c r="L79" s="78">
         <v>745476480000</v>
       </c>
-      <c r="N79" s="78">
+      <c r="M79" s="78">
         <v>745476480000</v>
       </c>
       <c r="O79" s="78">
         <v>745476480000</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P79" s="78">
+        <v>745476480000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -6475,14 +6721,17 @@
       <c r="L80" s="77">
         <v>100</v>
       </c>
-      <c r="N80" s="77">
+      <c r="M80" s="77">
         <v>100</v>
       </c>
       <c r="O80" s="77">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P80" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -6517,16 +6766,19 @@
         <v>88</v>
       </c>
       <c r="L81" s="77" t="s">
-        <v>88</v>
-      </c>
-      <c r="N81" s="77" t="s">
-        <v>88</v>
+        <v>87</v>
+      </c>
+      <c r="M81" s="77" t="s">
+        <v>87</v>
       </c>
       <c r="O81" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P81" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -6563,14 +6815,17 @@
       <c r="L82" s="85">
         <v>21600</v>
       </c>
-      <c r="N82" s="85">
+      <c r="M82" s="85">
         <v>21600</v>
       </c>
       <c r="O82" s="85">
         <v>21600</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P82" s="85">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -6607,14 +6862,17 @@
       <c r="L83" s="77">
         <v>0.5</v>
       </c>
-      <c r="N83" s="77">
+      <c r="M83" s="77">
         <v>0.5</v>
       </c>
       <c r="O83" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P83" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -6651,14 +6909,17 @@
       <c r="L84" s="85">
         <v>60479.999999999993</v>
       </c>
-      <c r="N84" s="85">
+      <c r="M84" s="85">
         <v>60479.999999999993</v>
       </c>
       <c r="O84" s="85">
         <v>60479.999999999993</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -6695,14 +6956,17 @@
       <c r="L85" s="77">
         <v>0.85</v>
       </c>
-      <c r="N85" s="77">
+      <c r="M85" s="77">
         <v>0.85</v>
       </c>
       <c r="O85" s="77">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P85" s="77">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -6739,14 +7003,17 @@
       <c r="L86" s="77">
         <v>518400</v>
       </c>
-      <c r="N86" s="77">
+      <c r="M86" s="77">
         <v>518400</v>
       </c>
       <c r="O86" s="77">
         <v>518400</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P86" s="77">
+        <v>518400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -6783,14 +7050,17 @@
       <c r="L87" s="77">
         <v>5184000</v>
       </c>
-      <c r="N87" s="77">
+      <c r="M87" s="77">
         <v>5184000</v>
       </c>
       <c r="O87" s="77">
         <v>5184000</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P87" s="77">
+        <v>5184000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -6827,14 +7097,17 @@
       <c r="L88" s="86">
         <v>50000</v>
       </c>
-      <c r="N88" s="86">
+      <c r="M88" s="86">
         <v>50000</v>
       </c>
       <c r="O88" s="86">
         <v>50000</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P88" s="86">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -6871,14 +7144,17 @@
       <c r="L89" s="77">
         <v>140000</v>
       </c>
-      <c r="N89" s="77">
+      <c r="M89" s="77">
         <v>140000</v>
       </c>
       <c r="O89" s="77">
         <v>140000</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P89" s="77">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -6915,14 +7191,17 @@
       <c r="L90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-      <c r="N90" s="78">
+      <c r="M90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
       <c r="O90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -6959,14 +7238,17 @@
       <c r="L91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="N91" s="77">
+      <c r="M91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="O91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -7003,14 +7285,17 @@
       <c r="L92" s="77">
         <v>0.05</v>
       </c>
-      <c r="N92" s="77">
+      <c r="M92" s="77">
         <v>0.05</v>
       </c>
       <c r="O92" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P92" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -7047,14 +7332,17 @@
       <c r="L93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="N93" s="77">
+      <c r="M93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
       <c r="O93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -7091,14 +7379,17 @@
       <c r="L94" s="77">
         <v>1E-3</v>
       </c>
-      <c r="N94" s="77">
-        <v>0</v>
+      <c r="M94" s="77">
+        <v>1E-3</v>
       </c>
       <c r="O94" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P94" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -7135,14 +7426,17 @@
       <c r="L95" s="77">
         <v>374999999.99999994</v>
       </c>
-      <c r="N95" s="77">
+      <c r="M95" s="77">
         <v>374999999.99999994</v>
       </c>
       <c r="O95" s="77">
         <v>374999999.99999994</v>
       </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -7179,14 +7473,17 @@
       <c r="L96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="N96" s="78">
+      <c r="M96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
       <c r="O96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -7223,14 +7520,17 @@
       <c r="L97" s="77">
         <v>165600</v>
       </c>
-      <c r="N97" s="77">
+      <c r="M97" s="77">
         <v>165600</v>
       </c>
       <c r="O97" s="77">
         <v>165600</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P97" s="77">
+        <v>165600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -7267,14 +7567,17 @@
       <c r="L98" s="77">
         <v>20</v>
       </c>
-      <c r="N98" s="77">
+      <c r="M98" s="77">
         <v>20</v>
       </c>
       <c r="O98" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P98" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -7311,14 +7614,17 @@
       <c r="L99" s="77">
         <v>1</v>
       </c>
-      <c r="N99" s="77">
+      <c r="M99" s="77">
         <v>1</v>
       </c>
       <c r="O99" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P99" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -7355,14 +7661,17 @@
       <c r="L100" s="77">
         <v>21</v>
       </c>
-      <c r="N100" s="77">
+      <c r="M100" s="77">
         <v>21</v>
       </c>
       <c r="O100" s="77">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P100" s="77">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -7399,14 +7708,17 @@
       <c r="L101" s="77">
         <v>0.64</v>
       </c>
-      <c r="N101" s="77">
+      <c r="M101" s="77">
         <v>0.64</v>
       </c>
       <c r="O101" s="77">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P101" s="77">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -7443,14 +7755,17 @@
       <c r="L102" s="77">
         <v>8</v>
       </c>
-      <c r="N102" s="77">
+      <c r="M102" s="77">
         <v>8</v>
       </c>
       <c r="O102" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P102" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -7487,14 +7802,17 @@
       <c r="L103" s="77">
         <v>10</v>
       </c>
-      <c r="N103" s="77">
+      <c r="M103" s="77">
         <v>10</v>
       </c>
       <c r="O103" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P103" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -7531,14 +7849,17 @@
       <c r="L104" s="77">
         <v>8</v>
       </c>
-      <c r="N104" s="77">
+      <c r="M104" s="77">
         <v>8</v>
       </c>
       <c r="O104" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P104" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="23" t="s">
         <v>500</v>
       </c>
@@ -7575,14 +7896,17 @@
       <c r="L105" s="77">
         <v>1</v>
       </c>
-      <c r="N105" s="77">
+      <c r="M105" s="77">
         <v>1</v>
       </c>
       <c r="O105" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P105" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -7619,14 +7943,17 @@
       <c r="L106" s="77">
         <v>0.5</v>
       </c>
-      <c r="N106" s="77">
+      <c r="M106" s="77">
         <v>0.5</v>
       </c>
       <c r="O106" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P106" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="23" t="s">
         <v>501</v>
       </c>
@@ -7669,14 +7996,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="N107" s="58">
+      <c r="M107" s="58">
+        <f t="shared" ref="M107" si="2">M105</f>
         <v>1</v>
       </c>
       <c r="O107" s="58">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P107" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="23" t="s">
         <v>502</v>
       </c>
@@ -7700,33 +8031,37 @@
         <v>3</v>
       </c>
       <c r="H108" s="58">
-        <f>150*H105</f>
+        <f t="shared" ref="H108:M108" si="3">150*H105</f>
         <v>150</v>
       </c>
       <c r="I108" s="58">
-        <f>150*I105</f>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
       <c r="J108" s="58">
-        <f>150*J105</f>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
       <c r="K108" s="58">
-        <f>150*K105</f>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
       <c r="L108" s="58">
-        <f>150*L105</f>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
-      <c r="N108" s="58">
+      <c r="M108" s="58">
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
       <c r="O108" s="58">
         <v>150</v>
       </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P108" s="58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="23" t="s">
         <v>503</v>
       </c>
@@ -7746,37 +8081,41 @@
         <v>506</v>
       </c>
       <c r="G109" s="58">
-        <f t="shared" ref="G109:L109" si="2">G100</f>
+        <f t="shared" ref="G109:L109" si="4">G100</f>
         <v>21</v>
       </c>
       <c r="H109" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="I109" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="J109" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="K109" s="58">
-        <f t="shared" ref="K109" si="3">K100</f>
+        <f t="shared" ref="K109" si="5">K100</f>
         <v>21</v>
       </c>
       <c r="L109" s="58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="N109" s="58">
+      <c r="M109" s="58">
+        <f t="shared" ref="M109" si="6">M100</f>
         <v>21</v>
       </c>
       <c r="O109" s="58">
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P109" s="58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="23" t="s">
         <v>504</v>
       </c>
@@ -7800,33 +8139,37 @@
         <v>210</v>
       </c>
       <c r="H110" s="58">
-        <f>70*H100</f>
+        <f t="shared" ref="H110:M110" si="7">70*H100</f>
         <v>1470</v>
       </c>
       <c r="I110" s="58">
-        <f>70*I100</f>
+        <f t="shared" si="7"/>
         <v>1470</v>
       </c>
       <c r="J110" s="58">
-        <f>70*J100</f>
+        <f t="shared" si="7"/>
         <v>1470</v>
       </c>
       <c r="K110" s="58">
-        <f>70*K100</f>
+        <f t="shared" si="7"/>
         <v>1470</v>
       </c>
       <c r="L110" s="58">
-        <f>70*L100</f>
+        <f t="shared" si="7"/>
         <v>1470</v>
       </c>
-      <c r="N110" s="58">
+      <c r="M110" s="58">
+        <f t="shared" si="7"/>
         <v>1470</v>
       </c>
       <c r="O110" s="58">
         <v>1470</v>
       </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P110" s="58">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -7863,14 +8206,17 @@
       <c r="L111" s="77">
         <v>0</v>
       </c>
-      <c r="N111" s="77">
+      <c r="M111" s="77">
         <v>0</v>
       </c>
       <c r="O111" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P111" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -7907,14 +8253,17 @@
       <c r="L112" s="82">
         <v>1589759.9999999998</v>
       </c>
-      <c r="N112" s="82">
+      <c r="M112" s="82">
         <v>1589759.9999999998</v>
       </c>
       <c r="O112" s="82">
         <v>1589759.9999999998</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -7951,14 +8300,17 @@
       <c r="L113" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="N113" s="82">
+      <c r="M113" s="82">
         <v>6171428.5714285718</v>
       </c>
       <c r="O113" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -7995,14 +8347,17 @@
       <c r="L114" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="N114" s="82">
+      <c r="M114" s="82">
         <v>6171428.5714285718</v>
       </c>
       <c r="O114" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -8039,14 +8394,17 @@
       <c r="L115" s="82">
         <v>100</v>
       </c>
-      <c r="N115" s="82">
+      <c r="M115" s="82">
         <v>100</v>
       </c>
       <c r="O115" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P115" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -8070,33 +8428,37 @@
         <v>280800</v>
       </c>
       <c r="H116" s="67">
-        <f>0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" ref="H116:M116" si="8">0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
       <c r="I116" s="67">
-        <f>0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" si="8"/>
         <v>28080</v>
       </c>
       <c r="J116" s="67">
-        <f>0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" si="8"/>
         <v>28080</v>
       </c>
       <c r="K116" s="67">
-        <f>0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" si="8"/>
         <v>28080</v>
       </c>
       <c r="L116" s="67">
-        <f>0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" si="8"/>
         <v>28080</v>
       </c>
-      <c r="N116" s="67">
+      <c r="M116" s="67">
+        <f t="shared" si="8"/>
         <v>28080</v>
       </c>
       <c r="O116" s="67">
         <v>28080</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P116" s="67">
+        <v>28080</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -8120,33 +8482,37 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H117" s="67">
-        <f>1.11 / 10</f>
+        <f t="shared" ref="H117:M117" si="9">1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
       <c r="I117" s="67">
-        <f>1.11 / 10</f>
+        <f t="shared" si="9"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="J117" s="67">
-        <f>1.11 / 10</f>
+        <f t="shared" si="9"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="K117" s="67">
-        <f>1.11 / 10</f>
+        <f t="shared" si="9"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="L117" s="67">
-        <f>1.11 / 10</f>
+        <f t="shared" si="9"/>
         <v>0.11100000000000002</v>
       </c>
-      <c r="N117" s="67">
+      <c r="M117" s="67">
+        <f t="shared" si="9"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="O117" s="67">
         <v>0.11100000000000002</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P117" s="67">
+        <v>0.11100000000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="23" t="s">
         <v>497</v>
       </c>
@@ -8183,14 +8549,17 @@
       <c r="L118" s="82">
         <v>100</v>
       </c>
-      <c r="N118" s="82">
+      <c r="M118" s="82">
         <v>100</v>
       </c>
       <c r="O118" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="119" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P118" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="23" t="s">
         <v>498</v>
       </c>
@@ -8210,37 +8579,41 @@
         <v>431</v>
       </c>
       <c r="G119" s="67">
-        <f t="shared" ref="G119:L119" si="4">5.32 * (60*60*24)</f>
+        <f t="shared" ref="G119:M119" si="10">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H119" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>459648</v>
       </c>
       <c r="I119" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>459648</v>
       </c>
       <c r="J119" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>459648</v>
       </c>
       <c r="K119" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>459648</v>
       </c>
       <c r="L119" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>459648</v>
       </c>
-      <c r="N119" s="67">
+      <c r="M119" s="67">
+        <f t="shared" si="10"/>
         <v>459648</v>
       </c>
       <c r="O119" s="67">
         <v>459648</v>
       </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P119" s="67">
+        <v>459648</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="23" t="s">
         <v>499</v>
       </c>
@@ -8264,33 +8637,37 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H120" s="67">
-        <f>1.11/8</f>
+        <f t="shared" ref="H120:M120" si="11">1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
       <c r="I120" s="67">
-        <f>1.11/8</f>
+        <f t="shared" si="11"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="J120" s="67">
-        <f>1.11/8</f>
+        <f t="shared" si="11"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="K120" s="67">
-        <f>1.11/8</f>
+        <f t="shared" si="11"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="L120" s="67">
-        <f>1.11/8</f>
+        <f t="shared" si="11"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="N120" s="67">
+      <c r="M120" s="67">
+        <f t="shared" si="11"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="O120" s="67">
         <v>0.13875000000000001</v>
       </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P120" s="67">
+        <v>0.13875000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -8327,14 +8704,17 @@
       <c r="L121" s="82">
         <v>21600</v>
       </c>
-      <c r="N121" s="82">
+      <c r="M121" s="82">
         <v>21600</v>
       </c>
       <c r="O121" s="82">
         <v>21600</v>
       </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P121" s="82">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -8371,14 +8751,17 @@
       <c r="L122" s="88">
         <v>43200</v>
       </c>
-      <c r="N122" s="88">
+      <c r="M122" s="88">
         <v>43200</v>
       </c>
       <c r="O122" s="88">
         <v>43200</v>
       </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P122" s="88">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -8415,14 +8798,17 @@
       <c r="L123" s="77">
         <v>0.8</v>
       </c>
-      <c r="N123" s="77">
+      <c r="M123" s="77">
         <v>0.8</v>
       </c>
       <c r="O123" s="77">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P123" s="77">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -8460,14 +8846,17 @@
       <c r="L124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="N124" s="78">
+      <c r="M124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
       <c r="O124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P124" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -8504,14 +8893,17 @@
       <c r="L125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-      <c r="N125" s="77">
+      <c r="M125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
       <c r="O125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P125" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -8548,14 +8940,17 @@
       <c r="L126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="N126" s="78">
+      <c r="M126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
       <c r="O126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P126" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -8592,14 +8987,17 @@
       <c r="L127" s="78">
         <v>0</v>
       </c>
-      <c r="N127" s="78">
+      <c r="M127" s="78">
         <v>0</v>
       </c>
       <c r="O127" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P127" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -8636,14 +9034,17 @@
       <c r="L128" s="78">
         <v>0</v>
       </c>
-      <c r="N128" s="78">
+      <c r="M128" s="78">
         <v>0</v>
       </c>
       <c r="O128" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P128" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -8668,11 +9069,11 @@
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="I129" s="83">
-        <f t="shared" ref="I129:O129" si="5">0.0000002*3</f>
+        <f t="shared" ref="I129:P129" si="12">0.0000002*3</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J129" s="83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="K129" s="83">
@@ -8683,16 +9084,22 @@
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="N129" s="83">
-        <f t="shared" si="5"/>
+      <c r="M129" s="83">
+        <v>0</v>
+      </c>
+      <c r="N129" s="102">
+        <v>0</v>
+      </c>
+      <c r="O129" s="83">
+        <f t="shared" si="12"/>
         <v>5.9999999999999997E-7</v>
       </c>
-      <c r="O129" s="83">
-        <f t="shared" si="5"/>
+      <c r="P129" s="83">
+        <f t="shared" si="12"/>
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -8713,35 +9120,39 @@
       </c>
       <c r="G130" s="71"/>
       <c r="H130" s="83">
-        <f t="shared" ref="H130:O130" si="6">1000 * 0.000001 / 12</f>
+        <f t="shared" ref="H130:P130" si="13">1000 * 0.000001 / 12</f>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="I130" s="83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="J130" s="83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="K130" s="83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="L130" s="83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="N130" s="83">
-        <f t="shared" si="6"/>
+      <c r="M130" s="83">
+        <f t="shared" si="13"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="O130" s="83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P130" s="83">
+        <f t="shared" si="13"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -8778,14 +9189,17 @@
       <c r="L131" s="89" t="s">
         <v>533</v>
       </c>
-      <c r="N131" s="89" t="s">
+      <c r="M131" s="89" t="s">
         <v>533</v>
       </c>
       <c r="O131" s="89" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P131" s="89" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -8824,14 +9238,20 @@
         <f>0.0005 * 1.2</f>
         <v>5.9999999999999995E-4</v>
       </c>
+      <c r="M132" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
       <c r="N132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="O132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P132" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -8868,14 +9288,17 @@
       <c r="L133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="N133" s="83">
+      <c r="M133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
       <c r="O133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P133" s="83">
+        <v>4.9999999999999999E-13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -8912,14 +9335,17 @@
       <c r="L134" s="77">
         <v>10</v>
       </c>
-      <c r="N134" s="77">
+      <c r="M134" s="77">
         <v>10</v>
       </c>
       <c r="O134" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P134" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -8956,14 +9382,17 @@
       <c r="L135" s="77">
         <v>-0.04</v>
       </c>
-      <c r="N135" s="77">
+      <c r="M135" s="77">
         <v>-0.04</v>
       </c>
       <c r="O135" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P135" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -9000,14 +9429,17 @@
       <c r="L136" s="77">
         <v>2.9</v>
       </c>
-      <c r="N136" s="77">
+      <c r="M136" s="77">
         <v>2.9</v>
       </c>
       <c r="O136" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P136" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -9044,14 +9476,17 @@
       <c r="L137" s="77">
         <v>1</v>
       </c>
-      <c r="N137" s="77">
+      <c r="M137" s="77">
         <v>1</v>
       </c>
       <c r="O137" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P137" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
         <v>574</v>
       </c>
@@ -9090,14 +9525,20 @@
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="N138" s="80">
+      <c r="M138" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
+      <c r="N138" s="101">
         <v>1.9999999999999999E-7</v>
       </c>
       <c r="O138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P138" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -9134,14 +9575,17 @@
       <c r="L139" s="77">
         <v>10</v>
       </c>
-      <c r="N139" s="77">
+      <c r="M139" s="77">
         <v>10</v>
       </c>
       <c r="O139" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P139" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -9178,14 +9622,17 @@
       <c r="L140" s="77">
         <v>-0.04</v>
       </c>
-      <c r="N140" s="77">
+      <c r="M140" s="77">
         <v>-0.04</v>
       </c>
       <c r="O140" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P140" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -9222,14 +9669,17 @@
       <c r="L141" s="77">
         <v>2.9</v>
       </c>
-      <c r="N141" s="77">
+      <c r="M141" s="77">
         <v>2.9</v>
       </c>
       <c r="O141" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P141" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -9266,14 +9716,17 @@
       <c r="L142" s="77">
         <v>1</v>
       </c>
-      <c r="N142" s="77">
+      <c r="M142" s="77">
         <v>1</v>
       </c>
       <c r="O142" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P142" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -9310,14 +9763,17 @@
       <c r="L143" s="77">
         <v>0</v>
       </c>
-      <c r="N143" s="77">
+      <c r="M143" s="77">
         <v>0</v>
       </c>
       <c r="O143" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P143" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -9354,14 +9810,17 @@
       <c r="L144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="N144" s="80">
+      <c r="M144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="O144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P144" s="80">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -9398,14 +9857,17 @@
       <c r="L145" s="77">
         <v>0</v>
       </c>
-      <c r="N145" s="77">
+      <c r="M145" s="77">
         <v>0</v>
       </c>
       <c r="O145" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P145" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -9442,14 +9904,17 @@
       <c r="L146" s="77">
         <v>2E-3</v>
       </c>
-      <c r="N146" s="77">
+      <c r="M146" s="77">
         <v>2E-3</v>
       </c>
       <c r="O146" s="77">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P146" s="77">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -9486,14 +9951,17 @@
       <c r="L147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-      <c r="N147" s="80">
+      <c r="M147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
       <c r="O147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P147" s="80">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -9530,14 +9998,17 @@
       <c r="L148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-      <c r="N148" s="80">
+      <c r="M148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
       <c r="O148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P148" s="80">
+        <v>3.7699999999999999E-10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -9574,14 +10045,17 @@
       <c r="L149" s="77">
         <v>20</v>
       </c>
-      <c r="N149" s="77">
+      <c r="M149" s="77">
         <v>20</v>
       </c>
       <c r="O149" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P149" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -9618,14 +10092,17 @@
       <c r="L150" s="77">
         <v>-0.06</v>
       </c>
-      <c r="N150" s="77">
+      <c r="M150" s="77">
         <v>-0.06</v>
       </c>
       <c r="O150" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P150" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -9662,14 +10139,17 @@
       <c r="L151" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="N151" s="77">
+      <c r="M151" s="77">
         <v>0.89100000000000001</v>
       </c>
       <c r="O151" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P151" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -9706,14 +10186,17 @@
       <c r="L152" s="77">
         <v>1</v>
       </c>
-      <c r="N152" s="77">
+      <c r="M152" s="77">
         <v>1</v>
       </c>
       <c r="O152" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P152" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -9750,14 +10233,17 @@
       <c r="L153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="N153" s="80">
+      <c r="M153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="O153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P153" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -9794,14 +10280,17 @@
       <c r="L154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-      <c r="N154" s="80">
+      <c r="M154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
       <c r="O154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P154" s="80">
+        <v>5.8333333333333335E-9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -9838,14 +10327,17 @@
       <c r="L155" s="77">
         <v>20</v>
       </c>
-      <c r="N155" s="77">
+      <c r="M155" s="77">
         <v>20</v>
       </c>
       <c r="O155" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P155" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -9882,14 +10374,17 @@
       <c r="L156" s="77">
         <v>-0.06</v>
       </c>
-      <c r="N156" s="77">
+      <c r="M156" s="77">
         <v>-0.06</v>
       </c>
       <c r="O156" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P156" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -9926,14 +10421,17 @@
       <c r="L157" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="N157" s="77">
+      <c r="M157" s="77">
         <v>0.89100000000000001</v>
       </c>
       <c r="O157" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P157" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -9970,14 +10468,17 @@
       <c r="L158" s="77">
         <v>1</v>
       </c>
-      <c r="N158" s="77">
+      <c r="M158" s="77">
         <v>1</v>
       </c>
       <c r="O158" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P158" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -10014,14 +10515,17 @@
       <c r="L159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="N159" s="80">
+      <c r="M159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="O159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P159" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -10058,14 +10562,17 @@
       <c r="L160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="N160" s="83">
+      <c r="M160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="O160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P160" s="83">
+        <v>4.0000000000000001E-8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -10102,14 +10609,17 @@
       <c r="L161" s="77">
         <v>20</v>
       </c>
-      <c r="N161" s="77">
+      <c r="M161" s="77">
         <v>20</v>
       </c>
       <c r="O161" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P161" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -10146,14 +10656,17 @@
       <c r="L162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-      <c r="N162" s="77">
+      <c r="M162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
       <c r="O162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P162" s="77">
+        <v>-4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -10190,14 +10703,17 @@
       <c r="L163" s="77">
         <v>1.55</v>
       </c>
-      <c r="N163" s="77">
+      <c r="M163" s="77">
         <v>1.55</v>
       </c>
       <c r="O163" s="77">
         <v>1.55</v>
       </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P163" s="77">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -10234,14 +10750,17 @@
       <c r="L164" s="77">
         <v>1</v>
       </c>
-      <c r="N164" s="77">
+      <c r="M164" s="77">
         <v>1</v>
       </c>
       <c r="O164" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P164" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -10278,14 +10797,17 @@
       <c r="L165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="N165" s="77">
+      <c r="M165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
       <c r="O165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P165" s="77">
+        <v>2.7799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -10322,14 +10844,17 @@
       <c r="L166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="N166" s="84">
+      <c r="M166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="O166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P166" s="84">
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -10366,14 +10891,17 @@
       <c r="L167" s="77">
         <v>20</v>
       </c>
-      <c r="N167" s="77">
+      <c r="M167" s="77">
         <v>20</v>
       </c>
       <c r="O167" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P167" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -10410,14 +10938,17 @@
       <c r="L168" s="77">
         <v>0</v>
       </c>
-      <c r="N168" s="77">
+      <c r="M168" s="77">
         <v>0</v>
       </c>
       <c r="O168" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P168" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -10454,14 +10985,17 @@
       <c r="L169" s="77">
         <v>1</v>
       </c>
-      <c r="N169" s="77">
+      <c r="M169" s="77">
         <v>1</v>
       </c>
       <c r="O169" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P169" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -10498,14 +11032,17 @@
       <c r="L170" s="77">
         <v>0</v>
       </c>
-      <c r="N170" s="77">
+      <c r="M170" s="77">
         <v>0</v>
       </c>
       <c r="O170" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P170" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -10542,14 +11079,17 @@
       <c r="L171" s="77">
         <v>0.4</v>
       </c>
-      <c r="N171" s="77">
+      <c r="M171" s="77">
         <v>0.4</v>
       </c>
       <c r="O171" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P171" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -10586,14 +11126,17 @@
       <c r="L172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-      <c r="N172" s="86">
+      <c r="M172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
       <c r="O172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P172" s="86">
+        <v>2.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -10630,14 +11173,17 @@
       <c r="L173" s="77">
         <v>25</v>
       </c>
-      <c r="N173" s="77">
+      <c r="M173" s="77">
         <v>25</v>
       </c>
       <c r="O173" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P173" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -10674,14 +11220,17 @@
       <c r="L174" s="77">
         <v>0</v>
       </c>
-      <c r="N174" s="77">
+      <c r="M174" s="77">
         <v>0</v>
       </c>
       <c r="O174" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P174" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -10718,14 +11267,17 @@
       <c r="L175" s="77">
         <v>3.98</v>
       </c>
-      <c r="N175" s="77">
+      <c r="M175" s="77">
         <v>3.98</v>
       </c>
       <c r="O175" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P175" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -10762,14 +11314,17 @@
       <c r="L176" s="77">
         <v>1</v>
       </c>
-      <c r="N176" s="77">
+      <c r="M176" s="77">
         <v>1</v>
       </c>
       <c r="O176" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P176" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -10806,14 +11361,17 @@
       <c r="L177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-      <c r="N177" s="78">
+      <c r="M177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
       <c r="O177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P177" s="78">
+        <v>1.6666666666666666E-4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -10850,14 +11408,17 @@
       <c r="L178" s="80">
         <v>1E-8</v>
       </c>
-      <c r="N178" s="80">
+      <c r="M178" s="80">
         <v>1E-8</v>
       </c>
       <c r="O178" s="80">
         <v>1E-8</v>
       </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P178" s="80">
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -10894,14 +11455,17 @@
       <c r="L179" s="77">
         <v>20</v>
       </c>
-      <c r="N179" s="77">
+      <c r="M179" s="77">
         <v>20</v>
       </c>
       <c r="O179" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P179" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -10938,14 +11502,17 @@
       <c r="L180" s="77">
         <v>0</v>
       </c>
-      <c r="N180" s="77">
+      <c r="M180" s="77">
         <v>0</v>
       </c>
       <c r="O180" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P180" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -10982,14 +11549,17 @@
       <c r="L181" s="77">
         <v>2</v>
       </c>
-      <c r="N181" s="77">
+      <c r="M181" s="77">
         <v>2</v>
       </c>
       <c r="O181" s="77">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P181" s="77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -11026,14 +11596,17 @@
       <c r="L182" s="77">
         <v>1</v>
       </c>
-      <c r="N182" s="77">
+      <c r="M182" s="77">
         <v>1</v>
       </c>
       <c r="O182" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P182" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -11070,14 +11643,17 @@
       <c r="L183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="N183" s="78">
+      <c r="M183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="O183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P183" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -11114,14 +11690,17 @@
       <c r="L184" s="77">
         <v>1</v>
       </c>
-      <c r="N184" s="77">
+      <c r="M184" s="77">
         <v>1</v>
       </c>
       <c r="O184" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P184" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -11158,14 +11737,17 @@
       <c r="L185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-      <c r="N185" s="77">
+      <c r="M185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
       <c r="O185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P185" s="77">
+        <v>2.3533050791148899E-8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -11202,14 +11784,17 @@
       <c r="L186" s="77">
         <v>20</v>
       </c>
-      <c r="N186" s="77">
+      <c r="M186" s="77">
         <v>20</v>
       </c>
       <c r="O186" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P186" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -11246,14 +11831,17 @@
       <c r="L187" s="77">
         <v>-0.187</v>
       </c>
-      <c r="N187" s="77">
+      <c r="M187" s="77">
         <v>-0.187</v>
       </c>
       <c r="O187" s="77">
         <v>-0.187</v>
       </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P187" s="77">
+        <v>-0.187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -11290,14 +11878,17 @@
       <c r="L188" s="77">
         <v>2.48</v>
       </c>
-      <c r="N188" s="77">
+      <c r="M188" s="77">
         <v>2.48</v>
       </c>
       <c r="O188" s="77">
         <v>2.48</v>
       </c>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P188" s="77">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -11334,14 +11925,17 @@
       <c r="L189" s="77">
         <v>1</v>
       </c>
-      <c r="N189" s="77">
+      <c r="M189" s="77">
         <v>1</v>
       </c>
       <c r="O189" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P189" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -11378,14 +11972,17 @@
       <c r="L190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-      <c r="N190" s="77">
+      <c r="M190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
       <c r="O190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P190" s="77">
+        <v>6.1060227588121015E-4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -11422,14 +12019,17 @@
       <c r="L191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="N191" s="85">
+      <c r="M191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
       <c r="O191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P191" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -11466,14 +12066,17 @@
       <c r="L192" s="77">
         <v>25</v>
       </c>
-      <c r="N192" s="77">
+      <c r="M192" s="77">
         <v>25</v>
       </c>
       <c r="O192" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P192" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -11510,14 +12113,17 @@
       <c r="L193" s="77">
         <v>0</v>
       </c>
-      <c r="N193" s="77">
+      <c r="M193" s="77">
         <v>0</v>
       </c>
       <c r="O193" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P193" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -11554,14 +12160,17 @@
       <c r="L194" s="77">
         <v>3.98</v>
       </c>
-      <c r="N194" s="77">
+      <c r="M194" s="77">
         <v>3.98</v>
       </c>
       <c r="O194" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P194" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -11598,14 +12207,17 @@
       <c r="L195" s="77">
         <v>1</v>
       </c>
-      <c r="N195" s="77">
+      <c r="M195" s="77">
         <v>1</v>
       </c>
       <c r="O195" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P195" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -11642,14 +12254,17 @@
       <c r="L196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="N196" s="78">
+      <c r="M196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="O196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P196" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -11686,14 +12301,17 @@
       <c r="L197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="N197" s="85">
+      <c r="M197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
       <c r="O197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P197" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -11730,14 +12348,17 @@
       <c r="L198" s="77">
         <v>25</v>
       </c>
-      <c r="N198" s="77">
+      <c r="M198" s="77">
         <v>25</v>
       </c>
       <c r="O198" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P198" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -11774,14 +12395,17 @@
       <c r="L199" s="77">
         <v>0</v>
       </c>
-      <c r="N199" s="77">
+      <c r="M199" s="77">
         <v>0</v>
       </c>
       <c r="O199" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P199" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -11818,14 +12442,17 @@
       <c r="L200" s="77">
         <v>3.98</v>
       </c>
-      <c r="N200" s="77">
+      <c r="M200" s="77">
         <v>3.98</v>
       </c>
       <c r="O200" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P200" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -11862,14 +12489,17 @@
       <c r="L201" s="77">
         <v>1</v>
       </c>
-      <c r="N201" s="77">
+      <c r="M201" s="77">
         <v>1</v>
       </c>
       <c r="O201" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P201" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -11906,14 +12536,17 @@
       <c r="L202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="N202" s="78">
+      <c r="M202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="O202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P202" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -11950,14 +12583,17 @@
       <c r="L203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="N203" s="85">
+      <c r="M203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
       <c r="O203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P203" s="85">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -11994,14 +12630,17 @@
       <c r="L204" s="77">
         <v>25</v>
       </c>
-      <c r="N204" s="77">
+      <c r="M204" s="77">
         <v>25</v>
       </c>
       <c r="O204" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P204" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -12038,14 +12677,17 @@
       <c r="L205" s="77">
         <v>0</v>
       </c>
-      <c r="N205" s="77">
+      <c r="M205" s="77">
         <v>0</v>
       </c>
       <c r="O205" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P205" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -12082,14 +12724,17 @@
       <c r="L206" s="77">
         <v>3.98</v>
       </c>
-      <c r="N206" s="77">
+      <c r="M206" s="77">
         <v>3.98</v>
       </c>
       <c r="O206" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P206" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -12126,14 +12771,17 @@
       <c r="L207" s="77">
         <v>1</v>
       </c>
-      <c r="N207" s="77">
+      <c r="M207" s="77">
         <v>1</v>
       </c>
       <c r="O207" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P207" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -12170,14 +12818,17 @@
       <c r="L208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="N208" s="78">
+      <c r="M208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="O208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P208" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -12214,14 +12865,17 @@
       <c r="L209" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="N209" s="95" t="s">
+      <c r="M209" s="95" t="s">
         <v>90</v>
       </c>
       <c r="O209" s="95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="210" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P209" s="95" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>557</v>
       </c>
@@ -12244,15 +12898,15 @@
         <v>0.5</v>
       </c>
       <c r="H210" s="83">
-        <f t="shared" ref="H210:J210" si="7">0.00002</f>
+        <f t="shared" ref="H210:J210" si="14">0.00002</f>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="I210" s="83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="J210" s="83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="K210" s="83">
@@ -12263,15 +12917,19 @@
         <f>0.00005 / 100</f>
         <v>4.9999999999999998E-7</v>
       </c>
-      <c r="M210" s="1"/>
-      <c r="N210" s="2">
-        <v>0.01</v>
-      </c>
+      <c r="M210" s="83">
+        <f>0.00005 / 100</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="N210" s="1"/>
       <c r="O210" s="2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="211" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P210" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>560</v>
       </c>
@@ -12308,15 +12966,18 @@
       <c r="L211" s="83">
         <v>0.1</v>
       </c>
-      <c r="M211" s="1"/>
-      <c r="N211" s="99">
-        <v>0</v>
-      </c>
+      <c r="M211" s="83">
+        <v>0.1</v>
+      </c>
+      <c r="N211" s="1"/>
       <c r="O211" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P211" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>563</v>
       </c>
@@ -12339,33 +13000,37 @@
         <v>0.5</v>
       </c>
       <c r="H212" s="83">
-        <f t="shared" ref="H212:L212" si="8">0.00002 / 14</f>
+        <f t="shared" ref="H212:M212" si="15">0.00002 / 14</f>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="I212" s="83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="J212" s="83">
         <v>2E-3</v>
       </c>
       <c r="K212" s="83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="L212" s="83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>1.4285714285714286E-6</v>
       </c>
-      <c r="M212" s="1"/>
-      <c r="N212" s="100">
-        <v>1</v>
-      </c>
+      <c r="M212" s="83">
+        <f t="shared" si="15"/>
+        <v>1.4285714285714286E-6</v>
+      </c>
+      <c r="N212" s="1"/>
       <c r="O212" s="100">
+        <v>1</v>
+      </c>
+      <c r="P212" s="100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="213" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>507</v>
       </c>
@@ -12402,15 +13067,18 @@
       <c r="L213" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="M213" s="1"/>
-      <c r="N213" s="98">
+      <c r="M213" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="N213" s="1"/>
+      <c r="O213" s="98">
         <v>0.1</v>
       </c>
-      <c r="O213" s="98" t="s">
+      <c r="P213" s="98" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="214" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -12447,15 +13115,18 @@
       <c r="L214" s="83">
         <v>0</v>
       </c>
-      <c r="M214" s="1"/>
-      <c r="N214" s="98">
-        <v>0.04</v>
-      </c>
+      <c r="M214" s="83">
+        <v>0</v>
+      </c>
+      <c r="N214" s="1"/>
       <c r="O214" s="98">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="215" spans="1:15" s="96" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P214" s="98">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -12492,15 +13163,18 @@
       <c r="L215" s="83">
         <v>1E-3</v>
       </c>
-      <c r="M215" s="1"/>
-      <c r="N215" s="98">
+      <c r="M215" s="83">
         <v>1E-3</v>
       </c>
+      <c r="N215" s="1"/>
       <c r="O215" s="98">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P215" s="98">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>515</v>
       </c>
@@ -12524,33 +13198,37 @@
         <v>1.2499999999999999E-6</v>
       </c>
       <c r="H216" s="99">
-        <f>1250*0.000001/5</f>
+        <f t="shared" ref="H216:M216" si="16">1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="I216" s="99">
-        <f>1250*0.000001/5</f>
+        <f t="shared" si="16"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="J216" s="99">
-        <f>1250*0.000001/5</f>
+        <f t="shared" si="16"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="K216" s="99">
-        <f>1250*0.000001/5</f>
+        <f t="shared" si="16"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="L216" s="99">
-        <f>1250*0.000001/5</f>
+        <f t="shared" si="16"/>
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="N216" s="99">
+      <c r="M216" s="99">
+        <f t="shared" si="16"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="O216" s="99">
         <v>2.5000000000000001E-4</v>
       </c>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P216" s="99">
+        <v>2.5000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -12587,14 +13265,17 @@
       <c r="L217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="N217" s="99">
+      <c r="M217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="O217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>534</v>
       </c>
@@ -12634,8 +13315,12 @@
         <f xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M218" s="83">
+        <f xml:space="preserve"> 0.0000000000025</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>535</v>
       </c>
@@ -12677,8 +13362,12 @@
         <f>0.00000000005</f>
         <v>5.0000000000000002E-11</v>
       </c>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M219" s="83">
+        <f>0.00000000005</f>
+        <v>5.0000000000000002E-11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>569</v>
       </c>
@@ -12711,8 +13400,12 @@
         <f>0.0000001 * 10 /2</f>
         <v>4.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M220" s="83">
+        <f>0.0000001 * 10 /2</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>571</v>
       </c>
@@ -12745,8 +13438,12 @@
         <f>100</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M221" s="83">
+        <f>100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>536</v>
       </c>
@@ -12788,8 +13485,12 @@
         <f>0.000001 / 10000 / 4</f>
         <v>2.4999999999999998E-11</v>
       </c>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M222" s="83">
+        <f>0.000001 / 10000 / 4</f>
+        <v>2.4999999999999998E-11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>537</v>
       </c>
@@ -12829,10 +13530,14 @@
         <v>1E-4</v>
       </c>
       <c r="M223" s="83">
+        <f>0.00001 * 10</f>
+        <v>1E-4</v>
+      </c>
+      <c r="N223" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>538</v>
       </c>
@@ -12856,27 +13561,31 @@
         <v>0.10886399999999999</v>
       </c>
       <c r="H224" s="83">
-        <f t="shared" ref="H224:L224" si="9">0.84*(0.36^2)</f>
+        <f t="shared" ref="H224:M224" si="17">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
       <c r="I224" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="J224" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="K224" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="L224" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0.10886399999999999</v>
       </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M224" s="83">
+        <f t="shared" si="17"/>
+        <v>0.10886399999999999</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>539</v>
       </c>
@@ -12913,8 +13622,11 @@
       <c r="L225" s="83">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M225" s="83">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>540</v>
       </c>
@@ -12951,8 +13663,11 @@
       <c r="L226" s="83" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M226" s="83" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>541</v>
       </c>
@@ -12976,27 +13691,31 @@
         <v>0.2</v>
       </c>
       <c r="H227" s="83">
-        <f t="shared" ref="H227:L227" si="10">2*0.1</f>
+        <f t="shared" ref="H227:M227" si="18">2*0.1</f>
         <v>0.2</v>
       </c>
       <c r="I227" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
       <c r="J227" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
       <c r="K227" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
       <c r="L227" s="83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M227" s="83">
+        <f t="shared" si="18"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>542</v>
       </c>
@@ -13033,8 +13752,11 @@
       <c r="L228" s="83">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M228" s="83">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>543</v>
       </c>
@@ -13073,8 +13795,12 @@
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M229" s="83">
+        <f>0.00001 / 2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>566</v>
       </c>
@@ -13094,18 +13820,18 @@
         <v>559</v>
       </c>
       <c r="G230" s="83">
-        <f t="shared" ref="G230:J230" si="11">0.00002 / 14 / 5</f>
+        <f t="shared" ref="G230:J230" si="19">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="H230" s="83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="I230" s="83">
         <v>0</v>
       </c>
       <c r="J230" s="83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="K230" s="83">
@@ -13114,8 +13840,11 @@
       <c r="L230" s="83">
         <v>0</v>
       </c>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M230" s="83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>567</v>
       </c>
@@ -13135,27 +13864,31 @@
         <v>559</v>
       </c>
       <c r="G231" s="83">
-        <f t="shared" ref="G231:L231" si="12">0.00002 / 14 / 5 /10</f>
+        <f t="shared" ref="G231:M231" si="20">0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="H231" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="I231" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="J231" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="K231" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="L231" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
+        <v>2.8571428571428575E-8</v>
+      </c>
+      <c r="M231" s="83">
+        <f t="shared" si="20"/>
         <v>2.8571428571428575E-8</v>
       </c>
     </row>
@@ -13182,7 +13915,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G231:L231">
+  <conditionalFormatting sqref="G231:M231">
     <cfRule type="colorScale" priority="361">
       <colorScale>
         <cfvo type="min"/>
@@ -13204,7 +13937,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H127:L128">
+  <conditionalFormatting sqref="H127:M128">
     <cfRule type="colorScale" priority="363">
       <colorScale>
         <cfvo type="min"/>
@@ -13216,7 +13949,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H210:L210">
+  <conditionalFormatting sqref="H210:M210">
     <cfRule type="colorScale" priority="365">
       <colorScale>
         <cfvo type="min"/>
@@ -13238,7 +13971,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H211:L211">
+  <conditionalFormatting sqref="H211:M211">
     <cfRule type="colorScale" priority="367">
       <colorScale>
         <cfvo type="min"/>
@@ -13260,7 +13993,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H212:L212">
+  <conditionalFormatting sqref="H212:M212">
     <cfRule type="colorScale" priority="368">
       <colorScale>
         <cfvo type="min"/>
@@ -13282,7 +14015,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H213:L213">
+  <conditionalFormatting sqref="H213:M213">
     <cfRule type="colorScale" priority="371">
       <colorScale>
         <cfvo type="min"/>
@@ -13304,7 +14037,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H214:L214">
+  <conditionalFormatting sqref="H214:M214">
     <cfRule type="colorScale" priority="373">
       <colorScale>
         <cfvo type="min"/>
@@ -13326,7 +14059,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H215:L215">
+  <conditionalFormatting sqref="H215:M215">
     <cfRule type="colorScale" priority="375">
       <colorScale>
         <cfvo type="min"/>
@@ -13348,7 +14081,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H218:L218">
+  <conditionalFormatting sqref="H218:M218">
     <cfRule type="colorScale" priority="377">
       <colorScale>
         <cfvo type="min"/>
@@ -13370,7 +14103,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H219:L221">
+  <conditionalFormatting sqref="H219:M221">
     <cfRule type="colorScale" priority="391">
       <colorScale>
         <cfvo type="min"/>
@@ -13392,7 +14125,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H222:L222">
+  <conditionalFormatting sqref="H222:M222">
+    <cfRule type="colorScale" priority="380">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="381">
       <colorScale>
         <cfvo type="min"/>
@@ -13403,7 +14146,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="380">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H224:M224">
+    <cfRule type="colorScale" priority="385">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="384">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13414,7 +14169,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H223:M223">
+  <conditionalFormatting sqref="H225:M229">
+    <cfRule type="colorScale" priority="387">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="386">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H223:N223">
     <cfRule type="colorScale" priority="383">
       <colorScale>
         <cfvo type="min"/>
@@ -13436,8 +14213,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H224:L224">
-    <cfRule type="colorScale" priority="385">
+  <conditionalFormatting sqref="H132:P132">
+    <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13447,29 +14224,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="384">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H225:L229">
-    <cfRule type="colorScale" priority="386">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="387">
+    <cfRule type="colorScale" priority="303">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13524,7 +14279,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L230:L231">
+  <conditionalFormatting sqref="L230:M231">
     <cfRule type="colorScale" priority="388">
       <colorScale>
         <cfvo type="min"/>
@@ -13546,7 +14301,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N127:O128">
+  <conditionalFormatting sqref="O127:P128">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -13558,7 +14313,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N129:O129 H129:L129">
+  <conditionalFormatting sqref="O129:P129 H129:M129">
     <cfRule type="colorScale" priority="295">
       <colorScale>
         <cfvo type="min"/>
@@ -13580,7 +14335,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N130:O130 H130:L130">
+  <conditionalFormatting sqref="O130:P130 H130:M130">
     <cfRule type="colorScale" priority="299">
       <colorScale>
         <cfvo type="min"/>
@@ -13602,8 +14357,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N132:O132 H132:L132">
-    <cfRule type="colorScale" priority="304">
+  <conditionalFormatting sqref="O133:P133 H133:M133">
+    <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13613,7 +14368,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="303">
+    <cfRule type="colorScale" priority="308">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13624,29 +14379,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N133:O133 H133:L133">
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N138:O138 H138:L138">
+  <conditionalFormatting sqref="O138:P138 H138:M138">
     <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min"/>
@@ -13658,7 +14391,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N144:O144 H144:L144">
+  <conditionalFormatting sqref="O144:P144 H144:M144">
     <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min"/>
@@ -13690,7 +14423,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N160:O160 H160:L160">
+  <conditionalFormatting sqref="O160:P160 H160:M160">
     <cfRule type="colorScale" priority="321">
       <colorScale>
         <cfvo type="min"/>
@@ -13722,7 +14455,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N166:O166 H166:L166">
+  <conditionalFormatting sqref="O166:P166 H166:M166">
     <cfRule type="colorScale" priority="326">
       <colorScale>
         <cfvo type="min"/>
@@ -13762,13 +14495,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C169"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="35.6640625" customWidth="1"/>
-    <col min="3" max="3" width="49.5546875" customWidth="1"/>
+    <col min="1" max="2" width="35.7109375" customWidth="1"/>
+    <col min="3" max="3" width="49.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>286</v>
       </c>
@@ -13779,7 +14512,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>206</v>
       </c>
@@ -13791,7 +14524,7 @@
         <v>pi</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -13803,7 +14536,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -13815,7 +14548,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>207</v>
       </c>
@@ -13827,7 +14560,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -13839,7 +14572,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -13851,7 +14584,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -13863,7 +14596,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -13875,7 +14608,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -13887,7 +14620,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -13899,7 +14632,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -13911,7 +14644,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -13923,7 +14656,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -13935,7 +14668,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -13947,7 +14680,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>208</v>
       </c>
@@ -13959,7 +14692,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -13971,7 +14704,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -13983,7 +14716,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>205</v>
       </c>
@@ -13995,7 +14728,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -14007,7 +14740,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -14019,7 +14752,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -14031,7 +14764,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -14043,7 +14776,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -14055,7 +14788,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -14067,7 +14800,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>209</v>
       </c>
@@ -14079,7 +14812,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>210</v>
       </c>
@@ -14091,7 +14824,7 @@
         <v>root_growth_T_ref</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>211</v>
       </c>
@@ -14103,7 +14836,7 @@
         <v>root_growth_A</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>212</v>
       </c>
@@ -14115,7 +14848,7 @@
         <v>root_growth_B</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>213</v>
       </c>
@@ -14127,7 +14860,7 @@
         <v>root_growth_C</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>214</v>
       </c>
@@ -14139,7 +14872,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>215</v>
       </c>
@@ -14151,7 +14884,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>216</v>
       </c>
@@ -14163,7 +14896,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>217</v>
       </c>
@@ -14175,7 +14908,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>218</v>
       </c>
@@ -14187,7 +14920,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -14199,7 +14932,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -14211,7 +14944,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>219</v>
       </c>
@@ -14223,7 +14956,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>220</v>
       </c>
@@ -14235,7 +14968,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>221</v>
       </c>
@@ -14247,7 +14980,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>222</v>
       </c>
@@ -14259,7 +14992,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -14271,7 +15004,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>223</v>
       </c>
@@ -14283,7 +15016,7 @@
         <v>expected_C_sucrose_root</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>224</v>
       </c>
@@ -14295,7 +15028,7 @@
         <v>expected_C_hexose_root</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>225</v>
       </c>
@@ -14307,7 +15040,7 @@
         <v>expected_C_hexose_soil</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>226</v>
       </c>
@@ -14319,7 +15052,7 @@
         <v>expected_C_hexose_reserve</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>65</v>
       </c>
@@ -14331,7 +15064,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>77</v>
       </c>
@@ -14343,7 +15076,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>227</v>
       </c>
@@ -14355,7 +15088,7 @@
         <v>surfacic_unloading_rate_reference</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>228</v>
       </c>
@@ -14367,7 +15100,7 @@
         <v>surfacic_unloading_rate_primordium</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -14379,7 +15112,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>229</v>
       </c>
@@ -14391,7 +15124,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>230</v>
       </c>
@@ -14403,7 +15136,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>231</v>
       </c>
@@ -14415,7 +15148,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>232</v>
       </c>
@@ -14427,7 +15160,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -14439,7 +15172,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>233</v>
       </c>
@@ -14451,7 +15184,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>234</v>
       </c>
@@ -14463,7 +15196,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>235</v>
       </c>
@@ -14475,7 +15208,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>236</v>
       </c>
@@ -14487,7 +15220,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -14499,7 +15232,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -14511,7 +15244,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -14523,7 +15256,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -14535,7 +15268,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>56</v>
       </c>
@@ -14547,7 +15280,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>58</v>
       </c>
@@ -14559,7 +15292,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -14571,7 +15304,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>237</v>
       </c>
@@ -14583,7 +15316,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>238</v>
       </c>
@@ -14595,7 +15328,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>239</v>
       </c>
@@ -14607,7 +15340,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>240</v>
       </c>
@@ -14619,7 +15352,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -14631,7 +15364,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -14643,7 +15376,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>241</v>
       </c>
@@ -14655,7 +15388,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>242</v>
       </c>
@@ -14667,7 +15400,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>243</v>
       </c>
@@ -14679,7 +15412,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>244</v>
       </c>
@@ -14691,7 +15424,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>74</v>
       </c>
@@ -14703,7 +15436,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>245</v>
       </c>
@@ -14715,7 +15448,7 @@
         <v>expected_exudation_efflux</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -14727,7 +15460,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>246</v>
       </c>
@@ -14739,7 +15472,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>247</v>
       </c>
@@ -14751,7 +15484,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>248</v>
       </c>
@@ -14763,7 +15496,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>249</v>
       </c>
@@ -14775,7 +15508,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>79</v>
       </c>
@@ -14787,7 +15520,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>80</v>
       </c>
@@ -14799,7 +15532,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>250</v>
       </c>
@@ -14811,7 +15544,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>251</v>
       </c>
@@ -14823,7 +15556,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -14835,7 +15568,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>253</v>
       </c>
@@ -14847,7 +15580,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>81</v>
       </c>
@@ -14859,7 +15592,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>254</v>
       </c>
@@ -14871,7 +15604,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -14883,7 +15616,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>256</v>
       </c>
@@ -14895,7 +15628,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>257</v>
       </c>
@@ -14907,7 +15640,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>258</v>
       </c>
@@ -14919,7 +15652,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>259</v>
       </c>
@@ -14931,7 +15664,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>260</v>
       </c>
@@ -14943,7 +15676,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>261</v>
       </c>
@@ -14955,7 +15688,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>262</v>
       </c>
@@ -14967,7 +15700,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>263</v>
       </c>
@@ -14979,7 +15712,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>264</v>
       </c>
@@ -14991,7 +15724,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>265</v>
       </c>
@@ -15003,7 +15736,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>266</v>
       </c>
@@ -15015,7 +15748,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>267</v>
       </c>
@@ -15027,7 +15760,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>268</v>
       </c>
@@ -15039,7 +15772,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>269</v>
       </c>
@@ -15051,7 +15784,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>270</v>
       </c>
@@ -15063,7 +15796,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>271</v>
       </c>
@@ -15075,7 +15808,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>272</v>
       </c>
@@ -15087,7 +15820,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>273</v>
       </c>
@@ -15099,7 +15832,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>274</v>
       </c>
@@ -15111,7 +15844,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>275</v>
       </c>
@@ -15123,7 +15856,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>276</v>
       </c>
@@ -15135,7 +15868,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>277</v>
       </c>
@@ -15147,7 +15880,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>278</v>
       </c>
@@ -15159,7 +15892,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>279</v>
       </c>
@@ -15171,7 +15904,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>280</v>
       </c>
@@ -15183,7 +15916,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>281</v>
       </c>
@@ -15195,7 +15928,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>282</v>
       </c>
@@ -15207,7 +15940,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>283</v>
       </c>
@@ -15219,7 +15952,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>284</v>
       </c>
@@ -15231,7 +15964,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>59</v>
       </c>
@@ -15243,7 +15976,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>62</v>
       </c>
@@ -15255,7 +15988,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>64</v>
       </c>
@@ -15267,7 +16000,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>63</v>
       </c>
@@ -15279,7 +16012,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>82</v>
       </c>
@@ -15291,7 +16024,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>83</v>
       </c>
@@ -15303,7 +16036,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>85</v>
       </c>
@@ -15315,7 +16048,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>84</v>
       </c>
@@ -15327,7 +16060,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>2</v>
       </c>
@@ -15339,7 +16072,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -15351,7 +16084,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -15363,7 +16096,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>20</v>
       </c>
@@ -15375,7 +16108,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>0</v>
       </c>
@@ -15387,7 +16120,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1</v>
       </c>
@@ -15399,7 +16132,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>6</v>
       </c>
@@ -15411,7 +16144,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -15423,7 +16156,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -15435,7 +16168,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -15447,7 +16180,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -15459,7 +16192,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -15471,7 +16204,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>12</v>
       </c>
@@ -15483,7 +16216,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -15495,7 +16228,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>14</v>
       </c>
@@ -15507,7 +16240,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -15519,7 +16252,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -15531,7 +16264,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -15543,7 +16276,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -15555,7 +16288,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -15567,7 +16300,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>21</v>
       </c>
@@ -15579,7 +16312,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>22</v>
       </c>
@@ -15591,7 +16324,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>23</v>
       </c>
@@ -15603,7 +16336,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -15615,7 +16348,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>25</v>
       </c>
@@ -15627,7 +16360,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>26</v>
       </c>
@@ -15639,7 +16372,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>27</v>
       </c>
@@ -15651,7 +16384,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>28</v>
       </c>
@@ -15660,7 +16393,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>29</v>
       </c>
@@ -15669,7 +16402,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>30</v>
       </c>
@@ -15678,7 +16411,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>31</v>
       </c>
@@ -15687,7 +16420,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>32</v>
       </c>
@@ -15696,7 +16429,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>33</v>
       </c>
@@ -15705,7 +16438,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>34</v>
       </c>
@@ -15714,7 +16447,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>35</v>
       </c>
@@ -15723,7 +16456,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>36</v>
       </c>
@@ -15732,7 +16465,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>37</v>
       </c>
@@ -15741,7 +16474,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>38</v>
       </c>
@@ -15750,7 +16483,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>362</v>
       </c>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp30714\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp16152\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5E05B9-D7BF-4622-B7BF-7DCD11BD30F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8297F2DF-1CD3-49A1-B936-DC158CBDEFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="583">
   <si>
     <t>input_file</t>
   </si>
@@ -1768,6 +1768,21 @@
   </si>
   <si>
     <t>sucrose_input_Swinnen_et_al_1994_20degrees_interpolated.csv</t>
+  </si>
+  <si>
+    <t>equal</t>
+  </si>
+  <si>
+    <t>Km_Nm_xylem</t>
+  </si>
+  <si>
+    <t>Km parameter for mineral nitrogen xylem loading</t>
+  </si>
+  <si>
+    <t>vmax_AA_xylem</t>
+  </si>
+  <si>
+    <t>Vmax parameter for amino acids xylem loading</t>
   </si>
 </sst>
 </file>
@@ -2425,7 +2440,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2633,8 +2648,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="16" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2956,7 +2969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P231"/>
+  <dimension ref="A1:Q233"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
@@ -2964,10 +2977,10 @@
     <col min="5" max="5" width="23.28515625" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" style="37" customWidth="1"/>
-    <col min="8" max="16" width="39.85546875" style="1" customWidth="1"/>
+    <col min="8" max="17" width="39.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -3010,14 +3023,17 @@
       <c r="N1" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="O1" s="97" t="s">
+      <c r="O1" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="P1" s="97" t="s">
         <v>522</v>
       </c>
-      <c r="P1" s="97" t="s">
+      <c r="Q1" s="97" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>524</v>
       </c>
@@ -3057,14 +3073,18 @@
       <c r="M2" s="36" t="s">
         <v>476</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="1" t="b">
+        <f>L2=M2</f>
+        <v>1</v>
+      </c>
+      <c r="P2" s="36" t="s">
         <v>528</v>
       </c>
-      <c r="P2" s="36" t="s">
+      <c r="Q2" s="36" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3104,14 +3124,18 @@
       <c r="M3" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="O3" s="36" t="s">
-        <v>489</v>
+      <c r="O3" s="1" t="b">
+        <f t="shared" ref="O3:O66" si="0">L3=M3</f>
+        <v>1</v>
       </c>
       <c r="P3" s="36" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q3" s="36" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3151,14 +3175,18 @@
       <c r="M4" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="O4" s="36" t="s">
-        <v>482</v>
+      <c r="O4" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P4" s="36" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="36" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3198,14 +3226,18 @@
       <c r="M5" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="O5" s="36" t="s">
-        <v>494</v>
+      <c r="O5" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P5" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q5" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3245,14 +3277,18 @@
       <c r="M6" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="O6" s="36" t="s">
-        <v>521</v>
+      <c r="O6" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P6" s="36" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q6" s="36" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3292,14 +3328,18 @@
       <c r="M7" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="O7" s="36" t="s">
-        <v>494</v>
+      <c r="O7" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P7" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q7" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>529</v>
       </c>
@@ -3339,14 +3379,18 @@
       <c r="M8" s="36">
         <v>0</v>
       </c>
-      <c r="O8" s="36">
-        <v>0</v>
+      <c r="O8" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P8" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3386,14 +3430,18 @@
       <c r="M9" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O9" s="77" t="s">
-        <v>87</v>
+      <c r="O9" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P9" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3433,14 +3481,18 @@
       <c r="M10" s="77">
         <v>1</v>
       </c>
-      <c r="O10" s="77">
+      <c r="O10" s="1" t="b">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P10" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3480,14 +3532,18 @@
       <c r="M11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O11" s="77" t="s">
-        <v>88</v>
+      <c r="O11" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P11" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q11" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3527,14 +3583,18 @@
       <c r="M12" s="85">
         <v>180</v>
       </c>
-      <c r="O12" s="85">
-        <v>180</v>
+      <c r="O12" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P12" s="85">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q12" s="85">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3574,14 +3634,18 @@
       <c r="M13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="O13" s="78">
-        <v>4.1666666999999998E-2</v>
+      <c r="O13" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3621,14 +3685,18 @@
       <c r="M14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="O14" s="79">
-        <v>4.1666666999999998E-2</v>
+      <c r="O14" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3668,14 +3736,18 @@
       <c r="M15" s="77">
         <v>1</v>
       </c>
-      <c r="O15" s="77">
+      <c r="O15" s="1" t="b">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P15" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q15" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3715,14 +3787,18 @@
       <c r="M16" s="77">
         <v>0</v>
       </c>
-      <c r="O16" s="77">
-        <v>0</v>
+      <c r="O16" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P16" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3762,14 +3838,18 @@
       <c r="M17" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O17" s="77" t="s">
-        <v>88</v>
+      <c r="O17" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P17" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3809,14 +3889,18 @@
       <c r="M18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="O18" s="80">
-        <v>5.0000000000000001E-9</v>
+      <c r="O18" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -3856,14 +3940,18 @@
       <c r="M19" s="77">
         <v>10</v>
       </c>
-      <c r="O19" s="77">
-        <v>10</v>
+      <c r="O19" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P19" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q19" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -3903,14 +3991,18 @@
       <c r="M20" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O20" s="77" t="s">
-        <v>88</v>
+      <c r="O20" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P20" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q20" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -3950,14 +4042,18 @@
       <c r="M21" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O21" s="77" t="s">
-        <v>88</v>
+      <c r="O21" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P21" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q21" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -3997,14 +4093,18 @@
       <c r="M22" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O22" s="77" t="s">
-        <v>88</v>
+      <c r="O22" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P22" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q22" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -4044,14 +4144,18 @@
       <c r="M23" s="77">
         <v>86400</v>
       </c>
-      <c r="O23" s="77">
-        <v>86400</v>
+      <c r="O23" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P23" s="77">
         <v>86400</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q23" s="77">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -4091,14 +4195,18 @@
       <c r="M24" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O24" s="77" t="s">
-        <v>87</v>
+      <c r="O24" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P24" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q24" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -4138,14 +4246,18 @@
       <c r="M25" s="77">
         <v>3</v>
       </c>
-      <c r="O25" s="77">
-        <v>3</v>
+      <c r="O25" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P25" s="77">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q25" s="77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -4185,14 +4297,18 @@
       <c r="M26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O26" s="81" t="s">
-        <v>88</v>
+      <c r="O26" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P26" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q26" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -4232,14 +4348,18 @@
       <c r="M27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O27" s="81" t="s">
-        <v>88</v>
+      <c r="O27" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P27" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q27" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -4279,14 +4399,18 @@
       <c r="M28" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O28" s="77" t="s">
-        <v>88</v>
+      <c r="O28" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P28" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q28" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4326,14 +4450,18 @@
       <c r="M29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O29" s="81" t="s">
-        <v>88</v>
+      <c r="O29" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P29" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q29" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4373,14 +4501,18 @@
       <c r="M30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O30" s="81" t="s">
-        <v>88</v>
+      <c r="O30" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P30" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q30" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4420,14 +4552,18 @@
       <c r="M31" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="77" t="s">
-        <v>88</v>
+      <c r="O31" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P31" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q31" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4467,14 +4603,18 @@
       <c r="M32" s="77">
         <v>0.33</v>
       </c>
-      <c r="O32" s="77">
-        <v>0.33</v>
+      <c r="O32" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P32" s="77">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q32" s="77">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4514,14 +4654,18 @@
       <c r="M33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O33" s="77" t="s">
-        <v>88</v>
+      <c r="O33" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P33" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q33" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4561,14 +4705,18 @@
       <c r="M34" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O34" s="77" t="s">
-        <v>88</v>
+      <c r="O34" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P34" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q34" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4608,14 +4756,18 @@
       <c r="M35" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O35" s="77" t="s">
-        <v>88</v>
+      <c r="O35" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P35" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q35" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4655,14 +4807,18 @@
       <c r="M36" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O36" s="77" t="s">
-        <v>87</v>
+      <c r="O36" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P36" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q36" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4702,14 +4858,18 @@
       <c r="M37" s="85" t="s">
         <v>433</v>
       </c>
-      <c r="O37" s="85" t="s">
-        <v>433</v>
+      <c r="O37" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P37" s="85" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q37" s="85" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -4749,14 +4909,18 @@
       <c r="M38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="O38" s="80">
-        <v>9.9999999999999995E-7</v>
+      <c r="O38" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -4796,14 +4960,18 @@
       <c r="M39" s="86">
         <v>1E-3</v>
       </c>
-      <c r="O39" s="86">
-        <v>1E-3</v>
+      <c r="O39" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P39" s="86">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q39" s="86">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -4843,14 +5011,18 @@
       <c r="M40" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O40" s="77" t="s">
-        <v>87</v>
+      <c r="O40" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P40" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q40" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -4890,14 +5062,18 @@
       <c r="M41" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="O41" s="77" t="s">
-        <v>89</v>
+      <c r="O41" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P41" s="77" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q41" s="77" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -4937,14 +5113,18 @@
       <c r="M42" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O42" s="77" t="s">
-        <v>87</v>
+      <c r="O42" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P42" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q42" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -4984,14 +5164,18 @@
       <c r="M43" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O43" s="77" t="s">
-        <v>88</v>
+      <c r="O43" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P43" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q43" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -5031,14 +5215,18 @@
       <c r="M44" s="77">
         <v>120</v>
       </c>
-      <c r="O44" s="77">
-        <v>120</v>
+      <c r="O44" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P44" s="77">
         <v>120</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q44" s="77">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -5078,14 +5266,18 @@
       <c r="M45" s="77">
         <v>0</v>
       </c>
-      <c r="O45" s="77">
-        <v>0</v>
+      <c r="O45" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P45" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q45" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -5125,14 +5317,18 @@
       <c r="M46" s="77">
         <v>0</v>
       </c>
-      <c r="O46" s="77">
-        <v>0</v>
+      <c r="O46" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P46" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q46" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -5172,14 +5368,18 @@
       <c r="M47" s="77">
         <v>-0.1</v>
       </c>
-      <c r="O47" s="77">
-        <v>-0.1</v>
+      <c r="O47" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P47" s="77">
         <v>-0.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q47" s="77">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -5219,14 +5419,18 @@
       <c r="M48" s="77">
         <v>-0.2</v>
       </c>
-      <c r="O48" s="77">
-        <v>-0.2</v>
+      <c r="O48" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P48" s="77">
         <v>-0.2</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q48" s="77">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -5266,14 +5470,18 @@
       <c r="M49" s="77">
         <v>0.4</v>
       </c>
-      <c r="O49" s="77">
-        <v>0.4</v>
+      <c r="O49" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P49" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q49" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -5313,14 +5521,18 @@
       <c r="M50" s="77">
         <v>0</v>
       </c>
-      <c r="O50" s="77">
-        <v>0</v>
+      <c r="O50" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P50" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q50" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -5360,14 +5572,18 @@
       <c r="M51" s="77">
         <v>1200</v>
       </c>
-      <c r="O51" s="77">
-        <v>1200</v>
+      <c r="O51" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P51" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q51" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -5407,14 +5623,18 @@
       <c r="M52" s="77">
         <v>1200</v>
       </c>
-      <c r="O52" s="77">
-        <v>1200</v>
+      <c r="O52" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P52" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q52" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -5454,14 +5674,18 @@
       <c r="M53" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="O53" s="35" t="s">
-        <v>460</v>
+      <c r="O53" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P53" s="35" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q53" s="35" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -5501,14 +5725,18 @@
       <c r="M54" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O54" s="77" t="s">
-        <v>87</v>
+      <c r="O54" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P54" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q54" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5548,14 +5776,18 @@
       <c r="M55" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O55" s="77" t="s">
-        <v>87</v>
+      <c r="O55" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P55" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q55" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -5595,14 +5827,18 @@
       <c r="M56" s="77">
         <v>0</v>
       </c>
-      <c r="O56" s="77">
-        <v>0</v>
+      <c r="O56" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P56" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q56" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -5642,14 +5878,18 @@
       <c r="M57" s="77">
         <v>0.5</v>
       </c>
-      <c r="O57" s="77">
-        <v>0.5</v>
+      <c r="O57" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P57" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q57" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -5689,14 +5929,18 @@
       <c r="M58" s="77">
         <v>0.05</v>
       </c>
-      <c r="O58" s="77">
-        <v>0.05</v>
+      <c r="O58" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P58" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q58" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -5736,14 +5980,18 @@
       <c r="M59" s="80">
         <v>1E-3</v>
       </c>
-      <c r="O59" s="80">
-        <v>1E-3</v>
+      <c r="O59" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P59" s="80">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q59" s="80">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -5783,14 +6031,18 @@
       <c r="M60" s="77">
         <v>0</v>
       </c>
-      <c r="O60" s="77">
-        <v>0</v>
+      <c r="O60" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P60" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q60" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -5830,14 +6082,18 @@
       <c r="M61" s="77">
         <v>1E-4</v>
       </c>
-      <c r="O61" s="77">
-        <v>1E-4</v>
+      <c r="O61" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P61" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q61" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -5877,14 +6133,18 @@
       <c r="M62" s="77">
         <v>1E-4</v>
       </c>
-      <c r="O62" s="77">
-        <v>1E-4</v>
+      <c r="O62" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P62" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q62" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -5924,14 +6184,18 @@
       <c r="M63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="O63" s="77">
-        <v>6.9999999999999999E-4</v>
+      <c r="O63" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -5971,14 +6235,18 @@
       <c r="M64" s="77">
         <v>1.22E-4</v>
       </c>
-      <c r="O64" s="77">
-        <v>1.22E-4</v>
+      <c r="O64" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P64" s="77">
         <v>1.22E-4</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q64" s="77">
+        <v>1.22E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -6018,14 +6286,18 @@
       <c r="M65" s="77">
         <v>1</v>
       </c>
-      <c r="O65" s="77">
+      <c r="O65" s="1" t="b">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P65" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q65" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -6065,14 +6337,18 @@
       <c r="M66" s="77">
         <v>0.95</v>
       </c>
-      <c r="O66" s="77">
-        <v>0.95</v>
+      <c r="O66" s="1" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P66" s="77">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q66" s="77">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -6112,14 +6388,18 @@
       <c r="M67" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O67" s="77" t="s">
-        <v>88</v>
+      <c r="O67" s="1" t="b">
+        <f t="shared" ref="O67:O130" si="1">L67=M67</f>
+        <v>1</v>
       </c>
       <c r="P67" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q67" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -6159,14 +6439,18 @@
       <c r="M68" s="77">
         <v>5</v>
       </c>
-      <c r="O68" s="77">
-        <v>5</v>
+      <c r="O68" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P68" s="77">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q68" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -6206,14 +6490,18 @@
       <c r="M69" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O69" s="77" t="s">
-        <v>88</v>
+      <c r="O69" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P69" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q69" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -6253,14 +6541,18 @@
       <c r="M70" s="77">
         <v>50</v>
       </c>
-      <c r="O70" s="77">
-        <v>50</v>
+      <c r="O70" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P70" s="77">
         <v>50</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q70" s="77">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -6300,14 +6592,18 @@
       <c r="M71" s="78">
         <v>1453890.8941884842</v>
       </c>
-      <c r="O71" s="78">
-        <v>1453890.8941884842</v>
+      <c r="O71" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P71" s="78">
         <v>1453890.8941884842</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -6347,14 +6643,18 @@
       <c r="M72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-      <c r="O72" s="78">
-        <v>1.3888888888888888E-5</v>
+      <c r="O72" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -6394,14 +6694,18 @@
       <c r="M73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-      <c r="O73" s="79">
-        <v>6.5011574074074071E-4</v>
+      <c r="O73" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -6441,14 +6745,18 @@
       <c r="M74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-      <c r="O74" s="85">
-        <v>4.7400000000000003E-3</v>
+      <c r="O74" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -6489,14 +6797,18 @@
       <c r="M75" s="79">
         <v>282528</v>
       </c>
-      <c r="O75" s="79">
-        <v>282528</v>
+      <c r="O75" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P75" s="79">
         <v>282528</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q75" s="79">
+        <v>282528</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -6536,14 +6848,18 @@
       <c r="M76" s="85">
         <v>0.56999999999999995</v>
       </c>
-      <c r="O76" s="85">
-        <v>0.56999999999999995</v>
+      <c r="O76" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P76" s="85">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -6583,14 +6899,18 @@
       <c r="M77" s="87">
         <v>0.16</v>
       </c>
-      <c r="O77" s="87">
-        <v>0.16</v>
+      <c r="O77" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P77" s="87">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q77" s="87">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -6630,14 +6950,18 @@
       <c r="M78" s="77">
         <v>0</v>
       </c>
-      <c r="O78" s="77">
-        <v>0</v>
+      <c r="O78" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P78" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q78" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -6677,14 +7001,18 @@
       <c r="M79" s="78">
         <v>745476480000</v>
       </c>
-      <c r="O79" s="78">
-        <v>745476480000</v>
+      <c r="O79" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P79" s="78">
         <v>745476480000</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q79" s="78">
+        <v>745476480000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -6724,14 +7052,18 @@
       <c r="M80" s="77">
         <v>100</v>
       </c>
-      <c r="O80" s="77">
-        <v>100</v>
+      <c r="O80" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P80" s="77">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q80" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -6771,14 +7103,18 @@
       <c r="M81" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O81" s="77" t="s">
-        <v>88</v>
+      <c r="O81" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P81" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q81" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -6818,14 +7154,18 @@
       <c r="M82" s="85">
         <v>21600</v>
       </c>
-      <c r="O82" s="85">
-        <v>21600</v>
+      <c r="O82" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P82" s="85">
         <v>21600</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q82" s="85">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -6865,14 +7205,18 @@
       <c r="M83" s="77">
         <v>0.5</v>
       </c>
-      <c r="O83" s="77">
-        <v>0.5</v>
+      <c r="O83" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P83" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q83" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -6912,14 +7256,18 @@
       <c r="M84" s="85">
         <v>60479.999999999993</v>
       </c>
-      <c r="O84" s="85">
-        <v>60479.999999999993</v>
+      <c r="O84" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P84" s="85">
         <v>60479.999999999993</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -6959,14 +7307,18 @@
       <c r="M85" s="77">
         <v>0.85</v>
       </c>
-      <c r="O85" s="77">
-        <v>0.85</v>
+      <c r="O85" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P85" s="77">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q85" s="77">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -7006,14 +7358,18 @@
       <c r="M86" s="77">
         <v>518400</v>
       </c>
-      <c r="O86" s="77">
-        <v>518400</v>
+      <c r="O86" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P86" s="77">
         <v>518400</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q86" s="77">
+        <v>518400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -7053,14 +7409,18 @@
       <c r="M87" s="77">
         <v>5184000</v>
       </c>
-      <c r="O87" s="77">
-        <v>5184000</v>
+      <c r="O87" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P87" s="77">
         <v>5184000</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q87" s="77">
+        <v>5184000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -7100,14 +7460,18 @@
       <c r="M88" s="86">
         <v>50000</v>
       </c>
-      <c r="O88" s="86">
-        <v>50000</v>
+      <c r="O88" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P88" s="86">
         <v>50000</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q88" s="86">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -7147,14 +7511,18 @@
       <c r="M89" s="77">
         <v>140000</v>
       </c>
-      <c r="O89" s="77">
-        <v>140000</v>
+      <c r="O89" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P89" s="77">
         <v>140000</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q89" s="77">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -7194,14 +7562,18 @@
       <c r="M90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-      <c r="O90" s="78">
-        <v>3.6636136999999999E-2</v>
+      <c r="O90" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -7241,14 +7613,18 @@
       <c r="M91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="O91" s="77">
-        <v>4.4999999999999997E-3</v>
+      <c r="O91" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -7288,14 +7664,18 @@
       <c r="M92" s="77">
         <v>0.05</v>
       </c>
-      <c r="O92" s="77">
-        <v>0.05</v>
+      <c r="O92" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P92" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q92" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -7335,14 +7715,18 @@
       <c r="M93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="O93" s="77">
-        <v>6.0000000000000002E-6</v>
+      <c r="O93" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -7382,14 +7766,18 @@
       <c r="M94" s="77">
         <v>1E-3</v>
       </c>
-      <c r="O94" s="77">
-        <v>0</v>
+      <c r="O94" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P94" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q94" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -7429,14 +7817,18 @@
       <c r="M95" s="77">
         <v>374999999.99999994</v>
       </c>
-      <c r="O95" s="77">
-        <v>374999999.99999994</v>
+      <c r="O95" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P95" s="77">
         <v>374999999.99999994</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -7476,14 +7868,18 @@
       <c r="M96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="O96" s="78">
-        <v>3.7037037037037038E-3</v>
+      <c r="O96" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -7523,14 +7919,18 @@
       <c r="M97" s="77">
         <v>165600</v>
       </c>
-      <c r="O97" s="77">
-        <v>165600</v>
+      <c r="O97" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P97" s="77">
         <v>165600</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q97" s="77">
+        <v>165600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -7570,14 +7970,18 @@
       <c r="M98" s="77">
         <v>20</v>
       </c>
-      <c r="O98" s="77">
-        <v>20</v>
+      <c r="O98" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P98" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q98" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -7617,14 +8021,18 @@
       <c r="M99" s="77">
         <v>1</v>
       </c>
-      <c r="O99" s="77">
+      <c r="O99" s="1" t="b">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P99" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q99" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -7664,14 +8072,18 @@
       <c r="M100" s="77">
         <v>21</v>
       </c>
-      <c r="O100" s="77">
-        <v>21</v>
+      <c r="O100" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P100" s="77">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q100" s="77">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -7711,14 +8123,18 @@
       <c r="M101" s="77">
         <v>0.64</v>
       </c>
-      <c r="O101" s="77">
-        <v>0.64</v>
+      <c r="O101" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P101" s="77">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q101" s="77">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -7758,14 +8174,18 @@
       <c r="M102" s="77">
         <v>8</v>
       </c>
-      <c r="O102" s="77">
-        <v>8</v>
+      <c r="O102" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P102" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q102" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -7805,14 +8225,18 @@
       <c r="M103" s="77">
         <v>10</v>
       </c>
-      <c r="O103" s="77">
-        <v>10</v>
+      <c r="O103" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P103" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q103" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -7852,14 +8276,18 @@
       <c r="M104" s="77">
         <v>8</v>
       </c>
-      <c r="O104" s="77">
-        <v>8</v>
+      <c r="O104" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P104" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q104" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="23" t="s">
         <v>500</v>
       </c>
@@ -7899,14 +8327,18 @@
       <c r="M105" s="77">
         <v>1</v>
       </c>
-      <c r="O105" s="77">
+      <c r="O105" s="1" t="b">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P105" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q105" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -7946,14 +8378,18 @@
       <c r="M106" s="77">
         <v>0.5</v>
       </c>
-      <c r="O106" s="77">
-        <v>0.5</v>
+      <c r="O106" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P106" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q106" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="23" t="s">
         <v>501</v>
       </c>
@@ -7973,41 +8409,45 @@
         <v>506</v>
       </c>
       <c r="G107" s="58">
-        <f t="shared" ref="G107:L107" si="0">G105</f>
+        <f t="shared" ref="G107:L107" si="2">G105</f>
         <v>1</v>
       </c>
       <c r="H107" s="58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I107" s="58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J107" s="58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K107" s="58">
-        <f t="shared" ref="K107" si="1">K105</f>
+        <f t="shared" ref="K107" si="3">K105</f>
         <v>1</v>
       </c>
       <c r="L107" s="58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M107" s="58">
-        <f t="shared" ref="M107" si="2">M105</f>
-        <v>1</v>
-      </c>
-      <c r="O107" s="58">
+        <f t="shared" ref="M107" si="4">M105</f>
+        <v>1</v>
+      </c>
+      <c r="O107" s="1" t="b">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P107" s="58">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q107" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="23" t="s">
         <v>502</v>
       </c>
@@ -8031,37 +8471,41 @@
         <v>3</v>
       </c>
       <c r="H108" s="58">
-        <f t="shared" ref="H108:M108" si="3">150*H105</f>
+        <f t="shared" ref="H108:M108" si="5">150*H105</f>
         <v>150</v>
       </c>
       <c r="I108" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
       <c r="J108" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
       <c r="K108" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
       <c r="L108" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
       <c r="M108" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
-      <c r="O108" s="58">
-        <v>150</v>
+      <c r="O108" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P108" s="58">
         <v>150</v>
       </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q108" s="58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="23" t="s">
         <v>503</v>
       </c>
@@ -8081,41 +8525,45 @@
         <v>506</v>
       </c>
       <c r="G109" s="58">
-        <f t="shared" ref="G109:L109" si="4">G100</f>
+        <f t="shared" ref="G109:L109" si="6">G100</f>
         <v>21</v>
       </c>
       <c r="H109" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="I109" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="J109" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="K109" s="58">
-        <f t="shared" ref="K109" si="5">K100</f>
+        <f t="shared" ref="K109" si="7">K100</f>
         <v>21</v>
       </c>
       <c r="L109" s="58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="M109" s="58">
-        <f t="shared" ref="M109" si="6">M100</f>
+        <f t="shared" ref="M109" si="8">M100</f>
         <v>21</v>
       </c>
-      <c r="O109" s="58">
-        <v>21</v>
+      <c r="O109" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P109" s="58">
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q109" s="58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="23" t="s">
         <v>504</v>
       </c>
@@ -8139,37 +8587,41 @@
         <v>210</v>
       </c>
       <c r="H110" s="58">
-        <f t="shared" ref="H110:M110" si="7">70*H100</f>
+        <f t="shared" ref="H110:M110" si="9">70*H100</f>
         <v>1470</v>
       </c>
       <c r="I110" s="58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1470</v>
       </c>
       <c r="J110" s="58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1470</v>
       </c>
       <c r="K110" s="58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1470</v>
       </c>
       <c r="L110" s="58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1470</v>
       </c>
       <c r="M110" s="58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1470</v>
       </c>
-      <c r="O110" s="58">
-        <v>1470</v>
+      <c r="O110" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P110" s="58">
         <v>1470</v>
       </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q110" s="58">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -8209,14 +8661,18 @@
       <c r="M111" s="77">
         <v>0</v>
       </c>
-      <c r="O111" s="77">
-        <v>0</v>
+      <c r="O111" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P111" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q111" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -8256,14 +8712,18 @@
       <c r="M112" s="82">
         <v>1589759.9999999998</v>
       </c>
-      <c r="O112" s="82">
-        <v>1589759.9999999998</v>
+      <c r="O112" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P112" s="82">
         <v>1589759.9999999998</v>
       </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -8303,14 +8763,18 @@
       <c r="M113" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="O113" s="82">
-        <v>6171428.5714285718</v>
+      <c r="O113" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P113" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -8350,14 +8814,18 @@
       <c r="M114" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="O114" s="82">
-        <v>6171428.5714285718</v>
+      <c r="O114" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P114" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -8397,14 +8865,18 @@
       <c r="M115" s="82">
         <v>100</v>
       </c>
-      <c r="O115" s="82">
-        <v>100</v>
+      <c r="O115" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P115" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="116" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q115" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -8428,37 +8900,41 @@
         <v>280800</v>
       </c>
       <c r="H116" s="67">
-        <f t="shared" ref="H116:M116" si="8">0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" ref="H116:M116" si="10">0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
       <c r="I116" s="67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>28080</v>
       </c>
       <c r="J116" s="67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>28080</v>
       </c>
       <c r="K116" s="67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>28080</v>
       </c>
       <c r="L116" s="67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>28080</v>
       </c>
       <c r="M116" s="67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>28080</v>
       </c>
-      <c r="O116" s="67">
-        <v>28080</v>
+      <c r="O116" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P116" s="67">
         <v>28080</v>
       </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q116" s="67">
+        <v>28080</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -8482,37 +8958,41 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H117" s="67">
-        <f t="shared" ref="H117:M117" si="9">1.11 / 10</f>
+        <f t="shared" ref="H117:M117" si="11">1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
       <c r="I117" s="67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="J117" s="67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="K117" s="67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="L117" s="67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="M117" s="67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.11100000000000002</v>
       </c>
-      <c r="O117" s="67">
-        <v>0.11100000000000002</v>
+      <c r="O117" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P117" s="67">
         <v>0.11100000000000002</v>
       </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q117" s="67">
+        <v>0.11100000000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="23" t="s">
         <v>497</v>
       </c>
@@ -8552,14 +9032,18 @@
       <c r="M118" s="82">
         <v>100</v>
       </c>
-      <c r="O118" s="82">
-        <v>100</v>
+      <c r="O118" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P118" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="119" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q118" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="23" t="s">
         <v>498</v>
       </c>
@@ -8579,41 +9063,45 @@
         <v>431</v>
       </c>
       <c r="G119" s="67">
-        <f t="shared" ref="G119:M119" si="10">5.32 * (60*60*24)</f>
+        <f t="shared" ref="G119:M119" si="12">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H119" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>459648</v>
       </c>
       <c r="I119" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>459648</v>
       </c>
       <c r="J119" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>459648</v>
       </c>
       <c r="K119" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>459648</v>
       </c>
       <c r="L119" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>459648</v>
       </c>
       <c r="M119" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>459648</v>
       </c>
-      <c r="O119" s="67">
-        <v>459648</v>
+      <c r="O119" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P119" s="67">
         <v>459648</v>
       </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q119" s="67">
+        <v>459648</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="23" t="s">
         <v>499</v>
       </c>
@@ -8637,37 +9125,41 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H120" s="67">
-        <f t="shared" ref="H120:M120" si="11">1.11/8</f>
+        <f t="shared" ref="H120:M120" si="13">1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
       <c r="I120" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="J120" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="K120" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="L120" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="M120" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="O120" s="67">
-        <v>0.13875000000000001</v>
+      <c r="O120" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P120" s="67">
         <v>0.13875000000000001</v>
       </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q120" s="67">
+        <v>0.13875000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -8707,14 +9199,18 @@
       <c r="M121" s="82">
         <v>21600</v>
       </c>
-      <c r="O121" s="82">
-        <v>21600</v>
+      <c r="O121" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P121" s="82">
         <v>21600</v>
       </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q121" s="82">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -8754,14 +9250,18 @@
       <c r="M122" s="88">
         <v>43200</v>
       </c>
-      <c r="O122" s="88">
-        <v>43200</v>
+      <c r="O122" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P122" s="88">
         <v>43200</v>
       </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q122" s="88">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -8801,14 +9301,18 @@
       <c r="M123" s="77">
         <v>0.8</v>
       </c>
-      <c r="O123" s="77">
-        <v>0.8</v>
+      <c r="O123" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P123" s="77">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q123" s="77">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -8849,14 +9353,18 @@
       <c r="M124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="O124" s="78">
-        <v>2.0833333333333335E-4</v>
+      <c r="O124" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q124" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -8896,14 +9404,18 @@
       <c r="M125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-      <c r="O125" s="77">
-        <v>5.7899999999999998E-7</v>
+      <c r="O125" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q125" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -8943,14 +9455,18 @@
       <c r="M126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="O126" s="78">
-        <v>2.0833333333333335E-4</v>
+      <c r="O126" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q126" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -8990,14 +9506,18 @@
       <c r="M127" s="78">
         <v>0</v>
       </c>
-      <c r="O127" s="78">
-        <v>0</v>
+      <c r="O127" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P127" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q127" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -9037,14 +9557,18 @@
       <c r="M128" s="78">
         <v>0</v>
       </c>
-      <c r="O128" s="78">
-        <v>0</v>
+      <c r="O128" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P128" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q128" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -9069,11 +9593,11 @@
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="I129" s="83">
-        <f t="shared" ref="I129:P129" si="12">0.0000002*3</f>
+        <f t="shared" ref="I129:Q129" si="14">0.0000002*3</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J129" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="K129" s="83">
@@ -9081,25 +9605,30 @@
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="L129" s="83">
+        <f>0.0000002 * 2 / 1000</f>
+        <v>3.9999999999999996E-10</v>
+      </c>
+      <c r="M129" s="83">
+        <v>0</v>
+      </c>
+      <c r="N129" s="83">
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="M129" s="83">
-        <v>0</v>
-      </c>
-      <c r="N129" s="102">
-        <v>0</v>
-      </c>
-      <c r="O129" s="83">
-        <f t="shared" si="12"/>
+      <c r="O129" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P129" s="83">
+        <f t="shared" si="14"/>
         <v>5.9999999999999997E-7</v>
       </c>
-      <c r="P129" s="83">
-        <f t="shared" si="12"/>
+      <c r="Q129" s="83">
+        <f t="shared" si="14"/>
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -9120,39 +9649,43 @@
       </c>
       <c r="G130" s="71"/>
       <c r="H130" s="83">
-        <f t="shared" ref="H130:P130" si="13">1000 * 0.000001 / 12</f>
+        <f t="shared" ref="H130:Q130" si="15">1000 * 0.000001 / 12</f>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="I130" s="83">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="J130" s="83">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="K130" s="83">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="L130" s="83">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="M130" s="83">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O130" s="83">
-        <f t="shared" si="13"/>
+      <c r="O130" s="1" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P130" s="83">
+        <f t="shared" si="15"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="P130" s="83">
-        <f t="shared" si="13"/>
+      <c r="Q130" s="83">
+        <f t="shared" si="15"/>
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -9192,14 +9725,18 @@
       <c r="M131" s="89" t="s">
         <v>533</v>
       </c>
-      <c r="O131" s="89" t="s">
-        <v>533</v>
+      <c r="O131" s="1" t="b">
+        <f t="shared" ref="O131:O194" si="16">L131=M131</f>
+        <v>1</v>
       </c>
       <c r="P131" s="89" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q131" s="89" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -9235,23 +9772,29 @@
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="L132" s="83">
+        <f>0.0005 / 10</f>
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="M132" s="83">
+        <f>0.0005</f>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="N132" s="83">
         <f>0.0005 * 1.2</f>
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="M132" s="83">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="N132" s="83">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="O132" s="83">
-        <v>5.0000000000000001E-4</v>
+      <c r="O132" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="P132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q132" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -9291,14 +9834,18 @@
       <c r="M133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="O133" s="83">
-        <v>4.9999999999999999E-13</v>
+      <c r="O133" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q133" s="83">
+        <v>4.9999999999999999E-13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -9338,14 +9885,18 @@
       <c r="M134" s="77">
         <v>10</v>
       </c>
-      <c r="O134" s="77">
-        <v>10</v>
+      <c r="O134" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P134" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q134" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -9385,14 +9936,18 @@
       <c r="M135" s="77">
         <v>-0.04</v>
       </c>
-      <c r="O135" s="77">
-        <v>-0.04</v>
+      <c r="O135" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P135" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q135" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -9432,14 +9987,18 @@
       <c r="M136" s="77">
         <v>2.9</v>
       </c>
-      <c r="O136" s="77">
-        <v>2.9</v>
+      <c r="O136" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P136" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q136" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -9479,14 +10038,18 @@
       <c r="M137" s="77">
         <v>1</v>
       </c>
-      <c r="O137" s="77">
+      <c r="O137" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P137" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q137" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
         <v>574</v>
       </c>
@@ -9528,17 +10091,22 @@
       <c r="M138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="N138" s="101">
-        <v>1.9999999999999999E-7</v>
-      </c>
-      <c r="O138" s="80">
-        <v>1.9999999999999999E-7</v>
+      <c r="N138" s="80">
+        <f>0.0000002 * 2 / 10</f>
+        <v>4.0000000000000001E-8</v>
+      </c>
+      <c r="O138" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="P138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q138" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -9578,14 +10146,18 @@
       <c r="M139" s="77">
         <v>10</v>
       </c>
-      <c r="O139" s="77">
-        <v>10</v>
+      <c r="O139" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P139" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q139" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -9625,14 +10197,18 @@
       <c r="M140" s="77">
         <v>-0.04</v>
       </c>
-      <c r="O140" s="77">
-        <v>-0.04</v>
+      <c r="O140" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P140" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q140" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -9672,14 +10248,18 @@
       <c r="M141" s="77">
         <v>2.9</v>
       </c>
-      <c r="O141" s="77">
-        <v>2.9</v>
+      <c r="O141" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P141" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q141" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -9719,14 +10299,18 @@
       <c r="M142" s="77">
         <v>1</v>
       </c>
-      <c r="O142" s="77">
+      <c r="O142" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P142" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q142" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -9766,14 +10350,18 @@
       <c r="M143" s="77">
         <v>0</v>
       </c>
-      <c r="O143" s="77">
-        <v>0</v>
+      <c r="O143" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P143" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q143" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -9813,14 +10401,18 @@
       <c r="M144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="O144" s="80">
-        <v>5.0000000000000004E-6</v>
+      <c r="O144" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q144" s="80">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -9860,14 +10452,18 @@
       <c r="M145" s="77">
         <v>0</v>
       </c>
-      <c r="O145" s="77">
-        <v>0</v>
+      <c r="O145" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P145" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q145" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -9907,14 +10503,18 @@
       <c r="M146" s="77">
         <v>2E-3</v>
       </c>
-      <c r="O146" s="77">
-        <v>2E-3</v>
+      <c r="O146" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P146" s="77">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q146" s="77">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -9954,14 +10554,18 @@
       <c r="M147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-      <c r="O147" s="80">
-        <v>3.9999999999999998E-6</v>
+      <c r="O147" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q147" s="80">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -10001,14 +10605,18 @@
       <c r="M148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-      <c r="O148" s="80">
-        <v>3.7699999999999999E-10</v>
+      <c r="O148" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q148" s="80">
+        <v>3.7699999999999999E-10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -10048,14 +10656,18 @@
       <c r="M149" s="77">
         <v>20</v>
       </c>
-      <c r="O149" s="77">
-        <v>20</v>
+      <c r="O149" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P149" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q149" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -10095,14 +10707,18 @@
       <c r="M150" s="77">
         <v>-0.06</v>
       </c>
-      <c r="O150" s="77">
-        <v>-0.06</v>
+      <c r="O150" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P150" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q150" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -10142,14 +10758,18 @@
       <c r="M151" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="O151" s="77">
-        <v>0.89100000000000001</v>
+      <c r="O151" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P151" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q151" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -10189,14 +10809,18 @@
       <c r="M152" s="77">
         <v>1</v>
       </c>
-      <c r="O152" s="77">
+      <c r="O152" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P152" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q152" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -10236,14 +10860,18 @@
       <c r="M153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="O153" s="80">
-        <v>4.0000000000000003E-5</v>
+      <c r="O153" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q153" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -10283,14 +10911,18 @@
       <c r="M154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-      <c r="O154" s="80">
-        <v>5.8333333333333335E-9</v>
+      <c r="O154" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q154" s="80">
+        <v>5.8333333333333335E-9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -10330,14 +10962,18 @@
       <c r="M155" s="77">
         <v>20</v>
       </c>
-      <c r="O155" s="77">
-        <v>20</v>
+      <c r="O155" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P155" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q155" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -10377,14 +11013,18 @@
       <c r="M156" s="77">
         <v>-0.06</v>
       </c>
-      <c r="O156" s="77">
-        <v>-0.06</v>
+      <c r="O156" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P156" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q156" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -10424,14 +11064,18 @@
       <c r="M157" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="O157" s="77">
-        <v>0.89100000000000001</v>
+      <c r="O157" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P157" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q157" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -10471,14 +11115,18 @@
       <c r="M158" s="77">
         <v>1</v>
       </c>
-      <c r="O158" s="77">
+      <c r="O158" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P158" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q158" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -10518,14 +11166,18 @@
       <c r="M159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="O159" s="80">
-        <v>4.0000000000000003E-5</v>
+      <c r="O159" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q159" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -10565,14 +11217,18 @@
       <c r="M160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="O160" s="83">
-        <v>4.0000000000000001E-8</v>
+      <c r="O160" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-    </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q160" s="83">
+        <v>4.0000000000000001E-8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -10612,14 +11268,18 @@
       <c r="M161" s="77">
         <v>20</v>
       </c>
-      <c r="O161" s="77">
-        <v>20</v>
+      <c r="O161" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P161" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q161" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -10659,14 +11319,18 @@
       <c r="M162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-      <c r="O162" s="77">
-        <v>-4.4200000000000003E-2</v>
+      <c r="O162" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q162" s="77">
+        <v>-4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -10706,14 +11370,18 @@
       <c r="M163" s="77">
         <v>1.55</v>
       </c>
-      <c r="O163" s="77">
-        <v>1.55</v>
+      <c r="O163" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P163" s="77">
         <v>1.55</v>
       </c>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q163" s="77">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -10753,14 +11421,18 @@
       <c r="M164" s="77">
         <v>1</v>
       </c>
-      <c r="O164" s="77">
+      <c r="O164" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P164" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q164" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -10800,14 +11472,18 @@
       <c r="M165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="O165" s="77">
-        <v>2.7799999999999998E-4</v>
+      <c r="O165" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q165" s="77">
+        <v>2.7799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -10847,14 +11523,18 @@
       <c r="M166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="O166" s="84">
-        <v>2.4999999999999998E-12</v>
+      <c r="O166" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q166" s="84">
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -10894,14 +11574,18 @@
       <c r="M167" s="77">
         <v>20</v>
       </c>
-      <c r="O167" s="77">
-        <v>20</v>
+      <c r="O167" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P167" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q167" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -10941,14 +11625,18 @@
       <c r="M168" s="77">
         <v>0</v>
       </c>
-      <c r="O168" s="77">
-        <v>0</v>
+      <c r="O168" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P168" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q168" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -10988,14 +11676,18 @@
       <c r="M169" s="77">
         <v>1</v>
       </c>
-      <c r="O169" s="77">
+      <c r="O169" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P169" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q169" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -11035,14 +11727,18 @@
       <c r="M170" s="77">
         <v>0</v>
       </c>
-      <c r="O170" s="77">
-        <v>0</v>
+      <c r="O170" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P170" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q170" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -11082,14 +11778,18 @@
       <c r="M171" s="77">
         <v>0.4</v>
       </c>
-      <c r="O171" s="77">
-        <v>0.4</v>
+      <c r="O171" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P171" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q171" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -11129,14 +11829,18 @@
       <c r="M172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-      <c r="O172" s="86">
-        <v>2.0000000000000001E-9</v>
+      <c r="O172" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q172" s="86">
+        <v>2.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -11176,14 +11880,18 @@
       <c r="M173" s="77">
         <v>25</v>
       </c>
-      <c r="O173" s="77">
-        <v>25</v>
+      <c r="O173" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P173" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q173" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -11223,14 +11931,18 @@
       <c r="M174" s="77">
         <v>0</v>
       </c>
-      <c r="O174" s="77">
-        <v>0</v>
+      <c r="O174" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P174" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q174" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -11270,14 +11982,18 @@
       <c r="M175" s="77">
         <v>3.98</v>
       </c>
-      <c r="O175" s="77">
-        <v>3.98</v>
+      <c r="O175" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P175" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q175" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -11317,14 +12033,18 @@
       <c r="M176" s="77">
         <v>1</v>
       </c>
-      <c r="O176" s="77">
+      <c r="O176" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P176" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q176" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -11364,14 +12084,18 @@
       <c r="M177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-      <c r="O177" s="78">
-        <v>1.6666666666666666E-4</v>
+      <c r="O177" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q177" s="78">
+        <v>1.6666666666666666E-4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -11411,14 +12135,18 @@
       <c r="M178" s="80">
         <v>1E-8</v>
       </c>
-      <c r="O178" s="80">
-        <v>1E-8</v>
+      <c r="O178" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P178" s="80">
         <v>1E-8</v>
       </c>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q178" s="80">
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -11458,14 +12186,18 @@
       <c r="M179" s="77">
         <v>20</v>
       </c>
-      <c r="O179" s="77">
-        <v>20</v>
+      <c r="O179" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P179" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q179" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -11505,14 +12237,18 @@
       <c r="M180" s="77">
         <v>0</v>
       </c>
-      <c r="O180" s="77">
-        <v>0</v>
+      <c r="O180" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P180" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q180" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -11552,14 +12288,18 @@
       <c r="M181" s="77">
         <v>2</v>
       </c>
-      <c r="O181" s="77">
-        <v>2</v>
+      <c r="O181" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P181" s="77">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q181" s="77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -11599,14 +12339,18 @@
       <c r="M182" s="77">
         <v>1</v>
       </c>
-      <c r="O182" s="77">
+      <c r="O182" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P182" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q182" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -11646,14 +12390,18 @@
       <c r="M183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O183" s="78">
-        <v>8.3333333333333331E-5</v>
+      <c r="O183" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q183" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -11693,14 +12441,18 @@
       <c r="M184" s="77">
         <v>1</v>
       </c>
-      <c r="O184" s="77">
+      <c r="O184" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P184" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q184" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -11740,14 +12492,18 @@
       <c r="M185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-      <c r="O185" s="77">
-        <v>2.3533050791148899E-8</v>
+      <c r="O185" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q185" s="77">
+        <v>2.3533050791148899E-8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -11787,14 +12543,18 @@
       <c r="M186" s="77">
         <v>20</v>
       </c>
-      <c r="O186" s="77">
-        <v>20</v>
+      <c r="O186" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P186" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q186" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -11834,14 +12594,18 @@
       <c r="M187" s="77">
         <v>-0.187</v>
       </c>
-      <c r="O187" s="77">
-        <v>-0.187</v>
+      <c r="O187" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P187" s="77">
         <v>-0.187</v>
       </c>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q187" s="77">
+        <v>-0.187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -11881,14 +12645,18 @@
       <c r="M188" s="77">
         <v>2.48</v>
       </c>
-      <c r="O188" s="77">
-        <v>2.48</v>
+      <c r="O188" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P188" s="77">
         <v>2.48</v>
       </c>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q188" s="77">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -11928,14 +12696,18 @@
       <c r="M189" s="77">
         <v>1</v>
       </c>
-      <c r="O189" s="77">
+      <c r="O189" s="1" t="b">
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="P189" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q189" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -11975,14 +12747,18 @@
       <c r="M190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-      <c r="O190" s="77">
-        <v>6.1060227588121015E-4</v>
+      <c r="O190" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q190" s="77">
+        <v>6.1060227588121015E-4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -12022,14 +12798,18 @@
       <c r="M191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="O191" s="85">
-        <v>3.9999999999999998E-7</v>
+      <c r="O191" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q191" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -12069,14 +12849,18 @@
       <c r="M192" s="77">
         <v>25</v>
       </c>
-      <c r="O192" s="77">
-        <v>25</v>
+      <c r="O192" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P192" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q192" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -12116,14 +12900,18 @@
       <c r="M193" s="77">
         <v>0</v>
       </c>
-      <c r="O193" s="77">
-        <v>0</v>
+      <c r="O193" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P193" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q193" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -12163,14 +12951,18 @@
       <c r="M194" s="77">
         <v>3.98</v>
       </c>
-      <c r="O194" s="77">
-        <v>3.98</v>
+      <c r="O194" s="1" t="b">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="P194" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q194" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -12210,14 +13002,18 @@
       <c r="M195" s="77">
         <v>1</v>
       </c>
-      <c r="O195" s="77">
+      <c r="O195" s="1" t="b">
+        <f t="shared" ref="O195:O233" si="17">L195=M195</f>
         <v>1</v>
       </c>
       <c r="P195" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q195" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -12257,14 +13053,18 @@
       <c r="M196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O196" s="78">
-        <v>8.3333333333333331E-5</v>
+      <c r="O196" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q196" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -12304,14 +13104,18 @@
       <c r="M197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="O197" s="85">
-        <v>3.9999999999999998E-7</v>
+      <c r="O197" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q197" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -12351,14 +13155,18 @@
       <c r="M198" s="77">
         <v>25</v>
       </c>
-      <c r="O198" s="77">
-        <v>25</v>
+      <c r="O198" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P198" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q198" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -12398,14 +13206,18 @@
       <c r="M199" s="77">
         <v>0</v>
       </c>
-      <c r="O199" s="77">
-        <v>0</v>
+      <c r="O199" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P199" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q199" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -12445,14 +13257,18 @@
       <c r="M200" s="77">
         <v>3.98</v>
       </c>
-      <c r="O200" s="77">
-        <v>3.98</v>
+      <c r="O200" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P200" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q200" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -12492,14 +13308,18 @@
       <c r="M201" s="77">
         <v>1</v>
       </c>
-      <c r="O201" s="77">
+      <c r="O201" s="1" t="b">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="P201" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q201" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -12539,14 +13359,18 @@
       <c r="M202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O202" s="78">
-        <v>8.3333333333333331E-5</v>
+      <c r="O202" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q202" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -12586,14 +13410,18 @@
       <c r="M203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="O203" s="85">
-        <v>1.9999999999999999E-7</v>
+      <c r="O203" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q203" s="85">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -12633,14 +13461,18 @@
       <c r="M204" s="77">
         <v>25</v>
       </c>
-      <c r="O204" s="77">
-        <v>25</v>
+      <c r="O204" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P204" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q204" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -12680,14 +13512,18 @@
       <c r="M205" s="77">
         <v>0</v>
       </c>
-      <c r="O205" s="77">
-        <v>0</v>
+      <c r="O205" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P205" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q205" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -12727,14 +13563,18 @@
       <c r="M206" s="77">
         <v>3.98</v>
       </c>
-      <c r="O206" s="77">
-        <v>3.98</v>
+      <c r="O206" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P206" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q206" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -12774,14 +13614,18 @@
       <c r="M207" s="77">
         <v>1</v>
       </c>
-      <c r="O207" s="77">
+      <c r="O207" s="1" t="b">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="P207" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q207" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -12821,14 +13665,18 @@
       <c r="M208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O208" s="78">
-        <v>8.3333333333333331E-5</v>
+      <c r="O208" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q208" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -12868,14 +13716,18 @@
       <c r="M209" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="O209" s="95" t="s">
-        <v>90</v>
+      <c r="O209" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P209" s="95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="210" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q209" s="95" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>557</v>
       </c>
@@ -12898,15 +13750,15 @@
         <v>0.5</v>
       </c>
       <c r="H210" s="83">
-        <f t="shared" ref="H210:J210" si="14">0.00002</f>
+        <f t="shared" ref="H210:J210" si="18">0.00002</f>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="I210" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="J210" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="K210" s="83">
@@ -12922,14 +13774,18 @@
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="N210" s="1"/>
-      <c r="O210" s="2">
-        <v>0.01</v>
+      <c r="O210" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P210" s="2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="211" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q210" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>560</v>
       </c>
@@ -12970,14 +13826,18 @@
         <v>0.1</v>
       </c>
       <c r="N211" s="1"/>
-      <c r="O211" s="99">
-        <v>0</v>
+      <c r="O211" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P211" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q211" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>563</v>
       </c>
@@ -13000,37 +13860,41 @@
         <v>0.5</v>
       </c>
       <c r="H212" s="83">
-        <f t="shared" ref="H212:M212" si="15">0.00002 / 14</f>
+        <f t="shared" ref="H212:M212" si="19">0.00002 / 14</f>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="I212" s="83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="J212" s="83">
         <v>2E-3</v>
       </c>
       <c r="K212" s="83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="L212" s="83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="M212" s="83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="N212" s="1"/>
-      <c r="O212" s="100">
+      <c r="O212" s="1" t="b">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="P212" s="100">
+        <v>1</v>
+      </c>
+      <c r="Q212" s="100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="213" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>507</v>
       </c>
@@ -13071,14 +13935,18 @@
         <v>476</v>
       </c>
       <c r="N213" s="1"/>
-      <c r="O213" s="98">
+      <c r="O213" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="P213" s="98">
         <v>0.1</v>
       </c>
-      <c r="P213" s="98" t="s">
+      <c r="Q213" s="98" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="214" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -13119,14 +13987,18 @@
         <v>0</v>
       </c>
       <c r="N214" s="1"/>
-      <c r="O214" s="98">
-        <v>0.04</v>
+      <c r="O214" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P214" s="98">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="215" spans="1:16" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q214" s="98">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -13167,14 +14039,18 @@
         <v>1E-3</v>
       </c>
       <c r="N215" s="1"/>
-      <c r="O215" s="98">
-        <v>1E-3</v>
+      <c r="O215" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P215" s="98">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q215" s="98">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>515</v>
       </c>
@@ -13198,37 +14074,41 @@
         <v>1.2499999999999999E-6</v>
       </c>
       <c r="H216" s="99">
-        <f t="shared" ref="H216:M216" si="16">1250*0.000001/5</f>
+        <f t="shared" ref="H216:M216" si="20">1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="I216" s="99">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="J216" s="99">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="K216" s="99">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="L216" s="99">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="M216" s="99">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="O216" s="99">
-        <v>2.5000000000000001E-4</v>
+      <c r="O216" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P216" s="99">
         <v>2.5000000000000001E-4</v>
       </c>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q216" s="99">
+        <v>2.5000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -13268,14 +14148,18 @@
       <c r="M217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="O217" s="99">
-        <v>2.0000000000000001E-4</v>
+      <c r="O217" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="P217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>534</v>
       </c>
@@ -13319,8 +14203,12 @@
         <f xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O218" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>535</v>
       </c>
@@ -13366,8 +14254,12 @@
         <f>0.00000000005</f>
         <v>5.0000000000000002E-11</v>
       </c>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O219" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>569</v>
       </c>
@@ -13404,8 +14296,12 @@
         <f>0.0000001 * 10 /2</f>
         <v>4.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O220" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>571</v>
       </c>
@@ -13442,8 +14338,12 @@
         <f>100</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O221" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>536</v>
       </c>
@@ -13482,15 +14382,19 @@
         <v>2.4999999999999998E-11</v>
       </c>
       <c r="L222" s="83">
-        <f>0.000001 / 10000 / 4</f>
-        <v>2.4999999999999998E-11</v>
+        <f>0.000001 / 10000 / 4 / 10</f>
+        <v>2.4999999999999998E-12</v>
       </c>
       <c r="M222" s="83">
         <f>0.000001 / 10000 / 4</f>
         <v>2.4999999999999998E-11</v>
       </c>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O222" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>537</v>
       </c>
@@ -13526,8 +14430,8 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="L223" s="83">
-        <f>0.00001 * 10</f>
-        <v>1E-4</v>
+        <f>0.00001</f>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M223" s="83">
         <f>0.00001 * 10</f>
@@ -13536,364 +14440,492 @@
       <c r="N223" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-    </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O223" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E224" s="96" t="s">
+        <v>580</v>
+      </c>
+      <c r="F224" s="96" t="s">
+        <v>550</v>
+      </c>
+      <c r="G224" s="99">
+        <f>2*0.00001</f>
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="H224" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="I224" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="J224" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="K224" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="L224" s="83">
+        <f xml:space="preserve"> 0.001 * 10</f>
+        <v>0.01</v>
+      </c>
+      <c r="M224" s="83">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E225" s="96" t="s">
+        <v>582</v>
+      </c>
+      <c r="F225" s="96" t="s">
+        <v>550</v>
+      </c>
+      <c r="G225" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H225" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I225" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J225" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K225" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L225" s="99">
+        <f>0.00001 * 2 / 3</f>
+        <v>6.6666666666666675E-6</v>
+      </c>
+      <c r="M225" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N225" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E224" s="96" t="s">
+      <c r="B226" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E226" s="96" t="s">
         <v>551</v>
       </c>
-      <c r="F224" s="96" t="s">
+      <c r="F226" s="96" t="s">
         <v>506</v>
       </c>
-      <c r="G224" s="99">
+      <c r="G226" s="99">
         <f>0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
-      <c r="H224" s="83">
-        <f t="shared" ref="H224:M224" si="17">0.84*(0.36^2)</f>
+      <c r="H226" s="83">
+        <f t="shared" ref="H226:M226" si="21">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
-      <c r="I224" s="83">
+      <c r="I226" s="83">
+        <f t="shared" si="21"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="J226" s="83">
+        <f t="shared" si="21"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="K226" s="83">
+        <f t="shared" si="21"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="L226" s="83">
+        <f t="shared" si="21"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="M226" s="83">
+        <f t="shared" si="21"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="O226" s="1" t="b">
         <f t="shared" si="17"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="J224" s="83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E227" s="96" t="s">
+        <v>552</v>
+      </c>
+      <c r="F227" s="96" t="s">
+        <v>495</v>
+      </c>
+      <c r="G227" s="100">
+        <v>0.2</v>
+      </c>
+      <c r="H227" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="I227" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="J227" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="K227" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="L227" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="M227" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="O227" s="1" t="b">
         <f t="shared" si="17"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="K224" s="83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E228" s="96" t="s">
+        <v>553</v>
+      </c>
+      <c r="F228" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G228" s="100" t="s">
+        <v>476</v>
+      </c>
+      <c r="H228" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="I228" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="J228" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="K228" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="L228" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="M228" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="O228" s="1" t="b">
         <f t="shared" si="17"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="L224" s="83">
-        <f t="shared" si="17"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="M224" s="83">
-        <f t="shared" si="17"/>
-        <v>0.10886399999999999</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E225" s="96" t="s">
-        <v>552</v>
-      </c>
-      <c r="F225" s="96" t="s">
-        <v>495</v>
-      </c>
-      <c r="G225" s="100">
-        <v>0.2</v>
-      </c>
-      <c r="H225" s="83">
-        <v>0.2</v>
-      </c>
-      <c r="I225" s="83">
-        <v>0.2</v>
-      </c>
-      <c r="J225" s="83">
-        <v>0.2</v>
-      </c>
-      <c r="K225" s="83">
-        <v>0.2</v>
-      </c>
-      <c r="L225" s="83">
-        <v>0.2</v>
-      </c>
-      <c r="M225" s="83">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A226" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E226" s="96" t="s">
-        <v>553</v>
-      </c>
-      <c r="F226" s="96" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E229" s="96" t="s">
+        <v>554</v>
+      </c>
+      <c r="F229" s="96" t="s">
         <v>510</v>
       </c>
-      <c r="G226" s="100" t="s">
-        <v>476</v>
-      </c>
-      <c r="H226" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="I226" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="J226" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="K226" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="L226" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="M226" s="83" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A227" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E227" s="96" t="s">
-        <v>554</v>
-      </c>
-      <c r="F227" s="96" t="s">
-        <v>510</v>
-      </c>
-      <c r="G227" s="100">
+      <c r="G229" s="100">
         <f>2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="H227" s="83">
-        <f t="shared" ref="H227:M227" si="18">2*0.1</f>
+      <c r="H229" s="83">
+        <f t="shared" ref="H229:M229" si="22">2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="I227" s="83">
-        <f t="shared" si="18"/>
+      <c r="I229" s="83">
+        <f t="shared" si="22"/>
         <v>0.2</v>
       </c>
-      <c r="J227" s="83">
-        <f t="shared" si="18"/>
+      <c r="J229" s="83">
+        <f t="shared" si="22"/>
         <v>0.2</v>
       </c>
-      <c r="K227" s="83">
-        <f t="shared" si="18"/>
+      <c r="K229" s="83">
+        <f t="shared" si="22"/>
         <v>0.2</v>
       </c>
-      <c r="L227" s="83">
-        <f t="shared" si="18"/>
+      <c r="L229" s="83">
+        <f t="shared" si="22"/>
         <v>0.2</v>
       </c>
-      <c r="M227" s="83">
-        <f t="shared" si="18"/>
+      <c r="M229" s="83">
+        <f t="shared" si="22"/>
         <v>0.2</v>
       </c>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A228" s="2" t="s">
+      <c r="O229" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B228" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E228" s="96" t="s">
+      <c r="B230" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E230" s="96" t="s">
         <v>555</v>
       </c>
-      <c r="F228" s="96" t="s">
+      <c r="F230" s="96" t="s">
         <v>510</v>
       </c>
-      <c r="G228" s="100">
+      <c r="G230" s="100">
         <v>1E-3</v>
       </c>
-      <c r="H228" s="83">
+      <c r="H230" s="83">
         <v>1E-3</v>
       </c>
-      <c r="I228" s="83">
+      <c r="I230" s="83">
         <v>1E-3</v>
       </c>
-      <c r="J228" s="83">
+      <c r="J230" s="83">
         <v>1E-3</v>
       </c>
-      <c r="K228" s="83">
+      <c r="K230" s="83">
         <v>1E-3</v>
       </c>
-      <c r="L228" s="83">
+      <c r="L230" s="83">
         <v>1E-3</v>
       </c>
-      <c r="M228" s="83">
+      <c r="M230" s="83">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A229" s="2" t="s">
+      <c r="O230" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="B229" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E229" s="96" t="s">
+      <c r="B231" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E231" s="96" t="s">
         <v>556</v>
       </c>
-      <c r="F229" s="96" t="s">
+      <c r="F231" s="96" t="s">
         <v>510</v>
       </c>
-      <c r="G229" s="98">
+      <c r="G231" s="98">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="H229" s="83">
+      <c r="H231" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I229" s="83">
+      <c r="I231" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="J229" s="83">
+      <c r="J231" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="K229" s="83">
+      <c r="K231" s="83">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="L229" s="83">
+      <c r="L231" s="83">
+        <f>0.00001 / 2 / 3</f>
+        <v>1.6666666666666669E-6</v>
+      </c>
+      <c r="M231" s="83">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="M229" s="83">
+      <c r="N231" s="1">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A230" s="2" t="s">
+      <c r="O231" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B230" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="E230" s="30" t="s">
+      <c r="B232" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E232" s="30" t="s">
         <v>558</v>
       </c>
-      <c r="F230" s="30" t="s">
+      <c r="F232" s="30" t="s">
         <v>559</v>
       </c>
-      <c r="G230" s="83">
-        <f t="shared" ref="G230:J230" si="19">0.00002 / 14 / 5</f>
+      <c r="G232" s="83">
+        <f t="shared" ref="G232:J232" si="23">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
-      <c r="H230" s="83">
-        <f t="shared" si="19"/>
+      <c r="H232" s="83">
+        <f t="shared" si="23"/>
         <v>2.8571428571428575E-7</v>
       </c>
-      <c r="I230" s="83">
-        <v>0</v>
-      </c>
-      <c r="J230" s="83">
-        <f t="shared" si="19"/>
+      <c r="I232" s="83">
+        <v>0</v>
+      </c>
+      <c r="J232" s="83">
+        <f t="shared" si="23"/>
         <v>2.8571428571428575E-7</v>
       </c>
-      <c r="K230" s="83">
-        <v>0</v>
-      </c>
-      <c r="L230" s="83">
-        <v>0</v>
-      </c>
-      <c r="M230" s="83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A231" s="2" t="s">
+      <c r="K232" s="83">
+        <v>0</v>
+      </c>
+      <c r="L232" s="83">
+        <v>0</v>
+      </c>
+      <c r="M232" s="83">
+        <v>0</v>
+      </c>
+      <c r="O232" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="B231" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="E231" s="30" t="s">
+      <c r="B233" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E233" s="30" t="s">
         <v>558</v>
       </c>
-      <c r="F231" s="30" t="s">
+      <c r="F233" s="30" t="s">
         <v>559</v>
       </c>
-      <c r="G231" s="83">
-        <f t="shared" ref="G231:M231" si="20">0.00002 / 14 / 5 /10</f>
+      <c r="G233" s="83">
+        <f t="shared" ref="G233:M233" si="24">0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="H231" s="83">
-        <f t="shared" si="20"/>
+      <c r="H233" s="83">
+        <f t="shared" si="24"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="I231" s="83">
-        <f t="shared" si="20"/>
+      <c r="I233" s="83">
+        <f t="shared" si="24"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="J231" s="83">
-        <f t="shared" si="20"/>
+      <c r="J233" s="83">
+        <f t="shared" si="24"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="K231" s="83">
-        <f t="shared" si="20"/>
+      <c r="K233" s="83">
+        <f t="shared" si="24"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="L231" s="83">
-        <f t="shared" si="20"/>
+      <c r="L233" s="83">
+        <f t="shared" si="24"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="M231" s="83">
-        <f t="shared" si="20"/>
+      <c r="M233" s="83">
+        <f t="shared" si="24"/>
         <v>2.8571428571428575E-8</v>
       </c>
+      <c r="O233" s="1" t="b">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G230:I231">
+  <conditionalFormatting sqref="G232:I233">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -13915,7 +14947,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G231:M231">
+  <conditionalFormatting sqref="G233:M233">
     <cfRule type="colorScale" priority="361">
       <colorScale>
         <cfvo type="min"/>
@@ -13950,7 +14982,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H210:M210">
-    <cfRule type="colorScale" priority="365">
+    <cfRule type="colorScale" priority="364">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13960,7 +14992,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="364">
+    <cfRule type="colorScale" priority="365">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13972,7 +15004,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H211:M211">
-    <cfRule type="colorScale" priority="367">
+    <cfRule type="colorScale" priority="366">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -13982,7 +15014,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="366">
+    <cfRule type="colorScale" priority="367">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14016,7 +15048,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H213:M213">
-    <cfRule type="colorScale" priority="371">
+    <cfRule type="colorScale" priority="370">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14026,7 +15058,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="370">
+    <cfRule type="colorScale" priority="371">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14038,7 +15070,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H214:M214">
-    <cfRule type="colorScale" priority="373">
+    <cfRule type="colorScale" priority="372">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14048,7 +15080,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="372">
+    <cfRule type="colorScale" priority="373">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14060,7 +15092,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H215:M215">
-    <cfRule type="colorScale" priority="375">
+    <cfRule type="colorScale" priority="374">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14070,7 +15102,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="374">
+    <cfRule type="colorScale" priority="375">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14082,7 +15114,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H218:M218">
-    <cfRule type="colorScale" priority="377">
+    <cfRule type="colorScale" priority="376">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14092,7 +15124,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="376">
+    <cfRule type="colorScale" priority="377">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14104,7 +15136,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H219:M221">
-    <cfRule type="colorScale" priority="391">
+    <cfRule type="colorScale" priority="390">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14114,7 +15146,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="390">
+    <cfRule type="colorScale" priority="391">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14147,7 +15179,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H224:M224">
+  <conditionalFormatting sqref="H226:M226">
+    <cfRule type="colorScale" priority="384">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="385">
       <colorScale>
         <cfvo type="min"/>
@@ -14158,7 +15200,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="384">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H227:M231">
+    <cfRule type="colorScale" priority="386">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="387">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14169,8 +15223,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H225:M229">
-    <cfRule type="colorScale" priority="387">
+  <conditionalFormatting sqref="H223:N223 H224:M224">
+    <cfRule type="colorScale" priority="382">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14180,7 +15234,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="386">
+    <cfRule type="colorScale" priority="383">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14191,8 +15245,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H223:N223">
-    <cfRule type="colorScale" priority="383">
+  <conditionalFormatting sqref="P132:Q132 H132:N132">
+    <cfRule type="colorScale" priority="303">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14202,7 +15256,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="382">
+    <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14213,29 +15267,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H132:P132">
-    <cfRule type="colorScale" priority="304">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="303">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J230">
+  <conditionalFormatting sqref="J232">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -14257,7 +15289,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K230:K231">
+  <conditionalFormatting sqref="K232:K233">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -14268,18 +15310,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L230:M231">
+  <conditionalFormatting sqref="L232:M233">
     <cfRule type="colorScale" priority="388">
       <colorScale>
         <cfvo type="min"/>
@@ -14301,7 +15333,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O127:P128">
+  <conditionalFormatting sqref="P127:Q128">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -14313,7 +15345,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O129:P129 H129:M129">
+  <conditionalFormatting sqref="P129:Q129 H129:N129">
     <cfRule type="colorScale" priority="295">
       <colorScale>
         <cfvo type="min"/>
@@ -14335,7 +15367,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O130:P130 H130:M130">
+  <conditionalFormatting sqref="P130:Q130 H130:M130">
     <cfRule type="colorScale" priority="299">
       <colorScale>
         <cfvo type="min"/>
@@ -14357,7 +15389,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O133:P133 H133:M133">
+  <conditionalFormatting sqref="P133:Q133 H133:M133">
     <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min"/>
@@ -14379,7 +15411,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O138:P138 H138:M138">
+  <conditionalFormatting sqref="P138:Q138 H138:N138">
     <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min"/>
@@ -14391,7 +15423,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O144:P144 H144:M144">
+  <conditionalFormatting sqref="P144:Q144 H144:M144">
     <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min"/>
@@ -14423,17 +15455,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O160:P160 H160:M160">
-    <cfRule type="colorScale" priority="321">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
+  <conditionalFormatting sqref="P160:Q160 H160:M160">
     <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min"/>
@@ -14454,9 +15476,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O166:P166 H166:M166">
-    <cfRule type="colorScale" priority="326">
+    <cfRule type="colorScale" priority="321">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14466,7 +15486,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P166:Q166 H166:M166">
     <cfRule type="colorScale" priority="325">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="326">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp16152\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp31710\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8297F2DF-1CD3-49A1-B936-DC158CBDEFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB0F955-655A-409C-BE0D-A74A90ED9A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="-15990" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -14912,8 +14912,7 @@
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="L233" s="83">
-        <f t="shared" si="24"/>
-        <v>2.8571428571428575E-8</v>
+        <v>0</v>
       </c>
       <c r="M233" s="83">
         <f t="shared" si="24"/>
@@ -14921,7 +14920,7 @@
       </c>
       <c r="O233" s="1" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14982,7 +14981,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H210:M210">
-    <cfRule type="colorScale" priority="364">
+    <cfRule type="colorScale" priority="365">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14992,7 +14991,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="365">
+    <cfRule type="colorScale" priority="364">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15004,7 +15003,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H211:M211">
-    <cfRule type="colorScale" priority="366">
+    <cfRule type="colorScale" priority="367">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15014,7 +15013,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="367">
+    <cfRule type="colorScale" priority="366">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15048,7 +15047,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H213:M213">
-    <cfRule type="colorScale" priority="370">
+    <cfRule type="colorScale" priority="371">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15058,7 +15057,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="371">
+    <cfRule type="colorScale" priority="370">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15070,7 +15069,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H214:M214">
-    <cfRule type="colorScale" priority="372">
+    <cfRule type="colorScale" priority="373">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15080,7 +15079,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="373">
+    <cfRule type="colorScale" priority="372">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15092,7 +15091,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H215:M215">
-    <cfRule type="colorScale" priority="374">
+    <cfRule type="colorScale" priority="375">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15102,7 +15101,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="375">
+    <cfRule type="colorScale" priority="374">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15114,7 +15113,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H218:M218">
-    <cfRule type="colorScale" priority="376">
+    <cfRule type="colorScale" priority="377">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15124,7 +15123,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="377">
+    <cfRule type="colorScale" priority="376">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15136,7 +15135,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H219:M221">
-    <cfRule type="colorScale" priority="390">
+    <cfRule type="colorScale" priority="391">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15146,7 +15145,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="391">
+    <cfRule type="colorScale" priority="390">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15158,7 +15157,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H222:M222">
-    <cfRule type="colorScale" priority="380">
+    <cfRule type="colorScale" priority="381">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15168,7 +15167,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="381">
+    <cfRule type="colorScale" priority="380">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15180,7 +15179,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H226:M226">
-    <cfRule type="colorScale" priority="384">
+    <cfRule type="colorScale" priority="385">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15190,7 +15189,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="385">
+    <cfRule type="colorScale" priority="384">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15224,16 +15223,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H223:N223 H224:M224">
-    <cfRule type="colorScale" priority="382">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="383">
       <colorScale>
         <cfvo type="min"/>
@@ -15244,19 +15233,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P132:Q132 H132:N132">
-    <cfRule type="colorScale" priority="303">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="304">
+    <cfRule type="colorScale" priority="382">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15290,7 +15267,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K232:K233">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15300,7 +15277,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15389,8 +15366,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P133:Q133 H133:M133">
-    <cfRule type="colorScale" priority="307">
+  <conditionalFormatting sqref="P132:Q132 H132:N132">
+    <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15400,7 +15377,29 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="303">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P133:Q133 H133:M133">
     <cfRule type="colorScale" priority="308">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15456,6 +15455,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P160:Q160 H160:M160">
+    <cfRule type="colorScale" priority="321">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min"/>
@@ -15476,7 +15485,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="321">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P166:Q166 H166:M166">
+    <cfRule type="colorScale" priority="326">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15486,19 +15497,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P166:Q166 H166:M166">
     <cfRule type="colorScale" priority="325">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="326">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp31710\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp42483\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB0F955-655A-409C-BE0D-A74A90ED9A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFA639B-7CD0-4676-B02A-AD5B173D0023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="-15990" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="586">
   <si>
     <t>input_file</t>
   </si>
@@ -1783,6 +1783,15 @@
   </si>
   <si>
     <t>Vmax parameter for amino acids xylem loading</t>
+  </si>
+  <si>
+    <t>cmax_AA</t>
+  </si>
+  <si>
+    <t>Maximal rate of amino acid catabolism in the root segment</t>
+  </si>
+  <si>
+    <t>RC_ref_no_N_deficit</t>
   </si>
 </sst>
 </file>
@@ -2969,7 +2978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q233"/>
+  <dimension ref="A1:R234"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
@@ -2977,10 +2986,10 @@
     <col min="5" max="5" width="23.28515625" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" style="37" customWidth="1"/>
-    <col min="8" max="17" width="39.85546875" style="1" customWidth="1"/>
+    <col min="8" max="18" width="39.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -3018,22 +3027,25 @@
         <v>568</v>
       </c>
       <c r="M1" s="97" t="s">
+        <v>585</v>
+      </c>
+      <c r="N1" s="97" t="s">
         <v>576</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="P1" s="97" t="s">
+      <c r="Q1" s="97" t="s">
         <v>522</v>
       </c>
-      <c r="Q1" s="97" t="s">
+      <c r="R1" s="97" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>524</v>
       </c>
@@ -3073,18 +3085,21 @@
       <c r="M2" s="36" t="s">
         <v>476</v>
       </c>
-      <c r="O2" s="1" t="b">
-        <f>L2=M2</f>
-        <v>1</v>
-      </c>
-      <c r="P2" s="36" t="s">
+      <c r="N2" s="36" t="s">
+        <v>476</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <f>L2=N2</f>
+        <v>1</v>
+      </c>
+      <c r="Q2" s="36" t="s">
         <v>528</v>
       </c>
-      <c r="Q2" s="36" t="s">
+      <c r="R2" s="36" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" s="1" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3124,18 +3139,21 @@
       <c r="M3" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="O3" s="1" t="b">
-        <f t="shared" ref="O3:O66" si="0">L3=M3</f>
-        <v>1</v>
-      </c>
-      <c r="P3" s="36" t="s">
-        <v>489</v>
+      <c r="N3" s="36" t="s">
+        <v>577</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <f t="shared" ref="P3:P66" si="0">L3=N3</f>
+        <v>1</v>
       </c>
       <c r="Q3" s="36" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R3" s="36" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3175,18 +3193,21 @@
       <c r="M4" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="O4" s="1" t="b">
+      <c r="N4" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="P4" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P4" s="36" t="s">
-        <v>482</v>
       </c>
       <c r="Q4" s="36" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R4" s="36" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3226,18 +3247,21 @@
       <c r="M5" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="O5" s="1" t="b">
+      <c r="N5" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="P5" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P5" s="36" t="s">
-        <v>494</v>
       </c>
       <c r="Q5" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R5" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3277,18 +3301,21 @@
       <c r="M6" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="O6" s="1" t="b">
+      <c r="N6" s="36" t="s">
+        <v>577</v>
+      </c>
+      <c r="P6" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P6" s="36" t="s">
-        <v>521</v>
       </c>
       <c r="Q6" s="36" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R6" s="36" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3328,18 +3355,21 @@
       <c r="M7" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="O7" s="1" t="b">
+      <c r="N7" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="P7" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P7" s="36" t="s">
-        <v>494</v>
       </c>
       <c r="Q7" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R7" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>529</v>
       </c>
@@ -3379,18 +3409,21 @@
       <c r="M8" s="36">
         <v>0</v>
       </c>
-      <c r="O8" s="1" t="b">
+      <c r="N8" s="36">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P8" s="36">
-        <v>0</v>
-      </c>
       <c r="Q8" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3430,18 +3463,21 @@
       <c r="M9" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O9" s="1" t="b">
+      <c r="N9" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P9" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="Q9" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3481,18 +3517,21 @@
       <c r="M10" s="77">
         <v>1</v>
       </c>
-      <c r="O10" s="1" t="b">
+      <c r="N10" s="77">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P10" s="77">
-        <v>1</v>
-      </c>
       <c r="Q10" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3532,18 +3571,21 @@
       <c r="M11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O11" s="1" t="b">
+      <c r="N11" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P11" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P11" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q11" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3583,18 +3625,21 @@
       <c r="M12" s="85">
         <v>180</v>
       </c>
-      <c r="O12" s="1" t="b">
+      <c r="N12" s="85">
+        <v>180</v>
+      </c>
+      <c r="P12" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P12" s="85">
-        <v>180</v>
       </c>
       <c r="Q12" s="85">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12" s="85">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3634,18 +3679,21 @@
       <c r="M13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="O13" s="1" t="b">
+      <c r="N13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+      <c r="P13" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P13" s="78">
-        <v>4.1666666999999998E-2</v>
       </c>
       <c r="Q13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3685,18 +3733,21 @@
       <c r="M14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="O14" s="1" t="b">
+      <c r="N14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+      <c r="P14" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P14" s="79">
-        <v>4.1666666999999998E-2</v>
       </c>
       <c r="Q14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3736,18 +3787,21 @@
       <c r="M15" s="77">
         <v>1</v>
       </c>
-      <c r="O15" s="1" t="b">
+      <c r="N15" s="77">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P15" s="77">
-        <v>1</v>
-      </c>
       <c r="Q15" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3787,18 +3841,21 @@
       <c r="M16" s="77">
         <v>0</v>
       </c>
-      <c r="O16" s="1" t="b">
+      <c r="N16" s="77">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P16" s="77">
-        <v>0</v>
-      </c>
       <c r="Q16" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3838,18 +3895,21 @@
       <c r="M17" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O17" s="1" t="b">
+      <c r="N17" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P17" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P17" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q17" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3889,18 +3949,21 @@
       <c r="M18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="O18" s="1" t="b">
+      <c r="N18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="P18" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P18" s="80">
-        <v>5.0000000000000001E-9</v>
       </c>
       <c r="Q18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -3940,18 +4003,21 @@
       <c r="M19" s="77">
         <v>10</v>
       </c>
-      <c r="O19" s="1" t="b">
+      <c r="N19" s="77">
+        <v>10</v>
+      </c>
+      <c r="P19" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P19" s="77">
-        <v>10</v>
       </c>
       <c r="Q19" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -3991,18 +4057,21 @@
       <c r="M20" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O20" s="1" t="b">
+      <c r="N20" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P20" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P20" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q20" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R20" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -4042,18 +4111,21 @@
       <c r="M21" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O21" s="1" t="b">
+      <c r="N21" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P21" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P21" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q21" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R21" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -4093,18 +4165,21 @@
       <c r="M22" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O22" s="1" t="b">
+      <c r="N22" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P22" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P22" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q22" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R22" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -4144,18 +4219,21 @@
       <c r="M23" s="77">
         <v>86400</v>
       </c>
-      <c r="O23" s="1" t="b">
+      <c r="N23" s="77">
+        <v>86400</v>
+      </c>
+      <c r="P23" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P23" s="77">
-        <v>86400</v>
       </c>
       <c r="Q23" s="77">
         <v>86400</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23" s="77">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -4195,18 +4273,21 @@
       <c r="M24" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O24" s="1" t="b">
+      <c r="N24" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P24" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P24" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="Q24" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R24" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -4246,18 +4327,21 @@
       <c r="M25" s="77">
         <v>3</v>
       </c>
-      <c r="O25" s="1" t="b">
+      <c r="N25" s="77">
+        <v>3</v>
+      </c>
+      <c r="P25" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P25" s="77">
-        <v>3</v>
       </c>
       <c r="Q25" s="77">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R25" s="77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -4297,18 +4381,21 @@
       <c r="M26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O26" s="1" t="b">
+      <c r="N26" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="P26" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P26" s="81" t="s">
-        <v>88</v>
       </c>
       <c r="Q26" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R26" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -4348,18 +4435,21 @@
       <c r="M27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O27" s="1" t="b">
+      <c r="N27" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="P27" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P27" s="81" t="s">
-        <v>88</v>
       </c>
       <c r="Q27" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R27" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -4399,18 +4489,21 @@
       <c r="M28" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O28" s="1" t="b">
+      <c r="N28" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P28" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P28" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q28" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R28" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4450,18 +4543,21 @@
       <c r="M29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O29" s="1" t="b">
+      <c r="N29" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="P29" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P29" s="81" t="s">
-        <v>88</v>
       </c>
       <c r="Q29" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R29" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4501,18 +4597,21 @@
       <c r="M30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="O30" s="1" t="b">
+      <c r="N30" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="P30" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P30" s="81" t="s">
-        <v>88</v>
       </c>
       <c r="Q30" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R30" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4552,18 +4651,21 @@
       <c r="M31" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="1" t="b">
+      <c r="N31" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P31" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P31" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q31" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R31" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4603,18 +4705,21 @@
       <c r="M32" s="77">
         <v>0.33</v>
       </c>
-      <c r="O32" s="1" t="b">
+      <c r="N32" s="77">
+        <v>0.33</v>
+      </c>
+      <c r="P32" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P32" s="77">
-        <v>0.33</v>
       </c>
       <c r="Q32" s="77">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R32" s="77">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4654,18 +4759,21 @@
       <c r="M33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O33" s="1" t="b">
+      <c r="N33" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P33" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P33" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q33" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4705,18 +4813,21 @@
       <c r="M34" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O34" s="1" t="b">
+      <c r="N34" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P34" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P34" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q34" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R34" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4756,18 +4867,21 @@
       <c r="M35" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O35" s="1" t="b">
+      <c r="N35" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P35" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P35" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q35" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R35" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4807,18 +4921,21 @@
       <c r="M36" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O36" s="1" t="b">
+      <c r="N36" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P36" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P36" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="Q36" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R36" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4858,18 +4975,21 @@
       <c r="M37" s="85" t="s">
         <v>433</v>
       </c>
-      <c r="O37" s="1" t="b">
+      <c r="N37" s="85" t="s">
+        <v>433</v>
+      </c>
+      <c r="P37" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P37" s="85" t="s">
-        <v>433</v>
       </c>
       <c r="Q37" s="85" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R37" s="85" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -4909,18 +5029,21 @@
       <c r="M38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="O38" s="1" t="b">
+      <c r="N38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="P38" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P38" s="80">
-        <v>9.9999999999999995E-7</v>
       </c>
       <c r="Q38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -4960,18 +5083,21 @@
       <c r="M39" s="86">
         <v>1E-3</v>
       </c>
-      <c r="O39" s="1" t="b">
+      <c r="N39" s="86">
+        <v>1E-3</v>
+      </c>
+      <c r="P39" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P39" s="86">
-        <v>1E-3</v>
       </c>
       <c r="Q39" s="86">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R39" s="86">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -5011,18 +5137,21 @@
       <c r="M40" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O40" s="1" t="b">
+      <c r="N40" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P40" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P40" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="Q40" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R40" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -5062,18 +5191,21 @@
       <c r="M41" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="O41" s="1" t="b">
+      <c r="N41" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="P41" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P41" s="77" t="s">
-        <v>89</v>
       </c>
       <c r="Q41" s="77" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R41" s="77" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -5113,18 +5245,21 @@
       <c r="M42" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O42" s="1" t="b">
+      <c r="N42" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P42" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P42" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="Q42" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R42" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -5164,18 +5299,21 @@
       <c r="M43" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O43" s="1" t="b">
+      <c r="N43" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P43" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P43" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q43" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R43" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -5215,18 +5353,21 @@
       <c r="M44" s="77">
         <v>120</v>
       </c>
-      <c r="O44" s="1" t="b">
+      <c r="N44" s="77">
+        <v>120</v>
+      </c>
+      <c r="P44" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P44" s="77">
-        <v>120</v>
       </c>
       <c r="Q44" s="77">
         <v>120</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R44" s="77">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -5266,18 +5407,21 @@
       <c r="M45" s="77">
         <v>0</v>
       </c>
-      <c r="O45" s="1" t="b">
+      <c r="N45" s="77">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P45" s="77">
-        <v>0</v>
-      </c>
       <c r="Q45" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R45" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -5317,18 +5461,21 @@
       <c r="M46" s="77">
         <v>0</v>
       </c>
-      <c r="O46" s="1" t="b">
+      <c r="N46" s="77">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P46" s="77">
-        <v>0</v>
-      </c>
       <c r="Q46" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R46" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -5368,18 +5515,21 @@
       <c r="M47" s="77">
         <v>-0.1</v>
       </c>
-      <c r="O47" s="1" t="b">
+      <c r="N47" s="77">
+        <v>-0.1</v>
+      </c>
+      <c r="P47" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P47" s="77">
-        <v>-0.1</v>
       </c>
       <c r="Q47" s="77">
         <v>-0.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R47" s="77">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -5419,18 +5569,21 @@
       <c r="M48" s="77">
         <v>-0.2</v>
       </c>
-      <c r="O48" s="1" t="b">
+      <c r="N48" s="77">
+        <v>-0.2</v>
+      </c>
+      <c r="P48" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P48" s="77">
-        <v>-0.2</v>
       </c>
       <c r="Q48" s="77">
         <v>-0.2</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R48" s="77">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -5470,18 +5623,21 @@
       <c r="M49" s="77">
         <v>0.4</v>
       </c>
-      <c r="O49" s="1" t="b">
+      <c r="N49" s="77">
+        <v>0.4</v>
+      </c>
+      <c r="P49" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P49" s="77">
-        <v>0.4</v>
       </c>
       <c r="Q49" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R49" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -5521,18 +5677,21 @@
       <c r="M50" s="77">
         <v>0</v>
       </c>
-      <c r="O50" s="1" t="b">
+      <c r="N50" s="77">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P50" s="77">
-        <v>0</v>
-      </c>
       <c r="Q50" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R50" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -5572,18 +5731,21 @@
       <c r="M51" s="77">
         <v>1200</v>
       </c>
-      <c r="O51" s="1" t="b">
+      <c r="N51" s="77">
+        <v>1200</v>
+      </c>
+      <c r="P51" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P51" s="77">
-        <v>1200</v>
       </c>
       <c r="Q51" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R51" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -5623,18 +5785,21 @@
       <c r="M52" s="77">
         <v>1200</v>
       </c>
-      <c r="O52" s="1" t="b">
+      <c r="N52" s="77">
+        <v>1200</v>
+      </c>
+      <c r="P52" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P52" s="77">
-        <v>1200</v>
       </c>
       <c r="Q52" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R52" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -5674,18 +5839,21 @@
       <c r="M53" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="O53" s="1" t="b">
+      <c r="N53" s="35" t="s">
+        <v>460</v>
+      </c>
+      <c r="P53" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P53" s="35" t="s">
-        <v>460</v>
       </c>
       <c r="Q53" s="35" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R53" s="35" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -5725,18 +5893,21 @@
       <c r="M54" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O54" s="1" t="b">
+      <c r="N54" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P54" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P54" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="Q54" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R54" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5776,18 +5947,21 @@
       <c r="M55" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O55" s="1" t="b">
+      <c r="N55" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P55" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P55" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="Q55" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R55" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -5827,18 +6001,21 @@
       <c r="M56" s="77">
         <v>0</v>
       </c>
-      <c r="O56" s="1" t="b">
+      <c r="N56" s="77">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P56" s="77">
-        <v>0</v>
-      </c>
       <c r="Q56" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R56" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -5878,18 +6055,21 @@
       <c r="M57" s="77">
         <v>0.5</v>
       </c>
-      <c r="O57" s="1" t="b">
+      <c r="N57" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="P57" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P57" s="77">
-        <v>0.5</v>
       </c>
       <c r="Q57" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R57" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -5929,18 +6109,21 @@
       <c r="M58" s="77">
         <v>0.05</v>
       </c>
-      <c r="O58" s="1" t="b">
+      <c r="N58" s="77">
+        <v>0.05</v>
+      </c>
+      <c r="P58" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P58" s="77">
-        <v>0.05</v>
       </c>
       <c r="Q58" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R58" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -5980,18 +6163,21 @@
       <c r="M59" s="80">
         <v>1E-3</v>
       </c>
-      <c r="O59" s="1" t="b">
+      <c r="N59" s="80">
+        <v>1E-3</v>
+      </c>
+      <c r="P59" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P59" s="80">
-        <v>1E-3</v>
       </c>
       <c r="Q59" s="80">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R59" s="80">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -6031,18 +6217,21 @@
       <c r="M60" s="77">
         <v>0</v>
       </c>
-      <c r="O60" s="1" t="b">
+      <c r="N60" s="77">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P60" s="77">
-        <v>0</v>
-      </c>
       <c r="Q60" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R60" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -6082,18 +6271,21 @@
       <c r="M61" s="77">
         <v>1E-4</v>
       </c>
-      <c r="O61" s="1" t="b">
+      <c r="N61" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="P61" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P61" s="77">
-        <v>1E-4</v>
       </c>
       <c r="Q61" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R61" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -6133,18 +6325,21 @@
       <c r="M62" s="77">
         <v>1E-4</v>
       </c>
-      <c r="O62" s="1" t="b">
+      <c r="N62" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="P62" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P62" s="77">
-        <v>1E-4</v>
       </c>
       <c r="Q62" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R62" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -6184,18 +6379,21 @@
       <c r="M63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="O63" s="1" t="b">
+      <c r="N63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="P63" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P63" s="77">
-        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -6235,18 +6433,21 @@
       <c r="M64" s="77">
         <v>1.22E-4</v>
       </c>
-      <c r="O64" s="1" t="b">
+      <c r="N64" s="77">
+        <v>1.22E-4</v>
+      </c>
+      <c r="P64" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P64" s="77">
-        <v>1.22E-4</v>
       </c>
       <c r="Q64" s="77">
         <v>1.22E-4</v>
       </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R64" s="77">
+        <v>1.22E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -6286,18 +6487,21 @@
       <c r="M65" s="77">
         <v>1</v>
       </c>
-      <c r="O65" s="1" t="b">
+      <c r="N65" s="77">
+        <v>1</v>
+      </c>
+      <c r="P65" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P65" s="77">
-        <v>1</v>
-      </c>
       <c r="Q65" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R65" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -6337,18 +6541,21 @@
       <c r="M66" s="77">
         <v>0.95</v>
       </c>
-      <c r="O66" s="1" t="b">
+      <c r="N66" s="77">
+        <v>0.95</v>
+      </c>
+      <c r="P66" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="P66" s="77">
-        <v>0.95</v>
       </c>
       <c r="Q66" s="77">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R66" s="77">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -6388,18 +6595,21 @@
       <c r="M67" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O67" s="1" t="b">
-        <f t="shared" ref="O67:O130" si="1">L67=M67</f>
-        <v>1</v>
-      </c>
-      <c r="P67" s="77" t="s">
+      <c r="N67" s="77" t="s">
         <v>88</v>
+      </c>
+      <c r="P67" s="1" t="b">
+        <f t="shared" ref="P67:P130" si="1">L67=N67</f>
+        <v>1</v>
       </c>
       <c r="Q67" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R67" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -6439,18 +6649,21 @@
       <c r="M68" s="77">
         <v>5</v>
       </c>
-      <c r="O68" s="1" t="b">
+      <c r="N68" s="77">
+        <v>5</v>
+      </c>
+      <c r="P68" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P68" s="77">
-        <v>5</v>
       </c>
       <c r="Q68" s="77">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R68" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -6490,18 +6703,21 @@
       <c r="M69" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="O69" s="1" t="b">
+      <c r="N69" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P69" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P69" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q69" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R69" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -6541,18 +6757,21 @@
       <c r="M70" s="77">
         <v>50</v>
       </c>
-      <c r="O70" s="1" t="b">
+      <c r="N70" s="77">
+        <v>50</v>
+      </c>
+      <c r="P70" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P70" s="77">
-        <v>50</v>
       </c>
       <c r="Q70" s="77">
         <v>50</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R70" s="77">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -6592,18 +6811,21 @@
       <c r="M71" s="78">
         <v>1453890.8941884842</v>
       </c>
-      <c r="O71" s="1" t="b">
+      <c r="N71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+      <c r="P71" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P71" s="78">
-        <v>1453890.8941884842</v>
       </c>
       <c r="Q71" s="78">
         <v>1453890.8941884842</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -6643,18 +6865,21 @@
       <c r="M72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-      <c r="O72" s="1" t="b">
+      <c r="N72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+      <c r="P72" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P72" s="78">
-        <v>1.3888888888888888E-5</v>
       </c>
       <c r="Q72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -6694,18 +6919,21 @@
       <c r="M73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-      <c r="O73" s="1" t="b">
+      <c r="N73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+      <c r="P73" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P73" s="79">
-        <v>6.5011574074074071E-4</v>
       </c>
       <c r="Q73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -6745,18 +6973,21 @@
       <c r="M74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-      <c r="O74" s="1" t="b">
+      <c r="N74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+      <c r="P74" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P74" s="85">
-        <v>4.7400000000000003E-3</v>
       </c>
       <c r="Q74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -6795,20 +7026,24 @@
         <v>282528</v>
       </c>
       <c r="M75" s="79">
+        <f>282528</f>
         <v>282528</v>
       </c>
-      <c r="O75" s="1" t="b">
+      <c r="N75" s="79">
+        <v>282528</v>
+      </c>
+      <c r="P75" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P75" s="79">
-        <v>282528</v>
       </c>
       <c r="Q75" s="79">
         <v>282528</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R75" s="79">
+        <v>282528</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -6848,18 +7083,21 @@
       <c r="M76" s="85">
         <v>0.56999999999999995</v>
       </c>
-      <c r="O76" s="1" t="b">
+      <c r="N76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="P76" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P76" s="85">
-        <v>0.56999999999999995</v>
       </c>
       <c r="Q76" s="85">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -6899,18 +7137,21 @@
       <c r="M77" s="87">
         <v>0.16</v>
       </c>
-      <c r="O77" s="1" t="b">
+      <c r="N77" s="87">
+        <v>0.16</v>
+      </c>
+      <c r="P77" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P77" s="87">
-        <v>0.16</v>
       </c>
       <c r="Q77" s="87">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R77" s="87">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -6950,18 +7191,21 @@
       <c r="M78" s="77">
         <v>0</v>
       </c>
-      <c r="O78" s="1" t="b">
+      <c r="N78" s="77">
+        <v>0</v>
+      </c>
+      <c r="P78" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P78" s="77">
-        <v>0</v>
-      </c>
       <c r="Q78" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R78" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -7001,18 +7245,21 @@
       <c r="M79" s="78">
         <v>745476480000</v>
       </c>
-      <c r="O79" s="1" t="b">
+      <c r="N79" s="78">
+        <v>745476480000</v>
+      </c>
+      <c r="P79" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P79" s="78">
-        <v>745476480000</v>
       </c>
       <c r="Q79" s="78">
         <v>745476480000</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R79" s="78">
+        <v>745476480000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -7052,18 +7299,21 @@
       <c r="M80" s="77">
         <v>100</v>
       </c>
-      <c r="O80" s="1" t="b">
+      <c r="N80" s="77">
+        <v>100</v>
+      </c>
+      <c r="P80" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P80" s="77">
-        <v>100</v>
       </c>
       <c r="Q80" s="77">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R80" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -7103,18 +7353,21 @@
       <c r="M81" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="O81" s="1" t="b">
+      <c r="N81" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P81" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P81" s="77" t="s">
-        <v>88</v>
       </c>
       <c r="Q81" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R81" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -7154,18 +7407,21 @@
       <c r="M82" s="85">
         <v>21600</v>
       </c>
-      <c r="O82" s="1" t="b">
+      <c r="N82" s="85">
+        <v>21600</v>
+      </c>
+      <c r="P82" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P82" s="85">
-        <v>21600</v>
       </c>
       <c r="Q82" s="85">
         <v>21600</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R82" s="85">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -7205,18 +7461,21 @@
       <c r="M83" s="77">
         <v>0.5</v>
       </c>
-      <c r="O83" s="1" t="b">
+      <c r="N83" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="P83" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P83" s="77">
-        <v>0.5</v>
       </c>
       <c r="Q83" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R83" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -7256,18 +7515,21 @@
       <c r="M84" s="85">
         <v>60479.999999999993</v>
       </c>
-      <c r="O84" s="1" t="b">
+      <c r="N84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+      <c r="P84" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P84" s="85">
-        <v>60479.999999999993</v>
       </c>
       <c r="Q84" s="85">
         <v>60479.999999999993</v>
       </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -7307,18 +7569,21 @@
       <c r="M85" s="77">
         <v>0.85</v>
       </c>
-      <c r="O85" s="1" t="b">
+      <c r="N85" s="77">
+        <v>0.85</v>
+      </c>
+      <c r="P85" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P85" s="77">
-        <v>0.85</v>
       </c>
       <c r="Q85" s="77">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R85" s="77">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -7358,18 +7623,21 @@
       <c r="M86" s="77">
         <v>518400</v>
       </c>
-      <c r="O86" s="1" t="b">
+      <c r="N86" s="77">
+        <v>518400</v>
+      </c>
+      <c r="P86" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P86" s="77">
-        <v>518400</v>
       </c>
       <c r="Q86" s="77">
         <v>518400</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R86" s="77">
+        <v>518400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -7409,18 +7677,21 @@
       <c r="M87" s="77">
         <v>5184000</v>
       </c>
-      <c r="O87" s="1" t="b">
+      <c r="N87" s="77">
+        <v>5184000</v>
+      </c>
+      <c r="P87" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P87" s="77">
-        <v>5184000</v>
       </c>
       <c r="Q87" s="77">
         <v>5184000</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R87" s="77">
+        <v>5184000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -7460,18 +7731,21 @@
       <c r="M88" s="86">
         <v>50000</v>
       </c>
-      <c r="O88" s="1" t="b">
+      <c r="N88" s="86">
+        <v>50000</v>
+      </c>
+      <c r="P88" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P88" s="86">
-        <v>50000</v>
       </c>
       <c r="Q88" s="86">
         <v>50000</v>
       </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R88" s="86">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -7511,18 +7785,21 @@
       <c r="M89" s="77">
         <v>140000</v>
       </c>
-      <c r="O89" s="1" t="b">
+      <c r="N89" s="77">
+        <v>140000</v>
+      </c>
+      <c r="P89" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P89" s="77">
-        <v>140000</v>
       </c>
       <c r="Q89" s="77">
         <v>140000</v>
       </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R89" s="77">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -7562,18 +7839,21 @@
       <c r="M90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-      <c r="O90" s="1" t="b">
+      <c r="N90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+      <c r="P90" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P90" s="78">
-        <v>3.6636136999999999E-2</v>
       </c>
       <c r="Q90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -7613,18 +7893,21 @@
       <c r="M91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="O91" s="1" t="b">
+      <c r="N91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="P91" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P91" s="77">
-        <v>4.4999999999999997E-3</v>
       </c>
       <c r="Q91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -7664,18 +7947,21 @@
       <c r="M92" s="77">
         <v>0.05</v>
       </c>
-      <c r="O92" s="1" t="b">
+      <c r="N92" s="77">
+        <v>0.05</v>
+      </c>
+      <c r="P92" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P92" s="77">
-        <v>0.05</v>
       </c>
       <c r="Q92" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R92" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -7715,18 +8001,21 @@
       <c r="M93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="O93" s="1" t="b">
+      <c r="N93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="P93" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P93" s="77">
-        <v>6.0000000000000002E-6</v>
       </c>
       <c r="Q93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -7766,18 +8055,21 @@
       <c r="M94" s="77">
         <v>1E-3</v>
       </c>
-      <c r="O94" s="1" t="b">
+      <c r="N94" s="77">
+        <v>1E-3</v>
+      </c>
+      <c r="P94" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P94" s="77">
-        <v>0</v>
-      </c>
       <c r="Q94" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R94" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -7817,18 +8109,21 @@
       <c r="M95" s="77">
         <v>374999999.99999994</v>
       </c>
-      <c r="O95" s="1" t="b">
+      <c r="N95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+      <c r="P95" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P95" s="77">
-        <v>374999999.99999994</v>
       </c>
       <c r="Q95" s="77">
         <v>374999999.99999994</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -7868,18 +8163,21 @@
       <c r="M96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="O96" s="1" t="b">
+      <c r="N96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="P96" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P96" s="78">
-        <v>3.7037037037037038E-3</v>
       </c>
       <c r="Q96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -7919,18 +8217,21 @@
       <c r="M97" s="77">
         <v>165600</v>
       </c>
-      <c r="O97" s="1" t="b">
+      <c r="N97" s="77">
+        <v>165600</v>
+      </c>
+      <c r="P97" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P97" s="77">
-        <v>165600</v>
       </c>
       <c r="Q97" s="77">
         <v>165600</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R97" s="77">
+        <v>165600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -7970,18 +8271,21 @@
       <c r="M98" s="77">
         <v>20</v>
       </c>
-      <c r="O98" s="1" t="b">
+      <c r="N98" s="77">
+        <v>20</v>
+      </c>
+      <c r="P98" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P98" s="77">
-        <v>20</v>
       </c>
       <c r="Q98" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R98" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -8021,18 +8325,21 @@
       <c r="M99" s="77">
         <v>1</v>
       </c>
-      <c r="O99" s="1" t="b">
+      <c r="N99" s="77">
+        <v>1</v>
+      </c>
+      <c r="P99" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P99" s="77">
-        <v>1</v>
-      </c>
       <c r="Q99" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R99" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -8072,18 +8379,21 @@
       <c r="M100" s="77">
         <v>21</v>
       </c>
-      <c r="O100" s="1" t="b">
+      <c r="N100" s="77">
+        <v>21</v>
+      </c>
+      <c r="P100" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P100" s="77">
-        <v>21</v>
       </c>
       <c r="Q100" s="77">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R100" s="77">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -8123,18 +8433,21 @@
       <c r="M101" s="77">
         <v>0.64</v>
       </c>
-      <c r="O101" s="1" t="b">
+      <c r="N101" s="77">
+        <v>0.64</v>
+      </c>
+      <c r="P101" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P101" s="77">
-        <v>0.64</v>
       </c>
       <c r="Q101" s="77">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R101" s="77">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -8174,18 +8487,21 @@
       <c r="M102" s="77">
         <v>8</v>
       </c>
-      <c r="O102" s="1" t="b">
+      <c r="N102" s="77">
+        <v>8</v>
+      </c>
+      <c r="P102" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P102" s="77">
-        <v>8</v>
       </c>
       <c r="Q102" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R102" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -8225,18 +8541,21 @@
       <c r="M103" s="77">
         <v>10</v>
       </c>
-      <c r="O103" s="1" t="b">
+      <c r="N103" s="77">
+        <v>10</v>
+      </c>
+      <c r="P103" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P103" s="77">
-        <v>10</v>
       </c>
       <c r="Q103" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R103" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -8276,18 +8595,21 @@
       <c r="M104" s="77">
         <v>8</v>
       </c>
-      <c r="O104" s="1" t="b">
+      <c r="N104" s="77">
+        <v>8</v>
+      </c>
+      <c r="P104" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P104" s="77">
-        <v>8</v>
       </c>
       <c r="Q104" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R104" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="23" t="s">
         <v>500</v>
       </c>
@@ -8327,18 +8649,21 @@
       <c r="M105" s="77">
         <v>1</v>
       </c>
-      <c r="O105" s="1" t="b">
+      <c r="N105" s="77">
+        <v>1</v>
+      </c>
+      <c r="P105" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P105" s="77">
-        <v>1</v>
-      </c>
       <c r="Q105" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R105" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -8378,18 +8703,21 @@
       <c r="M106" s="77">
         <v>0.5</v>
       </c>
-      <c r="O106" s="1" t="b">
+      <c r="N106" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="P106" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P106" s="77">
-        <v>0.5</v>
       </c>
       <c r="Q106" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R106" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="23" t="s">
         <v>501</v>
       </c>
@@ -8436,18 +8764,22 @@
         <f t="shared" ref="M107" si="4">M105</f>
         <v>1</v>
       </c>
-      <c r="O107" s="1" t="b">
+      <c r="N107" s="58">
+        <f t="shared" ref="N107" si="5">N105</f>
+        <v>1</v>
+      </c>
+      <c r="P107" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P107" s="58">
-        <v>1</v>
-      </c>
       <c r="Q107" s="58">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R107" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="23" t="s">
         <v>502</v>
       </c>
@@ -8471,41 +8803,45 @@
         <v>3</v>
       </c>
       <c r="H108" s="58">
-        <f t="shared" ref="H108:M108" si="5">150*H105</f>
+        <f t="shared" ref="H108:N108" si="6">150*H105</f>
         <v>150</v>
       </c>
       <c r="I108" s="58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>150</v>
       </c>
       <c r="J108" s="58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>150</v>
       </c>
       <c r="K108" s="58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>150</v>
       </c>
       <c r="L108" s="58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>150</v>
       </c>
       <c r="M108" s="58">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="M108" si="7">150*M105</f>
         <v>150</v>
       </c>
-      <c r="O108" s="1" t="b">
+      <c r="N108" s="58">
+        <f t="shared" si="6"/>
+        <v>150</v>
+      </c>
+      <c r="P108" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P108" s="58">
-        <v>150</v>
       </c>
       <c r="Q108" s="58">
         <v>150</v>
       </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R108" s="58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="23" t="s">
         <v>503</v>
       </c>
@@ -8525,45 +8861,49 @@
         <v>506</v>
       </c>
       <c r="G109" s="58">
-        <f t="shared" ref="G109:L109" si="6">G100</f>
+        <f t="shared" ref="G109:L109" si="8">G100</f>
         <v>21</v>
       </c>
       <c r="H109" s="58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="I109" s="58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="J109" s="58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="K109" s="58">
-        <f t="shared" ref="K109" si="7">K100</f>
+        <f t="shared" ref="K109" si="9">K100</f>
         <v>21</v>
       </c>
       <c r="L109" s="58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="M109" s="58">
-        <f t="shared" ref="M109" si="8">M100</f>
+        <f t="shared" ref="M109" si="10">M100</f>
         <v>21</v>
       </c>
-      <c r="O109" s="1" t="b">
+      <c r="N109" s="58">
+        <f t="shared" ref="N109" si="11">N100</f>
+        <v>21</v>
+      </c>
+      <c r="P109" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P109" s="58">
-        <v>21</v>
       </c>
       <c r="Q109" s="58">
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R109" s="58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="23" t="s">
         <v>504</v>
       </c>
@@ -8587,41 +8927,45 @@
         <v>210</v>
       </c>
       <c r="H110" s="58">
-        <f t="shared" ref="H110:M110" si="9">70*H100</f>
+        <f t="shared" ref="H110:N110" si="12">70*H100</f>
         <v>1470</v>
       </c>
       <c r="I110" s="58">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1470</v>
       </c>
       <c r="J110" s="58">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1470</v>
       </c>
       <c r="K110" s="58">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1470</v>
       </c>
       <c r="L110" s="58">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1470</v>
       </c>
       <c r="M110" s="58">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="M110" si="13">70*M100</f>
         <v>1470</v>
       </c>
-      <c r="O110" s="1" t="b">
+      <c r="N110" s="58">
+        <f t="shared" si="12"/>
+        <v>1470</v>
+      </c>
+      <c r="P110" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P110" s="58">
-        <v>1470</v>
       </c>
       <c r="Q110" s="58">
         <v>1470</v>
       </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R110" s="58">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -8661,18 +9005,21 @@
       <c r="M111" s="77">
         <v>0</v>
       </c>
-      <c r="O111" s="1" t="b">
+      <c r="N111" s="77">
+        <v>0</v>
+      </c>
+      <c r="P111" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P111" s="77">
-        <v>0</v>
-      </c>
       <c r="Q111" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R111" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -8712,18 +9059,21 @@
       <c r="M112" s="82">
         <v>1589759.9999999998</v>
       </c>
-      <c r="O112" s="1" t="b">
+      <c r="N112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+      <c r="P112" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P112" s="82">
-        <v>1589759.9999999998</v>
       </c>
       <c r="Q112" s="82">
         <v>1589759.9999999998</v>
       </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -8763,18 +9113,21 @@
       <c r="M113" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="O113" s="1" t="b">
+      <c r="N113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+      <c r="P113" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P113" s="82">
-        <v>6171428.5714285718</v>
       </c>
       <c r="Q113" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -8814,18 +9167,21 @@
       <c r="M114" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="O114" s="1" t="b">
+      <c r="N114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+      <c r="P114" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P114" s="82">
-        <v>6171428.5714285718</v>
       </c>
       <c r="Q114" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -8865,18 +9221,21 @@
       <c r="M115" s="82">
         <v>100</v>
       </c>
-      <c r="O115" s="1" t="b">
+      <c r="N115" s="82">
+        <v>100</v>
+      </c>
+      <c r="P115" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P115" s="82">
-        <v>100</v>
       </c>
       <c r="Q115" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="116" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R115" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -8900,41 +9259,45 @@
         <v>280800</v>
       </c>
       <c r="H116" s="67">
-        <f t="shared" ref="H116:M116" si="10">0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" ref="H116:N116" si="14">0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
       <c r="I116" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>28080</v>
       </c>
       <c r="J116" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>28080</v>
       </c>
       <c r="K116" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>28080</v>
       </c>
       <c r="L116" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>28080</v>
       </c>
       <c r="M116" s="67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>28080</v>
       </c>
-      <c r="O116" s="1" t="b">
+      <c r="N116" s="67">
+        <f t="shared" si="14"/>
+        <v>28080</v>
+      </c>
+      <c r="P116" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P116" s="67">
-        <v>28080</v>
       </c>
       <c r="Q116" s="67">
         <v>28080</v>
       </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R116" s="67">
+        <v>28080</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -8958,41 +9321,45 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H117" s="67">
-        <f t="shared" ref="H117:M117" si="11">1.11 / 10</f>
+        <f t="shared" ref="H117:N117" si="15">1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
       <c r="I117" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="J117" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="K117" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="L117" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="M117" s="67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0.11100000000000002</v>
       </c>
-      <c r="O117" s="1" t="b">
+      <c r="N117" s="67">
+        <f t="shared" si="15"/>
+        <v>0.11100000000000002</v>
+      </c>
+      <c r="P117" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P117" s="67">
-        <v>0.11100000000000002</v>
       </c>
       <c r="Q117" s="67">
         <v>0.11100000000000002</v>
       </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R117" s="67">
+        <v>0.11100000000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="23" t="s">
         <v>497</v>
       </c>
@@ -9032,18 +9399,21 @@
       <c r="M118" s="82">
         <v>100</v>
       </c>
-      <c r="O118" s="1" t="b">
+      <c r="N118" s="82">
+        <v>100</v>
+      </c>
+      <c r="P118" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P118" s="82">
-        <v>100</v>
       </c>
       <c r="Q118" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="119" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R118" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="23" t="s">
         <v>498</v>
       </c>
@@ -9063,45 +9433,49 @@
         <v>431</v>
       </c>
       <c r="G119" s="67">
-        <f t="shared" ref="G119:M119" si="12">5.32 * (60*60*24)</f>
+        <f t="shared" ref="G119:N119" si="16">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H119" s="67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>459648</v>
       </c>
       <c r="I119" s="67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>459648</v>
       </c>
       <c r="J119" s="67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>459648</v>
       </c>
       <c r="K119" s="67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>459648</v>
       </c>
       <c r="L119" s="67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>459648</v>
       </c>
       <c r="M119" s="67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>459648</v>
       </c>
-      <c r="O119" s="1" t="b">
+      <c r="N119" s="67">
+        <f t="shared" si="16"/>
+        <v>459648</v>
+      </c>
+      <c r="P119" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P119" s="67">
-        <v>459648</v>
       </c>
       <c r="Q119" s="67">
         <v>459648</v>
       </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R119" s="67">
+        <v>459648</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="23" t="s">
         <v>499</v>
       </c>
@@ -9125,41 +9499,45 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H120" s="67">
-        <f t="shared" ref="H120:M120" si="13">1.11/8</f>
+        <f t="shared" ref="H120:N120" si="17">1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
       <c r="I120" s="67">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="J120" s="67">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="K120" s="67">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="L120" s="67">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="M120" s="67">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="O120" s="1" t="b">
+      <c r="N120" s="67">
+        <f t="shared" si="17"/>
+        <v>0.13875000000000001</v>
+      </c>
+      <c r="P120" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P120" s="67">
-        <v>0.13875000000000001</v>
       </c>
       <c r="Q120" s="67">
         <v>0.13875000000000001</v>
       </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R120" s="67">
+        <v>0.13875000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -9199,18 +9577,21 @@
       <c r="M121" s="82">
         <v>21600</v>
       </c>
-      <c r="O121" s="1" t="b">
+      <c r="N121" s="82">
+        <v>21600</v>
+      </c>
+      <c r="P121" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P121" s="82">
-        <v>21600</v>
       </c>
       <c r="Q121" s="82">
         <v>21600</v>
       </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R121" s="82">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -9250,18 +9631,21 @@
       <c r="M122" s="88">
         <v>43200</v>
       </c>
-      <c r="O122" s="1" t="b">
+      <c r="N122" s="88">
+        <v>43200</v>
+      </c>
+      <c r="P122" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P122" s="88">
-        <v>43200</v>
       </c>
       <c r="Q122" s="88">
         <v>43200</v>
       </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R122" s="88">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -9301,18 +9685,21 @@
       <c r="M123" s="77">
         <v>0.8</v>
       </c>
-      <c r="O123" s="1" t="b">
+      <c r="N123" s="77">
+        <v>0.8</v>
+      </c>
+      <c r="P123" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P123" s="77">
-        <v>0.8</v>
       </c>
       <c r="Q123" s="77">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R123" s="77">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -9353,18 +9740,21 @@
       <c r="M124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="O124" s="1" t="b">
+      <c r="N124" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="P124" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P124" s="78">
-        <v>2.0833333333333335E-4</v>
       </c>
       <c r="Q124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R124" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -9404,18 +9794,21 @@
       <c r="M125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-      <c r="O125" s="1" t="b">
+      <c r="N125" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+      <c r="P125" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P125" s="77">
-        <v>5.7899999999999998E-7</v>
       </c>
       <c r="Q125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R125" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -9455,18 +9848,21 @@
       <c r="M126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="O126" s="1" t="b">
+      <c r="N126" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="P126" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="P126" s="78">
-        <v>2.0833333333333335E-4</v>
       </c>
       <c r="Q126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R126" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -9506,18 +9902,21 @@
       <c r="M127" s="78">
         <v>0</v>
       </c>
-      <c r="O127" s="1" t="b">
+      <c r="N127" s="78">
+        <v>0</v>
+      </c>
+      <c r="P127" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P127" s="78">
-        <v>0</v>
-      </c>
       <c r="Q127" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R127" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -9557,18 +9956,21 @@
       <c r="M128" s="78">
         <v>0</v>
       </c>
-      <c r="O128" s="1" t="b">
+      <c r="N128" s="78">
+        <v>0</v>
+      </c>
+      <c r="P128" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P128" s="78">
-        <v>0</v>
-      </c>
       <c r="Q128" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R128" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -9593,11 +9995,11 @@
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="I129" s="83">
-        <f t="shared" ref="I129:Q129" si="14">0.0000002*3</f>
+        <f t="shared" ref="I129:R129" si="18">0.0000002*3</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J129" s="83">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="K129" s="83">
@@ -9609,26 +10011,30 @@
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="M129" s="83">
-        <v>0</v>
+        <f>0.0000002 * 2 / 1000</f>
+        <v>3.9999999999999996E-10</v>
       </c>
       <c r="N129" s="83">
+        <v>0</v>
+      </c>
+      <c r="O129" s="83">
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="O129" s="1" t="b">
+      <c r="P129" s="1" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P129" s="83">
-        <f t="shared" si="14"/>
+      <c r="Q129" s="83">
+        <f t="shared" si="18"/>
         <v>5.9999999999999997E-7</v>
       </c>
-      <c r="Q129" s="83">
-        <f t="shared" si="14"/>
+      <c r="R129" s="83">
+        <f t="shared" si="18"/>
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -9649,43 +10055,47 @@
       </c>
       <c r="G130" s="71"/>
       <c r="H130" s="83">
-        <f t="shared" ref="H130:Q130" si="15">1000 * 0.000001 / 12</f>
+        <f t="shared" ref="H130:R130" si="19">1000 * 0.000001 / 12</f>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="I130" s="83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="J130" s="83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="K130" s="83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="L130" s="83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="M130" s="83">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O130" s="1" t="b">
+      <c r="N130" s="83">
+        <f t="shared" si="19"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="P130" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P130" s="83">
-        <f t="shared" si="15"/>
+      <c r="Q130" s="83">
+        <f t="shared" si="19"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="Q130" s="83">
-        <f t="shared" si="15"/>
+      <c r="R130" s="83">
+        <f t="shared" si="19"/>
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -9725,18 +10135,21 @@
       <c r="M131" s="89" t="s">
         <v>533</v>
       </c>
-      <c r="O131" s="1" t="b">
-        <f t="shared" ref="O131:O194" si="16">L131=M131</f>
-        <v>1</v>
-      </c>
-      <c r="P131" s="89" t="s">
+      <c r="N131" s="89" t="s">
         <v>533</v>
+      </c>
+      <c r="P131" s="1" t="b">
+        <f t="shared" ref="P131:P194" si="20">L131=N131</f>
+        <v>1</v>
       </c>
       <c r="Q131" s="89" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R131" s="89" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -9776,25 +10189,29 @@
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="M132" s="83">
+        <f>0.0005 / 10</f>
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="N132" s="83">
         <f>0.0005</f>
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="N132" s="83">
+      <c r="O132" s="83">
         <f>0.0005 * 1.2</f>
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="O132" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="P132" s="83">
-        <v>5.0000000000000001E-4</v>
+      <c r="P132" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="Q132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R132" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -9834,18 +10251,21 @@
       <c r="M133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="O133" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P133" s="83">
+      <c r="N133" s="83">
         <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="P133" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R133" s="83">
+        <v>4.9999999999999999E-13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -9885,18 +10305,21 @@
       <c r="M134" s="77">
         <v>10</v>
       </c>
-      <c r="O134" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P134" s="77">
+      <c r="N134" s="77">
         <v>10</v>
+      </c>
+      <c r="P134" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q134" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R134" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -9936,18 +10359,21 @@
       <c r="M135" s="77">
         <v>-0.04</v>
       </c>
-      <c r="O135" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P135" s="77">
+      <c r="N135" s="77">
         <v>-0.04</v>
+      </c>
+      <c r="P135" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q135" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R135" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -9987,18 +10413,21 @@
       <c r="M136" s="77">
         <v>2.9</v>
       </c>
-      <c r="O136" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P136" s="77">
+      <c r="N136" s="77">
         <v>2.9</v>
+      </c>
+      <c r="P136" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q136" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R136" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -10038,18 +10467,21 @@
       <c r="M137" s="77">
         <v>1</v>
       </c>
-      <c r="O137" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P137" s="77">
+      <c r="N137" s="77">
+        <v>1</v>
+      </c>
+      <c r="P137" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q137" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R137" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
         <v>574</v>
       </c>
@@ -10089,24 +10521,28 @@
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="M138" s="80">
-        <v>1.9999999999999999E-7</v>
-      </c>
-      <c r="N138" s="80">
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="O138" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="P138" s="80">
+      <c r="N138" s="80">
         <v>1.9999999999999999E-7</v>
+      </c>
+      <c r="O138" s="80">
+        <f>0.0000002 * 2 / 10</f>
+        <v>4.0000000000000001E-8</v>
+      </c>
+      <c r="P138" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="Q138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R138" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -10146,18 +10582,21 @@
       <c r="M139" s="77">
         <v>10</v>
       </c>
-      <c r="O139" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P139" s="77">
+      <c r="N139" s="77">
         <v>10</v>
+      </c>
+      <c r="P139" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q139" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R139" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -10197,18 +10636,21 @@
       <c r="M140" s="77">
         <v>-0.04</v>
       </c>
-      <c r="O140" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P140" s="77">
+      <c r="N140" s="77">
         <v>-0.04</v>
+      </c>
+      <c r="P140" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q140" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R140" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -10248,18 +10690,21 @@
       <c r="M141" s="77">
         <v>2.9</v>
       </c>
-      <c r="O141" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P141" s="77">
+      <c r="N141" s="77">
         <v>2.9</v>
+      </c>
+      <c r="P141" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q141" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R141" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -10299,18 +10744,21 @@
       <c r="M142" s="77">
         <v>1</v>
       </c>
-      <c r="O142" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P142" s="77">
+      <c r="N142" s="77">
+        <v>1</v>
+      </c>
+      <c r="P142" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q142" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R142" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -10350,18 +10798,21 @@
       <c r="M143" s="77">
         <v>0</v>
       </c>
-      <c r="O143" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P143" s="77">
-        <v>0</v>
+      <c r="N143" s="77">
+        <v>0</v>
+      </c>
+      <c r="P143" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q143" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R143" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -10401,18 +10852,21 @@
       <c r="M144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="O144" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P144" s="80">
+      <c r="N144" s="80">
         <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="P144" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R144" s="80">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -10452,18 +10906,21 @@
       <c r="M145" s="77">
         <v>0</v>
       </c>
-      <c r="O145" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P145" s="77">
-        <v>0</v>
+      <c r="N145" s="77">
+        <v>0</v>
+      </c>
+      <c r="P145" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q145" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R145" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -10503,18 +10960,21 @@
       <c r="M146" s="77">
         <v>2E-3</v>
       </c>
-      <c r="O146" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P146" s="77">
+      <c r="N146" s="77">
         <v>2E-3</v>
+      </c>
+      <c r="P146" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q146" s="77">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R146" s="77">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -10554,18 +11014,21 @@
       <c r="M147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-      <c r="O147" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P147" s="80">
+      <c r="N147" s="80">
         <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="P147" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R147" s="80">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -10605,18 +11068,21 @@
       <c r="M148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-      <c r="O148" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P148" s="80">
+      <c r="N148" s="80">
         <v>3.7699999999999999E-10</v>
+      </c>
+      <c r="P148" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R148" s="80">
+        <v>3.7699999999999999E-10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -10656,18 +11122,21 @@
       <c r="M149" s="77">
         <v>20</v>
       </c>
-      <c r="O149" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P149" s="77">
+      <c r="N149" s="77">
         <v>20</v>
+      </c>
+      <c r="P149" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q149" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R149" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -10707,18 +11176,21 @@
       <c r="M150" s="77">
         <v>-0.06</v>
       </c>
-      <c r="O150" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P150" s="77">
+      <c r="N150" s="77">
         <v>-0.06</v>
+      </c>
+      <c r="P150" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q150" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R150" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -10758,18 +11230,21 @@
       <c r="M151" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="O151" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P151" s="77">
+      <c r="N151" s="77">
         <v>0.89100000000000001</v>
+      </c>
+      <c r="P151" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q151" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R151" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -10809,18 +11284,21 @@
       <c r="M152" s="77">
         <v>1</v>
       </c>
-      <c r="O152" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P152" s="77">
+      <c r="N152" s="77">
+        <v>1</v>
+      </c>
+      <c r="P152" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q152" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R152" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -10860,18 +11338,21 @@
       <c r="M153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="O153" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P153" s="80">
+      <c r="N153" s="80">
         <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="P153" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R153" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -10911,18 +11392,21 @@
       <c r="M154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-      <c r="O154" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P154" s="80">
+      <c r="N154" s="80">
         <v>5.8333333333333335E-9</v>
+      </c>
+      <c r="P154" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R154" s="80">
+        <v>5.8333333333333335E-9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -10962,18 +11446,21 @@
       <c r="M155" s="77">
         <v>20</v>
       </c>
-      <c r="O155" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P155" s="77">
+      <c r="N155" s="77">
         <v>20</v>
+      </c>
+      <c r="P155" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q155" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R155" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -11013,18 +11500,21 @@
       <c r="M156" s="77">
         <v>-0.06</v>
       </c>
-      <c r="O156" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P156" s="77">
+      <c r="N156" s="77">
         <v>-0.06</v>
+      </c>
+      <c r="P156" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q156" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R156" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -11064,18 +11554,21 @@
       <c r="M157" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="O157" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P157" s="77">
+      <c r="N157" s="77">
         <v>0.89100000000000001</v>
+      </c>
+      <c r="P157" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q157" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R157" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -11115,18 +11608,21 @@
       <c r="M158" s="77">
         <v>1</v>
       </c>
-      <c r="O158" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P158" s="77">
+      <c r="N158" s="77">
+        <v>1</v>
+      </c>
+      <c r="P158" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q158" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R158" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -11166,18 +11662,21 @@
       <c r="M159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="O159" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P159" s="80">
+      <c r="N159" s="80">
         <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="P159" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R159" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -11217,18 +11716,21 @@
       <c r="M160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="O160" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P160" s="83">
+      <c r="N160" s="83">
         <v>4.0000000000000001E-8</v>
+      </c>
+      <c r="P160" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R160" s="83">
+        <v>4.0000000000000001E-8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -11268,18 +11770,21 @@
       <c r="M161" s="77">
         <v>20</v>
       </c>
-      <c r="O161" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P161" s="77">
+      <c r="N161" s="77">
         <v>20</v>
+      </c>
+      <c r="P161" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q161" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R161" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -11319,18 +11824,21 @@
       <c r="M162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-      <c r="O162" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P162" s="77">
+      <c r="N162" s="77">
         <v>-4.4200000000000003E-2</v>
+      </c>
+      <c r="P162" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R162" s="77">
+        <v>-4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -11370,18 +11878,21 @@
       <c r="M163" s="77">
         <v>1.55</v>
       </c>
-      <c r="O163" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P163" s="77">
+      <c r="N163" s="77">
         <v>1.55</v>
+      </c>
+      <c r="P163" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q163" s="77">
         <v>1.55</v>
       </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R163" s="77">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -11421,18 +11932,21 @@
       <c r="M164" s="77">
         <v>1</v>
       </c>
-      <c r="O164" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P164" s="77">
+      <c r="N164" s="77">
+        <v>1</v>
+      </c>
+      <c r="P164" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q164" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R164" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -11472,18 +11986,21 @@
       <c r="M165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="O165" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P165" s="77">
+      <c r="N165" s="77">
         <v>2.7799999999999998E-4</v>
+      </c>
+      <c r="P165" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R165" s="77">
+        <v>2.7799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -11523,18 +12040,21 @@
       <c r="M166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="O166" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P166" s="84">
+      <c r="N166" s="84">
         <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="P166" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R166" s="84">
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -11574,18 +12094,21 @@
       <c r="M167" s="77">
         <v>20</v>
       </c>
-      <c r="O167" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P167" s="77">
+      <c r="N167" s="77">
         <v>20</v>
+      </c>
+      <c r="P167" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q167" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R167" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -11625,18 +12148,21 @@
       <c r="M168" s="77">
         <v>0</v>
       </c>
-      <c r="O168" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P168" s="77">
-        <v>0</v>
+      <c r="N168" s="77">
+        <v>0</v>
+      </c>
+      <c r="P168" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q168" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R168" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -11676,18 +12202,21 @@
       <c r="M169" s="77">
         <v>1</v>
       </c>
-      <c r="O169" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P169" s="77">
+      <c r="N169" s="77">
+        <v>1</v>
+      </c>
+      <c r="P169" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q169" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R169" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -11727,18 +12256,21 @@
       <c r="M170" s="77">
         <v>0</v>
       </c>
-      <c r="O170" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P170" s="77">
-        <v>0</v>
+      <c r="N170" s="77">
+        <v>0</v>
+      </c>
+      <c r="P170" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q170" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R170" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -11778,18 +12310,21 @@
       <c r="M171" s="77">
         <v>0.4</v>
       </c>
-      <c r="O171" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P171" s="77">
+      <c r="N171" s="77">
         <v>0.4</v>
+      </c>
+      <c r="P171" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q171" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R171" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -11829,18 +12364,21 @@
       <c r="M172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-      <c r="O172" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P172" s="86">
+      <c r="N172" s="86">
         <v>2.0000000000000001E-9</v>
+      </c>
+      <c r="P172" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R172" s="86">
+        <v>2.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -11880,18 +12418,21 @@
       <c r="M173" s="77">
         <v>25</v>
       </c>
-      <c r="O173" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P173" s="77">
+      <c r="N173" s="77">
         <v>25</v>
+      </c>
+      <c r="P173" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q173" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R173" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -11931,18 +12472,21 @@
       <c r="M174" s="77">
         <v>0</v>
       </c>
-      <c r="O174" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P174" s="77">
-        <v>0</v>
+      <c r="N174" s="77">
+        <v>0</v>
+      </c>
+      <c r="P174" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q174" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R174" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -11982,18 +12526,21 @@
       <c r="M175" s="77">
         <v>3.98</v>
       </c>
-      <c r="O175" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P175" s="77">
+      <c r="N175" s="77">
         <v>3.98</v>
+      </c>
+      <c r="P175" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q175" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R175" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -12033,18 +12580,21 @@
       <c r="M176" s="77">
         <v>1</v>
       </c>
-      <c r="O176" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P176" s="77">
+      <c r="N176" s="77">
+        <v>1</v>
+      </c>
+      <c r="P176" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q176" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R176" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -12084,18 +12634,21 @@
       <c r="M177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-      <c r="O177" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P177" s="78">
+      <c r="N177" s="78">
         <v>1.6666666666666666E-4</v>
+      </c>
+      <c r="P177" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R177" s="78">
+        <v>1.6666666666666666E-4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -12135,18 +12688,21 @@
       <c r="M178" s="80">
         <v>1E-8</v>
       </c>
-      <c r="O178" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P178" s="80">
+      <c r="N178" s="80">
         <v>1E-8</v>
+      </c>
+      <c r="P178" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q178" s="80">
         <v>1E-8</v>
       </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R178" s="80">
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -12186,18 +12742,21 @@
       <c r="M179" s="77">
         <v>20</v>
       </c>
-      <c r="O179" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P179" s="77">
+      <c r="N179" s="77">
         <v>20</v>
+      </c>
+      <c r="P179" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q179" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R179" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -12237,18 +12796,21 @@
       <c r="M180" s="77">
         <v>0</v>
       </c>
-      <c r="O180" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P180" s="77">
-        <v>0</v>
+      <c r="N180" s="77">
+        <v>0</v>
+      </c>
+      <c r="P180" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q180" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R180" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -12288,18 +12850,21 @@
       <c r="M181" s="77">
         <v>2</v>
       </c>
-      <c r="O181" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P181" s="77">
+      <c r="N181" s="77">
         <v>2</v>
+      </c>
+      <c r="P181" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q181" s="77">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R181" s="77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -12339,18 +12904,21 @@
       <c r="M182" s="77">
         <v>1</v>
       </c>
-      <c r="O182" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P182" s="77">
+      <c r="N182" s="77">
+        <v>1</v>
+      </c>
+      <c r="P182" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q182" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R182" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -12390,18 +12958,21 @@
       <c r="M183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O183" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P183" s="78">
+      <c r="N183" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="P183" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R183" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -12441,18 +13012,21 @@
       <c r="M184" s="77">
         <v>1</v>
       </c>
-      <c r="O184" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P184" s="77">
+      <c r="N184" s="77">
+        <v>1</v>
+      </c>
+      <c r="P184" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q184" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R184" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -12492,18 +13066,21 @@
       <c r="M185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-      <c r="O185" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P185" s="77">
+      <c r="N185" s="77">
         <v>2.3533050791148899E-8</v>
+      </c>
+      <c r="P185" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R185" s="77">
+        <v>2.3533050791148899E-8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -12543,18 +13120,21 @@
       <c r="M186" s="77">
         <v>20</v>
       </c>
-      <c r="O186" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P186" s="77">
+      <c r="N186" s="77">
         <v>20</v>
+      </c>
+      <c r="P186" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q186" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R186" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -12594,18 +13174,21 @@
       <c r="M187" s="77">
         <v>-0.187</v>
       </c>
-      <c r="O187" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P187" s="77">
+      <c r="N187" s="77">
         <v>-0.187</v>
+      </c>
+      <c r="P187" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q187" s="77">
         <v>-0.187</v>
       </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R187" s="77">
+        <v>-0.187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -12645,18 +13228,21 @@
       <c r="M188" s="77">
         <v>2.48</v>
       </c>
-      <c r="O188" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P188" s="77">
+      <c r="N188" s="77">
         <v>2.48</v>
+      </c>
+      <c r="P188" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q188" s="77">
         <v>2.48</v>
       </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R188" s="77">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -12696,18 +13282,21 @@
       <c r="M189" s="77">
         <v>1</v>
       </c>
-      <c r="O189" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P189" s="77">
+      <c r="N189" s="77">
+        <v>1</v>
+      </c>
+      <c r="P189" s="1" t="b">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q189" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R189" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -12747,18 +13336,21 @@
       <c r="M190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-      <c r="O190" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P190" s="77">
+      <c r="N190" s="77">
         <v>6.1060227588121015E-4</v>
+      </c>
+      <c r="P190" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R190" s="77">
+        <v>6.1060227588121015E-4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -12798,18 +13390,21 @@
       <c r="M191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="O191" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P191" s="85">
+      <c r="N191" s="85">
         <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="P191" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R191" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -12849,18 +13444,21 @@
       <c r="M192" s="77">
         <v>25</v>
       </c>
-      <c r="O192" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P192" s="77">
+      <c r="N192" s="77">
         <v>25</v>
+      </c>
+      <c r="P192" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q192" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R192" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -12900,18 +13498,21 @@
       <c r="M193" s="77">
         <v>0</v>
       </c>
-      <c r="O193" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P193" s="77">
-        <v>0</v>
+      <c r="N193" s="77">
+        <v>0</v>
+      </c>
+      <c r="P193" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q193" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R193" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -12951,18 +13552,21 @@
       <c r="M194" s="77">
         <v>3.98</v>
       </c>
-      <c r="O194" s="1" t="b">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="P194" s="77">
+      <c r="N194" s="77">
         <v>3.98</v>
+      </c>
+      <c r="P194" s="1" t="b">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="Q194" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R194" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -13002,18 +13606,21 @@
       <c r="M195" s="77">
         <v>1</v>
       </c>
-      <c r="O195" s="1" t="b">
-        <f t="shared" ref="O195:O233" si="17">L195=M195</f>
-        <v>1</v>
-      </c>
-      <c r="P195" s="77">
+      <c r="N195" s="77">
+        <v>1</v>
+      </c>
+      <c r="P195" s="1" t="b">
+        <f t="shared" ref="P195:P234" si="21">L195=N195</f>
         <v>1</v>
       </c>
       <c r="Q195" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R195" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -13053,18 +13660,21 @@
       <c r="M196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O196" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P196" s="78">
+      <c r="N196" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="P196" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R196" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -13104,18 +13714,21 @@
       <c r="M197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="O197" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P197" s="85">
+      <c r="N197" s="85">
         <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="P197" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R197" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -13155,18 +13768,21 @@
       <c r="M198" s="77">
         <v>25</v>
       </c>
-      <c r="O198" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P198" s="77">
+      <c r="N198" s="77">
         <v>25</v>
+      </c>
+      <c r="P198" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q198" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R198" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -13206,18 +13822,21 @@
       <c r="M199" s="77">
         <v>0</v>
       </c>
-      <c r="O199" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P199" s="77">
-        <v>0</v>
+      <c r="N199" s="77">
+        <v>0</v>
+      </c>
+      <c r="P199" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q199" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R199" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -13257,18 +13876,21 @@
       <c r="M200" s="77">
         <v>3.98</v>
       </c>
-      <c r="O200" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P200" s="77">
+      <c r="N200" s="77">
         <v>3.98</v>
+      </c>
+      <c r="P200" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q200" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R200" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -13308,18 +13930,21 @@
       <c r="M201" s="77">
         <v>1</v>
       </c>
-      <c r="O201" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P201" s="77">
+      <c r="N201" s="77">
+        <v>1</v>
+      </c>
+      <c r="P201" s="1" t="b">
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="Q201" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R201" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -13359,18 +13984,21 @@
       <c r="M202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O202" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P202" s="78">
+      <c r="N202" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="P202" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R202" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -13410,18 +14038,21 @@
       <c r="M203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="O203" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P203" s="85">
+      <c r="N203" s="85">
         <v>1.9999999999999999E-7</v>
+      </c>
+      <c r="P203" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R203" s="85">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -13461,18 +14092,21 @@
       <c r="M204" s="77">
         <v>25</v>
       </c>
-      <c r="O204" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P204" s="77">
+      <c r="N204" s="77">
         <v>25</v>
+      </c>
+      <c r="P204" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q204" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R204" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -13512,18 +14146,21 @@
       <c r="M205" s="77">
         <v>0</v>
       </c>
-      <c r="O205" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P205" s="77">
-        <v>0</v>
+      <c r="N205" s="77">
+        <v>0</v>
+      </c>
+      <c r="P205" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q205" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R205" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -13563,18 +14200,21 @@
       <c r="M206" s="77">
         <v>3.98</v>
       </c>
-      <c r="O206" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P206" s="77">
+      <c r="N206" s="77">
         <v>3.98</v>
+      </c>
+      <c r="P206" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q206" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R206" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -13614,18 +14254,21 @@
       <c r="M207" s="77">
         <v>1</v>
       </c>
-      <c r="O207" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P207" s="77">
+      <c r="N207" s="77">
+        <v>1</v>
+      </c>
+      <c r="P207" s="1" t="b">
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="Q207" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R207" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -13665,18 +14308,21 @@
       <c r="M208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="O208" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P208" s="78">
+      <c r="N208" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="P208" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R208" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -13716,18 +14362,21 @@
       <c r="M209" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="O209" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P209" s="95" t="s">
+      <c r="N209" s="95" t="s">
         <v>90</v>
+      </c>
+      <c r="P209" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q209" s="95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="210" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R209" s="95" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>557</v>
       </c>
@@ -13750,15 +14399,15 @@
         <v>0.5</v>
       </c>
       <c r="H210" s="83">
-        <f t="shared" ref="H210:J210" si="18">0.00002</f>
+        <f t="shared" ref="H210:J210" si="22">0.00002</f>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="I210" s="83">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="J210" s="83">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="K210" s="83">
@@ -13773,19 +14422,23 @@
         <f>0.00005 / 100</f>
         <v>4.9999999999999998E-7</v>
       </c>
-      <c r="N210" s="1"/>
-      <c r="O210" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P210" s="2">
-        <v>0.01</v>
+      <c r="N210" s="83">
+        <f>0.00005 / 100</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="O210" s="1"/>
+      <c r="P210" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q210" s="2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="211" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R210" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>560</v>
       </c>
@@ -13820,24 +14473,27 @@
         <v>0.1</v>
       </c>
       <c r="L211" s="83">
+        <v>0.3</v>
+      </c>
+      <c r="M211" s="83">
+        <v>0.3</v>
+      </c>
+      <c r="N211" s="83">
         <v>0.1</v>
       </c>
-      <c r="M211" s="83">
-        <v>0.1</v>
-      </c>
-      <c r="N211" s="1"/>
-      <c r="O211" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P211" s="99">
+      <c r="O211" s="1"/>
+      <c r="P211" s="1" t="b">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q211" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R211" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>563</v>
       </c>
@@ -13860,41 +14516,45 @@
         <v>0.5</v>
       </c>
       <c r="H212" s="83">
-        <f t="shared" ref="H212:M212" si="19">0.00002 / 14</f>
+        <f t="shared" ref="H212:N212" si="23">0.00002 / 14</f>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="I212" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="J212" s="83">
         <v>2E-3</v>
       </c>
       <c r="K212" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="L212" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="M212" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1.4285714285714286E-6</v>
       </c>
-      <c r="N212" s="1"/>
-      <c r="O212" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P212" s="100">
+      <c r="N212" s="83">
+        <f t="shared" si="23"/>
+        <v>1.4285714285714286E-6</v>
+      </c>
+      <c r="O212" s="1"/>
+      <c r="P212" s="1" t="b">
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="Q212" s="100">
+        <v>1</v>
+      </c>
+      <c r="R212" s="100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>507</v>
       </c>
@@ -13934,19 +14594,22 @@
       <c r="M213" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="N213" s="1"/>
-      <c r="O213" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P213" s="98">
+      <c r="N213" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="O213" s="1"/>
+      <c r="P213" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="Q213" s="98">
         <v>0.1</v>
       </c>
-      <c r="Q213" s="98" t="s">
+      <c r="R213" s="98" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -13986,19 +14649,22 @@
       <c r="M214" s="83">
         <v>0</v>
       </c>
-      <c r="N214" s="1"/>
-      <c r="O214" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P214" s="98">
-        <v>0.04</v>
+      <c r="N214" s="83">
+        <v>0</v>
+      </c>
+      <c r="O214" s="1"/>
+      <c r="P214" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q214" s="98">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="215" spans="1:17" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R214" s="98">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -14038,19 +14704,22 @@
       <c r="M215" s="83">
         <v>1E-3</v>
       </c>
-      <c r="N215" s="1"/>
-      <c r="O215" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P215" s="98">
+      <c r="N215" s="83">
         <v>1E-3</v>
+      </c>
+      <c r="O215" s="1"/>
+      <c r="P215" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q215" s="98">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R215" s="98">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>515</v>
       </c>
@@ -14074,41 +14743,45 @@
         <v>1.2499999999999999E-6</v>
       </c>
       <c r="H216" s="99">
-        <f t="shared" ref="H216:M216" si="20">1250*0.000001/5</f>
+        <f t="shared" ref="H216:N216" si="24">1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="I216" s="99">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="J216" s="99">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="K216" s="99">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="L216" s="99">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="M216" s="99">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="O216" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P216" s="99">
+      <c r="N216" s="99">
+        <f t="shared" si="24"/>
         <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="P216" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q216" s="99">
         <v>2.5000000000000001E-4</v>
       </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R216" s="99">
+        <v>2.5000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -14148,18 +14821,21 @@
       <c r="M217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="O217" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="P217" s="99">
+      <c r="N217" s="99">
         <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="P217" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="Q217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>534</v>
       </c>
@@ -14203,12 +14879,16 @@
         <f xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="O218" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N218" s="83">
+        <f xml:space="preserve"> 0.0000000000025</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="P218" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>535</v>
       </c>
@@ -14247,19 +14927,23 @@
         <v>5.0000000000000002E-11</v>
       </c>
       <c r="L219" s="83">
+        <f>0.00000000005 / 10 / 8</f>
+        <v>6.2500000000000006E-13</v>
+      </c>
+      <c r="M219" s="83">
+        <f>0.00000000005 / 10 / 8</f>
+        <v>6.2500000000000006E-13</v>
+      </c>
+      <c r="N219" s="83">
         <f>0.00000000005</f>
         <v>5.0000000000000002E-11</v>
       </c>
-      <c r="M219" s="83">
-        <f>0.00000000005</f>
-        <v>5.0000000000000002E-11</v>
-      </c>
-      <c r="O219" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P219" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>569</v>
       </c>
@@ -14289,19 +14973,23 @@
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="L220" s="83">
+        <f>0.0000001 / 2</f>
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="M220" s="83">
+        <f>0.0000001 / 2</f>
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="N220" s="83">
         <f>0.0000001 * 10 /2</f>
         <v>4.9999999999999998E-7</v>
       </c>
-      <c r="M220" s="83">
-        <f>0.0000001 * 10 /2</f>
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="O220" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P220" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>571</v>
       </c>
@@ -14338,12 +15026,16 @@
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="O221" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N221" s="83">
+        <f>100</f>
+        <v>100</v>
+      </c>
+      <c r="P221" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>536</v>
       </c>
@@ -14386,15 +15078,19 @@
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="M222" s="83">
+        <f>0.000001 / 10000 / 4 / 10</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="N222" s="83">
         <f>0.000001 / 10000 / 4</f>
         <v>2.4999999999999998E-11</v>
       </c>
-      <c r="O222" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P222" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>537</v>
       </c>
@@ -14434,18 +15130,22 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M223" s="83">
+        <f>0.00001</f>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N223" s="83">
         <f>0.00001 * 10</f>
         <v>1E-4</v>
       </c>
-      <c r="N223" s="83">
+      <c r="O223" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="O223" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P223" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>579</v>
       </c>
@@ -14485,10 +15185,14 @@
         <v>0.01</v>
       </c>
       <c r="M224" s="83">
+        <f xml:space="preserve"> 0.001 * 10</f>
+        <v>0.01</v>
+      </c>
+      <c r="N224" s="83">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>581</v>
       </c>
@@ -14523,17 +15227,21 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="L225" s="99">
-        <f>0.00001 * 2 / 3</f>
-        <v>6.6666666666666675E-6</v>
+        <f>0.00001 / 3</f>
+        <v>3.3333333333333337E-6</v>
       </c>
       <c r="M225" s="99">
-        <v>1.0000000000000001E-5</v>
+        <f>0.00001 / 3</f>
+        <v>3.3333333333333337E-6</v>
       </c>
       <c r="N225" s="99">
         <v>1.0000000000000001E-5</v>
       </c>
-    </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O225" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>538</v>
       </c>
@@ -14557,35 +15265,39 @@
         <v>0.10886399999999999</v>
       </c>
       <c r="H226" s="83">
-        <f t="shared" ref="H226:M226" si="21">0.84*(0.36^2)</f>
+        <f t="shared" ref="H226:N226" si="25">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
       <c r="I226" s="83">
+        <f t="shared" si="25"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="J226" s="83">
+        <f t="shared" si="25"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="K226" s="83">
+        <f t="shared" si="25"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="L226" s="83">
+        <f t="shared" si="25"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="M226" s="83">
+        <f t="shared" si="25"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="N226" s="83">
+        <f t="shared" si="25"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="P226" s="1" t="b">
         <f t="shared" si="21"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="J226" s="83">
-        <f t="shared" si="21"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="K226" s="83">
-        <f t="shared" si="21"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="L226" s="83">
-        <f t="shared" si="21"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="M226" s="83">
-        <f t="shared" si="21"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="O226" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>539</v>
       </c>
@@ -14625,12 +15337,15 @@
       <c r="M227" s="83">
         <v>0.2</v>
       </c>
-      <c r="O227" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N227" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="P227" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>540</v>
       </c>
@@ -14670,12 +15385,15 @@
       <c r="M228" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="O228" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N228" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="P228" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>541</v>
       </c>
@@ -14699,35 +15417,39 @@
         <v>0.2</v>
       </c>
       <c r="H229" s="83">
-        <f t="shared" ref="H229:M229" si="22">2*0.1</f>
+        <f t="shared" ref="H229:N229" si="26">2*0.1</f>
         <v>0.2</v>
       </c>
       <c r="I229" s="83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.2</v>
       </c>
       <c r="J229" s="83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.2</v>
       </c>
       <c r="K229" s="83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.2</v>
       </c>
       <c r="L229" s="83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.2</v>
       </c>
       <c r="M229" s="83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.2</v>
       </c>
-      <c r="O229" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N229" s="83">
+        <f t="shared" si="26"/>
+        <v>0.2</v>
+      </c>
+      <c r="P229" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>542</v>
       </c>
@@ -14767,12 +15489,15 @@
       <c r="M230" s="83">
         <v>1E-3</v>
       </c>
-      <c r="O230" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N230" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="P230" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>543</v>
       </c>
@@ -14808,73 +15533,77 @@
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="L231" s="83">
-        <f>0.00001 / 2 / 3</f>
-        <v>1.6666666666666669E-6</v>
+        <f>0.00001 /2</f>
+        <v>5.0000000000000004E-6</v>
       </c>
       <c r="M231" s="83">
+        <f>0.00001 /2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="N231" s="83">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="N231" s="1">
+      <c r="O231" s="1">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="O231" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P231" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E232" s="96" t="s">
+        <v>584</v>
+      </c>
+      <c r="F232" s="96" t="s">
+        <v>510</v>
+      </c>
+      <c r="G232" s="98">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H232" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I232" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J232" s="83">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K232" s="83">
+        <f>0.00001 / 2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="L232" s="83">
+        <f>0.000000005 / 5</f>
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="M232" s="83">
+        <f>0.000000005 / 5</f>
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="N232" s="83">
+        <f>0.00001 / 2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="E232" s="30" t="s">
-        <v>558</v>
-      </c>
-      <c r="F232" s="30" t="s">
-        <v>559</v>
-      </c>
-      <c r="G232" s="83">
-        <f t="shared" ref="G232:J232" si="23">0.00002 / 14 / 5</f>
-        <v>2.8571428571428575E-7</v>
-      </c>
-      <c r="H232" s="83">
-        <f t="shared" si="23"/>
-        <v>2.8571428571428575E-7</v>
-      </c>
-      <c r="I232" s="83">
-        <v>0</v>
-      </c>
-      <c r="J232" s="83">
-        <f t="shared" si="23"/>
-        <v>2.8571428571428575E-7</v>
-      </c>
-      <c r="K232" s="83">
-        <v>0</v>
-      </c>
-      <c r="L232" s="83">
-        <v>0</v>
-      </c>
-      <c r="M232" s="83">
-        <v>0</v>
-      </c>
-      <c r="O232" s="1" t="b">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A233" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>471</v>
@@ -14892,39 +15621,93 @@
         <v>559</v>
       </c>
       <c r="G233" s="83">
-        <f t="shared" ref="G233:M233" si="24">0.00002 / 14 / 5 /10</f>
+        <f t="shared" ref="G233:J233" si="27">0.00002 / 14 / 5</f>
+        <v>2.8571428571428575E-7</v>
+      </c>
+      <c r="H233" s="83">
+        <f t="shared" si="27"/>
+        <v>2.8571428571428575E-7</v>
+      </c>
+      <c r="I233" s="83">
+        <v>0</v>
+      </c>
+      <c r="J233" s="83">
+        <f t="shared" si="27"/>
+        <v>2.8571428571428575E-7</v>
+      </c>
+      <c r="K233" s="83">
+        <v>0</v>
+      </c>
+      <c r="L233" s="83">
+        <v>0</v>
+      </c>
+      <c r="M233" s="83">
+        <v>0</v>
+      </c>
+      <c r="N233" s="83">
+        <v>0</v>
+      </c>
+      <c r="P233" s="1" t="b">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E234" s="30" t="s">
+        <v>558</v>
+      </c>
+      <c r="F234" s="30" t="s">
+        <v>559</v>
+      </c>
+      <c r="G234" s="83">
+        <f t="shared" ref="G234:N234" si="28">0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="H233" s="83">
-        <f t="shared" si="24"/>
+      <c r="H234" s="83">
+        <f t="shared" si="28"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="I233" s="83">
-        <f t="shared" si="24"/>
+      <c r="I234" s="83">
+        <f t="shared" si="28"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="J233" s="83">
-        <f t="shared" si="24"/>
+      <c r="J234" s="83">
+        <f t="shared" si="28"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="K233" s="83">
-        <f t="shared" si="24"/>
+      <c r="K234" s="83">
+        <f t="shared" si="28"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="L233" s="83">
-        <v>0</v>
-      </c>
-      <c r="M233" s="83">
-        <f t="shared" si="24"/>
+      <c r="L234" s="83">
+        <v>0</v>
+      </c>
+      <c r="M234" s="83">
+        <v>0</v>
+      </c>
+      <c r="N234" s="83">
+        <f t="shared" si="28"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="O233" s="1" t="b">
-        <f t="shared" si="17"/>
+      <c r="P234" s="1" t="b">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G232:I233">
+  <conditionalFormatting sqref="G233:I234">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -14946,7 +15729,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G233:M233">
+  <conditionalFormatting sqref="G234:N234">
     <cfRule type="colorScale" priority="361">
       <colorScale>
         <cfvo type="min"/>
@@ -14968,7 +15751,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H127:M128">
+  <conditionalFormatting sqref="H127:N128">
     <cfRule type="colorScale" priority="363">
       <colorScale>
         <cfvo type="min"/>
@@ -14980,7 +15763,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H210:M210">
+  <conditionalFormatting sqref="H210:N210">
+    <cfRule type="colorScale" priority="364">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="365">
       <colorScale>
         <cfvo type="min"/>
@@ -14991,7 +15784,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="364">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H211:N211">
+    <cfRule type="colorScale" priority="366">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="367">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15002,29 +15807,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H211:M211">
-    <cfRule type="colorScale" priority="367">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="366">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H212:M212">
+  <conditionalFormatting sqref="H212:N212">
     <cfRule type="colorScale" priority="368">
       <colorScale>
         <cfvo type="min"/>
@@ -15046,7 +15829,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H213:M213">
+  <conditionalFormatting sqref="H213:N213">
+    <cfRule type="colorScale" priority="370">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="371">
       <colorScale>
         <cfvo type="min"/>
@@ -15057,7 +15850,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="370">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H214:N214">
+    <cfRule type="colorScale" priority="372">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="373">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15068,8 +15873,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H214:M214">
-    <cfRule type="colorScale" priority="373">
+  <conditionalFormatting sqref="H215:N215">
+    <cfRule type="colorScale" priority="374">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15079,7 +15884,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="372">
+    <cfRule type="colorScale" priority="375">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15090,8 +15895,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H215:M215">
-    <cfRule type="colorScale" priority="375">
+  <conditionalFormatting sqref="H218:N218">
+    <cfRule type="colorScale" priority="376">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15101,7 +15906,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="374">
+    <cfRule type="colorScale" priority="377">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15112,8 +15917,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H218:M218">
-    <cfRule type="colorScale" priority="377">
+  <conditionalFormatting sqref="H219:N221">
+    <cfRule type="colorScale" priority="390">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15123,7 +15928,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="376">
+    <cfRule type="colorScale" priority="391">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15134,8 +15939,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H219:M221">
-    <cfRule type="colorScale" priority="391">
+  <conditionalFormatting sqref="H222:N222">
+    <cfRule type="colorScale" priority="380">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15145,7 +15950,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="390">
+    <cfRule type="colorScale" priority="381">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15156,8 +15961,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H222:M222">
-    <cfRule type="colorScale" priority="381">
+  <conditionalFormatting sqref="H226:N226">
+    <cfRule type="colorScale" priority="384">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15167,7 +15972,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="380">
+    <cfRule type="colorScale" priority="385">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15178,29 +15983,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H226:M226">
-    <cfRule type="colorScale" priority="385">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="384">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H227:M231">
+  <conditionalFormatting sqref="H227:N232">
     <cfRule type="colorScale" priority="386">
       <colorScale>
         <cfvo type="min"/>
@@ -15222,7 +16005,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H223:N223 H224:M224">
+  <conditionalFormatting sqref="N223:O223 N224 H223:M224">
+    <cfRule type="colorScale" priority="382">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="383">
       <colorScale>
         <cfvo type="min"/>
@@ -15233,18 +16026,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="382">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J232">
+  <conditionalFormatting sqref="J233">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -15266,7 +16049,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K232:K233">
+  <conditionalFormatting sqref="K233:K234">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -15277,18 +16070,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L232:M233">
+  <conditionalFormatting sqref="L233:N234">
     <cfRule type="colorScale" priority="388">
       <colorScale>
         <cfvo type="min"/>
@@ -15310,7 +16093,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P127:Q128">
+  <conditionalFormatting sqref="Q127:R128">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -15322,7 +16105,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P129:Q129 H129:N129">
+  <conditionalFormatting sqref="Q129:R129 H129:O129">
     <cfRule type="colorScale" priority="295">
       <colorScale>
         <cfvo type="min"/>
@@ -15344,7 +16127,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P130:Q130 H130:M130">
+  <conditionalFormatting sqref="Q130:R130 H130:N130">
     <cfRule type="colorScale" priority="299">
       <colorScale>
         <cfvo type="min"/>
@@ -15366,7 +16149,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P132:Q132 H132:N132">
+  <conditionalFormatting sqref="Q132:R132 H132:O132">
+    <cfRule type="colorScale" priority="303">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="min"/>
@@ -15377,7 +16170,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="303">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q133:R133 H133:N133">
+    <cfRule type="colorScale" priority="307">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="308">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15388,29 +16193,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P133:Q133 H133:M133">
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P138:Q138 H138:N138">
+  <conditionalFormatting sqref="Q138:R138 H138:O138">
     <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min"/>
@@ -15422,7 +16205,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P144:Q144 H144:M144">
+  <conditionalFormatting sqref="Q144:R144 H144:N144">
     <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min"/>
@@ -15454,17 +16237,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P160:Q160 H160:M160">
-    <cfRule type="colorScale" priority="321">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
+  <conditionalFormatting sqref="Q160:R160 H160:N160">
     <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min"/>
@@ -15485,9 +16258,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P166:Q166 H166:M166">
-    <cfRule type="colorScale" priority="326">
+    <cfRule type="colorScale" priority="321">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15497,7 +16268,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q166:R166 H166:N166">
     <cfRule type="colorScale" priority="325">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="326">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp42483\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFA639B-7CD0-4676-B02A-AD5B173D0023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906177BC-82C0-493E-BDBC-DCBB17CA2CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="587">
   <si>
     <t>input_file</t>
   </si>
@@ -1791,7 +1791,10 @@
     <t>Maximal rate of amino acid catabolism in the root segment</t>
   </si>
   <si>
-    <t>RC_ref_no_N_deficit</t>
+    <t>RC_ref_no_N_deficit (25_03_30)</t>
+  </si>
+  <si>
+    <t>RC_no_hair</t>
   </si>
 </sst>
 </file>
@@ -2978,7 +2981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R234"/>
+  <dimension ref="A1:S234"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
@@ -2986,10 +2989,10 @@
     <col min="5" max="5" width="23.28515625" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" style="37" customWidth="1"/>
-    <col min="8" max="18" width="39.85546875" style="1" customWidth="1"/>
+    <col min="8" max="19" width="39.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>469</v>
       </c>
@@ -3027,25 +3030,28 @@
         <v>568</v>
       </c>
       <c r="M1" s="97" t="s">
+        <v>586</v>
+      </c>
+      <c r="N1" s="97" t="s">
         <v>585</v>
       </c>
-      <c r="N1" s="97" t="s">
+      <c r="O1" s="97" t="s">
         <v>576</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="Q1" s="97" t="s">
+      <c r="R1" s="97" t="s">
         <v>522</v>
       </c>
-      <c r="R1" s="97" t="s">
+      <c r="S1" s="97" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>524</v>
       </c>
@@ -3088,18 +3094,21 @@
       <c r="N2" s="36" t="s">
         <v>476</v>
       </c>
-      <c r="P2" s="1" t="b">
-        <f>L2=N2</f>
-        <v>1</v>
-      </c>
-      <c r="Q2" s="36" t="s">
+      <c r="O2" s="36" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q2" s="1" t="b">
+        <f>L2=O2</f>
+        <v>1</v>
+      </c>
+      <c r="R2" s="36" t="s">
         <v>528</v>
       </c>
-      <c r="R2" s="36" t="s">
+      <c r="S2" s="36" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="1" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" s="1" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>472</v>
       </c>
@@ -3142,18 +3151,21 @@
       <c r="N3" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="P3" s="1" t="b">
-        <f t="shared" ref="P3:P66" si="0">L3=N3</f>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="36" t="s">
-        <v>489</v>
+      <c r="O3" s="36" t="s">
+        <v>577</v>
+      </c>
+      <c r="Q3" s="1" t="b">
+        <f t="shared" ref="Q3:Q66" si="0">L3=O3</f>
+        <v>1</v>
       </c>
       <c r="R3" s="36" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S3" s="36" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>484</v>
       </c>
@@ -3196,18 +3208,21 @@
       <c r="N4" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="P4" s="1" t="b">
+      <c r="O4" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q4" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q4" s="36" t="s">
-        <v>482</v>
       </c>
       <c r="R4" s="36" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S4" s="36" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>483</v>
       </c>
@@ -3250,18 +3265,21 @@
       <c r="N5" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="P5" s="1" t="b">
+      <c r="O5" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q5" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q5" s="36" t="s">
-        <v>494</v>
       </c>
       <c r="R5" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S5" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>490</v>
       </c>
@@ -3304,18 +3322,21 @@
       <c r="N6" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="P6" s="1" t="b">
+      <c r="O6" s="36" t="s">
+        <v>577</v>
+      </c>
+      <c r="Q6" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q6" s="36" t="s">
-        <v>521</v>
       </c>
       <c r="R6" s="36" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S6" s="36" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>485</v>
       </c>
@@ -3358,18 +3379,21 @@
       <c r="N7" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="P7" s="1" t="b">
+      <c r="O7" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q7" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q7" s="36" t="s">
-        <v>494</v>
       </c>
       <c r="R7" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S7" s="36" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>529</v>
       </c>
@@ -3412,18 +3436,21 @@
       <c r="N8" s="36">
         <v>0</v>
       </c>
-      <c r="P8" s="1" t="b">
+      <c r="O8" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="36">
-        <v>0</v>
-      </c>
       <c r="R8" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3466,18 +3493,21 @@
       <c r="N9" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="1" t="b">
+      <c r="O9" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q9" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="R9" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S9" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3520,18 +3550,21 @@
       <c r="N10" s="77">
         <v>1</v>
       </c>
-      <c r="P10" s="1" t="b">
+      <c r="O10" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q10" s="77">
-        <v>1</v>
-      </c>
       <c r="R10" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S10" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
         <v>444</v>
       </c>
@@ -3574,18 +3607,21 @@
       <c r="N11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P11" s="1" t="b">
+      <c r="O11" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q11" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q11" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R11" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S11" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -3628,18 +3664,21 @@
       <c r="N12" s="85">
         <v>180</v>
       </c>
-      <c r="P12" s="1" t="b">
+      <c r="O12" s="85">
+        <v>180</v>
+      </c>
+      <c r="Q12" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q12" s="85">
-        <v>180</v>
       </c>
       <c r="R12" s="85">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S12" s="85">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -3682,18 +3721,21 @@
       <c r="N13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="P13" s="1" t="b">
+      <c r="O13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+      <c r="Q13" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q13" s="78">
-        <v>4.1666666999999998E-2</v>
       </c>
       <c r="R13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3736,18 +3778,21 @@
       <c r="N14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="P14" s="1" t="b">
+      <c r="O14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+      <c r="Q14" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q14" s="79">
-        <v>4.1666666999999998E-2</v>
       </c>
       <c r="R14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -3790,18 +3835,21 @@
       <c r="N15" s="77">
         <v>1</v>
       </c>
-      <c r="P15" s="1" t="b">
+      <c r="O15" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q15" s="77">
-        <v>1</v>
-      </c>
       <c r="R15" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S15" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>448</v>
       </c>
@@ -3844,18 +3892,21 @@
       <c r="N16" s="77">
         <v>0</v>
       </c>
-      <c r="P16" s="1" t="b">
+      <c r="O16" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q16" s="77">
-        <v>0</v>
-      </c>
       <c r="R16" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S16" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -3898,18 +3949,21 @@
       <c r="N17" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P17" s="1" t="b">
+      <c r="O17" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q17" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q17" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R17" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S17" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -3952,18 +4006,21 @@
       <c r="N18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="P18" s="1" t="b">
+      <c r="O18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="Q18" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q18" s="80">
-        <v>5.0000000000000001E-9</v>
       </c>
       <c r="R18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -4006,18 +4063,21 @@
       <c r="N19" s="77">
         <v>10</v>
       </c>
-      <c r="P19" s="1" t="b">
+      <c r="O19" s="77">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q19" s="77">
-        <v>10</v>
       </c>
       <c r="R19" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S19" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>461</v>
       </c>
@@ -4060,18 +4120,21 @@
       <c r="N20" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P20" s="1" t="b">
+      <c r="O20" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q20" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q20" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R20" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S20" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>462</v>
       </c>
@@ -4114,18 +4177,21 @@
       <c r="N21" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P21" s="1" t="b">
+      <c r="O21" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q21" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q21" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R21" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S21" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>465</v>
       </c>
@@ -4168,18 +4234,21 @@
       <c r="N22" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P22" s="1" t="b">
+      <c r="O22" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q22" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q22" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R22" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S22" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>467</v>
       </c>
@@ -4222,18 +4291,21 @@
       <c r="N23" s="77">
         <v>86400</v>
       </c>
-      <c r="P23" s="1" t="b">
+      <c r="O23" s="77">
+        <v>86400</v>
+      </c>
+      <c r="Q23" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q23" s="77">
-        <v>86400</v>
       </c>
       <c r="R23" s="77">
         <v>86400</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S23" s="77">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -4276,18 +4348,21 @@
       <c r="N24" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="P24" s="1" t="b">
+      <c r="O24" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q24" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q24" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="R24" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S24" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -4330,18 +4405,21 @@
       <c r="N25" s="77">
         <v>3</v>
       </c>
-      <c r="P25" s="1" t="b">
+      <c r="O25" s="77">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q25" s="77">
-        <v>3</v>
       </c>
       <c r="R25" s="77">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S25" s="77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -4384,18 +4462,21 @@
       <c r="N26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="P26" s="1" t="b">
+      <c r="O26" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q26" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q26" s="81" t="s">
-        <v>88</v>
-      </c>
       <c r="R26" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S26" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -4438,18 +4519,21 @@
       <c r="N27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="P27" s="1" t="b">
+      <c r="O27" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q27" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q27" s="81" t="s">
-        <v>88</v>
-      </c>
       <c r="R27" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S27" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -4492,18 +4576,21 @@
       <c r="N28" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P28" s="1" t="b">
+      <c r="O28" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q28" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q28" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R28" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S28" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -4546,18 +4633,21 @@
       <c r="N29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="P29" s="1" t="b">
+      <c r="O29" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q29" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q29" s="81" t="s">
-        <v>88</v>
-      </c>
       <c r="R29" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S29" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -4600,18 +4690,21 @@
       <c r="N30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="P30" s="1" t="b">
+      <c r="O30" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q30" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q30" s="81" t="s">
-        <v>88</v>
-      </c>
       <c r="R30" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S30" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -4654,18 +4747,21 @@
       <c r="N31" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P31" s="1" t="b">
+      <c r="O31" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q31" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q31" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R31" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S31" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4708,18 +4804,21 @@
       <c r="N32" s="77">
         <v>0.33</v>
       </c>
-      <c r="P32" s="1" t="b">
+      <c r="O32" s="77">
+        <v>0.33</v>
+      </c>
+      <c r="Q32" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q32" s="77">
-        <v>0.33</v>
       </c>
       <c r="R32" s="77">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S32" s="77">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4762,18 +4861,21 @@
       <c r="N33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P33" s="1" t="b">
+      <c r="O33" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q33" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q33" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R33" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S33" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -4816,18 +4918,21 @@
       <c r="N34" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P34" s="1" t="b">
+      <c r="O34" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q34" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q34" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R34" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S34" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>454</v>
       </c>
@@ -4870,18 +4975,21 @@
       <c r="N35" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P35" s="1" t="b">
+      <c r="O35" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q35" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q35" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R35" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S35" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -4924,18 +5032,21 @@
       <c r="N36" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="P36" s="1" t="b">
+      <c r="O36" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q36" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q36" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="R36" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S36" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -4978,18 +5089,21 @@
       <c r="N37" s="85" t="s">
         <v>433</v>
       </c>
-      <c r="P37" s="1" t="b">
+      <c r="O37" s="85" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q37" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q37" s="85" t="s">
-        <v>433</v>
       </c>
       <c r="R37" s="85" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S37" s="85" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -5032,18 +5146,21 @@
       <c r="N38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="P38" s="1" t="b">
+      <c r="O38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="Q38" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q38" s="80">
-        <v>9.9999999999999995E-7</v>
       </c>
       <c r="R38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -5086,18 +5203,21 @@
       <c r="N39" s="86">
         <v>1E-3</v>
       </c>
-      <c r="P39" s="1" t="b">
+      <c r="O39" s="86">
+        <v>1E-3</v>
+      </c>
+      <c r="Q39" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q39" s="86">
-        <v>1E-3</v>
       </c>
       <c r="R39" s="86">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S39" s="86">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -5140,18 +5260,21 @@
       <c r="N40" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="P40" s="1" t="b">
+      <c r="O40" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q40" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q40" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="R40" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S40" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -5194,18 +5317,21 @@
       <c r="N41" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="P41" s="1" t="b">
+      <c r="O41" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q41" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q41" s="77" t="s">
-        <v>89</v>
       </c>
       <c r="R41" s="77" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S41" s="77" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -5248,18 +5374,21 @@
       <c r="N42" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="P42" s="1" t="b">
+      <c r="O42" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q42" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q42" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="R42" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S42" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -5302,18 +5431,21 @@
       <c r="N43" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P43" s="1" t="b">
+      <c r="O43" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q43" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q43" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R43" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S43" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -5356,18 +5488,21 @@
       <c r="N44" s="77">
         <v>120</v>
       </c>
-      <c r="P44" s="1" t="b">
+      <c r="O44" s="77">
+        <v>120</v>
+      </c>
+      <c r="Q44" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q44" s="77">
-        <v>120</v>
       </c>
       <c r="R44" s="77">
         <v>120</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S44" s="77">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -5410,18 +5545,21 @@
       <c r="N45" s="77">
         <v>0</v>
       </c>
-      <c r="P45" s="1" t="b">
+      <c r="O45" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q45" s="77">
-        <v>0</v>
-      </c>
       <c r="R45" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S45" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -5464,18 +5602,21 @@
       <c r="N46" s="77">
         <v>0</v>
       </c>
-      <c r="P46" s="1" t="b">
+      <c r="O46" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q46" s="77">
-        <v>0</v>
-      </c>
       <c r="R46" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S46" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -5518,18 +5659,21 @@
       <c r="N47" s="77">
         <v>-0.1</v>
       </c>
-      <c r="P47" s="1" t="b">
+      <c r="O47" s="77">
+        <v>-0.1</v>
+      </c>
+      <c r="Q47" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q47" s="77">
-        <v>-0.1</v>
       </c>
       <c r="R47" s="77">
         <v>-0.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S47" s="77">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -5572,18 +5716,21 @@
       <c r="N48" s="77">
         <v>-0.2</v>
       </c>
-      <c r="P48" s="1" t="b">
+      <c r="O48" s="77">
+        <v>-0.2</v>
+      </c>
+      <c r="Q48" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q48" s="77">
-        <v>-0.2</v>
       </c>
       <c r="R48" s="77">
         <v>-0.2</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S48" s="77">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -5626,18 +5773,21 @@
       <c r="N49" s="77">
         <v>0.4</v>
       </c>
-      <c r="P49" s="1" t="b">
+      <c r="O49" s="77">
+        <v>0.4</v>
+      </c>
+      <c r="Q49" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q49" s="77">
-        <v>0.4</v>
       </c>
       <c r="R49" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S49" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -5680,18 +5830,21 @@
       <c r="N50" s="77">
         <v>0</v>
       </c>
-      <c r="P50" s="1" t="b">
+      <c r="O50" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q50" s="77">
-        <v>0</v>
-      </c>
       <c r="R50" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S50" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>434</v>
       </c>
@@ -5734,18 +5887,21 @@
       <c r="N51" s="77">
         <v>1200</v>
       </c>
-      <c r="P51" s="1" t="b">
+      <c r="O51" s="77">
+        <v>1200</v>
+      </c>
+      <c r="Q51" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q51" s="77">
-        <v>1200</v>
       </c>
       <c r="R51" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S51" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>435</v>
       </c>
@@ -5788,18 +5944,21 @@
       <c r="N52" s="77">
         <v>1200</v>
       </c>
-      <c r="P52" s="1" t="b">
+      <c r="O52" s="77">
+        <v>1200</v>
+      </c>
+      <c r="Q52" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q52" s="77">
-        <v>1200</v>
       </c>
       <c r="R52" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S52" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>457</v>
       </c>
@@ -5842,18 +6001,21 @@
       <c r="N53" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="P53" s="1" t="b">
+      <c r="O53" s="35" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q53" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q53" s="35" t="s">
-        <v>460</v>
       </c>
       <c r="R53" s="35" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S53" s="35" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -5896,18 +6058,21 @@
       <c r="N54" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="P54" s="1" t="b">
+      <c r="O54" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q54" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q54" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="R54" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S54" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -5950,18 +6115,21 @@
       <c r="N55" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="P55" s="1" t="b">
+      <c r="O55" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q55" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q55" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="R55" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S55" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -6004,18 +6172,21 @@
       <c r="N56" s="77">
         <v>0</v>
       </c>
-      <c r="P56" s="1" t="b">
+      <c r="O56" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q56" s="77">
-        <v>0</v>
-      </c>
       <c r="R56" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S56" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -6058,18 +6229,21 @@
       <c r="N57" s="77">
         <v>0.5</v>
       </c>
-      <c r="P57" s="1" t="b">
+      <c r="O57" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="Q57" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q57" s="77">
-        <v>0.5</v>
       </c>
       <c r="R57" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S57" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -6112,18 +6286,21 @@
       <c r="N58" s="77">
         <v>0.05</v>
       </c>
-      <c r="P58" s="1" t="b">
+      <c r="O58" s="77">
+        <v>0.05</v>
+      </c>
+      <c r="Q58" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q58" s="77">
-        <v>0.05</v>
       </c>
       <c r="R58" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S58" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -6166,18 +6343,21 @@
       <c r="N59" s="80">
         <v>1E-3</v>
       </c>
-      <c r="P59" s="1" t="b">
+      <c r="O59" s="80">
+        <v>1E-3</v>
+      </c>
+      <c r="Q59" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q59" s="80">
-        <v>1E-3</v>
       </c>
       <c r="R59" s="80">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S59" s="80">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -6220,18 +6400,21 @@
       <c r="N60" s="77">
         <v>0</v>
       </c>
-      <c r="P60" s="1" t="b">
+      <c r="O60" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q60" s="77">
-        <v>0</v>
-      </c>
       <c r="R60" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S60" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -6274,18 +6457,21 @@
       <c r="N61" s="77">
         <v>1E-4</v>
       </c>
-      <c r="P61" s="1" t="b">
+      <c r="O61" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="Q61" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q61" s="77">
-        <v>1E-4</v>
       </c>
       <c r="R61" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S61" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -6328,18 +6514,21 @@
       <c r="N62" s="77">
         <v>1E-4</v>
       </c>
-      <c r="P62" s="1" t="b">
+      <c r="O62" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="Q62" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q62" s="77">
-        <v>1E-4</v>
       </c>
       <c r="R62" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S62" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -6382,18 +6571,21 @@
       <c r="N63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="P63" s="1" t="b">
+      <c r="O63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q63" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q63" s="77">
-        <v>6.9999999999999999E-4</v>
       </c>
       <c r="R63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -6436,18 +6628,21 @@
       <c r="N64" s="77">
         <v>1.22E-4</v>
       </c>
-      <c r="P64" s="1" t="b">
+      <c r="O64" s="77">
+        <v>1.22E-4</v>
+      </c>
+      <c r="Q64" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q64" s="77">
-        <v>1.22E-4</v>
       </c>
       <c r="R64" s="77">
         <v>1.22E-4</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S64" s="77">
+        <v>1.22E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -6490,18 +6685,21 @@
       <c r="N65" s="77">
         <v>1</v>
       </c>
-      <c r="P65" s="1" t="b">
+      <c r="O65" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q65" s="77">
-        <v>1</v>
-      </c>
       <c r="R65" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S65" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -6544,18 +6742,21 @@
       <c r="N66" s="77">
         <v>0.95</v>
       </c>
-      <c r="P66" s="1" t="b">
+      <c r="O66" s="77">
+        <v>0.95</v>
+      </c>
+      <c r="Q66" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="Q66" s="77">
-        <v>0.95</v>
       </c>
       <c r="R66" s="77">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S66" s="77">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -6598,18 +6799,21 @@
       <c r="N67" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P67" s="1" t="b">
-        <f t="shared" ref="P67:P130" si="1">L67=N67</f>
-        <v>1</v>
-      </c>
-      <c r="Q67" s="77" t="s">
-        <v>88</v>
+      <c r="O67" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q67" s="1" t="b">
+        <f t="shared" ref="Q67:Q130" si="1">L67=O67</f>
+        <v>1</v>
       </c>
       <c r="R67" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S67" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -6652,18 +6856,21 @@
       <c r="N68" s="77">
         <v>5</v>
       </c>
-      <c r="P68" s="1" t="b">
+      <c r="O68" s="77">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q68" s="77">
-        <v>5</v>
       </c>
       <c r="R68" s="77">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S68" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -6706,18 +6913,21 @@
       <c r="N69" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="P69" s="1" t="b">
+      <c r="O69" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q69" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q69" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R69" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S69" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -6760,18 +6970,21 @@
       <c r="N70" s="77">
         <v>50</v>
       </c>
-      <c r="P70" s="1" t="b">
+      <c r="O70" s="77">
+        <v>50</v>
+      </c>
+      <c r="Q70" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q70" s="77">
-        <v>50</v>
       </c>
       <c r="R70" s="77">
         <v>50</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S70" s="77">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -6814,18 +7027,21 @@
       <c r="N71" s="78">
         <v>1453890.8941884842</v>
       </c>
-      <c r="P71" s="1" t="b">
+      <c r="O71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+      <c r="Q71" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q71" s="78">
-        <v>1453890.8941884842</v>
       </c>
       <c r="R71" s="78">
         <v>1453890.8941884842</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -6868,18 +7084,21 @@
       <c r="N72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-      <c r="P72" s="1" t="b">
+      <c r="O72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+      <c r="Q72" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q72" s="78">
-        <v>1.3888888888888888E-5</v>
       </c>
       <c r="R72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -6922,18 +7141,21 @@
       <c r="N73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-      <c r="P73" s="1" t="b">
+      <c r="O73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+      <c r="Q73" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q73" s="79">
-        <v>6.5011574074074071E-4</v>
       </c>
       <c r="R73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -6976,18 +7198,21 @@
       <c r="N74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-      <c r="P74" s="1" t="b">
+      <c r="O74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+      <c r="Q74" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q74" s="85">
-        <v>4.7400000000000003E-3</v>
       </c>
       <c r="R74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -7030,20 +7255,24 @@
         <v>282528</v>
       </c>
       <c r="N75" s="79">
+        <f>282528</f>
         <v>282528</v>
       </c>
-      <c r="P75" s="1" t="b">
+      <c r="O75" s="79">
+        <v>282528</v>
+      </c>
+      <c r="Q75" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q75" s="79">
-        <v>282528</v>
       </c>
       <c r="R75" s="79">
         <v>282528</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S75" s="79">
+        <v>282528</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -7086,18 +7315,21 @@
       <c r="N76" s="85">
         <v>0.56999999999999995</v>
       </c>
-      <c r="P76" s="1" t="b">
+      <c r="O76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="Q76" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q76" s="85">
-        <v>0.56999999999999995</v>
       </c>
       <c r="R76" s="85">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -7140,18 +7372,21 @@
       <c r="N77" s="87">
         <v>0.16</v>
       </c>
-      <c r="P77" s="1" t="b">
+      <c r="O77" s="87">
+        <v>0.16</v>
+      </c>
+      <c r="Q77" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q77" s="87">
-        <v>0.16</v>
       </c>
       <c r="R77" s="87">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S77" s="87">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -7194,18 +7429,21 @@
       <c r="N78" s="77">
         <v>0</v>
       </c>
-      <c r="P78" s="1" t="b">
+      <c r="O78" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q78" s="77">
-        <v>0</v>
-      </c>
       <c r="R78" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S78" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -7248,18 +7486,21 @@
       <c r="N79" s="78">
         <v>745476480000</v>
       </c>
-      <c r="P79" s="1" t="b">
+      <c r="O79" s="78">
+        <v>745476480000</v>
+      </c>
+      <c r="Q79" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q79" s="78">
-        <v>745476480000</v>
       </c>
       <c r="R79" s="78">
         <v>745476480000</v>
       </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S79" s="78">
+        <v>745476480000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -7302,18 +7543,21 @@
       <c r="N80" s="77">
         <v>100</v>
       </c>
-      <c r="P80" s="1" t="b">
+      <c r="O80" s="77">
+        <v>100</v>
+      </c>
+      <c r="Q80" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q80" s="77">
-        <v>100</v>
       </c>
       <c r="R80" s="77">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S80" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -7356,18 +7600,21 @@
       <c r="N81" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="P81" s="1" t="b">
+      <c r="O81" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q81" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q81" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="R81" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S81" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -7410,18 +7657,21 @@
       <c r="N82" s="85">
         <v>21600</v>
       </c>
-      <c r="P82" s="1" t="b">
+      <c r="O82" s="85">
+        <v>21600</v>
+      </c>
+      <c r="Q82" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q82" s="85">
-        <v>21600</v>
       </c>
       <c r="R82" s="85">
         <v>21600</v>
       </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S82" s="85">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -7464,18 +7714,21 @@
       <c r="N83" s="77">
         <v>0.5</v>
       </c>
-      <c r="P83" s="1" t="b">
+      <c r="O83" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="Q83" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q83" s="77">
-        <v>0.5</v>
       </c>
       <c r="R83" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S83" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -7518,18 +7771,21 @@
       <c r="N84" s="85">
         <v>60479.999999999993</v>
       </c>
-      <c r="P84" s="1" t="b">
+      <c r="O84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+      <c r="Q84" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q84" s="85">
-        <v>60479.999999999993</v>
       </c>
       <c r="R84" s="85">
         <v>60479.999999999993</v>
       </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -7572,18 +7828,21 @@
       <c r="N85" s="77">
         <v>0.85</v>
       </c>
-      <c r="P85" s="1" t="b">
+      <c r="O85" s="77">
+        <v>0.85</v>
+      </c>
+      <c r="Q85" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q85" s="77">
-        <v>0.85</v>
       </c>
       <c r="R85" s="77">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S85" s="77">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -7626,18 +7885,21 @@
       <c r="N86" s="77">
         <v>518400</v>
       </c>
-      <c r="P86" s="1" t="b">
+      <c r="O86" s="77">
+        <v>518400</v>
+      </c>
+      <c r="Q86" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q86" s="77">
-        <v>518400</v>
       </c>
       <c r="R86" s="77">
         <v>518400</v>
       </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S86" s="77">
+        <v>518400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -7680,18 +7942,21 @@
       <c r="N87" s="77">
         <v>5184000</v>
       </c>
-      <c r="P87" s="1" t="b">
+      <c r="O87" s="77">
+        <v>5184000</v>
+      </c>
+      <c r="Q87" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q87" s="77">
-        <v>5184000</v>
       </c>
       <c r="R87" s="77">
         <v>5184000</v>
       </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S87" s="77">
+        <v>5184000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -7734,18 +7999,21 @@
       <c r="N88" s="86">
         <v>50000</v>
       </c>
-      <c r="P88" s="1" t="b">
+      <c r="O88" s="86">
+        <v>50000</v>
+      </c>
+      <c r="Q88" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q88" s="86">
-        <v>50000</v>
       </c>
       <c r="R88" s="86">
         <v>50000</v>
       </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S88" s="86">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -7788,18 +8056,21 @@
       <c r="N89" s="77">
         <v>140000</v>
       </c>
-      <c r="P89" s="1" t="b">
+      <c r="O89" s="77">
+        <v>140000</v>
+      </c>
+      <c r="Q89" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q89" s="77">
-        <v>140000</v>
       </c>
       <c r="R89" s="77">
         <v>140000</v>
       </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S89" s="77">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -7842,18 +8113,21 @@
       <c r="N90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-      <c r="P90" s="1" t="b">
+      <c r="O90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+      <c r="Q90" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q90" s="78">
-        <v>3.6636136999999999E-2</v>
       </c>
       <c r="R90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -7896,18 +8170,21 @@
       <c r="N91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="P91" s="1" t="b">
+      <c r="O91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="Q91" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q91" s="77">
-        <v>4.4999999999999997E-3</v>
       </c>
       <c r="R91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -7950,18 +8227,21 @@
       <c r="N92" s="77">
         <v>0.05</v>
       </c>
-      <c r="P92" s="1" t="b">
+      <c r="O92" s="77">
+        <v>0.05</v>
+      </c>
+      <c r="Q92" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q92" s="77">
-        <v>0.05</v>
       </c>
       <c r="R92" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S92" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -8004,18 +8284,21 @@
       <c r="N93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="P93" s="1" t="b">
+      <c r="O93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="Q93" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q93" s="77">
-        <v>6.0000000000000002E-6</v>
       </c>
       <c r="R93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -8053,23 +8336,26 @@
         <v>1E-3</v>
       </c>
       <c r="M94" s="77">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="N94" s="77">
         <v>1E-3</v>
       </c>
-      <c r="P94" s="1" t="b">
+      <c r="O94" s="77">
+        <v>1E-3</v>
+      </c>
+      <c r="Q94" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q94" s="77">
-        <v>0</v>
-      </c>
       <c r="R94" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S94" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -8112,18 +8398,21 @@
       <c r="N95" s="77">
         <v>374999999.99999994</v>
       </c>
-      <c r="P95" s="1" t="b">
+      <c r="O95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+      <c r="Q95" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q95" s="77">
-        <v>374999999.99999994</v>
       </c>
       <c r="R95" s="77">
         <v>374999999.99999994</v>
       </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -8161,23 +8450,26 @@
         <v>3.7037037037037038E-3</v>
       </c>
       <c r="M96" s="78">
-        <v>3.7037037037037038E-3</v>
+        <v>0</v>
       </c>
       <c r="N96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="P96" s="1" t="b">
+      <c r="O96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="Q96" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q96" s="78">
-        <v>3.7037037037037038E-3</v>
       </c>
       <c r="R96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -8220,18 +8512,21 @@
       <c r="N97" s="77">
         <v>165600</v>
       </c>
-      <c r="P97" s="1" t="b">
+      <c r="O97" s="77">
+        <v>165600</v>
+      </c>
+      <c r="Q97" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q97" s="77">
-        <v>165600</v>
       </c>
       <c r="R97" s="77">
         <v>165600</v>
       </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S97" s="77">
+        <v>165600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -8274,18 +8569,21 @@
       <c r="N98" s="77">
         <v>20</v>
       </c>
-      <c r="P98" s="1" t="b">
+      <c r="O98" s="77">
+        <v>20</v>
+      </c>
+      <c r="Q98" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q98" s="77">
-        <v>20</v>
       </c>
       <c r="R98" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S98" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -8328,18 +8626,21 @@
       <c r="N99" s="77">
         <v>1</v>
       </c>
-      <c r="P99" s="1" t="b">
+      <c r="O99" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q99" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q99" s="77">
-        <v>1</v>
-      </c>
       <c r="R99" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S99" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -8382,18 +8683,21 @@
       <c r="N100" s="77">
         <v>21</v>
       </c>
-      <c r="P100" s="1" t="b">
+      <c r="O100" s="77">
+        <v>21</v>
+      </c>
+      <c r="Q100" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q100" s="77">
-        <v>21</v>
       </c>
       <c r="R100" s="77">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S100" s="77">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -8436,18 +8740,21 @@
       <c r="N101" s="77">
         <v>0.64</v>
       </c>
-      <c r="P101" s="1" t="b">
+      <c r="O101" s="77">
+        <v>0.64</v>
+      </c>
+      <c r="Q101" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q101" s="77">
-        <v>0.64</v>
       </c>
       <c r="R101" s="77">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S101" s="77">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -8490,18 +8797,21 @@
       <c r="N102" s="77">
         <v>8</v>
       </c>
-      <c r="P102" s="1" t="b">
+      <c r="O102" s="77">
+        <v>8</v>
+      </c>
+      <c r="Q102" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q102" s="77">
-        <v>8</v>
       </c>
       <c r="R102" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S102" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -8544,18 +8854,21 @@
       <c r="N103" s="77">
         <v>10</v>
       </c>
-      <c r="P103" s="1" t="b">
+      <c r="O103" s="77">
+        <v>10</v>
+      </c>
+      <c r="Q103" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q103" s="77">
-        <v>10</v>
       </c>
       <c r="R103" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S103" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -8598,18 +8911,21 @@
       <c r="N104" s="77">
         <v>8</v>
       </c>
-      <c r="P104" s="1" t="b">
+      <c r="O104" s="77">
+        <v>8</v>
+      </c>
+      <c r="Q104" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q104" s="77">
-        <v>8</v>
       </c>
       <c r="R104" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S104" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="23" t="s">
         <v>500</v>
       </c>
@@ -8652,18 +8968,21 @@
       <c r="N105" s="77">
         <v>1</v>
       </c>
-      <c r="P105" s="1" t="b">
+      <c r="O105" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q105" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q105" s="77">
-        <v>1</v>
-      </c>
       <c r="R105" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S105" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -8706,18 +9025,21 @@
       <c r="N106" s="77">
         <v>0.5</v>
       </c>
-      <c r="P106" s="1" t="b">
+      <c r="O106" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="Q106" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q106" s="77">
-        <v>0.5</v>
       </c>
       <c r="R106" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S106" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="23" t="s">
         <v>501</v>
       </c>
@@ -8768,18 +9090,22 @@
         <f t="shared" ref="N107" si="5">N105</f>
         <v>1</v>
       </c>
-      <c r="P107" s="1" t="b">
+      <c r="O107" s="58">
+        <f t="shared" ref="O107" si="6">O105</f>
+        <v>1</v>
+      </c>
+      <c r="Q107" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q107" s="58">
-        <v>1</v>
-      </c>
       <c r="R107" s="58">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S107" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="23" t="s">
         <v>502</v>
       </c>
@@ -8803,45 +9129,49 @@
         <v>3</v>
       </c>
       <c r="H108" s="58">
-        <f t="shared" ref="H108:N108" si="6">150*H105</f>
+        <f t="shared" ref="H108:O108" si="7">150*H105</f>
         <v>150</v>
       </c>
       <c r="I108" s="58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>150</v>
       </c>
       <c r="J108" s="58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>150</v>
       </c>
       <c r="K108" s="58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>150</v>
       </c>
       <c r="L108" s="58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>150</v>
       </c>
       <c r="M108" s="58">
-        <f t="shared" ref="M108" si="7">150*M105</f>
+        <f t="shared" ref="M108" si="8">150*M105</f>
         <v>150</v>
       </c>
       <c r="N108" s="58">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="N108" si="9">150*N105</f>
         <v>150</v>
       </c>
-      <c r="P108" s="1" t="b">
+      <c r="O108" s="58">
+        <f t="shared" si="7"/>
+        <v>150</v>
+      </c>
+      <c r="Q108" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q108" s="58">
-        <v>150</v>
       </c>
       <c r="R108" s="58">
         <v>150</v>
       </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S108" s="58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="23" t="s">
         <v>503</v>
       </c>
@@ -8861,49 +9191,53 @@
         <v>506</v>
       </c>
       <c r="G109" s="58">
-        <f t="shared" ref="G109:L109" si="8">G100</f>
+        <f t="shared" ref="G109:L109" si="10">G100</f>
         <v>21</v>
       </c>
       <c r="H109" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="I109" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="J109" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="K109" s="58">
-        <f t="shared" ref="K109" si="9">K100</f>
+        <f t="shared" ref="K109" si="11">K100</f>
         <v>21</v>
       </c>
       <c r="L109" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="M109" s="58">
-        <f t="shared" ref="M109" si="10">M100</f>
+        <f t="shared" ref="M109" si="12">M100</f>
         <v>21</v>
       </c>
       <c r="N109" s="58">
-        <f t="shared" ref="N109" si="11">N100</f>
+        <f t="shared" ref="N109" si="13">N100</f>
         <v>21</v>
       </c>
-      <c r="P109" s="1" t="b">
+      <c r="O109" s="58">
+        <f t="shared" ref="O109" si="14">O100</f>
+        <v>21</v>
+      </c>
+      <c r="Q109" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q109" s="58">
-        <v>21</v>
       </c>
       <c r="R109" s="58">
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S109" s="58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="23" t="s">
         <v>504</v>
       </c>
@@ -8927,45 +9261,49 @@
         <v>210</v>
       </c>
       <c r="H110" s="58">
-        <f t="shared" ref="H110:N110" si="12">70*H100</f>
+        <f t="shared" ref="H110:O110" si="15">70*H100</f>
         <v>1470</v>
       </c>
       <c r="I110" s="58">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1470</v>
       </c>
       <c r="J110" s="58">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1470</v>
       </c>
       <c r="K110" s="58">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1470</v>
       </c>
       <c r="L110" s="58">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1470</v>
       </c>
       <c r="M110" s="58">
-        <f t="shared" ref="M110" si="13">70*M100</f>
+        <f t="shared" ref="M110" si="16">70*M100</f>
         <v>1470</v>
       </c>
       <c r="N110" s="58">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="N110" si="17">70*N100</f>
         <v>1470</v>
       </c>
-      <c r="P110" s="1" t="b">
+      <c r="O110" s="58">
+        <f t="shared" si="15"/>
+        <v>1470</v>
+      </c>
+      <c r="Q110" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q110" s="58">
-        <v>1470</v>
       </c>
       <c r="R110" s="58">
         <v>1470</v>
       </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S110" s="58">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -9008,18 +9346,21 @@
       <c r="N111" s="77">
         <v>0</v>
       </c>
-      <c r="P111" s="1" t="b">
+      <c r="O111" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q111" s="77">
-        <v>0</v>
-      </c>
       <c r="R111" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S111" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -9062,18 +9403,21 @@
       <c r="N112" s="82">
         <v>1589759.9999999998</v>
       </c>
-      <c r="P112" s="1" t="b">
+      <c r="O112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+      <c r="Q112" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q112" s="82">
-        <v>1589759.9999999998</v>
       </c>
       <c r="R112" s="82">
         <v>1589759.9999999998</v>
       </c>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -9116,18 +9460,21 @@
       <c r="N113" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="P113" s="1" t="b">
+      <c r="O113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+      <c r="Q113" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q113" s="82">
-        <v>6171428.5714285718</v>
       </c>
       <c r="R113" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -9170,18 +9517,21 @@
       <c r="N114" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="P114" s="1" t="b">
+      <c r="O114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+      <c r="Q114" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q114" s="82">
-        <v>6171428.5714285718</v>
       </c>
       <c r="R114" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="23" t="s">
         <v>421</v>
       </c>
@@ -9224,18 +9574,21 @@
       <c r="N115" s="82">
         <v>100</v>
       </c>
-      <c r="P115" s="1" t="b">
+      <c r="O115" s="82">
+        <v>100</v>
+      </c>
+      <c r="Q115" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q115" s="82">
-        <v>100</v>
       </c>
       <c r="R115" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="116" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S115" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="23" t="s">
         <v>423</v>
       </c>
@@ -9259,45 +9612,49 @@
         <v>280800</v>
       </c>
       <c r="H116" s="67">
-        <f t="shared" ref="H116:N116" si="14">0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" ref="H116:O116" si="18">0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
       <c r="I116" s="67">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>28080</v>
       </c>
       <c r="J116" s="67">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>28080</v>
       </c>
       <c r="K116" s="67">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>28080</v>
       </c>
       <c r="L116" s="67">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>28080</v>
       </c>
       <c r="M116" s="67">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>28080</v>
       </c>
       <c r="N116" s="67">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>28080</v>
       </c>
-      <c r="P116" s="1" t="b">
+      <c r="O116" s="67">
+        <f t="shared" si="18"/>
+        <v>28080</v>
+      </c>
+      <c r="Q116" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q116" s="67">
-        <v>28080</v>
       </c>
       <c r="R116" s="67">
         <v>28080</v>
       </c>
-    </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S116" s="67">
+        <v>28080</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="23" t="s">
         <v>425</v>
       </c>
@@ -9321,45 +9678,49 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H117" s="67">
-        <f t="shared" ref="H117:N117" si="15">1.11 / 10</f>
+        <f t="shared" ref="H117:O117" si="19">1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
       <c r="I117" s="67">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="J117" s="67">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="K117" s="67">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="L117" s="67">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="M117" s="67">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="N117" s="67">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.11100000000000002</v>
       </c>
-      <c r="P117" s="1" t="b">
+      <c r="O117" s="67">
+        <f t="shared" si="19"/>
+        <v>0.11100000000000002</v>
+      </c>
+      <c r="Q117" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q117" s="67">
-        <v>0.11100000000000002</v>
       </c>
       <c r="R117" s="67">
         <v>0.11100000000000002</v>
       </c>
-    </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S117" s="67">
+        <v>0.11100000000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="23" t="s">
         <v>497</v>
       </c>
@@ -9402,18 +9763,21 @@
       <c r="N118" s="82">
         <v>100</v>
       </c>
-      <c r="P118" s="1" t="b">
+      <c r="O118" s="82">
+        <v>100</v>
+      </c>
+      <c r="Q118" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q118" s="82">
-        <v>100</v>
       </c>
       <c r="R118" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="119" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S118" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="23" t="s">
         <v>498</v>
       </c>
@@ -9433,49 +9797,53 @@
         <v>431</v>
       </c>
       <c r="G119" s="67">
-        <f t="shared" ref="G119:N119" si="16">5.32 * (60*60*24)</f>
+        <f t="shared" ref="G119:O119" si="20">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H119" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>459648</v>
       </c>
       <c r="I119" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>459648</v>
       </c>
       <c r="J119" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>459648</v>
       </c>
       <c r="K119" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>459648</v>
       </c>
       <c r="L119" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>459648</v>
       </c>
       <c r="M119" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>459648</v>
       </c>
       <c r="N119" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>459648</v>
       </c>
-      <c r="P119" s="1" t="b">
+      <c r="O119" s="67">
+        <f t="shared" si="20"/>
+        <v>459648</v>
+      </c>
+      <c r="Q119" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q119" s="67">
-        <v>459648</v>
       </c>
       <c r="R119" s="67">
         <v>459648</v>
       </c>
-    </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S119" s="67">
+        <v>459648</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="23" t="s">
         <v>499</v>
       </c>
@@ -9499,45 +9867,49 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H120" s="67">
-        <f t="shared" ref="H120:N120" si="17">1.11/8</f>
+        <f t="shared" ref="H120:O120" si="21">1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
       <c r="I120" s="67">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="J120" s="67">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="K120" s="67">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="L120" s="67">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="M120" s="67">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="N120" s="67">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="P120" s="1" t="b">
+      <c r="O120" s="67">
+        <f t="shared" si="21"/>
+        <v>0.13875000000000001</v>
+      </c>
+      <c r="Q120" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q120" s="67">
-        <v>0.13875000000000001</v>
       </c>
       <c r="R120" s="67">
         <v>0.13875000000000001</v>
       </c>
-    </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S120" s="67">
+        <v>0.13875000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="23" t="s">
         <v>395</v>
       </c>
@@ -9580,18 +9952,21 @@
       <c r="N121" s="82">
         <v>21600</v>
       </c>
-      <c r="P121" s="1" t="b">
+      <c r="O121" s="82">
+        <v>21600</v>
+      </c>
+      <c r="Q121" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q121" s="82">
-        <v>21600</v>
       </c>
       <c r="R121" s="82">
         <v>21600</v>
       </c>
-    </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S121" s="82">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="23" t="s">
         <v>397</v>
       </c>
@@ -9634,18 +10009,21 @@
       <c r="N122" s="88">
         <v>43200</v>
       </c>
-      <c r="P122" s="1" t="b">
+      <c r="O122" s="88">
+        <v>43200</v>
+      </c>
+      <c r="Q122" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q122" s="88">
-        <v>43200</v>
       </c>
       <c r="R122" s="88">
         <v>43200</v>
       </c>
-    </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S122" s="88">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
         <v>61</v>
       </c>
@@ -9688,18 +10066,21 @@
       <c r="N123" s="77">
         <v>0.8</v>
       </c>
-      <c r="P123" s="1" t="b">
+      <c r="O123" s="77">
+        <v>0.8</v>
+      </c>
+      <c r="Q123" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q123" s="77">
-        <v>0.8</v>
       </c>
       <c r="R123" s="77">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S123" s="77">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
         <v>62</v>
       </c>
@@ -9743,18 +10124,21 @@
       <c r="N124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="P124" s="1" t="b">
+      <c r="O124" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="Q124" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q124" s="78">
-        <v>2.0833333333333335E-4</v>
       </c>
       <c r="R124" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S124" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
         <v>63</v>
       </c>
@@ -9797,18 +10181,21 @@
       <c r="N125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-      <c r="P125" s="1" t="b">
+      <c r="O125" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+      <c r="Q125" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q125" s="77">
-        <v>5.7899999999999998E-7</v>
       </c>
       <c r="R125" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-    </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S125" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="13" t="s">
         <v>64</v>
       </c>
@@ -9851,18 +10238,21 @@
       <c r="N126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="P126" s="1" t="b">
+      <c r="O126" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="Q126" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="Q126" s="78">
-        <v>2.0833333333333335E-4</v>
       </c>
       <c r="R126" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S126" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
@@ -9905,18 +10295,21 @@
       <c r="N127" s="78">
         <v>0</v>
       </c>
-      <c r="P127" s="1" t="b">
+      <c r="O127" s="78">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q127" s="78">
-        <v>0</v>
-      </c>
       <c r="R127" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S127" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
@@ -9959,18 +10352,21 @@
       <c r="N128" s="78">
         <v>0</v>
       </c>
-      <c r="P128" s="1" t="b">
+      <c r="O128" s="78">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q128" s="78">
-        <v>0</v>
-      </c>
       <c r="R128" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S128" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" s="68" t="s">
         <v>441</v>
       </c>
@@ -9995,11 +10391,11 @@
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="I129" s="83">
-        <f t="shared" ref="I129:R129" si="18">0.0000002*3</f>
+        <f t="shared" ref="I129:S129" si="22">0.0000002*3</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J129" s="83">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="K129" s="83">
@@ -10015,26 +10411,30 @@
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="N129" s="83">
-        <v>0</v>
+        <f>0.0000002 * 2 / 1000</f>
+        <v>3.9999999999999996E-10</v>
       </c>
       <c r="O129" s="83">
+        <v>0</v>
+      </c>
+      <c r="P129" s="83">
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="P129" s="1" t="b">
+      <c r="Q129" s="1" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q129" s="83">
-        <f t="shared" si="18"/>
+      <c r="R129" s="83">
+        <f t="shared" si="22"/>
         <v>5.9999999999999997E-7</v>
       </c>
-      <c r="R129" s="83">
-        <f t="shared" si="18"/>
+      <c r="S129" s="83">
+        <f t="shared" si="22"/>
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" s="68" t="s">
         <v>67</v>
       </c>
@@ -10055,47 +10455,51 @@
       </c>
       <c r="G130" s="71"/>
       <c r="H130" s="83">
-        <f t="shared" ref="H130:R130" si="19">1000 * 0.000001 / 12</f>
+        <f t="shared" ref="H130:S130" si="23">1000 * 0.000001 / 12</f>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="I130" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="J130" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="K130" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="L130" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="M130" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N130" s="83">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="P130" s="1" t="b">
+      <c r="O130" s="83">
+        <f t="shared" si="23"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="Q130" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q130" s="83">
-        <f t="shared" si="19"/>
+      <c r="R130" s="83">
+        <f t="shared" si="23"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="R130" s="83">
-        <f t="shared" si="19"/>
+      <c r="S130" s="83">
+        <f t="shared" si="23"/>
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="68" t="s">
         <v>446</v>
       </c>
@@ -10138,18 +10542,21 @@
       <c r="N131" s="89" t="s">
         <v>533</v>
       </c>
-      <c r="P131" s="1" t="b">
-        <f t="shared" ref="P131:P194" si="20">L131=N131</f>
-        <v>1</v>
-      </c>
-      <c r="Q131" s="89" t="s">
+      <c r="O131" s="89" t="s">
         <v>533</v>
+      </c>
+      <c r="Q131" s="1" t="b">
+        <f t="shared" ref="Q131:Q194" si="24">L131=O131</f>
+        <v>1</v>
       </c>
       <c r="R131" s="89" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S131" s="89" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
         <v>66</v>
       </c>
@@ -10193,25 +10600,29 @@
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="N132" s="83">
+        <f>0.0005 / 10</f>
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="O132" s="83">
         <f>0.0005</f>
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="O132" s="83">
+      <c r="P132" s="83">
         <f>0.0005 * 1.2</f>
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="P132" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q132" s="83">
-        <v>5.0000000000000001E-4</v>
+      <c r="Q132" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="R132" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S132" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" s="21" t="s">
         <v>438</v>
       </c>
@@ -10254,18 +10665,21 @@
       <c r="N133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="P133" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q133" s="83">
+      <c r="O133" s="83">
         <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="Q133" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R133" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-    </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S133" s="83">
+        <v>4.9999999999999999E-13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" s="21" t="s">
         <v>229</v>
       </c>
@@ -10308,18 +10722,21 @@
       <c r="N134" s="77">
         <v>10</v>
       </c>
-      <c r="P134" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q134" s="77">
+      <c r="O134" s="77">
         <v>10</v>
+      </c>
+      <c r="Q134" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R134" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S134" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" s="21" t="s">
         <v>230</v>
       </c>
@@ -10362,18 +10779,21 @@
       <c r="N135" s="77">
         <v>-0.04</v>
       </c>
-      <c r="P135" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q135" s="77">
+      <c r="O135" s="77">
         <v>-0.04</v>
+      </c>
+      <c r="Q135" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R135" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S135" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" s="21" t="s">
         <v>231</v>
       </c>
@@ -10416,18 +10836,21 @@
       <c r="N136" s="77">
         <v>2.9</v>
       </c>
-      <c r="P136" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q136" s="77">
+      <c r="O136" s="77">
         <v>2.9</v>
+      </c>
+      <c r="Q136" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R136" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S136" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" s="21" t="s">
         <v>232</v>
       </c>
@@ -10470,18 +10893,21 @@
       <c r="N137" s="77">
         <v>1</v>
       </c>
-      <c r="P137" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q137" s="77">
+      <c r="O137" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q137" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R137" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S137" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
         <v>574</v>
       </c>
@@ -10525,24 +10951,28 @@
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="N138" s="80">
-        <v>1.9999999999999999E-7</v>
-      </c>
-      <c r="O138" s="80">
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="P138" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q138" s="80">
+      <c r="O138" s="80">
         <v>1.9999999999999999E-7</v>
+      </c>
+      <c r="P138" s="80">
+        <f>0.0000002 * 2 / 10</f>
+        <v>4.0000000000000001E-8</v>
+      </c>
+      <c r="Q138" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="R138" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S138" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
         <v>233</v>
       </c>
@@ -10585,18 +11015,21 @@
       <c r="N139" s="77">
         <v>10</v>
       </c>
-      <c r="P139" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q139" s="77">
+      <c r="O139" s="77">
         <v>10</v>
+      </c>
+      <c r="Q139" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R139" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S139" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" s="21" t="s">
         <v>234</v>
       </c>
@@ -10639,18 +11072,21 @@
       <c r="N140" s="77">
         <v>-0.04</v>
       </c>
-      <c r="P140" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q140" s="77">
+      <c r="O140" s="77">
         <v>-0.04</v>
+      </c>
+      <c r="Q140" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R140" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S140" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" s="21" t="s">
         <v>235</v>
       </c>
@@ -10693,18 +11129,21 @@
       <c r="N141" s="77">
         <v>2.9</v>
       </c>
-      <c r="P141" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q141" s="77">
+      <c r="O141" s="77">
         <v>2.9</v>
+      </c>
+      <c r="Q141" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R141" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S141" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
         <v>236</v>
       </c>
@@ -10747,18 +11186,21 @@
       <c r="N142" s="77">
         <v>1</v>
       </c>
-      <c r="P142" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q142" s="77">
+      <c r="O142" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q142" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R142" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S142" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
         <v>69</v>
       </c>
@@ -10801,18 +11243,21 @@
       <c r="N143" s="77">
         <v>0</v>
       </c>
-      <c r="P143" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q143" s="77">
-        <v>0</v>
+      <c r="O143" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R143" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S143" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="72" t="s">
         <v>70</v>
       </c>
@@ -10855,18 +11300,21 @@
       <c r="N144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="P144" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q144" s="80">
+      <c r="O144" s="80">
         <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="Q144" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R144" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S144" s="80">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" s="23" t="s">
         <v>56</v>
       </c>
@@ -10909,18 +11357,21 @@
       <c r="N145" s="77">
         <v>0</v>
       </c>
-      <c r="P145" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q145" s="77">
-        <v>0</v>
+      <c r="O145" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R145" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S145" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" s="23" t="s">
         <v>57</v>
       </c>
@@ -10963,18 +11414,21 @@
       <c r="N146" s="77">
         <v>2E-3</v>
       </c>
-      <c r="P146" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q146" s="77">
+      <c r="O146" s="77">
         <v>2E-3</v>
+      </c>
+      <c r="Q146" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R146" s="77">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S146" s="77">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" s="23" t="s">
         <v>58</v>
       </c>
@@ -11017,18 +11471,21 @@
       <c r="N147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-      <c r="P147" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q147" s="80">
+      <c r="O147" s="80">
         <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="Q147" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R147" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-    </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S147" s="80">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" s="23" t="s">
         <v>71</v>
       </c>
@@ -11071,18 +11528,21 @@
       <c r="N148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-      <c r="P148" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q148" s="80">
+      <c r="O148" s="80">
         <v>3.7699999999999999E-10</v>
+      </c>
+      <c r="Q148" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R148" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-    </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S148" s="80">
+        <v>3.7699999999999999E-10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" s="23" t="s">
         <v>237</v>
       </c>
@@ -11125,18 +11585,21 @@
       <c r="N149" s="77">
         <v>20</v>
       </c>
-      <c r="P149" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q149" s="77">
+      <c r="O149" s="77">
         <v>20</v>
+      </c>
+      <c r="Q149" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R149" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S149" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" s="23" t="s">
         <v>238</v>
       </c>
@@ -11179,18 +11642,21 @@
       <c r="N150" s="77">
         <v>-0.06</v>
       </c>
-      <c r="P150" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q150" s="77">
+      <c r="O150" s="77">
         <v>-0.06</v>
+      </c>
+      <c r="Q150" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R150" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S150" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" s="23" t="s">
         <v>239</v>
       </c>
@@ -11233,18 +11699,21 @@
       <c r="N151" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="P151" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q151" s="77">
+      <c r="O151" s="77">
         <v>0.89100000000000001</v>
+      </c>
+      <c r="Q151" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R151" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S151" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" s="23" t="s">
         <v>240</v>
       </c>
@@ -11287,18 +11756,21 @@
       <c r="N152" s="77">
         <v>1</v>
       </c>
-      <c r="P152" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q152" s="77">
+      <c r="O152" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q152" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R152" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S152" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" s="23" t="s">
         <v>72</v>
       </c>
@@ -11341,18 +11813,21 @@
       <c r="N153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="P153" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q153" s="80">
+      <c r="O153" s="80">
         <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="Q153" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R153" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S153" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" s="13" t="s">
         <v>73</v>
       </c>
@@ -11395,18 +11870,21 @@
       <c r="N154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-      <c r="P154" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q154" s="80">
+      <c r="O154" s="80">
         <v>5.8333333333333335E-9</v>
+      </c>
+      <c r="Q154" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R154" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S154" s="80">
+        <v>5.8333333333333335E-9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" s="13" t="s">
         <v>241</v>
       </c>
@@ -11449,18 +11927,21 @@
       <c r="N155" s="77">
         <v>20</v>
       </c>
-      <c r="P155" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q155" s="77">
+      <c r="O155" s="77">
         <v>20</v>
+      </c>
+      <c r="Q155" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R155" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S155" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" s="13" t="s">
         <v>242</v>
       </c>
@@ -11503,18 +11984,21 @@
       <c r="N156" s="77">
         <v>-0.06</v>
       </c>
-      <c r="P156" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q156" s="77">
+      <c r="O156" s="77">
         <v>-0.06</v>
+      </c>
+      <c r="Q156" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R156" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S156" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" s="13" t="s">
         <v>243</v>
       </c>
@@ -11557,18 +12041,21 @@
       <c r="N157" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="P157" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q157" s="77">
+      <c r="O157" s="77">
         <v>0.89100000000000001</v>
+      </c>
+      <c r="Q157" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R157" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S157" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" s="13" t="s">
         <v>244</v>
       </c>
@@ -11611,18 +12098,21 @@
       <c r="N158" s="77">
         <v>1</v>
       </c>
-      <c r="P158" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q158" s="77">
+      <c r="O158" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q158" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R158" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S158" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" s="13" t="s">
         <v>74</v>
       </c>
@@ -11665,18 +12155,21 @@
       <c r="N159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="P159" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q159" s="80">
+      <c r="O159" s="80">
         <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="Q159" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R159" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S159" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>75</v>
       </c>
@@ -11719,18 +12212,21 @@
       <c r="N160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="P160" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q160" s="83">
+      <c r="O160" s="83">
         <v>4.0000000000000001E-8</v>
+      </c>
+      <c r="Q160" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R160" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-    </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S160" s="83">
+        <v>4.0000000000000001E-8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>219</v>
       </c>
@@ -11773,18 +12269,21 @@
       <c r="N161" s="77">
         <v>20</v>
       </c>
-      <c r="P161" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q161" s="77">
+      <c r="O161" s="77">
         <v>20</v>
+      </c>
+      <c r="Q161" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R161" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S161" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>220</v>
       </c>
@@ -11827,18 +12326,21 @@
       <c r="N162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-      <c r="P162" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q162" s="77">
+      <c r="O162" s="77">
         <v>-4.4200000000000003E-2</v>
+      </c>
+      <c r="Q162" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R162" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-    </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S162" s="77">
+        <v>-4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>221</v>
       </c>
@@ -11881,18 +12383,21 @@
       <c r="N163" s="77">
         <v>1.55</v>
       </c>
-      <c r="P163" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q163" s="77">
+      <c r="O163" s="77">
         <v>1.55</v>
+      </c>
+      <c r="Q163" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R163" s="77">
         <v>1.55</v>
       </c>
-    </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S163" s="77">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>222</v>
       </c>
@@ -11935,18 +12440,21 @@
       <c r="N164" s="77">
         <v>1</v>
       </c>
-      <c r="P164" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q164" s="77">
+      <c r="O164" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q164" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R164" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S164" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>76</v>
       </c>
@@ -11989,18 +12497,21 @@
       <c r="N165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="P165" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q165" s="77">
+      <c r="O165" s="77">
         <v>2.7799999999999998E-4</v>
+      </c>
+      <c r="Q165" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R165" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-    </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S165" s="77">
+        <v>2.7799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
         <v>78</v>
       </c>
@@ -12043,18 +12554,21 @@
       <c r="N166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="P166" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q166" s="84">
+      <c r="O166" s="84">
         <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="Q166" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R166" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S166" s="84">
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
         <v>246</v>
       </c>
@@ -12097,18 +12611,21 @@
       <c r="N167" s="77">
         <v>20</v>
       </c>
-      <c r="P167" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q167" s="77">
+      <c r="O167" s="77">
         <v>20</v>
+      </c>
+      <c r="Q167" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R167" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S167" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" s="25" t="s">
         <v>247</v>
       </c>
@@ -12151,18 +12668,21 @@
       <c r="N168" s="77">
         <v>0</v>
       </c>
-      <c r="P168" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q168" s="77">
-        <v>0</v>
+      <c r="O168" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R168" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S168" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
         <v>248</v>
       </c>
@@ -12205,18 +12725,21 @@
       <c r="N169" s="77">
         <v>1</v>
       </c>
-      <c r="P169" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q169" s="77">
+      <c r="O169" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q169" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R169" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S169" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
         <v>249</v>
       </c>
@@ -12259,18 +12782,21 @@
       <c r="N170" s="77">
         <v>0</v>
       </c>
-      <c r="P170" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q170" s="77">
-        <v>0</v>
+      <c r="O170" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R170" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S170" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
         <v>79</v>
       </c>
@@ -12313,18 +12839,21 @@
       <c r="N171" s="77">
         <v>0.4</v>
       </c>
-      <c r="P171" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q171" s="77">
+      <c r="O171" s="77">
         <v>0.4</v>
+      </c>
+      <c r="Q171" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R171" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S171" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" s="31" t="s">
         <v>80</v>
       </c>
@@ -12367,18 +12896,21 @@
       <c r="N172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-      <c r="P172" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q172" s="86">
+      <c r="O172" s="86">
         <v>2.0000000000000001E-9</v>
+      </c>
+      <c r="Q172" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R172" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S172" s="86">
+        <v>2.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" s="31" t="s">
         <v>250</v>
       </c>
@@ -12421,18 +12953,21 @@
       <c r="N173" s="77">
         <v>25</v>
       </c>
-      <c r="P173" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q173" s="77">
+      <c r="O173" s="77">
         <v>25</v>
+      </c>
+      <c r="Q173" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R173" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S173" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" s="31" t="s">
         <v>251</v>
       </c>
@@ -12475,18 +13010,21 @@
       <c r="N174" s="77">
         <v>0</v>
       </c>
-      <c r="P174" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q174" s="77">
-        <v>0</v>
+      <c r="O174" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R174" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S174" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" s="31" t="s">
         <v>252</v>
       </c>
@@ -12529,18 +13067,21 @@
       <c r="N175" s="77">
         <v>3.98</v>
       </c>
-      <c r="P175" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q175" s="77">
+      <c r="O175" s="77">
         <v>3.98</v>
+      </c>
+      <c r="Q175" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R175" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S175" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" s="31" t="s">
         <v>253</v>
       </c>
@@ -12583,18 +13124,21 @@
       <c r="N176" s="77">
         <v>1</v>
       </c>
-      <c r="P176" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q176" s="77">
+      <c r="O176" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q176" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R176" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S176" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" s="31" t="s">
         <v>81</v>
       </c>
@@ -12637,18 +13181,21 @@
       <c r="N177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-      <c r="P177" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q177" s="78">
+      <c r="O177" s="78">
         <v>1.6666666666666666E-4</v>
+      </c>
+      <c r="Q177" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R177" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-    </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S177" s="78">
+        <v>1.6666666666666666E-4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>254</v>
       </c>
@@ -12691,18 +13238,21 @@
       <c r="N178" s="80">
         <v>1E-8</v>
       </c>
-      <c r="P178" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q178" s="80">
+      <c r="O178" s="80">
         <v>1E-8</v>
+      </c>
+      <c r="Q178" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R178" s="80">
         <v>1E-8</v>
       </c>
-    </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S178" s="80">
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>255</v>
       </c>
@@ -12745,18 +13295,21 @@
       <c r="N179" s="77">
         <v>20</v>
       </c>
-      <c r="P179" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q179" s="77">
+      <c r="O179" s="77">
         <v>20</v>
+      </c>
+      <c r="Q179" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R179" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S179" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>256</v>
       </c>
@@ -12799,18 +13352,21 @@
       <c r="N180" s="77">
         <v>0</v>
       </c>
-      <c r="P180" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q180" s="77">
-        <v>0</v>
+      <c r="O180" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R180" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S180" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>257</v>
       </c>
@@ -12853,18 +13409,21 @@
       <c r="N181" s="77">
         <v>2</v>
       </c>
-      <c r="P181" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q181" s="77">
+      <c r="O181" s="77">
         <v>2</v>
+      </c>
+      <c r="Q181" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R181" s="77">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S181" s="77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
         <v>258</v>
       </c>
@@ -12907,18 +13466,21 @@
       <c r="N182" s="77">
         <v>1</v>
       </c>
-      <c r="P182" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q182" s="77">
+      <c r="O182" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q182" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R182" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S182" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
         <v>259</v>
       </c>
@@ -12961,18 +13523,21 @@
       <c r="N183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="P183" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q183" s="78">
+      <c r="O183" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="Q183" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R183" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S183" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
         <v>260</v>
       </c>
@@ -13015,18 +13580,21 @@
       <c r="N184" s="77">
         <v>1</v>
       </c>
-      <c r="P184" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q184" s="77">
+      <c r="O184" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q184" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R184" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S184" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" s="27" t="s">
         <v>261</v>
       </c>
@@ -13069,18 +13637,21 @@
       <c r="N185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-      <c r="P185" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q185" s="77">
+      <c r="O185" s="77">
         <v>2.3533050791148899E-8</v>
+      </c>
+      <c r="Q185" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R185" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-    </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S185" s="77">
+        <v>2.3533050791148899E-8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" s="27" t="s">
         <v>262</v>
       </c>
@@ -13123,18 +13694,21 @@
       <c r="N186" s="77">
         <v>20</v>
       </c>
-      <c r="P186" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q186" s="77">
+      <c r="O186" s="77">
         <v>20</v>
+      </c>
+      <c r="Q186" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R186" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S186" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" s="27" t="s">
         <v>263</v>
       </c>
@@ -13177,18 +13751,21 @@
       <c r="N187" s="77">
         <v>-0.187</v>
       </c>
-      <c r="P187" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q187" s="77">
+      <c r="O187" s="77">
         <v>-0.187</v>
+      </c>
+      <c r="Q187" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R187" s="77">
         <v>-0.187</v>
       </c>
-    </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S187" s="77">
+        <v>-0.187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" s="27" t="s">
         <v>264</v>
       </c>
@@ -13231,18 +13808,21 @@
       <c r="N188" s="77">
         <v>2.48</v>
       </c>
-      <c r="P188" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q188" s="77">
+      <c r="O188" s="77">
         <v>2.48</v>
+      </c>
+      <c r="Q188" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R188" s="77">
         <v>2.48</v>
       </c>
-    </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S188" s="77">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" s="27" t="s">
         <v>265</v>
       </c>
@@ -13285,18 +13865,21 @@
       <c r="N189" s="77">
         <v>1</v>
       </c>
-      <c r="P189" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q189" s="77">
+      <c r="O189" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q189" s="1" t="b">
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R189" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S189" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" s="27" t="s">
         <v>266</v>
       </c>
@@ -13339,18 +13922,21 @@
       <c r="N190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-      <c r="P190" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q190" s="77">
+      <c r="O190" s="77">
         <v>6.1060227588121015E-4</v>
+      </c>
+      <c r="Q190" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R190" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-    </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S190" s="77">
+        <v>6.1060227588121015E-4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" s="23" t="s">
         <v>267</v>
       </c>
@@ -13393,18 +13979,21 @@
       <c r="N191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="P191" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q191" s="85">
+      <c r="O191" s="85">
         <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="Q191" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R191" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S191" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" s="23" t="s">
         <v>268</v>
       </c>
@@ -13447,18 +14036,21 @@
       <c r="N192" s="77">
         <v>25</v>
       </c>
-      <c r="P192" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q192" s="77">
+      <c r="O192" s="77">
         <v>25</v>
+      </c>
+      <c r="Q192" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R192" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S192" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" s="23" t="s">
         <v>269</v>
       </c>
@@ -13501,18 +14093,21 @@
       <c r="N193" s="77">
         <v>0</v>
       </c>
-      <c r="P193" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q193" s="77">
-        <v>0</v>
+      <c r="O193" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q193" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R193" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S193" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" s="23" t="s">
         <v>270</v>
       </c>
@@ -13555,18 +14150,21 @@
       <c r="N194" s="77">
         <v>3.98</v>
       </c>
-      <c r="P194" s="1" t="b">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="Q194" s="77">
+      <c r="O194" s="77">
         <v>3.98</v>
+      </c>
+      <c r="Q194" s="1" t="b">
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="R194" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S194" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" s="23" t="s">
         <v>271</v>
       </c>
@@ -13609,18 +14207,21 @@
       <c r="N195" s="77">
         <v>1</v>
       </c>
-      <c r="P195" s="1" t="b">
-        <f t="shared" ref="P195:P234" si="21">L195=N195</f>
-        <v>1</v>
-      </c>
-      <c r="Q195" s="77">
+      <c r="O195" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q195" s="1" t="b">
+        <f t="shared" ref="Q195:Q234" si="25">L195=O195</f>
         <v>1</v>
       </c>
       <c r="R195" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S195" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" s="23" t="s">
         <v>272</v>
       </c>
@@ -13663,18 +14264,21 @@
       <c r="N196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="P196" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q196" s="78">
+      <c r="O196" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="Q196" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R196" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S196" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>273</v>
       </c>
@@ -13717,18 +14321,21 @@
       <c r="N197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="P197" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q197" s="85">
+      <c r="O197" s="85">
         <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="Q197" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R197" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S197" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>274</v>
       </c>
@@ -13771,18 +14378,21 @@
       <c r="N198" s="77">
         <v>25</v>
       </c>
-      <c r="P198" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q198" s="77">
+      <c r="O198" s="77">
         <v>25</v>
+      </c>
+      <c r="Q198" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R198" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S198" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>275</v>
       </c>
@@ -13825,18 +14435,21 @@
       <c r="N199" s="77">
         <v>0</v>
       </c>
-      <c r="P199" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q199" s="77">
-        <v>0</v>
+      <c r="O199" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q199" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R199" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S199" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>276</v>
       </c>
@@ -13879,18 +14492,21 @@
       <c r="N200" s="77">
         <v>3.98</v>
       </c>
-      <c r="P200" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q200" s="77">
+      <c r="O200" s="77">
         <v>3.98</v>
+      </c>
+      <c r="Q200" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R200" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S200" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>277</v>
       </c>
@@ -13933,18 +14549,21 @@
       <c r="N201" s="77">
         <v>1</v>
       </c>
-      <c r="P201" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q201" s="77">
+      <c r="O201" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q201" s="1" t="b">
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="R201" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S201" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>278</v>
       </c>
@@ -13987,18 +14606,21 @@
       <c r="N202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="P202" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q202" s="78">
+      <c r="O202" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="Q202" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R202" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S202" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" s="29" t="s">
         <v>279</v>
       </c>
@@ -14041,18 +14663,21 @@
       <c r="N203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="P203" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q203" s="85">
+      <c r="O203" s="85">
         <v>1.9999999999999999E-7</v>
+      </c>
+      <c r="Q203" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R203" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S203" s="85">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" s="29" t="s">
         <v>280</v>
       </c>
@@ -14095,18 +14720,21 @@
       <c r="N204" s="77">
         <v>25</v>
       </c>
-      <c r="P204" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q204" s="77">
+      <c r="O204" s="77">
         <v>25</v>
+      </c>
+      <c r="Q204" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R204" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S204" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" s="29" t="s">
         <v>281</v>
       </c>
@@ -14149,18 +14777,21 @@
       <c r="N205" s="77">
         <v>0</v>
       </c>
-      <c r="P205" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q205" s="77">
-        <v>0</v>
+      <c r="O205" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q205" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R205" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S205" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" s="29" t="s">
         <v>282</v>
       </c>
@@ -14203,18 +14834,21 @@
       <c r="N206" s="77">
         <v>3.98</v>
       </c>
-      <c r="P206" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q206" s="77">
+      <c r="O206" s="77">
         <v>3.98</v>
+      </c>
+      <c r="Q206" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R206" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S206" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" s="29" t="s">
         <v>283</v>
       </c>
@@ -14257,18 +14891,21 @@
       <c r="N207" s="77">
         <v>1</v>
       </c>
-      <c r="P207" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q207" s="77">
+      <c r="O207" s="77">
+        <v>1</v>
+      </c>
+      <c r="Q207" s="1" t="b">
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="R207" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S207" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" s="29" t="s">
         <v>284</v>
       </c>
@@ -14311,18 +14948,21 @@
       <c r="N208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="P208" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q208" s="78">
+      <c r="O208" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="Q208" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R208" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S208" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" s="90" t="s">
         <v>362</v>
       </c>
@@ -14365,18 +15005,21 @@
       <c r="N209" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="P209" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q209" s="95" t="s">
+      <c r="O209" s="95" t="s">
         <v>90</v>
+      </c>
+      <c r="Q209" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R209" s="95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="210" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S209" s="95" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>557</v>
       </c>
@@ -14399,15 +15042,15 @@
         <v>0.5</v>
       </c>
       <c r="H210" s="83">
-        <f t="shared" ref="H210:J210" si="22">0.00002</f>
+        <f t="shared" ref="H210:J210" si="26">0.00002</f>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="I210" s="83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="J210" s="83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="K210" s="83">
@@ -14426,19 +15069,23 @@
         <f>0.00005 / 100</f>
         <v>4.9999999999999998E-7</v>
       </c>
-      <c r="O210" s="1"/>
-      <c r="P210" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q210" s="2">
-        <v>0.01</v>
+      <c r="O210" s="83">
+        <f>0.00005 / 100</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="P210" s="1"/>
+      <c r="Q210" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R210" s="2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="211" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S210" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>560</v>
       </c>
@@ -14479,21 +15126,24 @@
         <v>0.3</v>
       </c>
       <c r="N211" s="83">
+        <v>0.3</v>
+      </c>
+      <c r="O211" s="83">
         <v>0.1</v>
       </c>
-      <c r="O211" s="1"/>
-      <c r="P211" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="Q211" s="99">
+      <c r="P211" s="1"/>
+      <c r="Q211" s="1" t="b">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R211" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S211" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>563</v>
       </c>
@@ -14516,45 +15166,49 @@
         <v>0.5</v>
       </c>
       <c r="H212" s="83">
-        <f t="shared" ref="H212:N212" si="23">0.00002 / 14</f>
+        <f t="shared" ref="H212:O212" si="27">0.00002 / 14</f>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="I212" s="83">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="J212" s="83">
         <v>2E-3</v>
       </c>
       <c r="K212" s="83">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="L212" s="83">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="M212" s="83">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="N212" s="83">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1.4285714285714286E-6</v>
       </c>
-      <c r="O212" s="1"/>
-      <c r="P212" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q212" s="100">
+      <c r="O212" s="83">
+        <f t="shared" si="27"/>
+        <v>1.4285714285714286E-6</v>
+      </c>
+      <c r="P212" s="1"/>
+      <c r="Q212" s="1" t="b">
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="R212" s="100">
+        <v>1</v>
+      </c>
+      <c r="S212" s="100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="213" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>507</v>
       </c>
@@ -14597,19 +15251,22 @@
       <c r="N213" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="O213" s="1"/>
-      <c r="P213" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q213" s="98">
+      <c r="O213" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="P213" s="1"/>
+      <c r="Q213" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="R213" s="98">
         <v>0.1</v>
       </c>
-      <c r="R213" s="98" t="s">
+      <c r="S213" s="98" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="214" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>508</v>
       </c>
@@ -14652,19 +15309,22 @@
       <c r="N214" s="83">
         <v>0</v>
       </c>
-      <c r="O214" s="1"/>
-      <c r="P214" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q214" s="98">
-        <v>0.04</v>
+      <c r="O214" s="83">
+        <v>0</v>
+      </c>
+      <c r="P214" s="1"/>
+      <c r="Q214" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R214" s="98">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="215" spans="1:18" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S214" s="98">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>509</v>
       </c>
@@ -14707,19 +15367,22 @@
       <c r="N215" s="83">
         <v>1E-3</v>
       </c>
-      <c r="O215" s="1"/>
-      <c r="P215" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q215" s="98">
+      <c r="O215" s="83">
         <v>1E-3</v>
+      </c>
+      <c r="P215" s="1"/>
+      <c r="Q215" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R215" s="98">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S215" s="98">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>515</v>
       </c>
@@ -14743,45 +15406,49 @@
         <v>1.2499999999999999E-6</v>
       </c>
       <c r="H216" s="99">
-        <f t="shared" ref="H216:N216" si="24">1250*0.000001/5</f>
+        <f t="shared" ref="H216:O216" si="28">1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="I216" s="99">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="J216" s="99">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="K216" s="99">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="L216" s="99">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="M216" s="99">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="N216" s="99">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="P216" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q216" s="99">
+      <c r="O216" s="99">
+        <f t="shared" si="28"/>
         <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="Q216" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R216" s="99">
         <v>2.5000000000000001E-4</v>
       </c>
-    </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S216" s="99">
+        <v>2.5000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
@@ -14824,18 +15491,21 @@
       <c r="N217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="P217" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="Q217" s="99">
+      <c r="O217" s="99">
         <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="Q217" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="R217" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S217" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>534</v>
       </c>
@@ -14883,12 +15553,16 @@
         <f xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="P218" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O218" s="83">
+        <f xml:space="preserve"> 0.0000000000025</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="Q218" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>535</v>
       </c>
@@ -14935,15 +15609,19 @@
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="N219" s="83">
+        <f>0.00000000005 / 10 / 8</f>
+        <v>6.2500000000000006E-13</v>
+      </c>
+      <c r="O219" s="83">
         <f>0.00000000005</f>
         <v>5.0000000000000002E-11</v>
       </c>
-      <c r="P219" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q219" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>569</v>
       </c>
@@ -14981,15 +15659,19 @@
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="N220" s="83">
+        <f>0.0000001 / 2</f>
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="O220" s="83">
         <f>0.0000001 * 10 /2</f>
         <v>4.9999999999999998E-7</v>
       </c>
-      <c r="P220" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q220" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>571</v>
       </c>
@@ -15030,12 +15712,16 @@
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="P221" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O221" s="83">
+        <f>100</f>
+        <v>100</v>
+      </c>
+      <c r="Q221" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>536</v>
       </c>
@@ -15082,15 +15768,19 @@
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="N222" s="83">
+        <f>0.000001 / 10000 / 4 / 10</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="O222" s="83">
         <f>0.000001 / 10000 / 4</f>
         <v>2.4999999999999998E-11</v>
       </c>
-      <c r="P222" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q222" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>537</v>
       </c>
@@ -15134,18 +15824,22 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="N223" s="83">
+        <f>0.00001</f>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O223" s="83">
         <f>0.00001 * 10</f>
         <v>1E-4</v>
       </c>
-      <c r="O223" s="83">
+      <c r="P223" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P223" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q223" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>579</v>
       </c>
@@ -15189,10 +15883,14 @@
         <v>0.01</v>
       </c>
       <c r="N224" s="83">
+        <f xml:space="preserve"> 0.001 * 10</f>
+        <v>0.01</v>
+      </c>
+      <c r="O224" s="83">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>581</v>
       </c>
@@ -15235,13 +15933,17 @@
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="N225" s="99">
-        <v>1.0000000000000001E-5</v>
+        <f>0.00001 / 3</f>
+        <v>3.3333333333333337E-6</v>
       </c>
       <c r="O225" s="99">
         <v>1.0000000000000001E-5</v>
       </c>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P225" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>538</v>
       </c>
@@ -15265,39 +15967,43 @@
         <v>0.10886399999999999</v>
       </c>
       <c r="H226" s="83">
-        <f t="shared" ref="H226:N226" si="25">0.84*(0.36^2)</f>
+        <f t="shared" ref="H226:O226" si="29">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
       <c r="I226" s="83">
+        <f t="shared" si="29"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="J226" s="83">
+        <f t="shared" si="29"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="K226" s="83">
+        <f t="shared" si="29"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="L226" s="83">
+        <f t="shared" si="29"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="M226" s="83">
+        <f t="shared" si="29"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="N226" s="83">
+        <f t="shared" si="29"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="O226" s="83">
+        <f t="shared" si="29"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="Q226" s="1" t="b">
         <f t="shared" si="25"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="J226" s="83">
-        <f t="shared" si="25"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="K226" s="83">
-        <f t="shared" si="25"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="L226" s="83">
-        <f t="shared" si="25"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="M226" s="83">
-        <f t="shared" si="25"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="N226" s="83">
-        <f t="shared" si="25"/>
-        <v>0.10886399999999999</v>
-      </c>
-      <c r="P226" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>539</v>
       </c>
@@ -15340,12 +16046,15 @@
       <c r="N227" s="83">
         <v>0.2</v>
       </c>
-      <c r="P227" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O227" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="Q227" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>540</v>
       </c>
@@ -15388,12 +16097,15 @@
       <c r="N228" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="P228" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O228" s="83" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q228" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>541</v>
       </c>
@@ -15417,39 +16129,43 @@
         <v>0.2</v>
       </c>
       <c r="H229" s="83">
-        <f t="shared" ref="H229:N229" si="26">2*0.1</f>
+        <f t="shared" ref="H229:O229" si="30">2*0.1</f>
         <v>0.2</v>
       </c>
       <c r="I229" s="83">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.2</v>
       </c>
       <c r="J229" s="83">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.2</v>
       </c>
       <c r="K229" s="83">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.2</v>
       </c>
       <c r="L229" s="83">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.2</v>
       </c>
       <c r="M229" s="83">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.2</v>
       </c>
       <c r="N229" s="83">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.2</v>
       </c>
-      <c r="P229" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O229" s="83">
+        <f t="shared" si="30"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q229" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>542</v>
       </c>
@@ -15492,12 +16208,15 @@
       <c r="N230" s="83">
         <v>1E-3</v>
       </c>
-      <c r="P230" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O230" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="Q230" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>543</v>
       </c>
@@ -15541,19 +16260,23 @@
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="N231" s="83">
+        <f>0.00001 /2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="O231" s="83">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="O231" s="1">
+      <c r="P231" s="1">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="P231" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q231" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>583</v>
       </c>
@@ -15597,11 +16320,15 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="N232" s="83">
+        <f>0.000000005 / 5</f>
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="O232" s="83">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>566</v>
       </c>
@@ -15621,18 +16348,18 @@
         <v>559</v>
       </c>
       <c r="G233" s="83">
-        <f t="shared" ref="G233:J233" si="27">0.00002 / 14 / 5</f>
+        <f t="shared" ref="G233:J233" si="31">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="H233" s="83">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="I233" s="83">
         <v>0</v>
       </c>
       <c r="J233" s="83">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="K233" s="83">
@@ -15647,12 +16374,15 @@
       <c r="N233" s="83">
         <v>0</v>
       </c>
-      <c r="P233" s="1" t="b">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O233" s="83">
+        <v>0</v>
+      </c>
+      <c r="Q233" s="1" t="b">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>567</v>
       </c>
@@ -15672,23 +16402,23 @@
         <v>559</v>
       </c>
       <c r="G234" s="83">
-        <f t="shared" ref="G234:N234" si="28">0.00002 / 14 / 5 /10</f>
+        <f t="shared" ref="G234:O234" si="32">0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="H234" s="83">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="I234" s="83">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="J234" s="83">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="K234" s="83">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="L234" s="83">
@@ -15698,11 +16428,14 @@
         <v>0</v>
       </c>
       <c r="N234" s="83">
-        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="O234" s="83">
+        <f t="shared" si="32"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="P234" s="1" t="b">
-        <f t="shared" si="21"/>
+      <c r="Q234" s="1" t="b">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
@@ -15729,7 +16462,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G234:N234">
+  <conditionalFormatting sqref="G234:O234">
     <cfRule type="colorScale" priority="361">
       <colorScale>
         <cfvo type="min"/>
@@ -15751,7 +16484,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H127:N128">
+  <conditionalFormatting sqref="H127:O128">
     <cfRule type="colorScale" priority="363">
       <colorScale>
         <cfvo type="min"/>
@@ -15763,7 +16496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H210:N210">
+  <conditionalFormatting sqref="H210:O210">
     <cfRule type="colorScale" priority="364">
       <colorScale>
         <cfvo type="min"/>
@@ -15785,7 +16518,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H211:N211">
+  <conditionalFormatting sqref="H211:O211">
     <cfRule type="colorScale" priority="366">
       <colorScale>
         <cfvo type="min"/>
@@ -15807,7 +16540,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H212:N212">
+  <conditionalFormatting sqref="H212:O212">
     <cfRule type="colorScale" priority="368">
       <colorScale>
         <cfvo type="min"/>
@@ -15829,7 +16562,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H213:N213">
+  <conditionalFormatting sqref="H213:O213">
     <cfRule type="colorScale" priority="370">
       <colorScale>
         <cfvo type="min"/>
@@ -15851,7 +16584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H214:N214">
+  <conditionalFormatting sqref="H214:O214">
     <cfRule type="colorScale" priority="372">
       <colorScale>
         <cfvo type="min"/>
@@ -15873,7 +16606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H215:N215">
+  <conditionalFormatting sqref="H215:O215">
     <cfRule type="colorScale" priority="374">
       <colorScale>
         <cfvo type="min"/>
@@ -15895,7 +16628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H218:N218">
+  <conditionalFormatting sqref="H218:O218">
     <cfRule type="colorScale" priority="376">
       <colorScale>
         <cfvo type="min"/>
@@ -15917,7 +16650,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H219:N221">
+  <conditionalFormatting sqref="H219:O221">
     <cfRule type="colorScale" priority="390">
       <colorScale>
         <cfvo type="min"/>
@@ -15939,7 +16672,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H222:N222">
+  <conditionalFormatting sqref="H222:O222">
     <cfRule type="colorScale" priority="380">
       <colorScale>
         <cfvo type="min"/>
@@ -15961,7 +16694,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H226:N226">
+  <conditionalFormatting sqref="H226:O226">
     <cfRule type="colorScale" priority="384">
       <colorScale>
         <cfvo type="min"/>
@@ -15983,7 +16716,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H227:N232">
+  <conditionalFormatting sqref="H227:O232">
     <cfRule type="colorScale" priority="386">
       <colorScale>
         <cfvo type="min"/>
@@ -15995,28 +16728,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="387">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N223:O223 N224 H223:M224">
-    <cfRule type="colorScale" priority="382">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="383">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16071,7 +16782,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L233:N234">
+  <conditionalFormatting sqref="L233:O234">
     <cfRule type="colorScale" priority="388">
       <colorScale>
         <cfvo type="min"/>
@@ -16093,7 +16804,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q127:R128">
+  <conditionalFormatting sqref="O223:P223 O224 H223:N224">
+    <cfRule type="colorScale" priority="382">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="383">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R127:S128">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -16105,7 +16838,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q129:R129 H129:O129">
+  <conditionalFormatting sqref="R129:S129 H129:P129">
     <cfRule type="colorScale" priority="295">
       <colorScale>
         <cfvo type="min"/>
@@ -16127,7 +16860,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q130:R130 H130:N130">
+  <conditionalFormatting sqref="R130:S130 H130:O130">
     <cfRule type="colorScale" priority="299">
       <colorScale>
         <cfvo type="min"/>
@@ -16149,7 +16882,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q132:R132 H132:O132">
+  <conditionalFormatting sqref="R132:S132 H132:P132">
     <cfRule type="colorScale" priority="303">
       <colorScale>
         <cfvo type="min"/>
@@ -16171,7 +16904,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q133:R133 H133:N133">
+  <conditionalFormatting sqref="R133:S133 H133:O133">
     <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min"/>
@@ -16193,7 +16926,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q138:R138 H138:O138">
+  <conditionalFormatting sqref="R138:S138 H138:P138">
     <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min"/>
@@ -16205,7 +16938,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q144:R144 H144:N144">
+  <conditionalFormatting sqref="R144:S144 H144:O144">
     <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min"/>
@@ -16237,7 +16970,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q160:R160 H160:N160">
+  <conditionalFormatting sqref="R160:S160 H160:O160">
     <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min"/>
@@ -16269,7 +17002,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q166:R166 H166:N166">
+  <conditionalFormatting sqref="R166:S166 H166:O166">
     <cfRule type="colorScale" priority="325">
       <colorScale>
         <cfvo type="min"/>

--- a/simulations/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/inputs/Scenarios_24_11_10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp07754\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp45367\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651F1CB0-8DE9-4E0F-9C11-C3CE9B006777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7937E954-3C86-445D-9E19-5F7F09E14CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="0" windowWidth="28770" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28830" yWindow="-19695" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="601">
   <si>
     <t>input_file</t>
   </si>
@@ -1834,6 +1834,9 @@
   </si>
   <si>
     <t>RC_ref_0.1</t>
+  </si>
+  <si>
+    <t>RC_ref_big_lats</t>
   </si>
 </sst>
 </file>
@@ -3020,7 +3023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AC237"/>
+  <dimension ref="A1:AD237"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
@@ -3032,10 +3035,10 @@
     <col min="12" max="12" width="14.28515625" style="1" customWidth="1"/>
     <col min="13" max="21" width="39.85546875" style="1" customWidth="1"/>
     <col min="22" max="22" width="14.85546875" style="1" customWidth="1"/>
-    <col min="23" max="29" width="39.85546875" style="1" customWidth="1"/>
+    <col min="23" max="30" width="39.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>466</v>
       </c>
@@ -3099,28 +3102,31 @@
       </c>
       <c r="V1" s="97"/>
       <c r="W1" s="97" t="s">
+        <v>600</v>
+      </c>
+      <c r="X1" s="97" t="s">
         <v>580</v>
       </c>
-      <c r="X1" s="97" t="s">
+      <c r="Y1" s="97" t="s">
         <v>579</v>
       </c>
-      <c r="Y1" s="97" t="s">
+      <c r="Z1" s="97" t="s">
         <v>570</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="AB1" s="97" t="s">
+      <c r="AC1" s="97" t="s">
         <v>516</v>
       </c>
-      <c r="AC1" s="97" t="s">
+      <c r="AD1" s="97" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>518</v>
       </c>
@@ -3192,18 +3198,21 @@
       <c r="Y2" s="36" t="s">
         <v>473</v>
       </c>
-      <c r="AA2" s="1" t="b">
-        <f>M2=Y2</f>
-        <v>1</v>
-      </c>
-      <c r="AB2" s="36" t="s">
+      <c r="Z2" s="36" t="s">
+        <v>473</v>
+      </c>
+      <c r="AB2" s="1" t="b">
+        <f>M2=Z2</f>
+        <v>1</v>
+      </c>
+      <c r="AC2" s="36" t="s">
         <v>522</v>
       </c>
-      <c r="AC2" s="36" t="s">
+      <c r="AD2" s="36" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="1" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" s="1" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>469</v>
       </c>
@@ -3275,18 +3284,21 @@
       <c r="Y3" s="36" t="s">
         <v>571</v>
       </c>
-      <c r="AA3" s="1" t="b">
-        <f t="shared" ref="AA3:AA66" si="0">M3=Y3</f>
-        <v>1</v>
-      </c>
-      <c r="AB3" s="36" t="s">
-        <v>486</v>
+      <c r="Z3" s="36" t="s">
+        <v>571</v>
+      </c>
+      <c r="AB3" s="1" t="b">
+        <f t="shared" ref="AB3:AB66" si="0">M3=Z3</f>
+        <v>1</v>
       </c>
       <c r="AC3" s="36" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD3" s="36" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>481</v>
       </c>
@@ -3358,18 +3370,21 @@
       <c r="Y4" s="36" t="s">
         <v>479</v>
       </c>
-      <c r="AA4" s="1" t="b">
+      <c r="Z4" s="36" t="s">
+        <v>479</v>
+      </c>
+      <c r="AB4" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB4" s="36" t="s">
-        <v>479</v>
       </c>
       <c r="AC4" s="36" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD4" s="36" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>480</v>
       </c>
@@ -3441,18 +3456,21 @@
       <c r="Y5" s="36" t="s">
         <v>479</v>
       </c>
-      <c r="AA5" s="1" t="b">
+      <c r="Z5" s="36" t="s">
+        <v>479</v>
+      </c>
+      <c r="AB5" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB5" s="36" t="s">
-        <v>491</v>
       </c>
       <c r="AC5" s="36" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD5" s="36" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>487</v>
       </c>
@@ -3524,18 +3542,21 @@
       <c r="Y6" s="36" t="s">
         <v>571</v>
       </c>
-      <c r="AA6" s="1" t="b">
+      <c r="Z6" s="36" t="s">
+        <v>571</v>
+      </c>
+      <c r="AB6" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB6" s="36" t="s">
-        <v>515</v>
       </c>
       <c r="AC6" s="36" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD6" s="36" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>482</v>
       </c>
@@ -3607,18 +3628,21 @@
       <c r="Y7" s="36" t="s">
         <v>491</v>
       </c>
-      <c r="AA7" s="1" t="b">
+      <c r="Z7" s="36" t="s">
+        <v>491</v>
+      </c>
+      <c r="AB7" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB7" s="36" t="s">
-        <v>491</v>
       </c>
       <c r="AC7" s="36" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD7" s="36" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>523</v>
       </c>
@@ -3690,18 +3714,21 @@
       <c r="Y8" s="36">
         <v>0</v>
       </c>
-      <c r="AA8" s="1" t="b">
+      <c r="Z8" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB8" s="36">
-        <v>0</v>
-      </c>
       <c r="AC8" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -3773,18 +3800,21 @@
       <c r="Y9" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="AA9" s="1" t="b">
+      <c r="Z9" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB9" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB9" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="AC9" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD9" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -3856,18 +3886,21 @@
       <c r="Y10" s="77">
         <v>1</v>
       </c>
-      <c r="AA10" s="1" t="b">
+      <c r="Z10" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB10" s="77">
-        <v>1</v>
-      </c>
       <c r="AC10" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD10" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
         <v>441</v>
       </c>
@@ -3939,18 +3972,21 @@
       <c r="Y11" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA11" s="1" t="b">
+      <c r="Z11" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB11" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB11" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC11" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD11" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -4022,18 +4058,21 @@
       <c r="Y12" s="85">
         <v>180</v>
       </c>
-      <c r="AA12" s="1" t="b">
+      <c r="Z12" s="85">
+        <v>180</v>
+      </c>
+      <c r="AB12" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB12" s="85">
-        <v>180</v>
       </c>
       <c r="AC12" s="85">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD12" s="85">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -4105,18 +4144,21 @@
       <c r="Y13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="AA13" s="1" t="b">
+      <c r="Z13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+      <c r="AB13" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB13" s="78">
-        <v>4.1666666999999998E-2</v>
       </c>
       <c r="AC13" s="78">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD13" s="78">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -4188,18 +4230,21 @@
       <c r="Y14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-      <c r="AA14" s="1" t="b">
+      <c r="Z14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+      <c r="AB14" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB14" s="79">
-        <v>4.1666666999999998E-2</v>
       </c>
       <c r="AC14" s="79">
         <v>4.1666666999999998E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD14" s="79">
+        <v>4.1666666999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
@@ -4271,18 +4316,21 @@
       <c r="Y15" s="77">
         <v>1</v>
       </c>
-      <c r="AA15" s="1" t="b">
+      <c r="Z15" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB15" s="77">
-        <v>1</v>
-      </c>
       <c r="AC15" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD15" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>445</v>
       </c>
@@ -4354,18 +4402,21 @@
       <c r="Y16" s="77">
         <v>0</v>
       </c>
-      <c r="AA16" s="1" t="b">
+      <c r="Z16" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB16" s="77">
-        <v>0</v>
-      </c>
       <c r="AC16" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD16" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
@@ -4437,18 +4488,21 @@
       <c r="Y17" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA17" s="1" t="b">
+      <c r="Z17" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB17" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB17" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC17" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD17" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -4520,18 +4574,21 @@
       <c r="Y18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="AA18" s="1" t="b">
+      <c r="Z18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="AB18" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB18" s="80">
-        <v>5.0000000000000001E-9</v>
       </c>
       <c r="AC18" s="80">
         <v>5.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD18" s="80">
+        <v>5.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -4603,18 +4660,21 @@
       <c r="Y19" s="77">
         <v>10</v>
       </c>
-      <c r="AA19" s="1" t="b">
+      <c r="Z19" s="77">
+        <v>10</v>
+      </c>
+      <c r="AB19" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB19" s="77">
-        <v>10</v>
       </c>
       <c r="AC19" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD19" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>458</v>
       </c>
@@ -4686,18 +4746,21 @@
       <c r="Y20" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA20" s="1" t="b">
+      <c r="Z20" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB20" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB20" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC20" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD20" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>459</v>
       </c>
@@ -4769,18 +4832,21 @@
       <c r="Y21" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA21" s="1" t="b">
+      <c r="Z21" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB21" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB21" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC21" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD21" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>462</v>
       </c>
@@ -4852,18 +4918,21 @@
       <c r="Y22" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA22" s="1" t="b">
+      <c r="Z22" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB22" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB22" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC22" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD22" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>464</v>
       </c>
@@ -4935,18 +5004,21 @@
       <c r="Y23" s="77">
         <v>86400</v>
       </c>
-      <c r="AA23" s="1" t="b">
+      <c r="Z23" s="77">
+        <v>86400</v>
+      </c>
+      <c r="AB23" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB23" s="77">
-        <v>86400</v>
       </c>
       <c r="AC23" s="77">
         <v>86400</v>
       </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD23" s="77">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>10</v>
       </c>
@@ -5018,18 +5090,21 @@
       <c r="Y24" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="AA24" s="1" t="b">
+      <c r="Z24" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB24" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB24" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="AC24" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD24" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>11</v>
       </c>
@@ -5101,18 +5176,21 @@
       <c r="Y25" s="77">
         <v>3</v>
       </c>
-      <c r="AA25" s="1" t="b">
+      <c r="Z25" s="77">
+        <v>3</v>
+      </c>
+      <c r="AB25" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB25" s="77">
-        <v>3</v>
       </c>
       <c r="AC25" s="77">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD25" s="77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>363</v>
       </c>
@@ -5184,18 +5262,21 @@
       <c r="Y26" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AA26" s="1" t="b">
+      <c r="Z26" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB26" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB26" s="81" t="s">
-        <v>88</v>
-      </c>
       <c r="AC26" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD26" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>365</v>
       </c>
@@ -5267,18 +5348,21 @@
       <c r="Y27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AA27" s="1" t="b">
+      <c r="Z27" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB27" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB27" s="81" t="s">
-        <v>88</v>
-      </c>
       <c r="AC27" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD27" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>377</v>
       </c>
@@ -5350,18 +5434,21 @@
       <c r="Y28" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA28" s="1" t="b">
+      <c r="Z28" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB28" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB28" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC28" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD28" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>376</v>
       </c>
@@ -5433,18 +5520,21 @@
       <c r="Y29" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AA29" s="1" t="b">
+      <c r="Z29" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB29" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB29" s="81" t="s">
-        <v>88</v>
-      </c>
       <c r="AC29" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD29" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>375</v>
       </c>
@@ -5516,18 +5606,21 @@
       <c r="Y30" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AA30" s="1" t="b">
+      <c r="Z30" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB30" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB30" s="81" t="s">
-        <v>88</v>
-      </c>
       <c r="AC30" s="81" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD30" s="81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>12</v>
       </c>
@@ -5599,18 +5692,21 @@
       <c r="Y31" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA31" s="1" t="b">
+      <c r="Z31" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB31" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB31" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC31" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD31" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>13</v>
       </c>
@@ -5682,18 +5778,21 @@
       <c r="Y32" s="77">
         <v>0.33</v>
       </c>
-      <c r="AA32" s="1" t="b">
+      <c r="Z32" s="77">
+        <v>0.33</v>
+      </c>
+      <c r="AB32" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB32" s="77">
-        <v>0.33</v>
       </c>
       <c r="AC32" s="77">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD32" s="77">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>14</v>
       </c>
@@ -5765,18 +5864,21 @@
       <c r="Y33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA33" s="1" t="b">
+      <c r="Z33" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB33" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB33" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC33" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD33" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>9</v>
       </c>
@@ -5848,18 +5950,21 @@
       <c r="Y34" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA34" s="1" t="b">
+      <c r="Z34" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB34" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB34" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC34" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD34" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>451</v>
       </c>
@@ -5931,18 +6036,21 @@
       <c r="Y35" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA35" s="1" t="b">
+      <c r="Z35" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB35" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB35" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC35" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD35" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>21</v>
       </c>
@@ -6014,18 +6122,21 @@
       <c r="Y36" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="AA36" s="1" t="b">
+      <c r="Z36" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB36" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB36" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="AC36" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD36" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>22</v>
       </c>
@@ -6097,18 +6208,21 @@
       <c r="Y37" s="85" t="s">
         <v>430</v>
       </c>
-      <c r="AA37" s="1" t="b">
+      <c r="Z37" s="85" t="s">
+        <v>430</v>
+      </c>
+      <c r="AB37" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB37" s="85" t="s">
-        <v>430</v>
       </c>
       <c r="AC37" s="85" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD37" s="85" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
@@ -6180,18 +6294,21 @@
       <c r="Y38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="AA38" s="1" t="b">
+      <c r="Z38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AB38" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB38" s="80">
-        <v>9.9999999999999995E-7</v>
       </c>
       <c r="AC38" s="80">
         <v>9.9999999999999995E-7</v>
       </c>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD38" s="80">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>24</v>
       </c>
@@ -6263,18 +6380,21 @@
       <c r="Y39" s="86">
         <v>1E-3</v>
       </c>
-      <c r="AA39" s="1" t="b">
+      <c r="Z39" s="86">
+        <v>1E-3</v>
+      </c>
+      <c r="AB39" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB39" s="86">
-        <v>1E-3</v>
       </c>
       <c r="AC39" s="86">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD39" s="86">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>25</v>
       </c>
@@ -6346,18 +6466,21 @@
       <c r="Y40" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="AA40" s="1" t="b">
+      <c r="Z40" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB40" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB40" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="AC40" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD40" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>26</v>
       </c>
@@ -6429,18 +6552,21 @@
       <c r="Y41" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="AA41" s="1" t="b">
+      <c r="Z41" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB41" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB41" s="77" t="s">
-        <v>89</v>
       </c>
       <c r="AC41" s="77" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD41" s="77" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>27</v>
       </c>
@@ -6512,18 +6638,21 @@
       <c r="Y42" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="AA42" s="1" t="b">
+      <c r="Z42" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB42" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB42" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="AC42" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD42" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>28</v>
       </c>
@@ -6595,18 +6724,21 @@
       <c r="Y43" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA43" s="1" t="b">
+      <c r="Z43" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB43" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB43" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC43" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD43" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -6678,18 +6810,21 @@
       <c r="Y44" s="77">
         <v>120</v>
       </c>
-      <c r="AA44" s="1" t="b">
+      <c r="Z44" s="77">
+        <v>120</v>
+      </c>
+      <c r="AB44" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB44" s="77">
-        <v>120</v>
       </c>
       <c r="AC44" s="77">
         <v>120</v>
       </c>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD44" s="77">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>30</v>
       </c>
@@ -6761,18 +6896,21 @@
       <c r="Y45" s="77">
         <v>0</v>
       </c>
-      <c r="AA45" s="1" t="b">
+      <c r="Z45" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB45" s="77">
-        <v>0</v>
-      </c>
       <c r="AC45" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD45" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>31</v>
       </c>
@@ -6844,18 +6982,21 @@
       <c r="Y46" s="77">
         <v>0</v>
       </c>
-      <c r="AA46" s="1" t="b">
+      <c r="Z46" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB46" s="77">
-        <v>0</v>
-      </c>
       <c r="AC46" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD46" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>32</v>
       </c>
@@ -6927,18 +7068,21 @@
       <c r="Y47" s="77">
         <v>-0.1</v>
       </c>
-      <c r="AA47" s="1" t="b">
+      <c r="Z47" s="77">
+        <v>-0.1</v>
+      </c>
+      <c r="AB47" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB47" s="77">
-        <v>-0.1</v>
       </c>
       <c r="AC47" s="77">
         <v>-0.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD47" s="77">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>33</v>
       </c>
@@ -7010,18 +7154,21 @@
       <c r="Y48" s="77">
         <v>-0.2</v>
       </c>
-      <c r="AA48" s="1" t="b">
+      <c r="Z48" s="77">
+        <v>-0.2</v>
+      </c>
+      <c r="AB48" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB48" s="77">
-        <v>-0.2</v>
       </c>
       <c r="AC48" s="77">
         <v>-0.2</v>
       </c>
-    </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD48" s="77">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>34</v>
       </c>
@@ -7093,18 +7240,21 @@
       <c r="Y49" s="77">
         <v>0.4</v>
       </c>
-      <c r="AA49" s="1" t="b">
+      <c r="Z49" s="77">
+        <v>0.4</v>
+      </c>
+      <c r="AB49" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB49" s="77">
-        <v>0.4</v>
       </c>
       <c r="AC49" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD49" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>35</v>
       </c>
@@ -7176,18 +7326,21 @@
       <c r="Y50" s="77">
         <v>0</v>
       </c>
-      <c r="AA50" s="1" t="b">
+      <c r="Z50" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB50" s="77">
-        <v>0</v>
-      </c>
       <c r="AC50" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD50" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>431</v>
       </c>
@@ -7259,18 +7412,21 @@
       <c r="Y51" s="77">
         <v>1200</v>
       </c>
-      <c r="AA51" s="1" t="b">
+      <c r="Z51" s="77">
+        <v>1200</v>
+      </c>
+      <c r="AB51" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB51" s="77">
-        <v>1200</v>
       </c>
       <c r="AC51" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD51" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>432</v>
       </c>
@@ -7342,18 +7498,21 @@
       <c r="Y52" s="77">
         <v>1200</v>
       </c>
-      <c r="AA52" s="1" t="b">
+      <c r="Z52" s="77">
+        <v>1200</v>
+      </c>
+      <c r="AB52" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB52" s="77">
-        <v>1200</v>
       </c>
       <c r="AC52" s="77">
         <v>1200</v>
       </c>
-    </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD52" s="77">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>454</v>
       </c>
@@ -7425,18 +7584,21 @@
       <c r="Y53" s="35" t="s">
         <v>457</v>
       </c>
-      <c r="AA53" s="1" t="b">
+      <c r="Z53" s="35" t="s">
+        <v>457</v>
+      </c>
+      <c r="AB53" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB53" s="35" t="s">
-        <v>457</v>
       </c>
       <c r="AC53" s="35" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD53" s="35" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>15</v>
       </c>
@@ -7508,18 +7670,21 @@
       <c r="Y54" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="AA54" s="1" t="b">
+      <c r="Z54" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB54" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB54" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="AC54" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD54" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>16</v>
       </c>
@@ -7591,18 +7756,21 @@
       <c r="Y55" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="AA55" s="1" t="b">
+      <c r="Z55" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB55" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB55" s="77" t="s">
-        <v>87</v>
       </c>
       <c r="AC55" s="77" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD55" s="77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>17</v>
       </c>
@@ -7674,18 +7842,21 @@
       <c r="Y56" s="77">
         <v>0</v>
       </c>
-      <c r="AA56" s="1" t="b">
+      <c r="Z56" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB56" s="77">
-        <v>0</v>
-      </c>
       <c r="AC56" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD56" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -7757,18 +7928,21 @@
       <c r="Y57" s="77">
         <v>0.5</v>
       </c>
-      <c r="AA57" s="1" t="b">
+      <c r="Z57" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="AB57" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB57" s="77">
-        <v>0.5</v>
       </c>
       <c r="AC57" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD57" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>19</v>
       </c>
@@ -7840,18 +8014,21 @@
       <c r="Y58" s="77">
         <v>0.05</v>
       </c>
-      <c r="AA58" s="1" t="b">
+      <c r="Z58" s="77">
+        <v>0.05</v>
+      </c>
+      <c r="AB58" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB58" s="77">
-        <v>0.05</v>
       </c>
       <c r="AC58" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD58" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>36</v>
       </c>
@@ -7923,18 +8100,21 @@
       <c r="Y59" s="80">
         <v>1E-3</v>
       </c>
-      <c r="AA59" s="1" t="b">
+      <c r="Z59" s="80">
+        <v>1E-3</v>
+      </c>
+      <c r="AB59" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB59" s="80">
-        <v>1E-3</v>
       </c>
       <c r="AC59" s="80">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD59" s="80">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>380</v>
       </c>
@@ -8006,18 +8186,21 @@
       <c r="Y60" s="77">
         <v>0</v>
       </c>
-      <c r="AA60" s="1" t="b">
+      <c r="Z60" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB60" s="77">
-        <v>0</v>
-      </c>
       <c r="AC60" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD60" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>37</v>
       </c>
@@ -8089,18 +8272,21 @@
       <c r="Y61" s="77">
         <v>1E-4</v>
       </c>
-      <c r="AA61" s="1" t="b">
+      <c r="Z61" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="AB61" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB61" s="77">
-        <v>1E-4</v>
       </c>
       <c r="AC61" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD61" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>38</v>
       </c>
@@ -8172,18 +8358,21 @@
       <c r="Y62" s="77">
         <v>1E-4</v>
       </c>
-      <c r="AA62" s="1" t="b">
+      <c r="Z62" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="AB62" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB62" s="77">
-        <v>1E-4</v>
       </c>
       <c r="AC62" s="77">
         <v>1E-4</v>
       </c>
-    </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD62" s="77">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>39</v>
       </c>
@@ -8255,18 +8444,21 @@
       <c r="Y63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="AA63" s="1" t="b">
+      <c r="Z63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="AB63" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB63" s="77">
-        <v>6.9999999999999999E-4</v>
       </c>
       <c r="AC63" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
-    </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD63" s="77">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>40</v>
       </c>
@@ -8338,18 +8530,21 @@
       <c r="Y64" s="77">
         <v>1.22E-4</v>
       </c>
-      <c r="AA64" s="1" t="b">
+      <c r="Z64" s="77">
+        <v>1.22E-4</v>
+      </c>
+      <c r="AB64" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB64" s="77">
-        <v>1.22E-4</v>
       </c>
       <c r="AC64" s="77">
         <v>1.22E-4</v>
       </c>
-    </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD64" s="77">
+        <v>1.22E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>207</v>
       </c>
@@ -8421,18 +8616,21 @@
       <c r="Y65" s="77">
         <v>1</v>
       </c>
-      <c r="AA65" s="1" t="b">
+      <c r="Z65" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB65" s="77">
-        <v>1</v>
-      </c>
       <c r="AC65" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD65" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>41</v>
       </c>
@@ -8504,18 +8702,21 @@
       <c r="Y66" s="77">
         <v>0.95</v>
       </c>
-      <c r="AA66" s="1" t="b">
+      <c r="Z66" s="77">
+        <v>0.95</v>
+      </c>
+      <c r="AB66" s="1" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="AB66" s="77">
-        <v>0.95</v>
       </c>
       <c r="AC66" s="77">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD66" s="77">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>406</v>
       </c>
@@ -8587,18 +8788,21 @@
       <c r="Y67" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA67" s="1" t="b">
-        <f t="shared" ref="AA67:AA133" si="1">M67=Y67</f>
-        <v>1</v>
-      </c>
-      <c r="AB67" s="77" t="s">
-        <v>88</v>
+      <c r="Z67" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB67" s="1" t="b">
+        <f t="shared" ref="AB67:AB133" si="1">M67=Z67</f>
+        <v>1</v>
       </c>
       <c r="AC67" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD67" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
@@ -8670,18 +8874,21 @@
       <c r="Y68" s="77">
         <v>5</v>
       </c>
-      <c r="AA68" s="1" t="b">
+      <c r="Z68" s="77">
+        <v>5</v>
+      </c>
+      <c r="AB68" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB68" s="77">
-        <v>5</v>
       </c>
       <c r="AC68" s="77">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD68" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>408</v>
       </c>
@@ -8753,18 +8960,21 @@
       <c r="Y69" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AA69" s="1" t="b">
+      <c r="Z69" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB69" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB69" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC69" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD69" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>42</v>
       </c>
@@ -8836,18 +9046,21 @@
       <c r="Y70" s="77">
         <v>50</v>
       </c>
-      <c r="AA70" s="1" t="b">
+      <c r="Z70" s="77">
+        <v>50</v>
+      </c>
+      <c r="AB70" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB70" s="77">
-        <v>50</v>
       </c>
       <c r="AC70" s="77">
         <v>50</v>
       </c>
-    </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD70" s="77">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>208</v>
       </c>
@@ -8919,18 +9132,21 @@
       <c r="Y71" s="78">
         <v>1453890.8941884842</v>
       </c>
-      <c r="AA71" s="1" t="b">
+      <c r="Z71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+      <c r="AB71" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB71" s="78">
-        <v>1453890.8941884842</v>
       </c>
       <c r="AC71" s="78">
         <v>1453890.8941884842</v>
       </c>
-    </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD71" s="78">
+        <v>1453890.8941884842</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>43</v>
       </c>
@@ -9002,18 +9218,21 @@
       <c r="Y72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-      <c r="AA72" s="1" t="b">
+      <c r="Z72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+      <c r="AB72" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB72" s="78">
-        <v>1.3888888888888888E-5</v>
       </c>
       <c r="AC72" s="78">
         <v>1.3888888888888888E-5</v>
       </c>
-    </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD72" s="78">
+        <v>1.3888888888888888E-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>44</v>
       </c>
@@ -9085,18 +9304,21 @@
       <c r="Y73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-      <c r="AA73" s="1" t="b">
+      <c r="Z73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+      <c r="AB73" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB73" s="79">
-        <v>6.5011574074074071E-4</v>
       </c>
       <c r="AC73" s="79">
         <v>6.5011574074074071E-4</v>
       </c>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD73" s="79">
+        <v>6.5011574074074071E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
         <v>45</v>
       </c>
@@ -9168,18 +9390,21 @@
       <c r="Y74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-      <c r="AA74" s="1" t="b">
+      <c r="Z74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+      <c r="AB74" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB74" s="85">
-        <v>4.7400000000000003E-3</v>
       </c>
       <c r="AC74" s="85">
         <v>4.7400000000000003E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD74" s="85">
+        <v>4.7400000000000003E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>46</v>
       </c>
@@ -9215,7 +9440,7 @@
       </c>
       <c r="L75" s="79"/>
       <c r="M75" s="79">
-        <f t="shared" ref="M75:U75" si="2">282528</f>
+        <f t="shared" ref="M75:W75" si="2">282528</f>
         <v>282528</v>
       </c>
       <c r="N75" s="79">
@@ -9252,7 +9477,7 @@
       </c>
       <c r="V75" s="79"/>
       <c r="W75" s="79">
-        <f>282528</f>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="X75" s="79">
@@ -9260,20 +9485,24 @@
         <v>282528</v>
       </c>
       <c r="Y75" s="79">
+        <f>282528</f>
         <v>282528</v>
       </c>
-      <c r="AA75" s="1" t="b">
+      <c r="Z75" s="79">
+        <v>282528</v>
+      </c>
+      <c r="AB75" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB75" s="79">
-        <v>282528</v>
       </c>
       <c r="AC75" s="79">
         <v>282528</v>
       </c>
-    </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD75" s="79">
+        <v>282528</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
         <v>47</v>
       </c>
@@ -9337,7 +9566,7 @@
       </c>
       <c r="V76" s="85"/>
       <c r="W76" s="85">
-        <v>0.56999999999999995</v>
+        <v>1</v>
       </c>
       <c r="X76" s="85">
         <v>0.56999999999999995</v>
@@ -9345,18 +9574,21 @@
       <c r="Y76" s="85">
         <v>0.56999999999999995</v>
       </c>
-      <c r="AA76" s="1" t="b">
+      <c r="Z76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AB76" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB76" s="85">
-        <v>0.56999999999999995</v>
       </c>
       <c r="AC76" s="85">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD76" s="85">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>48</v>
       </c>
@@ -9428,18 +9660,21 @@
       <c r="Y77" s="87">
         <v>0.16</v>
       </c>
-      <c r="AA77" s="1" t="b">
+      <c r="Z77" s="87">
+        <v>0.16</v>
+      </c>
+      <c r="AB77" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB77" s="87">
-        <v>0.16</v>
       </c>
       <c r="AC77" s="87">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD77" s="87">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
         <v>49</v>
       </c>
@@ -9511,18 +9746,21 @@
       <c r="Y78" s="77">
         <v>0</v>
       </c>
-      <c r="AA78" s="1" t="b">
+      <c r="Z78" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB78" s="77">
-        <v>0</v>
-      </c>
       <c r="AC78" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD78" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="33" t="s">
         <v>50</v>
       </c>
@@ -9594,18 +9832,21 @@
       <c r="Y79" s="78">
         <v>745476480000</v>
       </c>
-      <c r="AA79" s="1" t="b">
+      <c r="Z79" s="78">
+        <v>745476480000</v>
+      </c>
+      <c r="AB79" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB79" s="78">
-        <v>745476480000</v>
       </c>
       <c r="AC79" s="78">
         <v>745476480000</v>
       </c>
-    </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD79" s="78">
+        <v>745476480000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
         <v>205</v>
       </c>
@@ -9677,18 +9918,21 @@
       <c r="Y80" s="77">
         <v>100</v>
       </c>
-      <c r="AA80" s="1" t="b">
+      <c r="Z80" s="77">
+        <v>100</v>
+      </c>
+      <c r="AB80" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB80" s="77">
-        <v>100</v>
       </c>
       <c r="AC80" s="77">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD80" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="33" t="s">
         <v>414</v>
       </c>
@@ -9760,18 +10004,21 @@
       <c r="Y81" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="AA81" s="1" t="b">
+      <c r="Z81" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB81" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB81" s="77" t="s">
-        <v>88</v>
-      </c>
       <c r="AC81" s="77" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD81" s="77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
         <v>400</v>
       </c>
@@ -9843,18 +10090,21 @@
       <c r="Y82" s="85">
         <v>21600</v>
       </c>
-      <c r="AA82" s="1" t="b">
+      <c r="Z82" s="85">
+        <v>21600</v>
+      </c>
+      <c r="AB82" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB82" s="85">
-        <v>21600</v>
       </c>
       <c r="AC82" s="85">
         <v>21600</v>
       </c>
-    </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD82" s="85">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="33" t="s">
         <v>410</v>
       </c>
@@ -9926,18 +10176,21 @@
       <c r="Y83" s="77">
         <v>0.5</v>
       </c>
-      <c r="AA83" s="1" t="b">
+      <c r="Z83" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="AB83" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB83" s="77">
-        <v>0.5</v>
       </c>
       <c r="AC83" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD83" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>401</v>
       </c>
@@ -10009,18 +10262,21 @@
       <c r="Y84" s="85">
         <v>60479.999999999993</v>
       </c>
-      <c r="AA84" s="1" t="b">
+      <c r="Z84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+      <c r="AB84" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB84" s="85">
-        <v>60479.999999999993</v>
       </c>
       <c r="AC84" s="85">
         <v>60479.999999999993</v>
       </c>
-    </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD84" s="85">
+        <v>60479.999999999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="s">
         <v>411</v>
       </c>
@@ -10092,18 +10348,21 @@
       <c r="Y85" s="77">
         <v>0.85</v>
       </c>
-      <c r="AA85" s="1" t="b">
+      <c r="Z85" s="77">
+        <v>0.85</v>
+      </c>
+      <c r="AB85" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB85" s="77">
-        <v>0.85</v>
       </c>
       <c r="AC85" s="77">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD85" s="77">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>402</v>
       </c>
@@ -10175,18 +10434,21 @@
       <c r="Y86" s="77">
         <v>518400</v>
       </c>
-      <c r="AA86" s="1" t="b">
+      <c r="Z86" s="77">
+        <v>518400</v>
+      </c>
+      <c r="AB86" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB86" s="77">
-        <v>518400</v>
       </c>
       <c r="AC86" s="77">
         <v>518400</v>
       </c>
-    </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD86" s="77">
+        <v>518400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>412</v>
       </c>
@@ -10258,18 +10520,21 @@
       <c r="Y87" s="77">
         <v>5184000</v>
       </c>
-      <c r="AA87" s="1" t="b">
+      <c r="Z87" s="77">
+        <v>5184000</v>
+      </c>
+      <c r="AB87" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB87" s="77">
-        <v>5184000</v>
       </c>
       <c r="AC87" s="77">
         <v>5184000</v>
       </c>
-    </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD87" s="77">
+        <v>5184000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
         <v>51</v>
       </c>
@@ -10341,18 +10606,21 @@
       <c r="Y88" s="86">
         <v>50000</v>
       </c>
-      <c r="AA88" s="1" t="b">
+      <c r="Z88" s="86">
+        <v>50000</v>
+      </c>
+      <c r="AB88" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB88" s="86">
-        <v>50000</v>
       </c>
       <c r="AC88" s="86">
         <v>50000</v>
       </c>
-    </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD88" s="86">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
         <v>52</v>
       </c>
@@ -10424,18 +10692,21 @@
       <c r="Y89" s="77">
         <v>140000</v>
       </c>
-      <c r="AA89" s="1" t="b">
+      <c r="Z89" s="77">
+        <v>140000</v>
+      </c>
+      <c r="AB89" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB89" s="77">
-        <v>140000</v>
       </c>
       <c r="AC89" s="77">
         <v>140000</v>
       </c>
-    </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD89" s="77">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
         <v>53</v>
       </c>
@@ -10507,18 +10778,21 @@
       <c r="Y90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-      <c r="AA90" s="1" t="b">
+      <c r="Z90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+      <c r="AB90" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB90" s="78">
-        <v>3.6636136999999999E-2</v>
       </c>
       <c r="AC90" s="78">
         <v>3.6636136999999999E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD90" s="78">
+        <v>3.6636136999999999E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
         <v>54</v>
       </c>
@@ -10590,18 +10864,21 @@
       <c r="Y91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="AA91" s="1" t="b">
+      <c r="Z91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="AB91" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB91" s="77">
-        <v>4.4999999999999997E-3</v>
       </c>
       <c r="AC91" s="77">
         <v>4.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD91" s="77">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
         <v>55</v>
       </c>
@@ -10673,18 +10950,21 @@
       <c r="Y92" s="77">
         <v>0.05</v>
       </c>
-      <c r="AA92" s="1" t="b">
+      <c r="Z92" s="77">
+        <v>0.05</v>
+      </c>
+      <c r="AB92" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB92" s="77">
-        <v>0.05</v>
       </c>
       <c r="AC92" s="77">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD92" s="77">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>214</v>
       </c>
@@ -10756,18 +11036,21 @@
       <c r="Y93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="AA93" s="1" t="b">
+      <c r="Z93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="AB93" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB93" s="77">
-        <v>6.0000000000000002E-6</v>
       </c>
       <c r="AC93" s="77">
         <v>6.0000000000000002E-6</v>
       </c>
-    </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD93" s="77">
+        <v>6.0000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>215</v>
       </c>
@@ -10831,26 +11114,29 @@
       </c>
       <c r="V94" s="77"/>
       <c r="W94" s="77">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="X94" s="77">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="Y94" s="77">
         <v>1E-3</v>
       </c>
-      <c r="AA94" s="1" t="b">
+      <c r="Z94" s="77">
+        <v>1E-3</v>
+      </c>
+      <c r="AB94" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB94" s="77">
-        <v>0</v>
-      </c>
       <c r="AC94" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD94" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>216</v>
       </c>
@@ -10922,18 +11208,21 @@
       <c r="Y95" s="77">
         <v>374999999.99999994</v>
       </c>
-      <c r="AA95" s="1" t="b">
+      <c r="Z95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+      <c r="AB95" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB95" s="77">
-        <v>374999999.99999994</v>
       </c>
       <c r="AC95" s="77">
         <v>374999999.99999994</v>
       </c>
-    </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD95" s="77">
+        <v>374999999.99999994</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>217</v>
       </c>
@@ -10997,26 +11286,29 @@
       </c>
       <c r="V96" s="78"/>
       <c r="W96" s="78">
-        <v>0</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="X96" s="78">
-        <v>3.7037037037037038E-3</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="AA96" s="1" t="b">
+      <c r="Z96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="AB96" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB96" s="78">
-        <v>3.7037037037037038E-3</v>
       </c>
       <c r="AC96" s="78">
         <v>3.7037037037037038E-3</v>
       </c>
-    </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD96" s="78">
+        <v>3.7037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>218</v>
       </c>
@@ -11088,18 +11380,21 @@
       <c r="Y97" s="77">
         <v>165600</v>
       </c>
-      <c r="AA97" s="1" t="b">
+      <c r="Z97" s="77">
+        <v>165600</v>
+      </c>
+      <c r="AB97" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB97" s="77">
-        <v>165600</v>
       </c>
       <c r="AC97" s="77">
         <v>165600</v>
       </c>
-    </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD97" s="77">
+        <v>165600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>60</v>
       </c>
@@ -11171,18 +11466,21 @@
       <c r="Y98" s="77">
         <v>20</v>
       </c>
-      <c r="AA98" s="1" t="b">
+      <c r="Z98" s="77">
+        <v>20</v>
+      </c>
+      <c r="AB98" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB98" s="77">
-        <v>20</v>
       </c>
       <c r="AC98" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD98" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
@@ -11254,18 +11552,21 @@
       <c r="Y99" s="77">
         <v>1</v>
       </c>
-      <c r="AA99" s="1" t="b">
+      <c r="Z99" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB99" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB99" s="77">
-        <v>1</v>
-      </c>
       <c r="AC99" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD99" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>59</v>
       </c>
@@ -11337,18 +11638,21 @@
       <c r="Y100" s="77">
         <v>21</v>
       </c>
-      <c r="AA100" s="1" t="b">
+      <c r="Z100" s="77">
+        <v>21</v>
+      </c>
+      <c r="AB100" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB100" s="77">
-        <v>21</v>
       </c>
       <c r="AC100" s="77">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD100" s="77">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="23" t="s">
         <v>65</v>
       </c>
@@ -11420,18 +11724,21 @@
       <c r="Y101" s="77">
         <v>0.64</v>
       </c>
-      <c r="AA101" s="1" t="b">
+      <c r="Z101" s="77">
+        <v>0.64</v>
+      </c>
+      <c r="AB101" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB101" s="77">
-        <v>0.64</v>
       </c>
       <c r="AC101" s="77">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD101" s="77">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="23" t="s">
         <v>367</v>
       </c>
@@ -11503,18 +11810,21 @@
       <c r="Y102" s="77">
         <v>8</v>
       </c>
-      <c r="AA102" s="1" t="b">
+      <c r="Z102" s="77">
+        <v>8</v>
+      </c>
+      <c r="AB102" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB102" s="77">
-        <v>8</v>
       </c>
       <c r="AC102" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD102" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="23" t="s">
         <v>368</v>
       </c>
@@ -11586,18 +11896,21 @@
       <c r="Y103" s="77">
         <v>10</v>
       </c>
-      <c r="AA103" s="1" t="b">
+      <c r="Z103" s="77">
+        <v>10</v>
+      </c>
+      <c r="AB103" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB103" s="77">
-        <v>10</v>
       </c>
       <c r="AC103" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD103" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="23" t="s">
         <v>369</v>
       </c>
@@ -11669,18 +11982,21 @@
       <c r="Y104" s="77">
         <v>8</v>
       </c>
-      <c r="AA104" s="1" t="b">
+      <c r="Z104" s="77">
+        <v>8</v>
+      </c>
+      <c r="AB104" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB104" s="77">
-        <v>8</v>
       </c>
       <c r="AC104" s="77">
         <v>8</v>
       </c>
-    </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD104" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="23" t="s">
         <v>494</v>
       </c>
@@ -11752,18 +12068,21 @@
       <c r="Y105" s="77">
         <v>1</v>
       </c>
-      <c r="AA105" s="1" t="b">
+      <c r="Z105" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB105" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB105" s="77">
-        <v>1</v>
-      </c>
       <c r="AC105" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD105" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="23" t="s">
         <v>385</v>
       </c>
@@ -11835,18 +12154,21 @@
       <c r="Y106" s="77">
         <v>0.5</v>
       </c>
-      <c r="AA106" s="1" t="b">
+      <c r="Z106" s="77">
+        <v>0.5</v>
+      </c>
+      <c r="AB106" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB106" s="77">
-        <v>0.5</v>
       </c>
       <c r="AC106" s="77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD106" s="77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="23" t="s">
         <v>495</v>
       </c>
@@ -11935,18 +12257,22 @@
         <f t="shared" ref="Y107" si="12">Y105</f>
         <v>1</v>
       </c>
-      <c r="AA107" s="1" t="b">
+      <c r="Z107" s="58">
+        <f t="shared" ref="Z107" si="13">Z105</f>
+        <v>1</v>
+      </c>
+      <c r="AB107" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB107" s="58">
-        <v>1</v>
-      </c>
       <c r="AC107" s="58">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD107" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="23" t="s">
         <v>496</v>
       </c>
@@ -11970,83 +12296,87 @@
         <v>3</v>
       </c>
       <c r="H108" s="58">
-        <f t="shared" ref="H108:Y108" si="13">150*H105</f>
+        <f t="shared" ref="H108:Z108" si="14">150*H105</f>
         <v>150</v>
       </c>
       <c r="I108" s="58">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>150</v>
       </c>
       <c r="J108" s="58">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>150</v>
       </c>
       <c r="K108" s="58">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>150</v>
       </c>
       <c r="L108" s="58"/>
       <c r="M108" s="58">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>150</v>
       </c>
       <c r="N108" s="58">
-        <f t="shared" ref="N108" si="14">150*N105</f>
+        <f t="shared" ref="N108" si="15">150*N105</f>
         <v>150</v>
       </c>
       <c r="O108" s="58">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>150</v>
       </c>
       <c r="P108" s="58">
-        <f t="shared" ref="P108" si="15">150*P105</f>
+        <f t="shared" ref="P108" si="16">150*P105</f>
         <v>150</v>
       </c>
       <c r="Q108" s="58">
-        <f t="shared" ref="Q108:U108" si="16">150*Q105</f>
+        <f t="shared" ref="Q108:U108" si="17">150*Q105</f>
         <v>150</v>
       </c>
       <c r="R108" s="58">
-        <f t="shared" ref="R108:S108" si="17">150*R105</f>
+        <f t="shared" ref="R108:S108" si="18">150*R105</f>
         <v>150</v>
       </c>
       <c r="S108" s="58">
+        <f t="shared" si="18"/>
+        <v>150</v>
+      </c>
+      <c r="T108" s="58">
+        <f t="shared" ref="T108" si="19">150*T105</f>
+        <v>150</v>
+      </c>
+      <c r="U108" s="58">
         <f t="shared" si="17"/>
         <v>150</v>
       </c>
-      <c r="T108" s="58">
-        <f t="shared" ref="T108" si="18">150*T105</f>
-        <v>150</v>
-      </c>
-      <c r="U108" s="58">
-        <f t="shared" si="16"/>
-        <v>150</v>
-      </c>
       <c r="V108" s="58"/>
       <c r="W108" s="58">
-        <f t="shared" ref="W108" si="19">150*W105</f>
+        <f t="shared" ref="W108" si="20">150*W105</f>
         <v>150</v>
       </c>
       <c r="X108" s="58">
-        <f t="shared" ref="X108" si="20">150*X105</f>
+        <f t="shared" ref="X108" si="21">150*X105</f>
         <v>150</v>
       </c>
       <c r="Y108" s="58">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="Y108" si="22">150*Y105</f>
         <v>150</v>
       </c>
-      <c r="AA108" s="1" t="b">
+      <c r="Z108" s="58">
+        <f t="shared" si="14"/>
+        <v>150</v>
+      </c>
+      <c r="AB108" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB108" s="58">
-        <v>150</v>
       </c>
       <c r="AC108" s="58">
         <v>150</v>
       </c>
-    </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD108" s="58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="23" t="s">
         <v>497</v>
       </c>
@@ -12066,87 +12396,91 @@
         <v>500</v>
       </c>
       <c r="G109" s="58">
-        <f t="shared" ref="G109:O109" si="21">G100</f>
+        <f t="shared" ref="G109:O109" si="23">G100</f>
         <v>21</v>
       </c>
       <c r="H109" s="58">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="I109" s="58">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="J109" s="58">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="K109" s="58">
-        <f t="shared" ref="K109" si="22">K100</f>
+        <f t="shared" ref="K109" si="24">K100</f>
         <v>21</v>
       </c>
       <c r="L109" s="58"/>
       <c r="M109" s="58">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="N109" s="58">
-        <f t="shared" ref="N109" si="23">N100</f>
+        <f t="shared" ref="N109" si="25">N100</f>
         <v>21</v>
       </c>
       <c r="O109" s="58">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="P109" s="58">
-        <f t="shared" ref="P109" si="24">P100</f>
+        <f t="shared" ref="P109" si="26">P100</f>
         <v>21</v>
       </c>
       <c r="Q109" s="58">
-        <f t="shared" ref="Q109:U109" si="25">Q100</f>
+        <f t="shared" ref="Q109:U109" si="27">Q100</f>
         <v>21</v>
       </c>
       <c r="R109" s="58">
-        <f t="shared" ref="R109:S109" si="26">R100</f>
+        <f t="shared" ref="R109:S109" si="28">R100</f>
         <v>21</v>
       </c>
       <c r="S109" s="58">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>21</v>
       </c>
       <c r="T109" s="58">
-        <f t="shared" ref="T109" si="27">T100</f>
+        <f t="shared" ref="T109" si="29">T100</f>
         <v>21</v>
       </c>
       <c r="U109" s="58">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21</v>
       </c>
       <c r="V109" s="58"/>
       <c r="W109" s="58">
-        <f t="shared" ref="W109" si="28">W100</f>
+        <f t="shared" ref="W109" si="30">W100</f>
         <v>21</v>
       </c>
       <c r="X109" s="58">
-        <f t="shared" ref="X109" si="29">X100</f>
+        <f t="shared" ref="X109" si="31">X100</f>
         <v>21</v>
       </c>
       <c r="Y109" s="58">
-        <f t="shared" ref="Y109" si="30">Y100</f>
+        <f t="shared" ref="Y109" si="32">Y100</f>
         <v>21</v>
       </c>
-      <c r="AA109" s="1" t="b">
+      <c r="Z109" s="58">
+        <f t="shared" ref="Z109" si="33">Z100</f>
+        <v>21</v>
+      </c>
+      <c r="AB109" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB109" s="58">
-        <v>21</v>
       </c>
       <c r="AC109" s="58">
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD109" s="58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" s="23" t="s">
         <v>498</v>
       </c>
@@ -12170,83 +12504,87 @@
         <v>210</v>
       </c>
       <c r="H110" s="58">
-        <f t="shared" ref="H110:Y110" si="31">70*H100</f>
+        <f t="shared" ref="H110:Z110" si="34">70*H100</f>
         <v>1470</v>
       </c>
       <c r="I110" s="58">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1470</v>
       </c>
       <c r="J110" s="58">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1470</v>
       </c>
       <c r="K110" s="58">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1470</v>
       </c>
       <c r="L110" s="58"/>
       <c r="M110" s="58">
-        <f t="shared" si="31"/>
-        <v>1470</v>
-      </c>
-      <c r="N110" s="58">
-        <f t="shared" ref="N110" si="32">70*N100</f>
-        <v>1470</v>
-      </c>
-      <c r="O110" s="58">
-        <f t="shared" si="31"/>
-        <v>1470</v>
-      </c>
-      <c r="P110" s="58">
-        <f t="shared" ref="P110" si="33">70*P100</f>
-        <v>1470</v>
-      </c>
-      <c r="Q110" s="58">
-        <f t="shared" ref="Q110:U110" si="34">70*Q100</f>
-        <v>1470</v>
-      </c>
-      <c r="R110" s="58">
-        <f t="shared" ref="R110:S110" si="35">70*R100</f>
-        <v>1470</v>
-      </c>
-      <c r="S110" s="58">
-        <f t="shared" si="35"/>
-        <v>1470</v>
-      </c>
-      <c r="T110" s="58">
-        <f t="shared" ref="T110" si="36">70*T100</f>
-        <v>1470</v>
-      </c>
-      <c r="U110" s="58">
         <f t="shared" si="34"/>
         <v>1470</v>
       </c>
+      <c r="N110" s="58">
+        <f t="shared" ref="N110" si="35">70*N100</f>
+        <v>1470</v>
+      </c>
+      <c r="O110" s="58">
+        <f t="shared" si="34"/>
+        <v>1470</v>
+      </c>
+      <c r="P110" s="58">
+        <f t="shared" ref="P110" si="36">70*P100</f>
+        <v>1470</v>
+      </c>
+      <c r="Q110" s="58">
+        <f t="shared" ref="Q110:U110" si="37">70*Q100</f>
+        <v>1470</v>
+      </c>
+      <c r="R110" s="58">
+        <f t="shared" ref="R110:S110" si="38">70*R100</f>
+        <v>1470</v>
+      </c>
+      <c r="S110" s="58">
+        <f t="shared" si="38"/>
+        <v>1470</v>
+      </c>
+      <c r="T110" s="58">
+        <f t="shared" ref="T110" si="39">70*T100</f>
+        <v>1470</v>
+      </c>
+      <c r="U110" s="58">
+        <f t="shared" si="37"/>
+        <v>1470</v>
+      </c>
       <c r="V110" s="58"/>
       <c r="W110" s="58">
-        <f t="shared" ref="W110" si="37">70*W100</f>
+        <f t="shared" ref="W110" si="40">70*W100</f>
         <v>1470</v>
       </c>
       <c r="X110" s="58">
-        <f t="shared" ref="X110" si="38">70*X100</f>
+        <f t="shared" ref="X110" si="41">70*X100</f>
         <v>1470</v>
       </c>
       <c r="Y110" s="58">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="Y110" si="42">70*Y100</f>
         <v>1470</v>
       </c>
-      <c r="AA110" s="1" t="b">
+      <c r="Z110" s="58">
+        <f t="shared" si="34"/>
+        <v>1470</v>
+      </c>
+      <c r="AB110" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB110" s="58">
-        <v>1470</v>
       </c>
       <c r="AC110" s="58">
         <v>1470</v>
       </c>
-    </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD110" s="58">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A111" s="23" t="s">
         <v>387</v>
       </c>
@@ -12318,18 +12656,21 @@
       <c r="Y111" s="77">
         <v>0</v>
       </c>
-      <c r="AA111" s="1" t="b">
+      <c r="Z111" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB111" s="77">
-        <v>0</v>
-      </c>
       <c r="AC111" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD111" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A112" s="23" t="s">
         <v>389</v>
       </c>
@@ -12401,18 +12742,21 @@
       <c r="Y112" s="82">
         <v>1589759.9999999998</v>
       </c>
-      <c r="AA112" s="1" t="b">
+      <c r="Z112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+      <c r="AB112" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB112" s="82">
-        <v>1589759.9999999998</v>
       </c>
       <c r="AC112" s="82">
         <v>1589759.9999999998</v>
       </c>
-    </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD112" s="82">
+        <v>1589759.9999999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A113" s="23" t="s">
         <v>391</v>
       </c>
@@ -12484,18 +12828,21 @@
       <c r="Y113" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="AA113" s="1" t="b">
+      <c r="Z113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+      <c r="AB113" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB113" s="82">
-        <v>6171428.5714285718</v>
       </c>
       <c r="AC113" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD113" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A114" s="23" t="s">
         <v>393</v>
       </c>
@@ -12567,18 +12914,21 @@
       <c r="Y114" s="82">
         <v>6171428.5714285718</v>
       </c>
-      <c r="AA114" s="1" t="b">
+      <c r="Z114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+      <c r="AB114" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB114" s="82">
-        <v>6171428.5714285718</v>
       </c>
       <c r="AC114" s="82">
         <v>6171428.5714285718</v>
       </c>
-    </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD114" s="82">
+        <v>6171428.5714285718</v>
+      </c>
+    </row>
+    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A115" s="23" t="s">
         <v>581</v>
       </c>
@@ -12650,18 +13000,21 @@
       <c r="Y115" s="82">
         <v>100</v>
       </c>
-      <c r="AA115" s="1" t="b">
+      <c r="Z115" s="82">
+        <v>100</v>
+      </c>
+      <c r="AB115" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB115" s="82">
-        <v>100</v>
       </c>
       <c r="AC115" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="116" spans="1:29" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD115" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:30" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="23" t="s">
         <v>582</v>
       </c>
@@ -12685,19 +13038,19 @@
         <v>280800</v>
       </c>
       <c r="H116" s="67">
-        <f t="shared" ref="H116:Y116" si="39">0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" ref="H116:Z116" si="43">0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
       <c r="I116" s="67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>28080</v>
       </c>
       <c r="J116" s="67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>28080</v>
       </c>
       <c r="K116" s="67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>28080</v>
       </c>
       <c r="L116" s="67"/>
@@ -12710,58 +13063,62 @@
         <v>86400</v>
       </c>
       <c r="O116" s="67">
-        <f t="shared" ref="O116:U116" si="40">1 * (60*60*24)</f>
+        <f t="shared" ref="O116:U116" si="44">1 * (60*60*24)</f>
         <v>86400</v>
       </c>
       <c r="P116" s="67">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>86400</v>
       </c>
       <c r="Q116" s="67">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>86400</v>
       </c>
       <c r="R116" s="67">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>86400</v>
       </c>
       <c r="S116" s="67">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>86400</v>
       </c>
       <c r="T116" s="67">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>86400</v>
       </c>
       <c r="U116" s="67">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>86400</v>
       </c>
       <c r="V116" s="67"/>
       <c r="W116" s="67">
-        <f t="shared" si="39"/>
+        <f>1 * (60*60*24)</f>
+        <v>86400</v>
+      </c>
+      <c r="X116" s="67">
+        <f t="shared" si="43"/>
         <v>28080</v>
       </c>
-      <c r="X116" s="67">
-        <f t="shared" si="39"/>
+      <c r="Y116" s="67">
+        <f t="shared" si="43"/>
         <v>28080</v>
       </c>
-      <c r="Y116" s="67">
-        <f t="shared" si="39"/>
+      <c r="Z116" s="67">
+        <f t="shared" si="43"/>
         <v>28080</v>
       </c>
-      <c r="AA116" s="1" t="b">
+      <c r="AB116" s="1" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
-      </c>
-      <c r="AB116" s="67">
-        <v>28080</v>
       </c>
       <c r="AC116" s="67">
         <v>28080</v>
       </c>
-    </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD116" s="67">
+        <v>28080</v>
+      </c>
+    </row>
+    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A117" s="23" t="s">
         <v>583</v>
       </c>
@@ -12785,19 +13142,19 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H117" s="67">
-        <f t="shared" ref="H117:Y117" si="41">1.11 / 10</f>
+        <f t="shared" ref="H117:Z117" si="45">1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
       <c r="I117" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="J117" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="K117" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="L117" s="67"/>
@@ -12810,58 +13167,62 @@
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="O117" s="67">
-        <f t="shared" ref="O117:U117" si="42">1.05 / (60*60*24)</f>
+        <f t="shared" ref="O117:U117" si="46">1.05 / (60*60*24)</f>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="P117" s="67">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="Q117" s="67">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="R117" s="67">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="S117" s="67">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="T117" s="67">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="U117" s="67">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="V117" s="67"/>
       <c r="W117" s="67">
-        <f t="shared" si="41"/>
+        <f>1.05 / (60*60*24)</f>
+        <v>1.2152777777777779E-5</v>
+      </c>
+      <c r="X117" s="67">
+        <f t="shared" si="45"/>
         <v>0.11100000000000002</v>
       </c>
-      <c r="X117" s="67">
-        <f t="shared" si="41"/>
+      <c r="Y117" s="67">
+        <f t="shared" si="45"/>
         <v>0.11100000000000002</v>
       </c>
-      <c r="Y117" s="67">
-        <f t="shared" si="41"/>
+      <c r="Z117" s="67">
+        <f t="shared" si="45"/>
         <v>0.11100000000000002</v>
       </c>
-      <c r="AA117" s="1" t="b">
+      <c r="AB117" s="1" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
-      </c>
-      <c r="AB117" s="67">
-        <v>0.11100000000000002</v>
       </c>
       <c r="AC117" s="67">
         <v>0.11100000000000002</v>
       </c>
-    </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD117" s="67">
+        <v>0.11100000000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A118" s="23" t="s">
         <v>584</v>
       </c>
@@ -12925,7 +13286,7 @@
       </c>
       <c r="V118" s="82"/>
       <c r="W118" s="82">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="X118" s="82">
         <v>100</v>
@@ -12933,18 +13294,21 @@
       <c r="Y118" s="82">
         <v>100</v>
       </c>
-      <c r="AA118" s="1" t="b">
+      <c r="Z118" s="82">
+        <v>100</v>
+      </c>
+      <c r="AB118" s="1" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
-      </c>
-      <c r="AB118" s="82">
-        <v>100</v>
       </c>
       <c r="AC118" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="119" spans="1:29" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD118" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:30" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="23" t="s">
         <v>585</v>
       </c>
@@ -12964,23 +13328,23 @@
         <v>428</v>
       </c>
       <c r="G119" s="67">
-        <f t="shared" ref="G119:Y119" si="43">5.32 * (60*60*24)</f>
+        <f t="shared" ref="G119:Z119" si="47">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H119" s="67">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>459648</v>
       </c>
       <c r="I119" s="67">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>459648</v>
       </c>
       <c r="J119" s="67">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>459648</v>
       </c>
       <c r="K119" s="67">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>459648</v>
       </c>
       <c r="L119" s="67"/>
@@ -12993,58 +13357,62 @@
         <v>43200</v>
       </c>
       <c r="O119" s="67">
-        <f t="shared" ref="O119:U119" si="44">0.5 * (60*60*24)</f>
+        <f t="shared" ref="O119:U119" si="48">0.5 * (60*60*24)</f>
         <v>43200</v>
       </c>
       <c r="P119" s="67">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>43200</v>
       </c>
       <c r="Q119" s="67">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>43200</v>
       </c>
       <c r="R119" s="67">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>43200</v>
       </c>
       <c r="S119" s="67">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>43200</v>
       </c>
       <c r="T119" s="67">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>43200</v>
       </c>
       <c r="U119" s="67">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>43200</v>
       </c>
       <c r="V119" s="67"/>
       <c r="W119" s="67">
-        <f t="shared" si="43"/>
+        <f>0.5 * (60*60*24)</f>
+        <v>43200</v>
+      </c>
+      <c r="X119" s="67">
+        <f t="shared" si="47"/>
         <v>459648</v>
       </c>
-      <c r="X119" s="67">
-        <f t="shared" si="43"/>
+      <c r="Y119" s="67">
+        <f t="shared" si="47"/>
         <v>459648</v>
       </c>
-      <c r="Y119" s="67">
-        <f t="shared" si="43"/>
+      <c r="Z119" s="67">
+        <f t="shared" si="47"/>
         <v>459648</v>
       </c>
-      <c r="AA119" s="1" t="b">
+      <c r="AB119" s="1" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
-      </c>
-      <c r="AB119" s="67">
-        <v>459648</v>
       </c>
       <c r="AC119" s="67">
         <v>459648</v>
       </c>
-    </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD119" s="67">
+        <v>459648</v>
+      </c>
+    </row>
+    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A120" s="23" t="s">
         <v>586</v>
       </c>
@@ -13068,19 +13436,19 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H120" s="67">
-        <f t="shared" ref="H120:Y120" si="45">1.11/8</f>
+        <f t="shared" ref="H120:Z120" si="49">1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
       <c r="I120" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="J120" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="K120" s="67">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="L120" s="67"/>
@@ -13093,58 +13461,62 @@
         <v>8.101851851851852E-6</v>
       </c>
       <c r="O120" s="67">
-        <f t="shared" ref="O120:U120" si="46">0.7 / (60*60*24)</f>
+        <f t="shared" ref="O120:U120" si="50">0.7 / (60*60*24)</f>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="P120" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="Q120" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="R120" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="S120" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="T120" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="U120" s="67">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="V120" s="67"/>
       <c r="W120" s="67">
-        <f t="shared" si="45"/>
+        <f>0.7 / (60*60*24)</f>
+        <v>8.101851851851852E-6</v>
+      </c>
+      <c r="X120" s="67">
+        <f t="shared" si="49"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="X120" s="67">
-        <f t="shared" si="45"/>
+      <c r="Y120" s="67">
+        <f t="shared" si="49"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="Y120" s="67">
-        <f t="shared" si="45"/>
+      <c r="Z120" s="67">
+        <f t="shared" si="49"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="AA120" s="1" t="b">
+      <c r="AB120" s="1" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
-      </c>
-      <c r="AB120" s="67">
-        <v>0.13875000000000001</v>
       </c>
       <c r="AC120" s="67">
         <v>0.13875000000000001</v>
       </c>
-    </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD120" s="67">
+        <v>0.13875000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A121" s="23" t="s">
         <v>587</v>
       </c>
@@ -13216,18 +13588,21 @@
       <c r="Y121" s="82">
         <v>100</v>
       </c>
-      <c r="AA121" s="1" t="b">
-        <f t="shared" ref="AA121:AA123" si="47">M121=Y121</f>
-        <v>1</v>
-      </c>
-      <c r="AB121" s="82">
+      <c r="Z121" s="82">
         <v>100</v>
+      </c>
+      <c r="AB121" s="1" t="b">
+        <f t="shared" ref="AB121:AB123" si="51">M121=Z121</f>
+        <v>1</v>
       </c>
       <c r="AC121" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="122" spans="1:29" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD121" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122" spans="1:30" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="23" t="s">
         <v>588</v>
       </c>
@@ -13247,23 +13622,23 @@
         <v>428</v>
       </c>
       <c r="G122" s="67">
-        <f t="shared" ref="G122:Y122" si="48">5.32 * (60*60*24)</f>
+        <f t="shared" ref="G122:Z122" si="52">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H122" s="67">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>459648</v>
       </c>
       <c r="I122" s="67">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>459648</v>
       </c>
       <c r="J122" s="67">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>459648</v>
       </c>
       <c r="K122" s="67">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>459648</v>
       </c>
       <c r="L122" s="67"/>
@@ -13276,58 +13651,62 @@
         <v>86400</v>
       </c>
       <c r="O122" s="67">
-        <f t="shared" ref="O122:U122" si="49">1 * (60*60*24)</f>
+        <f t="shared" ref="O122:U122" si="53">1 * (60*60*24)</f>
         <v>86400</v>
       </c>
       <c r="P122" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>86400</v>
       </c>
       <c r="Q122" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>86400</v>
       </c>
       <c r="R122" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>86400</v>
       </c>
       <c r="S122" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>86400</v>
       </c>
       <c r="T122" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>86400</v>
       </c>
       <c r="U122" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>86400</v>
       </c>
       <c r="V122" s="67"/>
       <c r="W122" s="67">
-        <f t="shared" si="48"/>
+        <f>1 * (60*60*24)</f>
+        <v>86400</v>
+      </c>
+      <c r="X122" s="67">
+        <f t="shared" si="52"/>
         <v>459648</v>
       </c>
-      <c r="X122" s="67">
-        <f t="shared" si="48"/>
+      <c r="Y122" s="67">
+        <f t="shared" si="52"/>
         <v>459648</v>
       </c>
-      <c r="Y122" s="67">
-        <f t="shared" si="48"/>
+      <c r="Z122" s="67">
+        <f t="shared" si="52"/>
         <v>459648</v>
       </c>
-      <c r="AA122" s="1" t="b">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="AB122" s="67">
-        <v>459648</v>
+      <c r="AB122" s="1" t="b">
+        <f t="shared" si="51"/>
+        <v>0</v>
       </c>
       <c r="AC122" s="67">
         <v>459648</v>
       </c>
-    </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD122" s="67">
+        <v>459648</v>
+      </c>
+    </row>
+    <row r="123" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A123" s="23" t="s">
         <v>589</v>
       </c>
@@ -13351,19 +13730,19 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H123" s="67">
-        <f t="shared" ref="H123:Y123" si="50">1.11/8</f>
+        <f t="shared" ref="H123:Z123" si="54">1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
       <c r="I123" s="67">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="J123" s="67">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="K123" s="67">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="L123" s="67"/>
@@ -13376,58 +13755,62 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="O123" s="67">
-        <f t="shared" ref="O123:U123" si="51">1.11 / (60*60*24)</f>
+        <f t="shared" ref="O123:U123" si="55">1.11 / (60*60*24)</f>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="P123" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="Q123" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="R123" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="S123" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="T123" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="U123" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="V123" s="67"/>
       <c r="W123" s="67">
-        <f t="shared" si="50"/>
+        <f>1.11 / (60*60*24)</f>
+        <v>1.2847222222222224E-5</v>
+      </c>
+      <c r="X123" s="67">
+        <f t="shared" si="54"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="X123" s="67">
-        <f t="shared" si="50"/>
+      <c r="Y123" s="67">
+        <f t="shared" si="54"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="Y123" s="67">
-        <f t="shared" si="50"/>
+      <c r="Z123" s="67">
+        <f t="shared" si="54"/>
         <v>0.13875000000000001</v>
       </c>
-      <c r="AA123" s="1" t="b">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="AB123" s="67">
-        <v>0.13875000000000001</v>
+      <c r="AB123" s="1" t="b">
+        <f t="shared" si="51"/>
+        <v>0</v>
       </c>
       <c r="AC123" s="67">
         <v>0.13875000000000001</v>
       </c>
-    </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD123" s="67">
+        <v>0.13875000000000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A124" s="23" t="s">
         <v>395</v>
       </c>
@@ -13499,18 +13882,21 @@
       <c r="Y124" s="82">
         <v>21600</v>
       </c>
-      <c r="AA124" s="1" t="b">
+      <c r="Z124" s="82">
+        <v>21600</v>
+      </c>
+      <c r="AB124" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB124" s="82">
-        <v>21600</v>
       </c>
       <c r="AC124" s="82">
         <v>21600</v>
       </c>
-    </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD124" s="82">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="125" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A125" s="23" t="s">
         <v>397</v>
       </c>
@@ -13582,18 +13968,21 @@
       <c r="Y125" s="88">
         <v>43200</v>
       </c>
-      <c r="AA125" s="1" t="b">
+      <c r="Z125" s="88">
+        <v>43200</v>
+      </c>
+      <c r="AB125" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB125" s="88">
-        <v>43200</v>
       </c>
       <c r="AC125" s="88">
         <v>43200</v>
       </c>
-    </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD125" s="88">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="126" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A126" s="13" t="s">
         <v>61</v>
       </c>
@@ -13665,18 +14054,21 @@
       <c r="Y126" s="77">
         <v>0.8</v>
       </c>
-      <c r="AA126" s="1" t="b">
+      <c r="Z126" s="77">
+        <v>0.8</v>
+      </c>
+      <c r="AB126" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB126" s="77">
-        <v>0.8</v>
       </c>
       <c r="AC126" s="77">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD126" s="77">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
         <v>62</v>
       </c>
@@ -13749,18 +14141,21 @@
       <c r="Y127" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="AA127" s="1" t="b">
+      <c r="Z127" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="AB127" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB127" s="78">
-        <v>2.0833333333333335E-4</v>
       </c>
       <c r="AC127" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD127" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
         <v>63</v>
       </c>
@@ -13832,18 +14227,21 @@
       <c r="Y128" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-      <c r="AA128" s="1" t="b">
+      <c r="Z128" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+      <c r="AB128" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB128" s="77">
-        <v>5.7899999999999998E-7</v>
       </c>
       <c r="AC128" s="77">
         <v>5.7899999999999998E-7</v>
       </c>
-    </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD128" s="77">
+        <v>5.7899999999999998E-7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A129" s="13" t="s">
         <v>64</v>
       </c>
@@ -13915,18 +14313,21 @@
       <c r="Y129" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-      <c r="AA129" s="1" t="b">
+      <c r="Z129" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="AB129" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="AB129" s="78">
-        <v>2.0833333333333335E-4</v>
       </c>
       <c r="AC129" s="78">
         <v>2.0833333333333335E-4</v>
       </c>
-    </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD129" s="78">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A130" s="13" t="s">
         <v>447</v>
       </c>
@@ -13998,18 +14399,21 @@
       <c r="Y130" s="78">
         <v>0</v>
       </c>
-      <c r="AA130" s="1" t="b">
+      <c r="Z130" s="78">
+        <v>0</v>
+      </c>
+      <c r="AB130" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB130" s="78">
-        <v>0</v>
-      </c>
       <c r="AC130" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD130" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A131" s="13" t="s">
         <v>449</v>
       </c>
@@ -14081,18 +14485,21 @@
       <c r="Y131" s="78">
         <v>0</v>
       </c>
-      <c r="AA131" s="1" t="b">
+      <c r="Z131" s="78">
+        <v>0</v>
+      </c>
+      <c r="AB131" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB131" s="78">
-        <v>0</v>
-      </c>
       <c r="AC131" s="78">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD131" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A132" s="68" t="s">
         <v>438</v>
       </c>
@@ -14117,11 +14524,11 @@
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="I132" s="83">
-        <f t="shared" ref="I132:AC132" si="52">0.0000002*3</f>
+        <f t="shared" ref="I132:AD132" si="56">0.0000002*3</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J132" s="83">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="K132" s="83">
@@ -14130,44 +14537,44 @@
       </c>
       <c r="L132" s="83"/>
       <c r="M132" s="83">
-        <f t="shared" ref="M132:U132" si="53">0.0000002 * 2 / 1000</f>
+        <f t="shared" ref="M132:W132" si="57">0.0000002 * 2 / 1000</f>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="N132" s="83">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="O132" s="83">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="P132" s="83">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="Q132" s="83">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="R132" s="83">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="S132" s="83">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="T132" s="83">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="U132" s="83">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="V132" s="83"/>
       <c r="W132" s="83">
-        <f>0.0000002 * 2 / 1000</f>
+        <f t="shared" si="57"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="X132" s="83">
@@ -14175,26 +14582,30 @@
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="Y132" s="83">
-        <v>0</v>
+        <f>0.0000002 * 2 / 1000</f>
+        <v>3.9999999999999996E-10</v>
       </c>
       <c r="Z132" s="83">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="83">
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="AA132" s="1" t="b">
+      <c r="AB132" s="1" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB132" s="83">
-        <f t="shared" si="52"/>
+      <c r="AC132" s="83">
+        <f t="shared" si="56"/>
         <v>5.9999999999999997E-7</v>
       </c>
-      <c r="AC132" s="83">
-        <f t="shared" si="52"/>
+      <c r="AD132" s="83">
+        <f t="shared" si="56"/>
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A133" s="68" t="s">
         <v>67</v>
       </c>
@@ -14215,85 +14626,89 @@
       </c>
       <c r="G133" s="71"/>
       <c r="H133" s="83">
-        <f t="shared" ref="H133:AC133" si="54">1000 * 0.000001 / 12</f>
+        <f t="shared" ref="H133:AD133" si="58">1000 * 0.000001 / 12</f>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="I133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="J133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="K133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="L133" s="83"/>
       <c r="M133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="O133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="P133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="Q133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="R133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="S133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="T133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="U133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="V133" s="83"/>
       <c r="W133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="X133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="Y133" s="83">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="AA133" s="1" t="b">
+      <c r="Z133" s="83">
+        <f t="shared" si="58"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="AB133" s="1" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AB133" s="83">
-        <f t="shared" si="54"/>
+      <c r="AC133" s="83">
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="AC133" s="83">
-        <f t="shared" si="54"/>
+      <c r="AD133" s="83">
+        <f t="shared" si="58"/>
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A134" s="68" t="s">
         <v>443</v>
       </c>
@@ -14365,18 +14780,21 @@
       <c r="Y134" s="89" t="s">
         <v>527</v>
       </c>
-      <c r="AA134" s="1" t="b">
-        <f t="shared" ref="AA134:AA197" si="55">M134=Y134</f>
-        <v>1</v>
-      </c>
-      <c r="AB134" s="89" t="s">
+      <c r="Z134" s="89" t="s">
         <v>527</v>
+      </c>
+      <c r="AB134" s="1" t="b">
+        <f t="shared" ref="AB134:AB197" si="59">M134=Z134</f>
+        <v>1</v>
       </c>
       <c r="AC134" s="89" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD134" s="89" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="135" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A135" s="21" t="s">
         <v>66</v>
       </c>
@@ -14413,44 +14831,44 @@
       </c>
       <c r="L135" s="83"/>
       <c r="M135" s="83">
-        <f t="shared" ref="M135:U135" si="56">0.0005 / 10</f>
+        <f t="shared" ref="M135:W135" si="60">0.0005 / 10</f>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="N135" s="83">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="O135" s="83">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="P135" s="83">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="Q135" s="83">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="R135" s="83">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="S135" s="83">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="T135" s="83">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="U135" s="83">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="V135" s="83"/>
       <c r="W135" s="83">
-        <f>0.0005 / 10</f>
+        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="X135" s="83">
@@ -14458,25 +14876,29 @@
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="Y135" s="83">
+        <f>0.0005 / 10</f>
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="Z135" s="83">
         <f>0.0005</f>
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="Z135" s="83">
+      <c r="AA135" s="83">
         <f>0.0005 * 1.2</f>
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="AA135" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AB135" s="83">
-        <v>5.0000000000000001E-4</v>
+      <c r="AB135" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>0</v>
       </c>
       <c r="AC135" s="83">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD135" s="83">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A136" s="21" t="s">
         <v>435</v>
       </c>
@@ -14548,18 +14970,21 @@
       <c r="Y136" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="AA136" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB136" s="83">
+      <c r="Z136" s="83">
         <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="AB136" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC136" s="83">
         <v>4.9999999999999999E-13</v>
       </c>
-    </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD136" s="83">
+        <v>4.9999999999999999E-13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A137" s="21" t="s">
         <v>229</v>
       </c>
@@ -14631,18 +15056,21 @@
       <c r="Y137" s="77">
         <v>10</v>
       </c>
-      <c r="AA137" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB137" s="77">
+      <c r="Z137" s="77">
         <v>10</v>
+      </c>
+      <c r="AB137" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC137" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD137" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
         <v>230</v>
       </c>
@@ -14714,18 +15142,21 @@
       <c r="Y138" s="77">
         <v>-0.04</v>
       </c>
-      <c r="AA138" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB138" s="77">
+      <c r="Z138" s="77">
         <v>-0.04</v>
+      </c>
+      <c r="AB138" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC138" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD138" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="139" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
         <v>231</v>
       </c>
@@ -14797,18 +15228,21 @@
       <c r="Y139" s="77">
         <v>2.9</v>
       </c>
-      <c r="AA139" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB139" s="77">
+      <c r="Z139" s="77">
         <v>2.9</v>
+      </c>
+      <c r="AB139" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC139" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD139" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A140" s="21" t="s">
         <v>232</v>
       </c>
@@ -14880,18 +15314,21 @@
       <c r="Y140" s="77">
         <v>1</v>
       </c>
-      <c r="AA140" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB140" s="77">
+      <c r="Z140" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB140" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC140" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD140" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A141" s="21" t="s">
         <v>568</v>
       </c>
@@ -14928,44 +15365,44 @@
       </c>
       <c r="L141" s="80"/>
       <c r="M141" s="80">
-        <f t="shared" ref="M141:U141" si="57">0.0000002 * 2 / 10</f>
+        <f t="shared" ref="M141:W141" si="61">0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="N141" s="80">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="O141" s="80">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="P141" s="80">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="Q141" s="80">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="R141" s="80">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="S141" s="80">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="T141" s="80">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="U141" s="80">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="V141" s="80"/>
       <c r="W141" s="80">
-        <f>0.0000002 * 2 / 10</f>
+        <f t="shared" si="61"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="X141" s="80">
@@ -14973,24 +15410,28 @@
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="Y141" s="80">
-        <v>1.9999999999999999E-7</v>
-      </c>
-      <c r="Z141" s="80">
         <f>0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="AA141" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AB141" s="80">
+      <c r="Z141" s="80">
         <v>1.9999999999999999E-7</v>
+      </c>
+      <c r="AA141" s="80">
+        <f>0.0000002 * 2 / 10</f>
+        <v>4.0000000000000001E-8</v>
+      </c>
+      <c r="AB141" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>0</v>
       </c>
       <c r="AC141" s="80">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD141" s="80">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
         <v>233</v>
       </c>
@@ -15062,18 +15503,21 @@
       <c r="Y142" s="77">
         <v>10</v>
       </c>
-      <c r="AA142" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB142" s="77">
+      <c r="Z142" s="77">
         <v>10</v>
+      </c>
+      <c r="AB142" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC142" s="77">
         <v>10</v>
       </c>
-    </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD142" s="77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
         <v>234</v>
       </c>
@@ -15145,18 +15589,21 @@
       <c r="Y143" s="77">
         <v>-0.04</v>
       </c>
-      <c r="AA143" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB143" s="77">
+      <c r="Z143" s="77">
         <v>-0.04</v>
+      </c>
+      <c r="AB143" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC143" s="77">
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD143" s="77">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="144" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A144" s="21" t="s">
         <v>235</v>
       </c>
@@ -15228,18 +15675,21 @@
       <c r="Y144" s="77">
         <v>2.9</v>
       </c>
-      <c r="AA144" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB144" s="77">
+      <c r="Z144" s="77">
         <v>2.9</v>
+      </c>
+      <c r="AB144" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC144" s="77">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD144" s="77">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A145" s="21" t="s">
         <v>236</v>
       </c>
@@ -15311,18 +15761,21 @@
       <c r="Y145" s="77">
         <v>1</v>
       </c>
-      <c r="AA145" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB145" s="77">
+      <c r="Z145" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB145" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC145" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD145" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A146" s="21" t="s">
         <v>69</v>
       </c>
@@ -15394,18 +15847,21 @@
       <c r="Y146" s="77">
         <v>0</v>
       </c>
-      <c r="AA146" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB146" s="77">
-        <v>0</v>
+      <c r="Z146" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB146" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC146" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD146" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A147" s="72" t="s">
         <v>70</v>
       </c>
@@ -15477,18 +15933,21 @@
       <c r="Y147" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="AA147" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB147" s="80">
+      <c r="Z147" s="80">
         <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="AB147" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC147" s="80">
         <v>5.0000000000000004E-6</v>
       </c>
-    </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD147" s="80">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A148" s="23" t="s">
         <v>56</v>
       </c>
@@ -15560,18 +16019,21 @@
       <c r="Y148" s="77">
         <v>0</v>
       </c>
-      <c r="AA148" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB148" s="77">
-        <v>0</v>
+      <c r="Z148" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC148" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD148" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A149" s="23" t="s">
         <v>57</v>
       </c>
@@ -15643,18 +16105,21 @@
       <c r="Y149" s="77">
         <v>2E-3</v>
       </c>
-      <c r="AA149" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB149" s="77">
+      <c r="Z149" s="77">
         <v>2E-3</v>
+      </c>
+      <c r="AB149" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC149" s="77">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD149" s="77">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A150" s="23" t="s">
         <v>58</v>
       </c>
@@ -15726,18 +16191,21 @@
       <c r="Y150" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-      <c r="AA150" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB150" s="80">
+      <c r="Z150" s="80">
         <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="AB150" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC150" s="80">
         <v>3.9999999999999998E-6</v>
       </c>
-    </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD150" s="80">
+        <v>3.9999999999999998E-6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A151" s="23" t="s">
         <v>71</v>
       </c>
@@ -15809,18 +16277,21 @@
       <c r="Y151" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-      <c r="AA151" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB151" s="80">
+      <c r="Z151" s="80">
         <v>3.7699999999999999E-10</v>
+      </c>
+      <c r="AB151" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC151" s="80">
         <v>3.7699999999999999E-10</v>
       </c>
-    </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD151" s="80">
+        <v>3.7699999999999999E-10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A152" s="23" t="s">
         <v>237</v>
       </c>
@@ -15892,18 +16363,21 @@
       <c r="Y152" s="77">
         <v>20</v>
       </c>
-      <c r="AA152" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB152" s="77">
+      <c r="Z152" s="77">
         <v>20</v>
+      </c>
+      <c r="AB152" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC152" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD152" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="153" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A153" s="23" t="s">
         <v>238</v>
       </c>
@@ -15975,18 +16449,21 @@
       <c r="Y153" s="77">
         <v>-0.06</v>
       </c>
-      <c r="AA153" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB153" s="77">
+      <c r="Z153" s="77">
         <v>-0.06</v>
+      </c>
+      <c r="AB153" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC153" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD153" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="154" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A154" s="23" t="s">
         <v>239</v>
       </c>
@@ -16058,18 +16535,21 @@
       <c r="Y154" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="AA154" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB154" s="77">
+      <c r="Z154" s="77">
         <v>0.89100000000000001</v>
+      </c>
+      <c r="AB154" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC154" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD154" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A155" s="23" t="s">
         <v>240</v>
       </c>
@@ -16141,18 +16621,21 @@
       <c r="Y155" s="77">
         <v>1</v>
       </c>
-      <c r="AA155" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB155" s="77">
+      <c r="Z155" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB155" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC155" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD155" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A156" s="23" t="s">
         <v>72</v>
       </c>
@@ -16224,18 +16707,21 @@
       <c r="Y156" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="AA156" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB156" s="80">
+      <c r="Z156" s="80">
         <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="AB156" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC156" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD156" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A157" s="13" t="s">
         <v>73</v>
       </c>
@@ -16307,18 +16793,21 @@
       <c r="Y157" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-      <c r="AA157" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB157" s="80">
+      <c r="Z157" s="80">
         <v>5.8333333333333335E-9</v>
+      </c>
+      <c r="AB157" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC157" s="80">
         <v>5.8333333333333335E-9</v>
       </c>
-    </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD157" s="80">
+        <v>5.8333333333333335E-9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A158" s="13" t="s">
         <v>241</v>
       </c>
@@ -16390,18 +16879,21 @@
       <c r="Y158" s="77">
         <v>20</v>
       </c>
-      <c r="AA158" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB158" s="77">
+      <c r="Z158" s="77">
         <v>20</v>
+      </c>
+      <c r="AB158" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC158" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD158" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A159" s="13" t="s">
         <v>242</v>
       </c>
@@ -16473,18 +16965,21 @@
       <c r="Y159" s="77">
         <v>-0.06</v>
       </c>
-      <c r="AA159" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB159" s="77">
+      <c r="Z159" s="77">
         <v>-0.06</v>
+      </c>
+      <c r="AB159" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC159" s="77">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD159" s="77">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="160" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A160" s="13" t="s">
         <v>243</v>
       </c>
@@ -16556,18 +17051,21 @@
       <c r="Y160" s="77">
         <v>0.89100000000000001</v>
       </c>
-      <c r="AA160" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB160" s="77">
+      <c r="Z160" s="77">
         <v>0.89100000000000001</v>
+      </c>
+      <c r="AB160" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC160" s="77">
         <v>0.89100000000000001</v>
       </c>
-    </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD160" s="77">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A161" s="13" t="s">
         <v>244</v>
       </c>
@@ -16639,18 +17137,21 @@
       <c r="Y161" s="77">
         <v>1</v>
       </c>
-      <c r="AA161" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB161" s="77">
+      <c r="Z161" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB161" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC161" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD161" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A162" s="13" t="s">
         <v>74</v>
       </c>
@@ -16722,18 +17223,21 @@
       <c r="Y162" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="AA162" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB162" s="80">
+      <c r="Z162" s="80">
         <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="AB162" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC162" s="80">
         <v>4.0000000000000003E-5</v>
       </c>
-    </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD162" s="80">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>75</v>
       </c>
@@ -16805,18 +17309,21 @@
       <c r="Y163" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-      <c r="AA163" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB163" s="83">
+      <c r="Z163" s="83">
         <v>4.0000000000000001E-8</v>
+      </c>
+      <c r="AB163" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC163" s="83">
         <v>4.0000000000000001E-8</v>
       </c>
-    </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD163" s="83">
+        <v>4.0000000000000001E-8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>219</v>
       </c>
@@ -16888,18 +17395,21 @@
       <c r="Y164" s="77">
         <v>20</v>
       </c>
-      <c r="AA164" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB164" s="77">
+      <c r="Z164" s="77">
         <v>20</v>
+      </c>
+      <c r="AB164" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC164" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD164" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="165" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>220</v>
       </c>
@@ -16971,18 +17481,21 @@
       <c r="Y165" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-      <c r="AA165" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB165" s="77">
+      <c r="Z165" s="77">
         <v>-4.4200000000000003E-2</v>
+      </c>
+      <c r="AB165" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC165" s="77">
         <v>-4.4200000000000003E-2</v>
       </c>
-    </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD165" s="77">
+        <v>-4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A166" s="9" t="s">
         <v>221</v>
       </c>
@@ -17054,18 +17567,21 @@
       <c r="Y166" s="77">
         <v>1.55</v>
       </c>
-      <c r="AA166" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB166" s="77">
+      <c r="Z166" s="77">
         <v>1.55</v>
+      </c>
+      <c r="AB166" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC166" s="77">
         <v>1.55</v>
       </c>
-    </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD166" s="77">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="167" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A167" s="9" t="s">
         <v>222</v>
       </c>
@@ -17137,18 +17653,21 @@
       <c r="Y167" s="77">
         <v>1</v>
       </c>
-      <c r="AA167" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB167" s="77">
+      <c r="Z167" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB167" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC167" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD167" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A168" s="9" t="s">
         <v>76</v>
       </c>
@@ -17220,18 +17739,21 @@
       <c r="Y168" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="AA168" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB168" s="77">
+      <c r="Z168" s="77">
         <v>2.7799999999999998E-4</v>
+      </c>
+      <c r="AB168" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC168" s="77">
         <v>2.7799999999999998E-4</v>
       </c>
-    </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD168" s="77">
+        <v>2.7799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
         <v>78</v>
       </c>
@@ -17303,18 +17825,21 @@
       <c r="Y169" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="AA169" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB169" s="84">
+      <c r="Z169" s="84">
         <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="AB169" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC169" s="84">
         <v>2.4999999999999998E-12</v>
       </c>
-    </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD169" s="84">
+        <v>2.4999999999999998E-12</v>
+      </c>
+    </row>
+    <row r="170" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
         <v>246</v>
       </c>
@@ -17386,18 +17911,21 @@
       <c r="Y170" s="77">
         <v>20</v>
       </c>
-      <c r="AA170" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB170" s="77">
+      <c r="Z170" s="77">
         <v>20</v>
+      </c>
+      <c r="AB170" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC170" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD170" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="171" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
         <v>247</v>
       </c>
@@ -17469,18 +17997,21 @@
       <c r="Y171" s="77">
         <v>0</v>
       </c>
-      <c r="AA171" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB171" s="77">
-        <v>0</v>
+      <c r="Z171" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB171" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC171" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD171" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A172" s="25" t="s">
         <v>248</v>
       </c>
@@ -17552,18 +18083,21 @@
       <c r="Y172" s="77">
         <v>1</v>
       </c>
-      <c r="AA172" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB172" s="77">
+      <c r="Z172" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB172" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC172" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD172" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A173" s="25" t="s">
         <v>249</v>
       </c>
@@ -17635,18 +18169,21 @@
       <c r="Y173" s="77">
         <v>0</v>
       </c>
-      <c r="AA173" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB173" s="77">
-        <v>0</v>
+      <c r="Z173" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB173" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC173" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD173" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A174" s="25" t="s">
         <v>79</v>
       </c>
@@ -17718,18 +18255,21 @@
       <c r="Y174" s="77">
         <v>0.4</v>
       </c>
-      <c r="AA174" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB174" s="77">
+      <c r="Z174" s="77">
         <v>0.4</v>
+      </c>
+      <c r="AB174" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC174" s="77">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD174" s="77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A175" s="31" t="s">
         <v>80</v>
       </c>
@@ -17801,18 +18341,21 @@
       <c r="Y175" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-      <c r="AA175" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB175" s="86">
+      <c r="Z175" s="86">
         <v>2.0000000000000001E-9</v>
+      </c>
+      <c r="AB175" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC175" s="86">
         <v>2.0000000000000001E-9</v>
       </c>
-    </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD175" s="86">
+        <v>2.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A176" s="31" t="s">
         <v>250</v>
       </c>
@@ -17884,18 +18427,21 @@
       <c r="Y176" s="77">
         <v>25</v>
       </c>
-      <c r="AA176" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB176" s="77">
+      <c r="Z176" s="77">
         <v>25</v>
+      </c>
+      <c r="AB176" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC176" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD176" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A177" s="31" t="s">
         <v>251</v>
       </c>
@@ -17967,18 +18513,21 @@
       <c r="Y177" s="77">
         <v>0</v>
       </c>
-      <c r="AA177" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB177" s="77">
-        <v>0</v>
+      <c r="Z177" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB177" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC177" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD177" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A178" s="31" t="s">
         <v>252</v>
       </c>
@@ -18050,18 +18599,21 @@
       <c r="Y178" s="77">
         <v>3.98</v>
       </c>
-      <c r="AA178" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB178" s="77">
+      <c r="Z178" s="77">
         <v>3.98</v>
+      </c>
+      <c r="AB178" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC178" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD178" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="179" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A179" s="31" t="s">
         <v>253</v>
       </c>
@@ -18133,18 +18685,21 @@
       <c r="Y179" s="77">
         <v>1</v>
       </c>
-      <c r="AA179" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB179" s="77">
+      <c r="Z179" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB179" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC179" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD179" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A180" s="31" t="s">
         <v>81</v>
       </c>
@@ -18216,18 +18771,21 @@
       <c r="Y180" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-      <c r="AA180" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB180" s="78">
+      <c r="Z180" s="78">
         <v>1.6666666666666666E-4</v>
+      </c>
+      <c r="AB180" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC180" s="78">
         <v>1.6666666666666666E-4</v>
       </c>
-    </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD180" s="78">
+        <v>1.6666666666666666E-4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>254</v>
       </c>
@@ -18299,18 +18857,21 @@
       <c r="Y181" s="80">
         <v>1E-8</v>
       </c>
-      <c r="AA181" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB181" s="80">
+      <c r="Z181" s="80">
         <v>1E-8</v>
+      </c>
+      <c r="AB181" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC181" s="80">
         <v>1E-8</v>
       </c>
-    </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD181" s="80">
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
         <v>255</v>
       </c>
@@ -18382,18 +18943,21 @@
       <c r="Y182" s="77">
         <v>20</v>
       </c>
-      <c r="AA182" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB182" s="77">
+      <c r="Z182" s="77">
         <v>20</v>
+      </c>
+      <c r="AB182" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC182" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD182" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
         <v>256</v>
       </c>
@@ -18465,18 +19029,21 @@
       <c r="Y183" s="77">
         <v>0</v>
       </c>
-      <c r="AA183" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB183" s="77">
-        <v>0</v>
+      <c r="Z183" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB183" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC183" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD183" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
         <v>257</v>
       </c>
@@ -18548,18 +19115,21 @@
       <c r="Y184" s="77">
         <v>2</v>
       </c>
-      <c r="AA184" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB184" s="77">
+      <c r="Z184" s="77">
         <v>2</v>
+      </c>
+      <c r="AB184" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC184" s="77">
         <v>2</v>
       </c>
-    </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD184" s="77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A185" s="11" t="s">
         <v>258</v>
       </c>
@@ -18631,18 +19201,21 @@
       <c r="Y185" s="77">
         <v>1</v>
       </c>
-      <c r="AA185" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB185" s="77">
+      <c r="Z185" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB185" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC185" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD185" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
         <v>259</v>
       </c>
@@ -18714,18 +19287,21 @@
       <c r="Y186" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="AA186" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB186" s="78">
+      <c r="Z186" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="AB186" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC186" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD186" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>260</v>
       </c>
@@ -18797,18 +19373,21 @@
       <c r="Y187" s="77">
         <v>1</v>
       </c>
-      <c r="AA187" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB187" s="77">
+      <c r="Z187" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB187" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC187" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD187" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A188" s="27" t="s">
         <v>261</v>
       </c>
@@ -18880,18 +19459,21 @@
       <c r="Y188" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-      <c r="AA188" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB188" s="77">
+      <c r="Z188" s="77">
         <v>2.3533050791148899E-8</v>
+      </c>
+      <c r="AB188" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC188" s="77">
         <v>2.3533050791148899E-8</v>
       </c>
-    </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD188" s="77">
+        <v>2.3533050791148899E-8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A189" s="27" t="s">
         <v>262</v>
       </c>
@@ -18963,18 +19545,21 @@
       <c r="Y189" s="77">
         <v>20</v>
       </c>
-      <c r="AA189" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB189" s="77">
+      <c r="Z189" s="77">
         <v>20</v>
+      </c>
+      <c r="AB189" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC189" s="77">
         <v>20</v>
       </c>
-    </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD189" s="77">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="190" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A190" s="27" t="s">
         <v>263</v>
       </c>
@@ -19046,18 +19631,21 @@
       <c r="Y190" s="77">
         <v>-0.187</v>
       </c>
-      <c r="AA190" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB190" s="77">
+      <c r="Z190" s="77">
         <v>-0.187</v>
+      </c>
+      <c r="AB190" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC190" s="77">
         <v>-0.187</v>
       </c>
-    </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD190" s="77">
+        <v>-0.187</v>
+      </c>
+    </row>
+    <row r="191" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A191" s="27" t="s">
         <v>264</v>
       </c>
@@ -19129,18 +19717,21 @@
       <c r="Y191" s="77">
         <v>2.48</v>
       </c>
-      <c r="AA191" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB191" s="77">
+      <c r="Z191" s="77">
         <v>2.48</v>
+      </c>
+      <c r="AB191" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC191" s="77">
         <v>2.48</v>
       </c>
-    </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD191" s="77">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="192" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A192" s="27" t="s">
         <v>265</v>
       </c>
@@ -19212,18 +19803,21 @@
       <c r="Y192" s="77">
         <v>1</v>
       </c>
-      <c r="AA192" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB192" s="77">
+      <c r="Z192" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB192" s="1" t="b">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="AC192" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD192" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A193" s="27" t="s">
         <v>266</v>
       </c>
@@ -19295,18 +19889,21 @@
       <c r="Y193" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-      <c r="AA193" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB193" s="77">
+      <c r="Z193" s="77">
         <v>6.1060227588121015E-4</v>
+      </c>
+      <c r="AB193" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC193" s="77">
         <v>6.1060227588121015E-4</v>
       </c>
-    </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD193" s="77">
+        <v>6.1060227588121015E-4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A194" s="23" t="s">
         <v>267</v>
       </c>
@@ -19378,18 +19975,21 @@
       <c r="Y194" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="AA194" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB194" s="85">
+      <c r="Z194" s="85">
         <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="AB194" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC194" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD194" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A195" s="23" t="s">
         <v>268</v>
       </c>
@@ -19461,18 +20061,21 @@
       <c r="Y195" s="77">
         <v>25</v>
       </c>
-      <c r="AA195" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB195" s="77">
+      <c r="Z195" s="77">
         <v>25</v>
+      </c>
+      <c r="AB195" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC195" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD195" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A196" s="23" t="s">
         <v>269</v>
       </c>
@@ -19544,18 +20147,21 @@
       <c r="Y196" s="77">
         <v>0</v>
       </c>
-      <c r="AA196" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB196" s="77">
-        <v>0</v>
+      <c r="Z196" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB196" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC196" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD196" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A197" s="23" t="s">
         <v>270</v>
       </c>
@@ -19627,18 +20233,21 @@
       <c r="Y197" s="77">
         <v>3.98</v>
       </c>
-      <c r="AA197" s="1" t="b">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AB197" s="77">
+      <c r="Z197" s="77">
         <v>3.98</v>
+      </c>
+      <c r="AB197" s="1" t="b">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="AC197" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD197" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="198" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A198" s="23" t="s">
         <v>271</v>
       </c>
@@ -19710,18 +20319,21 @@
       <c r="Y198" s="77">
         <v>1</v>
       </c>
-      <c r="AA198" s="1" t="b">
-        <f t="shared" ref="AA198:AA237" si="58">M198=Y198</f>
-        <v>1</v>
-      </c>
-      <c r="AB198" s="77">
+      <c r="Z198" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB198" s="1" t="b">
+        <f t="shared" ref="AB198:AB237" si="62">M198=Z198</f>
         <v>1</v>
       </c>
       <c r="AC198" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD198" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A199" s="23" t="s">
         <v>272</v>
       </c>
@@ -19793,18 +20405,21 @@
       <c r="Y199" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="AA199" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB199" s="78">
+      <c r="Z199" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="AB199" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC199" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD199" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>273</v>
       </c>
@@ -19876,18 +20491,21 @@
       <c r="Y200" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-      <c r="AA200" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB200" s="85">
+      <c r="Z200" s="85">
         <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="AB200" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC200" s="85">
         <v>3.9999999999999998E-7</v>
       </c>
-    </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD200" s="85">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>274</v>
       </c>
@@ -19959,18 +20577,21 @@
       <c r="Y201" s="77">
         <v>25</v>
       </c>
-      <c r="AA201" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB201" s="77">
+      <c r="Z201" s="77">
         <v>25</v>
+      </c>
+      <c r="AB201" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC201" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD201" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>275</v>
       </c>
@@ -20042,18 +20663,21 @@
       <c r="Y202" s="77">
         <v>0</v>
       </c>
-      <c r="AA202" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB202" s="77">
-        <v>0</v>
+      <c r="Z202" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB202" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC202" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD202" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>276</v>
       </c>
@@ -20125,18 +20749,21 @@
       <c r="Y203" s="77">
         <v>3.98</v>
       </c>
-      <c r="AA203" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB203" s="77">
+      <c r="Z203" s="77">
         <v>3.98</v>
+      </c>
+      <c r="AB203" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC203" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="204" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD203" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="204" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>277</v>
       </c>
@@ -20208,18 +20835,21 @@
       <c r="Y204" s="77">
         <v>1</v>
       </c>
-      <c r="AA204" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB204" s="77">
+      <c r="Z204" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB204" s="1" t="b">
+        <f t="shared" si="62"/>
         <v>1</v>
       </c>
       <c r="AC204" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="205" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD204" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>278</v>
       </c>
@@ -20291,18 +20921,21 @@
       <c r="Y205" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="AA205" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB205" s="78">
+      <c r="Z205" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="AB205" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC205" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="206" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD205" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A206" s="29" t="s">
         <v>279</v>
       </c>
@@ -20374,18 +21007,21 @@
       <c r="Y206" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="AA206" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB206" s="85">
+      <c r="Z206" s="85">
         <v>1.9999999999999999E-7</v>
+      </c>
+      <c r="AB206" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC206" s="85">
         <v>1.9999999999999999E-7</v>
       </c>
-    </row>
-    <row r="207" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD206" s="85">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A207" s="29" t="s">
         <v>280</v>
       </c>
@@ -20457,18 +21093,21 @@
       <c r="Y207" s="77">
         <v>25</v>
       </c>
-      <c r="AA207" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB207" s="77">
+      <c r="Z207" s="77">
         <v>25</v>
+      </c>
+      <c r="AB207" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC207" s="77">
         <v>25</v>
       </c>
-    </row>
-    <row r="208" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD207" s="77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="208" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A208" s="29" t="s">
         <v>281</v>
       </c>
@@ -20540,18 +21179,21 @@
       <c r="Y208" s="77">
         <v>0</v>
       </c>
-      <c r="AA208" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB208" s="77">
-        <v>0</v>
+      <c r="Z208" s="77">
+        <v>0</v>
+      </c>
+      <c r="AB208" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC208" s="77">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD208" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A209" s="29" t="s">
         <v>282</v>
       </c>
@@ -20623,18 +21265,21 @@
       <c r="Y209" s="77">
         <v>3.98</v>
       </c>
-      <c r="AA209" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB209" s="77">
+      <c r="Z209" s="77">
         <v>3.98</v>
+      </c>
+      <c r="AB209" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC209" s="77">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="210" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD209" s="77">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="210" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A210" s="29" t="s">
         <v>283</v>
       </c>
@@ -20706,18 +21351,21 @@
       <c r="Y210" s="77">
         <v>1</v>
       </c>
-      <c r="AA210" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB210" s="77">
+      <c r="Z210" s="77">
+        <v>1</v>
+      </c>
+      <c r="AB210" s="1" t="b">
+        <f t="shared" si="62"/>
         <v>1</v>
       </c>
       <c r="AC210" s="77">
         <v>1</v>
       </c>
-    </row>
-    <row r="211" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD210" s="77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A211" s="29" t="s">
         <v>284</v>
       </c>
@@ -20789,18 +21437,21 @@
       <c r="Y211" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="AA211" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB211" s="78">
+      <c r="Z211" s="78">
         <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="AB211" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC211" s="78">
         <v>8.3333333333333331E-5</v>
       </c>
-    </row>
-    <row r="212" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD211" s="78">
+        <v>8.3333333333333331E-5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A212" s="90" t="s">
         <v>362</v>
       </c>
@@ -20872,18 +21523,21 @@
       <c r="Y212" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="AA212" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB212" s="95" t="s">
+      <c r="Z212" s="95" t="s">
         <v>90</v>
+      </c>
+      <c r="AB212" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC212" s="95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="213" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD212" s="95" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="213" spans="1:30" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>551</v>
       </c>
@@ -20906,15 +21560,15 @@
         <v>0.5</v>
       </c>
       <c r="H213" s="83">
-        <f t="shared" ref="H213:J213" si="59">0.00002</f>
+        <f t="shared" ref="H213:J213" si="63">0.00002</f>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="I213" s="83">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="J213" s="83">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="K213" s="83">
@@ -20971,19 +21625,23 @@
         <f>0.00005 / 100</f>
         <v>4.9999999999999998E-7</v>
       </c>
-      <c r="Z213" s="1"/>
-      <c r="AA213" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB213" s="2">
-        <v>0.01</v>
+      <c r="Z213" s="83">
+        <f>0.00005 / 100</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="AA213" s="1"/>
+      <c r="AB213" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC213" s="2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="214" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD213" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="214" spans="1:30" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>554</v>
       </c>
@@ -21053,21 +21711,24 @@
         <v>0.3</v>
       </c>
       <c r="Y214" s="83">
+        <v>0.3</v>
+      </c>
+      <c r="Z214" s="83">
         <v>0.1</v>
       </c>
-      <c r="Z214" s="1"/>
-      <c r="AA214" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="AB214" s="99">
+      <c r="AA214" s="1"/>
+      <c r="AB214" s="1" t="b">
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="AC214" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="215" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD214" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:30" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>557</v>
       </c>
@@ -21090,83 +21751,87 @@
         <v>0.5</v>
       </c>
       <c r="H215" s="83">
-        <f t="shared" ref="H215:Y215" si="60">0.00002 / 14</f>
+        <f t="shared" ref="H215:Z215" si="64">0.00002 / 14</f>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="I215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="J215" s="83">
         <v>2E-3</v>
       </c>
       <c r="K215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="L215" s="83"/>
       <c r="M215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="N215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="O215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="P215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="Q215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="R215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="S215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="T215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="U215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="V215" s="83"/>
       <c r="W215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="X215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="Y215" s="83">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>1.4285714285714286E-6</v>
       </c>
-      <c r="Z215" s="1"/>
-      <c r="AA215" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB215" s="100">
+      <c r="Z215" s="83">
+        <f t="shared" si="64"/>
+        <v>1.4285714285714286E-6</v>
+      </c>
+      <c r="AA215" s="1"/>
+      <c r="AB215" s="1" t="b">
+        <f t="shared" si="62"/>
         <v>1</v>
       </c>
       <c r="AC215" s="100">
+        <v>1</v>
+      </c>
+      <c r="AD215" s="100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="216" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:30" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>501</v>
       </c>
@@ -21238,19 +21903,22 @@
       <c r="Y216" s="83" t="s">
         <v>473</v>
       </c>
-      <c r="Z216" s="1"/>
-      <c r="AA216" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB216" s="98">
+      <c r="Z216" s="83" t="s">
+        <v>473</v>
+      </c>
+      <c r="AA216" s="1"/>
+      <c r="AB216" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AC216" s="98">
         <v>0.1</v>
       </c>
-      <c r="AC216" s="98" t="s">
+      <c r="AD216" s="98" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="217" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:30" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>502</v>
       </c>
@@ -21322,19 +21990,22 @@
       <c r="Y217" s="83">
         <v>0</v>
       </c>
-      <c r="Z217" s="1"/>
-      <c r="AA217" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB217" s="98">
-        <v>0.04</v>
+      <c r="Z217" s="83">
+        <v>0</v>
+      </c>
+      <c r="AA217" s="1"/>
+      <c r="AB217" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC217" s="98">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="218" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD217" s="98">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="218" spans="1:30" s="96" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>503</v>
       </c>
@@ -21406,19 +22077,22 @@
       <c r="Y218" s="83">
         <v>1E-3</v>
       </c>
-      <c r="Z218" s="1"/>
-      <c r="AA218" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB218" s="98">
+      <c r="Z218" s="83">
         <v>1E-3</v>
+      </c>
+      <c r="AA218" s="1"/>
+      <c r="AB218" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC218" s="98">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD218" s="98">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>509</v>
       </c>
@@ -21442,83 +22116,87 @@
         <v>1.2499999999999999E-6</v>
       </c>
       <c r="H219" s="99">
-        <f t="shared" ref="H219:Y219" si="61">1250*0.000001/5</f>
+        <f t="shared" ref="H219:Z219" si="65">1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="I219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="J219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="K219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="L219" s="99"/>
       <c r="M219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="N219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="O219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="P219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="Q219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="R219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="S219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="T219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="U219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="V219" s="99"/>
       <c r="W219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="X219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="Y219" s="99">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="AA219" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB219" s="99">
+      <c r="Z219" s="99">
+        <f t="shared" si="65"/>
         <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="AB219" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC219" s="99">
         <v>2.5000000000000001E-4</v>
       </c>
-    </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD219" s="99">
+        <v>2.5000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>512</v>
       </c>
@@ -21590,18 +22268,21 @@
       <c r="Y220" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="AA220" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-      <c r="AB220" s="99">
+      <c r="Z220" s="99">
         <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="AB220" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
       </c>
       <c r="AC220" s="99">
         <v>2.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD220" s="99">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>528</v>
       </c>
@@ -21639,44 +22320,44 @@
       </c>
       <c r="L221" s="83"/>
       <c r="M221" s="83">
-        <f t="shared" ref="M221:U221" si="62" xml:space="preserve"> 0.0000000000025</f>
+        <f t="shared" ref="M221:W221" si="66" xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="N221" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="O221" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="P221" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="Q221" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="R221" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="S221" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="T221" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="U221" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="V221" s="83"/>
       <c r="W221" s="83">
-        <f xml:space="preserve"> 0.0000000000025</f>
+        <f t="shared" si="66"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="X221" s="83">
@@ -21687,12 +22368,16 @@
         <f xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
-      <c r="AA221" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z221" s="83">
+        <f xml:space="preserve"> 0.0000000000025</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="AB221" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>529</v>
       </c>
@@ -21732,44 +22417,44 @@
       </c>
       <c r="L222" s="83"/>
       <c r="M222" s="83">
-        <f t="shared" ref="M222:U222" si="63">0.00000000005 / 10 / 8</f>
+        <f t="shared" ref="M222:W222" si="67">0.00000000005 / 10 / 8</f>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="N222" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="O222" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="P222" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="Q222" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="R222" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="S222" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="T222" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="U222" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="V222" s="83"/>
       <c r="W222" s="83">
-        <f>0.00000000005 / 10 / 8</f>
+        <f t="shared" si="67"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="X222" s="83">
@@ -21777,15 +22462,19 @@
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="Y222" s="83">
+        <f>0.00000000005 / 10 / 8</f>
+        <v>6.2500000000000006E-13</v>
+      </c>
+      <c r="Z222" s="83">
         <f>0.00000000005</f>
         <v>5.0000000000000002E-11</v>
       </c>
-      <c r="AA222" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AB222" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>563</v>
       </c>
@@ -21816,44 +22505,44 @@
       </c>
       <c r="L223" s="83"/>
       <c r="M223" s="83">
-        <f t="shared" ref="M223:U223" si="64">0.0000001 / 2</f>
+        <f t="shared" ref="M223:W223" si="68">0.0000001 / 2</f>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="N223" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="O223" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="P223" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="Q223" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="R223" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="S223" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="T223" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="U223" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="V223" s="83"/>
       <c r="W223" s="83">
-        <f>0.0000001 / 2</f>
+        <f t="shared" si="68"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="X223" s="83">
@@ -21861,15 +22550,19 @@
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="Y223" s="83">
+        <f>0.0000001 / 2</f>
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="Z223" s="83">
         <f>0.0000001 * 10 /2</f>
         <v>4.9999999999999998E-7</v>
       </c>
-      <c r="AA223" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AB223" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>565</v>
       </c>
@@ -21948,12 +22641,16 @@
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="AA224" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Z224" s="83">
+        <f>100</f>
+        <v>100</v>
+      </c>
+      <c r="AB224" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>530</v>
       </c>
@@ -21993,44 +22690,44 @@
       </c>
       <c r="L225" s="83"/>
       <c r="M225" s="83">
-        <f t="shared" ref="M225:U225" si="65">0.000001 / 10000 / 4 / 10</f>
+        <f t="shared" ref="M225:W225" si="69">0.000001 / 10000 / 4 / 10</f>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="N225" s="83">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="O225" s="83">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="P225" s="83">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="Q225" s="83">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="R225" s="83">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="S225" s="83">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="T225" s="83">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="U225" s="83">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="V225" s="83"/>
       <c r="W225" s="83">
-        <f>0.000001 / 10000 / 4 / 10</f>
+        <f t="shared" si="69"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="X225" s="83">
@@ -22038,15 +22735,19 @@
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="Y225" s="83">
+        <f>0.000001 / 10000 / 4 / 10</f>
+        <v>2.4999999999999998E-12</v>
+      </c>
+      <c r="Z225" s="83">
         <f>0.000001 / 10000 / 4</f>
         <v>2.4999999999999998E-11</v>
       </c>
-      <c r="AA225" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB225" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>531</v>
       </c>
@@ -22083,44 +22784,44 @@
       </c>
       <c r="L226" s="83"/>
       <c r="M226" s="83">
-        <f t="shared" ref="M226:U226" si="66">0.00001</f>
+        <f t="shared" ref="M226:W226" si="70">0.00001</f>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="N226" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="O226" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="P226" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="Q226" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="R226" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="S226" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="T226" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="U226" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="V226" s="83"/>
       <c r="W226" s="83">
-        <f>0.00001</f>
+        <f t="shared" si="70"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="X226" s="83">
@@ -22128,18 +22829,22 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="Y226" s="83">
+        <f>0.00001</f>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Z226" s="83">
         <f>0.00001 * 10</f>
         <v>1E-4</v>
       </c>
-      <c r="Z226" s="83">
+      <c r="AA226" s="83">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="AA226" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB226" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>573</v>
       </c>
@@ -22176,44 +22881,44 @@
       </c>
       <c r="L227" s="83"/>
       <c r="M227" s="83">
-        <f t="shared" ref="M227:U227" si="67" xml:space="preserve"> 0.001 * 10</f>
+        <f t="shared" ref="M227:W227" si="71" xml:space="preserve"> 0.001 * 10</f>
         <v>0.01</v>
       </c>
       <c r="N227" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.01</v>
       </c>
       <c r="O227" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.01</v>
       </c>
       <c r="P227" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.01</v>
       </c>
       <c r="Q227" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.01</v>
       </c>
       <c r="R227" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.01</v>
       </c>
       <c r="S227" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.01</v>
       </c>
       <c r="T227" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.01</v>
       </c>
       <c r="U227" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.01</v>
       </c>
       <c r="V227" s="83"/>
       <c r="W227" s="83">
-        <f xml:space="preserve"> 0.001 * 10</f>
+        <f t="shared" si="71"/>
         <v>0.01</v>
       </c>
       <c r="X227" s="83">
@@ -22221,10 +22926,14 @@
         <v>0.01</v>
       </c>
       <c r="Y227" s="83">
+        <f xml:space="preserve"> 0.001 * 10</f>
+        <v>0.01</v>
+      </c>
+      <c r="Z227" s="83">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>575</v>
       </c>
@@ -22260,44 +22969,44 @@
       </c>
       <c r="L228" s="99"/>
       <c r="M228" s="99">
-        <f t="shared" ref="M228:U228" si="68">0.00001 / 3</f>
+        <f t="shared" ref="M228:W228" si="72">0.00001 / 3</f>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="N228" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="O228" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="P228" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="Q228" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="R228" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="S228" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="T228" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="U228" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="V228" s="99"/>
       <c r="W228" s="99">
-        <f>0.00001 / 3</f>
+        <f t="shared" si="72"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="X228" s="99">
@@ -22305,13 +23014,17 @@
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="Y228" s="99">
-        <v>1.0000000000000001E-5</v>
+        <f>0.00001 / 3</f>
+        <v>3.3333333333333337E-6</v>
       </c>
       <c r="Z228" s="99">
         <v>1.0000000000000001E-5</v>
       </c>
-    </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA228" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>532</v>
       </c>
@@ -22335,77 +23048,81 @@
         <v>0.10886399999999999</v>
       </c>
       <c r="H229" s="83">
-        <f t="shared" ref="H229:Y229" si="69">0.84*(0.36^2)</f>
+        <f t="shared" ref="H229:Z229" si="73">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
       <c r="I229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="J229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="K229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="L229" s="83"/>
       <c r="M229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="N229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="O229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="P229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="Q229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="R229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="S229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="T229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="U229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="V229" s="83"/>
       <c r="W229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="X229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="Y229" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10886399999999999</v>
       </c>
-      <c r="AA229" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Z229" s="83">
+        <f t="shared" si="73"/>
+        <v>0.10886399999999999</v>
+      </c>
+      <c r="AB229" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>533</v>
       </c>
@@ -22477,12 +23194,15 @@
       <c r="Y230" s="83">
         <v>0.2</v>
       </c>
-      <c r="AA230" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Z230" s="83">
+        <v>0.2</v>
+      </c>
+      <c r="AB230" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>534</v>
       </c>
@@ -22554,12 +23274,15 @@
       <c r="Y231" s="83" t="s">
         <v>473</v>
       </c>
-      <c r="AA231" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Z231" s="83" t="s">
+        <v>473</v>
+      </c>
+      <c r="AB231" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>535</v>
       </c>
@@ -22583,77 +23306,81 @@
         <v>0.2</v>
       </c>
       <c r="H232" s="83">
-        <f t="shared" ref="H232:Y232" si="70">2*0.1</f>
+        <f t="shared" ref="H232:Z232" si="74">2*0.1</f>
         <v>0.2</v>
       </c>
       <c r="I232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="J232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="K232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="L232" s="83"/>
       <c r="M232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="N232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="O232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="P232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="Q232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="R232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="S232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="T232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="U232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="V232" s="83"/>
       <c r="W232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="X232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
       <c r="Y232" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.2</v>
       </c>
-      <c r="AA232" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Z232" s="83">
+        <f t="shared" si="74"/>
+        <v>0.2</v>
+      </c>
+      <c r="AB232" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>536</v>
       </c>
@@ -22725,12 +23452,15 @@
       <c r="Y233" s="83">
         <v>1E-3</v>
       </c>
-      <c r="AA233" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Z233" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="AB233" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>537</v>
       </c>
@@ -22767,64 +23497,68 @@
       </c>
       <c r="L234" s="83"/>
       <c r="M234" s="83">
-        <f t="shared" ref="M234:U234" si="71">0.00001 /2</f>
+        <f>0.00001 /2</f>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="N234" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" ref="N234:U234" si="75">0.00001 /2</f>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="O234" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="P234" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="Q234" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="R234" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="S234" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="T234" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="U234" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="V234" s="83"/>
       <c r="W234" s="83">
-        <f>0.00001 /2</f>
-        <v>5.0000000000000004E-6</v>
+        <f>0.00001 /10</f>
+        <v>1.0000000000000002E-6</v>
       </c>
       <c r="X234" s="83">
         <f>0.00001 /2</f>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="Y234" s="83">
+        <f>0.00001 /2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="Z234" s="83">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="Z234" s="1">
+      <c r="AA234" s="1">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="AA234" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB234" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>577</v>
       </c>
@@ -22861,44 +23595,44 @@
       </c>
       <c r="L235" s="83"/>
       <c r="M235" s="83">
-        <f t="shared" ref="M235:U235" si="72">0.000000005 / 5</f>
+        <f t="shared" ref="M235:W235" si="76">0.000000005 / 5</f>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="N235" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O235" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="P235" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="Q235" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="R235" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="S235" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="T235" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="U235" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="V235" s="83"/>
       <c r="W235" s="83">
-        <f>0.000000005 / 5</f>
+        <f t="shared" si="76"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="X235" s="83">
@@ -22906,11 +23640,15 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="Y235" s="83">
+        <f>0.000000005 / 5</f>
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="Z235" s="83">
         <f>0.00001 / 2</f>
         <v>5.0000000000000004E-6</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>560</v>
       </c>
@@ -22930,18 +23668,18 @@
         <v>553</v>
       </c>
       <c r="G236" s="83">
-        <f t="shared" ref="G236:J236" si="73">0.00002 / 14 / 5</f>
+        <f t="shared" ref="G236:J236" si="77">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="H236" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="I236" s="83">
         <v>0</v>
       </c>
       <c r="J236" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="K236" s="83">
@@ -22985,12 +23723,15 @@
       <c r="Y236" s="83">
         <v>0</v>
       </c>
-      <c r="AA236" s="1" t="b">
-        <f t="shared" si="58"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Z236" s="83">
+        <v>0</v>
+      </c>
+      <c r="AB236" s="1" t="b">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>561</v>
       </c>
@@ -23010,23 +23751,23 @@
         <v>553</v>
       </c>
       <c r="G237" s="83">
-        <f t="shared" ref="G237:Y237" si="74">0.00002 / 14 / 5 /10</f>
+        <f t="shared" ref="G237:Z237" si="78">0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="H237" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="I237" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="J237" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="K237" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="L237" s="83"/>
@@ -23065,11 +23806,14 @@
         <v>0</v>
       </c>
       <c r="Y237" s="83">
-        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Z237" s="83">
+        <f t="shared" si="78"/>
         <v>2.8571428571428575E-8</v>
       </c>
-      <c r="AA237" s="1" t="b">
-        <f t="shared" si="58"/>
+      <c r="AB237" s="1" t="b">
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
     </row>
@@ -23096,7 +23840,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G237:Y237">
+  <conditionalFormatting sqref="G237:Z237">
     <cfRule type="colorScale" priority="361">
       <colorScale>
         <cfvo type="min"/>
@@ -23118,7 +23862,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H130:Y131">
+  <conditionalFormatting sqref="H130:Z131">
     <cfRule type="colorScale" priority="363">
       <colorScale>
         <cfvo type="min"/>
@@ -23130,7 +23874,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H213:Y213">
+  <conditionalFormatting sqref="H213:Z213">
+    <cfRule type="colorScale" priority="365">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="364">
       <colorScale>
         <cfvo type="min"/>
@@ -23141,7 +23895,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="365">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H214:Z214">
+    <cfRule type="colorScale" priority="367">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="366">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23152,29 +23918,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H214:Y214">
-    <cfRule type="colorScale" priority="366">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="367">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H215:Y215">
+  <conditionalFormatting sqref="H215:Z215">
     <cfRule type="colorScale" priority="368">
       <colorScale>
         <cfvo type="min"/>
@@ -23196,7 +23940,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H216:Y216">
+  <conditionalFormatting sqref="H216:Z216">
+    <cfRule type="colorScale" priority="371">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="370">
       <colorScale>
         <cfvo type="min"/>
@@ -23207,7 +23961,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="371">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H217:Z217">
+    <cfRule type="colorScale" priority="373">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="372">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23218,8 +23984,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H217:Y217">
-    <cfRule type="colorScale" priority="372">
+  <conditionalFormatting sqref="H218:Z218">
+    <cfRule type="colorScale" priority="375">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23229,7 +23995,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="373">
+    <cfRule type="colorScale" priority="374">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23240,8 +24006,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H218:Y218">
-    <cfRule type="colorScale" priority="374">
+  <conditionalFormatting sqref="H221:Z221">
+    <cfRule type="colorScale" priority="377">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23251,7 +24017,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="375">
+    <cfRule type="colorScale" priority="376">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23262,8 +24028,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H221:Y221">
-    <cfRule type="colorScale" priority="376">
+  <conditionalFormatting sqref="H222:Z224">
+    <cfRule type="colorScale" priority="391">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23273,7 +24039,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="377">
+    <cfRule type="colorScale" priority="390">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23284,8 +24050,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H222:Y224">
-    <cfRule type="colorScale" priority="390">
+  <conditionalFormatting sqref="H225:Z225">
+    <cfRule type="colorScale" priority="381">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23295,7 +24061,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="391">
+    <cfRule type="colorScale" priority="380">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23306,8 +24072,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H225:Y225">
-    <cfRule type="colorScale" priority="380">
+  <conditionalFormatting sqref="H229:Z229">
+    <cfRule type="colorScale" priority="385">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23317,7 +24083,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="381">
+    <cfRule type="colorScale" priority="384">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23328,8 +24094,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H229:Y229">
-    <cfRule type="colorScale" priority="384">
+  <conditionalFormatting sqref="H230:Z235">
+    <cfRule type="colorScale" priority="387">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23339,29 +24105,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="385">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H230:Y235">
     <cfRule type="colorScale" priority="386">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="387">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23395,6 +24139,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K236:L237">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -23405,18 +24159,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M236:Y237">
+  <conditionalFormatting sqref="M236:Z237">
     <cfRule type="colorScale" priority="388">
       <colorScale>
         <cfvo type="min"/>
@@ -23438,7 +24182,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y226:Z226 Y227 H226:X227">
+  <conditionalFormatting sqref="Z226:AA226 Z227 H226:Y227">
     <cfRule type="colorScale" priority="382">
       <colorScale>
         <cfvo type="min"/>
@@ -23460,7 +24204,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB130:AC131">
+  <conditionalFormatting sqref="AC130:AD131">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -23472,7 +24216,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB132:AC132 H132:Z132">
+  <conditionalFormatting sqref="AC132:AD132 H132:AA132">
     <cfRule type="colorScale" priority="295">
       <colorScale>
         <cfvo type="min"/>
@@ -23494,7 +24238,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB133:AC133 H133:Y133">
+  <conditionalFormatting sqref="AC133:AD133 H133:Z133">
     <cfRule type="colorScale" priority="299">
       <colorScale>
         <cfvo type="min"/>
@@ -23516,7 +24260,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB135:AC135 H135:Z135">
+  <conditionalFormatting sqref="AC135:AD135 H135:AA135">
+    <cfRule type="colorScale" priority="304">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="303">
       <colorScale>
         <cfvo type="min"/>
@@ -23527,7 +24281,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="304">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC136:AD136 H136:Z136">
+    <cfRule type="colorScale" priority="308">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23538,29 +24304,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB136:AC136 H136:Y136">
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB141:AC141 H141:Z141">
+  <conditionalFormatting sqref="AC141:AD141 H141:AA141">
     <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min"/>
@@ -23572,7 +24316,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB147:AC147 H147:Y147">
+  <conditionalFormatting sqref="AC147:AD147 H147:Z147">
     <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min"/>
@@ -23604,17 +24348,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB163:AC163 H163:Y163">
-    <cfRule type="colorScale" priority="319">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
+  <conditionalFormatting sqref="AC163:AD163 H163:Z163">
     <cfRule type="colorScale" priority="320">
       <colorScale>
         <cfvo type="min"/>
@@ -23635,9 +24369,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB169:AC169 H169:Y169">
-    <cfRule type="colorScale" priority="325">
+    <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23647,7 +24379,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC169:AD169 H169:Z169">
     <cfRule type="colorScale" priority="326">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="325">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
